--- a/Kỹ Thuật lập trình/C/C.xlsx
+++ b/Kỹ Thuật lập trình/C/C.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Linux\Kỹ Thuật lập trình\C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9EC24FF-5A90-45AB-B326-59E0325A8DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F520DE-04B1-4A63-B571-A64D57315927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D515FE12-8DDF-4954-9F3B-744B83BED5E7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="1010">
   <si>
     <t>🔧 TOOLS &amp; ENVIRONMENT</t>
   </si>
@@ -7943,9 +7943,6 @@
     <t>Dùng trong concurrent programming.</t>
   </si>
   <si>
-    <t>👉 Đây là phần lý thuyết nền tảng, cực kỳ quan trọng trong phỏng vấn Embedded C và cả Linux Kernel development.</t>
-  </si>
-  <si>
     <t>🧪 Các điểm cần chú ý:</t>
   </si>
   <si>
@@ -8275,10 +8272,1008 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">1.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>short</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>long</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>long long</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1.3 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>signed</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vs </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>unsigned</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Implications</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>size_t</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ptrdiff_t</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>intptr_t</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>_Bool</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (C99)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sử dụng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>&lt;stdint.h&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> với các kiểu như </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>int32_t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>uint64_t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để đảm bảo kích thước cố định.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2.1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>#define</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vs </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>const</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">🔍 1.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>short</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>long</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>long long</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">🔍 1.3 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>signed</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vs </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>unsigned</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3.1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>const</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> qualifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">🔍 1.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>size_t</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ptrdiff_t</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>intptr_t</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>volatile</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3.3 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>restrict</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (C99)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">🔍 1.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>_Bool</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (C99)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>_Atomic</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (C11)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Yêu cầu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>#include &lt;stdatomic.h&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>char</t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mặc định là </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>signed</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hay </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>unsigned</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>float</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>double</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> không chính xác tuyệt đối</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, do giới hạn IEEE 754:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>stdint.h</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là cách an toàn nhất: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>int16_t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>int32_t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>int64_t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>=&gt; chỉ áp dụng cho kiểu số nguyên vì kiểu số nguyên có thể có kích thước thay đổi tùy hệ thống</t>
+  </si>
+  <si>
+    <t>✅ Tình huống nâng cao</t>
+  </si>
+  <si>
+    <t>#define SQUARE(x) ((x) * (x))</t>
+  </si>
+  <si>
+    <t>⚠️ Nếu không dùng dấu ngoặc, có thể gây lỗi:</t>
+  </si>
+  <si>
+    <t>#define SQUARE(x) x * x  // SQUARE(1 + 2) → 1 + 2 * 1 + 2 = 5</t>
+  </si>
+  <si>
+    <t>const uint8_t data[] = {1,2,3};  // Có thể được lưu trong Flash (ROM)</t>
+  </si>
+  <si>
+    <t>static const int max_value = 100;  // scope giới hạn trong file</t>
+  </si>
+  <si>
+    <t>const int *p;       // pointer to const int (không thay đổi nội dung)</t>
+  </si>
+  <si>
+    <t>int * const p;      // const pointer to int (không thay đổi địa chỉ)</t>
+  </si>
+  <si>
+    <t>const int * const p;// cả 2 đều const</t>
+  </si>
+  <si>
+    <t>⚠️ Bẫy thường gặp</t>
+  </si>
+  <si>
+    <t>#define PI 3.14</t>
+  </si>
+  <si>
+    <t>float r = 5;</t>
+  </si>
+  <si>
+    <t>float a = PI * r * r;  // nếu PI là int, có thể gây sai số</t>
+  </si>
+  <si>
+    <t>Macro side effect:</t>
+  </si>
+  <si>
+    <t>#define INCREMENT(x) (x + 1)</t>
+  </si>
+  <si>
+    <t>int i = 5;</t>
+  </si>
+  <si>
+    <t>int a = INCREMENT(i++); // Không mong muốn: (i++ + 1)</t>
+  </si>
+  <si>
+    <t>const int n = 5;</t>
+  </si>
+  <si>
+    <t>int arr[n]; // ⛔ Có thể lỗi trên compiler C90 (không hỗ trợ VLA)</t>
+  </si>
+  <si>
+    <t>Đặt giá trị cụ thể cho từng phần tử</t>
+  </si>
+  <si>
+    <t>enum Status { IDLE = 0, RUNNING = 5, STOPPED = 10 };</t>
+  </si>
+  <si>
+    <t>enum { BUF_SIZE = 512 };</t>
+  </si>
+  <si>
+    <t>switch (state) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  case RUNNING: ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  case STOPPED: ...</t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t>Enum có thể bị cast ra ngoài phạm vi</t>
+  </si>
+  <si>
+    <t>enum Color { RED, GREEN, BLUE };</t>
+  </si>
+  <si>
+    <t>Color c = (Color)100;  // hợp lệ cú pháp, sai logic</t>
+  </si>
+  <si>
+    <t>enum Small : uint8_t { A, B, C }; // C không hỗ trợ enum kiểu nhỏ trừ khi là C++</t>
+  </si>
+  <si>
+    <t>Chuỗi bất biến (read-only)</t>
+  </si>
+  <si>
+    <t>char *s = "hello";  // s trỏ vào vùng bộ nhớ hằng → không được thay đổi nội dung</t>
+  </si>
+  <si>
+    <t>char c = 'a';       // kích thước 1 byte</t>
+  </si>
+  <si>
+    <t>char *p = "a";      // kích thước 2 byte ("a\0")</t>
+  </si>
+  <si>
+    <t>Dùng macro định nghĩa escape sequences</t>
+  </si>
+  <si>
+    <t>#define NEWLINE '\n'</t>
+  </si>
+  <si>
+    <t>Ghép chuỗi literal ở compile-time</t>
+  </si>
+  <si>
+    <t>printf("Hello " "World"); // → "Hello World"</t>
+  </si>
+  <si>
+    <t>char *s = "abc";</t>
+  </si>
+  <si>
+    <t>s[0] = 'A'; // lỗi runtime (segfault)</t>
+  </si>
+  <si>
+    <t>So sánh con trỏ thay vì nội dung chuỗi</t>
+  </si>
+  <si>
+    <t>if ("abc" == "abc") // ⛔ undefined behavior (so sánh địa chỉ)</t>
+  </si>
+  <si>
+    <t>Chuyển đổi giữa các hệ</t>
+  </si>
+  <si>
+    <t>printf("%x", 255);  // hex</t>
+  </si>
+  <si>
+    <t>printf("%o", 255);  // octal</t>
+  </si>
+  <si>
+    <t>int b = 0b1010;  // 10</t>
+  </si>
+  <si>
+    <t>In số ở các hệ khác nhau</t>
+  </si>
+  <si>
+    <t>printf("Bin: %d, Hex: 0x%x, Oct: 0%o\n", val, val, val);</t>
+  </si>
+  <si>
+    <t>int x = 0123; // = 83 trong hệ 10, không phải 123</t>
+  </si>
+  <si>
+    <t>Truyền mảng tạm thời vào hàm</t>
+  </si>
+  <si>
+    <t>void print_arr(int *a) { ... }</t>
+  </si>
+  <si>
+    <t>print_arr((int[]){1, 2, 3});</t>
+  </si>
+  <si>
+    <t>Khởi tạo cấu trúc tạm thời</t>
+  </si>
+  <si>
+    <t>struct Point { int x, y; };</t>
+  </si>
+  <si>
+    <t>struct Point p = (struct Point){ .x = 1, .y = 2 };</t>
+  </si>
+  <si>
+    <t>Dùng trong macro hoặc trả giá trị</t>
+  </si>
+  <si>
+    <t>#define MAKE_POINT(x, y) ((struct Point){x, y})</t>
+  </si>
+  <si>
+    <t>Không được dùng compound literals ở chuẩn C90</t>
+  </si>
+  <si>
+    <t>Vùng nhớ compound literal nội khối (block-scope) chỉ tồn tại trong block</t>
+  </si>
+  <si>
+    <t>int *p;</t>
+  </si>
+  <si>
+    <t>{</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    p = (int[]){1, 2, 3}; // hợp lệ</t>
+  </si>
+  <si>
+    <t>// p giờ trỏ vào vùng nhớ đã giải phóng</t>
+  </si>
+  <si>
+    <t>Bài toán khó / câu hỏi đánh đố</t>
+  </si>
+  <si>
+    <t>1. So sánh và phát hiện lỗi sai</t>
+  </si>
+  <si>
+    <t>#define SIZE 10 + 5</t>
+  </si>
+  <si>
+    <t>int a = SIZE * 2;  // Kết quả là? (Thực tế: 10 + 5 * 2 = 20 → sai)</t>
+  </si>
+  <si>
+    <t>2. Gán chuỗi literal rồi sửa</t>
+  </si>
+  <si>
+    <t>char *str = "test";</t>
+  </si>
+  <si>
+    <t>str[0] = 'T'; // Lỗi gì xảy ra?</t>
+  </si>
+  <si>
+    <t>printf("%lu %lu\n", sizeof('a'), sizeof("a"));  // Output là?</t>
+  </si>
+  <si>
+    <t>4. Khai báo enum và ép kiểu</t>
+  </si>
+  <si>
+    <t>enum Level { LOW, MEDIUM = 5, HIGH };</t>
+  </si>
+  <si>
+    <t>printf("%d\n", HIGH);  // Output?</t>
+  </si>
+  <si>
+    <t>5. Compound literal bị dùng sai scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  p = (int[]){1, 2, 3};</t>
+  </si>
+  <si>
+    <t>printf("%d\n", p[0]); // Behavior?</t>
+  </si>
+  <si>
+    <t>6. Macro side-effect</t>
+  </si>
+  <si>
+    <t>#define DOUBLE(x) (x + x)</t>
+  </si>
+  <si>
+    <t>int i = 2;</t>
+  </si>
+  <si>
+    <t>printf("%d\n", DOUBLE(i++));  // Output?</t>
+  </si>
+  <si>
+    <t>Nếu bạn cần mình viết thành các bài luyện tập có chấm điểm tự động hoặc đóng gói thành tài liệu PDF, mình cũng có thể làm giúp.</t>
+  </si>
+  <si>
+    <r>
+      <t>char</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
@@ -8339,20 +9334,283 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">1.2 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
+      <t xml:space="preserve">GCC: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>signed char</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mặc định trên x86.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ARM: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>unsigned char</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mặc định.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Do đó, nên luôn dùng rõ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>signed char</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>unsigned char</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>fabs(a - b) &lt; epsilon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để so sánh số thực.</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>short</t>
     </r>
     <r>
       <rPr>
-        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Kiểu số nguyên ngắn, thường 2 byte.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>long</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Kiểu số nguyên dài, thường 4 byte.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>long long</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Kiểu số nguyên rất dài, thường 8 byte.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">So sánh </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>unsigned &lt; 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>luôn là false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, gây lỗi logic tiềm ẩn.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>signed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Có thể biểu diễn cả số âm và dương.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>unsigned</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Chỉ biểu diễn số không âm, nhưng phạm vi gấp đôi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>signed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trên </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Windows 64-bit</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
@@ -8364,7 +9622,6 @@
     </r>
     <r>
       <rPr>
-        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
@@ -8373,7 +9630,320 @@
     </r>
     <r>
       <rPr>
-        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vẫn chỉ là </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4 bytes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không portable!</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>size_t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Kiểu không dấu dùng cho biểu diễn kích thước bộ nhớ (kết quả của </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sizeof</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>signed + unsigned</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → toàn bộ biểu thức được </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>promote sang unsigned</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, gây sai lệch kết quả.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ptrdiff_t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Kiểu có dấu biểu diễn hiệu của hai con trỏ.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>intptr_t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Kiểu nguyên có thể chứa giá trị địa chỉ con trỏ (C99).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Luôn kiểm tra khi mix </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>signed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>unsigned</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>-Wsign-compare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong GCC để bắt lỗi compile time.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>_Bool</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> chỉ lưu 0 hoặc 1 (non-zero chuyển thành 1), nhưng vẫn có thể gây </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>logic sai nếu không hiểu rõ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Giá trị </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là false, bất kỳ giá trị khác là true.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bao gồm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>&lt;stdbool.h&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để sử dụng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>bool</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
@@ -8385,32 +9955,96 @@
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>long long</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>short</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Kiểu số nguyên ngắn, thường 2 byte.</t>
-    </r>
-  </si>
-  <si>
-    <r>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Kết quả từ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sizeof</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, malloc...</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ILP32: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
       <t>long</t>
     </r>
     <r>
@@ -8422,110 +10056,194 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t>: Kiểu số nguyên dài, thường 4 byte.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>long long</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Kiểu số nguyên rất dài, thường 8 byte.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1.3 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>signed</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>unsigned</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Implications</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>signed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Có thể biểu diễn cả số âm và dương.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>unsigned</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Chỉ biểu diễn số không âm, nhưng phạm vi gấp đôi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>signed</t>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>pointer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 32 bit.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">LP64: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>long</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>pointer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 64 bit, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 32 bit.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#define</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Macro thời điểm tiền xử lý (preprocessor), không có kiểm tra kiểu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>const</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Biến có kiểu, được kiểm tra tại compile-time, có thể dùng debug và scope rõ ràng hơn.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>enum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để định nghĩa tập hợp các hằng số nguyên.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sử dụng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>#define</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để viết macro phức tạp với tham số</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'a'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Hằng số ký tự kiểu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>char</t>
     </r>
     <r>
       <rPr>
@@ -8541,20 +10259,107 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">1.4 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>size_t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
+      <t xml:space="preserve">Sử dụng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>uint*_t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>packed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để đảm bảo không bị padding, dễ truyền qua socket.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>"abc"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Chuỗi ký tự kết thúc bằng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>\0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, kiểu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>char[]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>'\n'</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Arial"/>
@@ -8566,436 +10371,127 @@
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>ptrdiff_t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>intptr_t</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>size_t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Kiểu không dấu dùng cho biểu diễn kích thước bộ nhớ (kết quả của </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>sizeof</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ptrdiff_t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Kiểu có dấu biểu diễn hiệu của hai con trỏ.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>intptr_t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Kiểu nguyên có thể chứa giá trị địa chỉ con trỏ (C99).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">GCC: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>signed char</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> mặc định trên x86.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1.5 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>_Bool</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C99)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">ARM: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>unsigned char</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> mặc định.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Giá trị </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> là false, bất kỳ giá trị khác là true.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Bao gồm </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>&lt;stdbool.h&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> để sử dụng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>bool</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>true</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>false</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Do đó, nên luôn dùng rõ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>signed char</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hoặc </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>unsigned char</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sử dụng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>&lt;stdint.h&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> với các kiểu như </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>int32_t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>uint64_t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> để đảm bảo kích thước cố định.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">So sánh </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>unsigned &lt; 0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>luôn là false</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, gây lỗi logic tiềm ẩn.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">2.1 </t>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>'\t'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Escape characters.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0123</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Số hệ 8 (octal).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0x7B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Số hệ 16 (hex).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>0b1011</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Không hỗ trợ chuẩn, nhưng nhiều compiler hỗ trợ mở rộng (GCC).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>const</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong embedded (đặt trong Flash)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>const</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> kết hợp </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>static</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khai báo enum ẩn danh dùng như </t>
     </r>
     <r>
       <rPr>
@@ -9006,27 +10502,232 @@
       </rPr>
       <t>#define</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Enum trong </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>switch-case</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dễ maintain hơn </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>#define</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khác biệt giữa </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>'a'</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>"a"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gán chuỗi literal vào </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>char[]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và sửa nội dung sẽ lỗi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">GCC hỗ trợ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>0b</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (non-standard)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Viết </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>0123</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → thực ra là octal!</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Không dùng được </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>0b</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong C chuẩn (trừ khi là extension)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. So sánh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>'a'</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>"a"</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>const</t>
     </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pointer vs pointer to const</t>
+    </r>
   </si>
   <si>
     <r>
@@ -9035,13 +10736,13 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Macro thời điểm tiền xử lý (preprocessor), không có kiểm tra kiểu.</t>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> không có kiểm tra kiểu → dễ gây bug</t>
     </r>
   </si>
   <si>
@@ -9051,937 +10752,30 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Biến có kiểu, được kiểm tra tại compile-time, có thể dùng debug và scope rõ ràng hơn.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dùng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>enum</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> để định nghĩa tập hợp các hằng số nguyên.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dùng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>fabs(a - b) &lt; epsilon</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> để so sánh số thực.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">🔍 1.2 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>short</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>long</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>long long</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>'a'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Hằng số ký tự kiểu </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>char</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>"abc"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Chuỗi ký tự kết thúc bằng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>\0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, kiểu </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>char[]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Trên </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Windows 64-bit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>long</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vẫn chỉ là </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4 bytes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>không portable!</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>'\n'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>'\t'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Escape characters.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0123</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Số hệ 8 (octal).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">🔍 1.3 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>signed</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>unsigned</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0x7B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Số hệ 16 (hex).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0b1011</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Không hỗ trợ chuẩn, nhưng nhiều compiler hỗ trợ mở rộng (GCC).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>signed + unsigned</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> → toàn bộ biểu thức được </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>promote sang unsigned</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, gây sai lệch kết quả.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Luôn kiểm tra khi mix </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>signed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>unsigned</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dùng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>-Wsign-compare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> trong GCC để bắt lỗi compile time.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">3.1 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>const</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> qualifier</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">🔍 1.4 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>size_t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>ptrdiff_t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>intptr_t</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">3.2 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>volatile</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Kết quả từ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>sizeof</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, malloc...</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">3.3 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>restrict</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C99)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">🔍 1.5 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>_Bool</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C99)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">3.4 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>_Atomic</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (C11)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>_Bool</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> chỉ lưu 0 hoặc 1 (non-zero chuyển thành 1), nhưng vẫn có thể gây </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>logic sai nếu không hiểu rõ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Yêu cầu </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>#include &lt;stdatomic.h&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">ILP32: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> không thật sự là hằng số với compiler (nó vẫn là biến), nên không thể dùng để định nghĩa mảng:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Enum mặc định là </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
       <t>int</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>long</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>pointer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> = 32 bit.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">LP64: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>long</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>pointer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> = 64 bit, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>int</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> = 32 bit.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sử dụng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>uint*_t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>packed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> để đảm bảo không bị padding, dễ truyền qua socket.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>char</t>
-    </r>
-    <r>
-      <rPr>
         <b/>
         <sz val="11"/>
         <color rgb="FF00B0F0"/>
@@ -9990,183 +10784,8 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> mặc định là </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>signed</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hay </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>unsigned</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>?</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>float</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> và </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>double</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> không chính xác tuyệt đối</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, do giới hạn IEEE 754:</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dùng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>stdint.h</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> là cách an toàn nhất: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>int16_t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>int32_t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>int64_t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>=&gt; chỉ áp dụng cho kiểu số nguyên vì kiểu số nguyên có thể có kích thước thay đổi tùy hệ thống</t>
+      <t xml:space="preserve"> → vấn đề alignment hoặc size</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -10255,15 +10874,6 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="163"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
       <name val="Arial Unicode MS"/>
@@ -10316,8 +10926,16 @@
       <charset val="163"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10327,6 +10945,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -10475,7 +11099,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -10497,9 +11121,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -10519,15 +11140,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10536,7 +11148,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -10561,23 +11173,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -10588,12 +11191,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15915,2016 +16580,3537 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B9A591E-590E-4D73-9F12-919C572F7BCA}">
-  <dimension ref="B1:CJ139"/>
+  <dimension ref="B1:CJ236"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16384" width="3" style="12"/>
+    <col min="1" max="16384" width="3" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:75" ht="21" thickBot="1">
-      <c r="B1" s="19" t="s">
+    <row r="1" spans="2:75" ht="15.75" thickBot="1">
+      <c r="B1" s="50" t="s">
         <v>770</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="21"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="17"/>
     </row>
     <row r="3" spans="2:75" ht="15">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="46" t="s">
         <v>771</v>
       </c>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
     </row>
     <row r="4" spans="2:75" ht="15.75" thickBot="1">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
+        <v>855</v>
+      </c>
+      <c r="AL4" s="10" t="s">
         <v>856</v>
       </c>
-      <c r="AL4" s="11" t="s">
+    </row>
+    <row r="5" spans="2:75" ht="15">
+      <c r="B5" s="12" t="s">
+        <v>958</v>
+      </c>
+      <c r="AL5" s="18" t="s">
+        <v>797</v>
+      </c>
+      <c r="AM5" s="19"/>
+      <c r="AN5" s="19"/>
+      <c r="AO5" s="19"/>
+      <c r="AP5" s="19"/>
+      <c r="AQ5" s="19"/>
+      <c r="AR5" s="19"/>
+      <c r="AS5" s="19"/>
+      <c r="AT5" s="19"/>
+      <c r="AU5" s="19"/>
+      <c r="AV5" s="19"/>
+      <c r="AW5" s="19"/>
+      <c r="AX5" s="19"/>
+      <c r="AY5" s="19"/>
+      <c r="AZ5" s="19"/>
+      <c r="BA5" s="19"/>
+      <c r="BB5" s="19"/>
+      <c r="BC5" s="20"/>
+      <c r="BE5" s="18" t="s">
+        <v>802</v>
+      </c>
+      <c r="BF5" s="19"/>
+      <c r="BG5" s="19"/>
+      <c r="BH5" s="19"/>
+      <c r="BI5" s="19"/>
+      <c r="BJ5" s="19"/>
+      <c r="BK5" s="19"/>
+      <c r="BL5" s="19"/>
+      <c r="BM5" s="19"/>
+      <c r="BN5" s="19"/>
+      <c r="BO5" s="19"/>
+      <c r="BP5" s="19"/>
+      <c r="BQ5" s="19"/>
+      <c r="BR5" s="19"/>
+      <c r="BS5" s="19"/>
+      <c r="BT5" s="19"/>
+      <c r="BU5" s="19"/>
+      <c r="BV5" s="19"/>
+      <c r="BW5" s="20"/>
+    </row>
+    <row r="6" spans="2:75" ht="15">
+      <c r="B6" s="12" t="s">
+        <v>959</v>
+      </c>
+      <c r="AL6" s="21"/>
+      <c r="AM6" s="22" t="s">
+        <v>872</v>
+      </c>
+      <c r="AN6" s="23"/>
+      <c r="AO6" s="23"/>
+      <c r="AP6" s="23"/>
+      <c r="AQ6" s="23"/>
+      <c r="AR6" s="23"/>
+      <c r="AS6" s="23"/>
+      <c r="AT6" s="23"/>
+      <c r="AU6" s="23"/>
+      <c r="AV6" s="23"/>
+      <c r="AW6" s="23"/>
+      <c r="AX6" s="23"/>
+      <c r="AY6" s="23"/>
+      <c r="AZ6" s="23"/>
+      <c r="BA6" s="23"/>
+      <c r="BB6" s="23"/>
+      <c r="BC6" s="24"/>
+      <c r="BE6" s="33" t="s">
+        <v>873</v>
+      </c>
+      <c r="BF6" s="23"/>
+      <c r="BG6" s="23"/>
+      <c r="BH6" s="23"/>
+      <c r="BI6" s="23"/>
+      <c r="BJ6" s="23"/>
+      <c r="BK6" s="23"/>
+      <c r="BL6" s="23"/>
+      <c r="BM6" s="23"/>
+      <c r="BN6" s="23"/>
+      <c r="BO6" s="23"/>
+      <c r="BP6" s="23"/>
+      <c r="BQ6" s="23"/>
+      <c r="BR6" s="23"/>
+      <c r="BS6" s="23"/>
+      <c r="BT6" s="23"/>
+      <c r="BU6" s="23"/>
+      <c r="BV6" s="23"/>
+      <c r="BW6" s="24"/>
+    </row>
+    <row r="7" spans="2:75">
+      <c r="B7" s="12" t="s">
+        <v>960</v>
+      </c>
+      <c r="AL7" s="21"/>
+      <c r="AM7" s="25" t="s">
+        <v>798</v>
+      </c>
+      <c r="AN7" s="23"/>
+      <c r="AO7" s="23"/>
+      <c r="AP7" s="23"/>
+      <c r="AQ7" s="23"/>
+      <c r="AR7" s="23"/>
+      <c r="AS7" s="23"/>
+      <c r="AT7" s="23"/>
+      <c r="AU7" s="23"/>
+      <c r="AV7" s="23"/>
+      <c r="AW7" s="23"/>
+      <c r="AX7" s="23"/>
+      <c r="AY7" s="23"/>
+      <c r="AZ7" s="23"/>
+      <c r="BA7" s="23"/>
+      <c r="BB7" s="23"/>
+      <c r="BC7" s="24"/>
+      <c r="BE7" s="21"/>
+      <c r="BF7" s="32" t="s">
+        <v>803</v>
+      </c>
+      <c r="BG7" s="23"/>
+      <c r="BH7" s="23"/>
+      <c r="BI7" s="23"/>
+      <c r="BJ7" s="23"/>
+      <c r="BK7" s="23"/>
+      <c r="BL7" s="23"/>
+      <c r="BM7" s="23"/>
+      <c r="BN7" s="23"/>
+      <c r="BO7" s="23"/>
+      <c r="BP7" s="23"/>
+      <c r="BQ7" s="23"/>
+      <c r="BR7" s="23"/>
+      <c r="BS7" s="23"/>
+      <c r="BT7" s="23"/>
+      <c r="BU7" s="23"/>
+      <c r="BV7" s="23"/>
+      <c r="BW7" s="24"/>
+    </row>
+    <row r="8" spans="2:75">
+      <c r="B8" s="12" t="s">
+        <v>961</v>
+      </c>
+      <c r="AL8" s="21"/>
+      <c r="AM8" s="26" t="s">
+        <v>962</v>
+      </c>
+      <c r="AN8" s="23"/>
+      <c r="AO8" s="23"/>
+      <c r="AP8" s="23"/>
+      <c r="AQ8" s="23"/>
+      <c r="AR8" s="23"/>
+      <c r="AS8" s="23"/>
+      <c r="AT8" s="23"/>
+      <c r="AU8" s="23"/>
+      <c r="AV8" s="23"/>
+      <c r="AW8" s="23"/>
+      <c r="AX8" s="23"/>
+      <c r="AY8" s="23"/>
+      <c r="AZ8" s="23"/>
+      <c r="BA8" s="23"/>
+      <c r="BB8" s="23"/>
+      <c r="BC8" s="24"/>
+      <c r="BE8" s="21"/>
+      <c r="BF8" s="32" t="s">
+        <v>804</v>
+      </c>
+      <c r="BG8" s="23"/>
+      <c r="BH8" s="23"/>
+      <c r="BI8" s="23"/>
+      <c r="BJ8" s="23"/>
+      <c r="BK8" s="23"/>
+      <c r="BL8" s="23"/>
+      <c r="BM8" s="23"/>
+      <c r="BN8" s="23"/>
+      <c r="BO8" s="23"/>
+      <c r="BP8" s="23"/>
+      <c r="BQ8" s="23"/>
+      <c r="BR8" s="23"/>
+      <c r="BS8" s="23"/>
+      <c r="BT8" s="23"/>
+      <c r="BU8" s="23"/>
+      <c r="BV8" s="23"/>
+      <c r="BW8" s="24"/>
+    </row>
+    <row r="9" spans="2:75" ht="15">
+      <c r="AL9" s="21"/>
+      <c r="AM9" s="26" t="s">
+        <v>963</v>
+      </c>
+      <c r="AN9" s="23"/>
+      <c r="AO9" s="23"/>
+      <c r="AP9" s="23"/>
+      <c r="AQ9" s="23"/>
+      <c r="AR9" s="23"/>
+      <c r="AS9" s="23"/>
+      <c r="AT9" s="23"/>
+      <c r="AU9" s="23"/>
+      <c r="AV9" s="23"/>
+      <c r="AW9" s="23"/>
+      <c r="AX9" s="23"/>
+      <c r="AY9" s="23"/>
+      <c r="AZ9" s="23"/>
+      <c r="BA9" s="23"/>
+      <c r="BB9" s="23"/>
+      <c r="BC9" s="24"/>
+      <c r="BE9" s="27" t="s">
+        <v>805</v>
+      </c>
+      <c r="BF9" s="23"/>
+      <c r="BG9" s="23"/>
+      <c r="BH9" s="23"/>
+      <c r="BI9" s="23"/>
+      <c r="BJ9" s="23"/>
+      <c r="BK9" s="23"/>
+      <c r="BL9" s="23"/>
+      <c r="BM9" s="23"/>
+      <c r="BN9" s="23"/>
+      <c r="BO9" s="23"/>
+      <c r="BP9" s="23"/>
+      <c r="BQ9" s="23"/>
+      <c r="BR9" s="23"/>
+      <c r="BS9" s="23"/>
+      <c r="BT9" s="23"/>
+      <c r="BU9" s="23"/>
+      <c r="BV9" s="23"/>
+      <c r="BW9" s="24"/>
+    </row>
+    <row r="10" spans="2:75" ht="15.75" thickBot="1">
+      <c r="B10" s="10" t="s">
         <v>857</v>
       </c>
-    </row>
-    <row r="5" spans="2:75" ht="15">
-      <c r="B5" s="13" t="s">
+      <c r="AL10" s="21"/>
+      <c r="AM10" s="25" t="s">
+        <v>964</v>
+      </c>
+      <c r="AN10" s="23"/>
+      <c r="AO10" s="23"/>
+      <c r="AP10" s="23"/>
+      <c r="AQ10" s="23"/>
+      <c r="AR10" s="23"/>
+      <c r="AS10" s="23"/>
+      <c r="AT10" s="23"/>
+      <c r="AU10" s="23"/>
+      <c r="AV10" s="23"/>
+      <c r="AW10" s="23"/>
+      <c r="AX10" s="23"/>
+      <c r="AY10" s="23"/>
+      <c r="AZ10" s="23"/>
+      <c r="BA10" s="23"/>
+      <c r="BB10" s="23"/>
+      <c r="BC10" s="24"/>
+      <c r="BE10" s="29" t="s">
+        <v>965</v>
+      </c>
+      <c r="BF10" s="30"/>
+      <c r="BG10" s="30"/>
+      <c r="BH10" s="30"/>
+      <c r="BI10" s="30"/>
+      <c r="BJ10" s="30"/>
+      <c r="BK10" s="30"/>
+      <c r="BL10" s="30"/>
+      <c r="BM10" s="30"/>
+      <c r="BN10" s="30"/>
+      <c r="BO10" s="30"/>
+      <c r="BP10" s="30"/>
+      <c r="BQ10" s="30"/>
+      <c r="BR10" s="30"/>
+      <c r="BS10" s="30"/>
+      <c r="BT10" s="30"/>
+      <c r="BU10" s="30"/>
+      <c r="BV10" s="30"/>
+      <c r="BW10" s="31"/>
+    </row>
+    <row r="11" spans="2:75" ht="15.75" thickBot="1">
+      <c r="B11" s="12" t="s">
+        <v>966</v>
+      </c>
+      <c r="AL11" s="27" t="s">
+        <v>799</v>
+      </c>
+      <c r="AM11" s="23"/>
+      <c r="AN11" s="23"/>
+      <c r="AO11" s="23"/>
+      <c r="AP11" s="23"/>
+      <c r="AQ11" s="23"/>
+      <c r="AR11" s="23"/>
+      <c r="AS11" s="23"/>
+      <c r="AT11" s="23"/>
+      <c r="AU11" s="23"/>
+      <c r="AV11" s="23"/>
+      <c r="AW11" s="23"/>
+      <c r="AX11" s="23"/>
+      <c r="AY11" s="23"/>
+      <c r="AZ11" s="23"/>
+      <c r="BA11" s="23"/>
+      <c r="BB11" s="23"/>
+      <c r="BC11" s="24"/>
+    </row>
+    <row r="12" spans="2:75" ht="15">
+      <c r="B12" s="12" t="s">
+        <v>967</v>
+      </c>
+      <c r="AL12" s="28" t="s">
+        <v>800</v>
+      </c>
+      <c r="AM12" s="23"/>
+      <c r="AN12" s="23"/>
+      <c r="AO12" s="23"/>
+      <c r="AP12" s="23"/>
+      <c r="AQ12" s="23"/>
+      <c r="AR12" s="23"/>
+      <c r="AS12" s="23"/>
+      <c r="AT12" s="23"/>
+      <c r="AU12" s="23"/>
+      <c r="AV12" s="23"/>
+      <c r="AW12" s="23"/>
+      <c r="AX12" s="23"/>
+      <c r="AY12" s="23"/>
+      <c r="AZ12" s="23"/>
+      <c r="BA12" s="23"/>
+      <c r="BB12" s="23"/>
+      <c r="BC12" s="24"/>
+      <c r="BE12" s="18" t="s">
+        <v>863</v>
+      </c>
+      <c r="BF12" s="19"/>
+      <c r="BG12" s="19"/>
+      <c r="BH12" s="19"/>
+      <c r="BI12" s="19"/>
+      <c r="BJ12" s="19"/>
+      <c r="BK12" s="19"/>
+      <c r="BL12" s="19"/>
+      <c r="BM12" s="19"/>
+      <c r="BN12" s="19"/>
+      <c r="BO12" s="19"/>
+      <c r="BP12" s="19"/>
+      <c r="BQ12" s="19"/>
+      <c r="BR12" s="19"/>
+      <c r="BS12" s="19"/>
+      <c r="BT12" s="19"/>
+      <c r="BU12" s="19"/>
+      <c r="BV12" s="19"/>
+      <c r="BW12" s="20"/>
+    </row>
+    <row r="13" spans="2:75" ht="15">
+      <c r="B13" s="12" t="s">
+        <v>968</v>
+      </c>
+      <c r="AL13" s="28" t="s">
+        <v>801</v>
+      </c>
+      <c r="AM13" s="23"/>
+      <c r="AN13" s="23"/>
+      <c r="AO13" s="23"/>
+      <c r="AP13" s="23"/>
+      <c r="AQ13" s="23"/>
+      <c r="AR13" s="23"/>
+      <c r="AS13" s="23"/>
+      <c r="AT13" s="23"/>
+      <c r="AU13" s="23"/>
+      <c r="AV13" s="23"/>
+      <c r="AW13" s="23"/>
+      <c r="AX13" s="23"/>
+      <c r="AY13" s="23"/>
+      <c r="AZ13" s="23"/>
+      <c r="BA13" s="23"/>
+      <c r="BB13" s="23"/>
+      <c r="BC13" s="24"/>
+      <c r="BE13" s="21"/>
+      <c r="BF13" s="43" t="s">
+        <v>806</v>
+      </c>
+      <c r="BG13" s="43"/>
+      <c r="BH13" s="43"/>
+      <c r="BI13" s="43"/>
+      <c r="BJ13" s="43" t="s">
+        <v>807</v>
+      </c>
+      <c r="BK13" s="43"/>
+      <c r="BL13" s="43"/>
+      <c r="BM13" s="43"/>
+      <c r="BN13" s="43"/>
+      <c r="BO13" s="43"/>
+      <c r="BP13" s="43" t="s">
+        <v>808</v>
+      </c>
+      <c r="BQ13" s="43"/>
+      <c r="BR13" s="43"/>
+      <c r="BS13" s="43"/>
+      <c r="BT13" s="43"/>
+      <c r="BU13" s="43"/>
+      <c r="BV13" s="43"/>
+      <c r="BW13" s="24"/>
+    </row>
+    <row r="14" spans="2:75" ht="15.75" thickBot="1">
+      <c r="AL14" s="29" t="s">
+        <v>969</v>
+      </c>
+      <c r="AM14" s="30"/>
+      <c r="AN14" s="30"/>
+      <c r="AO14" s="30"/>
+      <c r="AP14" s="30"/>
+      <c r="AQ14" s="30"/>
+      <c r="AR14" s="30"/>
+      <c r="AS14" s="30"/>
+      <c r="AT14" s="30"/>
+      <c r="AU14" s="30"/>
+      <c r="AV14" s="30"/>
+      <c r="AW14" s="30"/>
+      <c r="AX14" s="30"/>
+      <c r="AY14" s="30"/>
+      <c r="AZ14" s="30"/>
+      <c r="BA14" s="30"/>
+      <c r="BB14" s="30"/>
+      <c r="BC14" s="31"/>
+      <c r="BE14" s="21"/>
+      <c r="BF14" s="45" t="s">
+        <v>809</v>
+      </c>
+      <c r="BG14" s="45"/>
+      <c r="BH14" s="45"/>
+      <c r="BI14" s="45"/>
+      <c r="BJ14" s="44" t="s">
+        <v>810</v>
+      </c>
+      <c r="BK14" s="44"/>
+      <c r="BL14" s="44"/>
+      <c r="BM14" s="44"/>
+      <c r="BN14" s="44"/>
+      <c r="BO14" s="44"/>
+      <c r="BP14" s="44" t="s">
+        <v>810</v>
+      </c>
+      <c r="BQ14" s="44"/>
+      <c r="BR14" s="44"/>
+      <c r="BS14" s="44"/>
+      <c r="BT14" s="44"/>
+      <c r="BU14" s="44"/>
+      <c r="BV14" s="44"/>
+      <c r="BW14" s="24"/>
+    </row>
+    <row r="15" spans="2:75" ht="15.75" thickBot="1">
+      <c r="B15" s="10" t="s">
         <v>858</v>
       </c>
-      <c r="AL5" s="22" t="s">
-        <v>798</v>
-      </c>
-      <c r="AM5" s="23"/>
-      <c r="AN5" s="23"/>
-      <c r="AO5" s="23"/>
-      <c r="AP5" s="23"/>
-      <c r="AQ5" s="23"/>
-      <c r="AR5" s="23"/>
-      <c r="AS5" s="23"/>
-      <c r="AT5" s="23"/>
-      <c r="AU5" s="23"/>
-      <c r="AV5" s="23"/>
-      <c r="AW5" s="23"/>
-      <c r="AX5" s="23"/>
-      <c r="AY5" s="23"/>
-      <c r="AZ5" s="23"/>
-      <c r="BA5" s="23"/>
-      <c r="BB5" s="23"/>
-      <c r="BC5" s="24"/>
-      <c r="BE5" s="22" t="s">
-        <v>803</v>
-      </c>
-      <c r="BF5" s="23"/>
-      <c r="BG5" s="23"/>
-      <c r="BH5" s="23"/>
-      <c r="BI5" s="23"/>
-      <c r="BJ5" s="23"/>
-      <c r="BK5" s="23"/>
-      <c r="BL5" s="23"/>
-      <c r="BM5" s="23"/>
-      <c r="BN5" s="23"/>
-      <c r="BO5" s="23"/>
-      <c r="BP5" s="23"/>
-      <c r="BQ5" s="23"/>
-      <c r="BR5" s="23"/>
-      <c r="BS5" s="23"/>
-      <c r="BT5" s="23"/>
-      <c r="BU5" s="23"/>
-      <c r="BV5" s="23"/>
-      <c r="BW5" s="24"/>
-    </row>
-    <row r="6" spans="2:75" ht="15">
-      <c r="B6" s="13" t="s">
+      <c r="AL15" s="13"/>
+      <c r="BE15" s="21"/>
+      <c r="BF15" s="45" t="s">
+        <v>811</v>
+      </c>
+      <c r="BG15" s="45"/>
+      <c r="BH15" s="45"/>
+      <c r="BI15" s="45"/>
+      <c r="BJ15" s="44" t="s">
+        <v>812</v>
+      </c>
+      <c r="BK15" s="44"/>
+      <c r="BL15" s="44"/>
+      <c r="BM15" s="44"/>
+      <c r="BN15" s="44"/>
+      <c r="BO15" s="44"/>
+      <c r="BP15" s="44" t="s">
+        <v>813</v>
+      </c>
+      <c r="BQ15" s="44"/>
+      <c r="BR15" s="44"/>
+      <c r="BS15" s="44"/>
+      <c r="BT15" s="44"/>
+      <c r="BU15" s="44"/>
+      <c r="BV15" s="44"/>
+      <c r="BW15" s="24"/>
+    </row>
+    <row r="16" spans="2:75" ht="15">
+      <c r="B16" s="12" t="s">
+        <v>970</v>
+      </c>
+      <c r="AL16" s="18" t="s">
+        <v>864</v>
+      </c>
+      <c r="AM16" s="19"/>
+      <c r="AN16" s="19"/>
+      <c r="AO16" s="19"/>
+      <c r="AP16" s="19"/>
+      <c r="AQ16" s="19"/>
+      <c r="AR16" s="19"/>
+      <c r="AS16" s="19"/>
+      <c r="AT16" s="19"/>
+      <c r="AU16" s="19"/>
+      <c r="AV16" s="19"/>
+      <c r="AW16" s="19"/>
+      <c r="AX16" s="19"/>
+      <c r="AY16" s="19"/>
+      <c r="AZ16" s="19"/>
+      <c r="BA16" s="19"/>
+      <c r="BB16" s="19"/>
+      <c r="BC16" s="20"/>
+      <c r="BE16" s="21"/>
+      <c r="BF16" s="45" t="s">
+        <v>814</v>
+      </c>
+      <c r="BG16" s="45"/>
+      <c r="BH16" s="45"/>
+      <c r="BI16" s="45"/>
+      <c r="BJ16" s="44" t="s">
+        <v>815</v>
+      </c>
+      <c r="BK16" s="44"/>
+      <c r="BL16" s="44"/>
+      <c r="BM16" s="44"/>
+      <c r="BN16" s="44"/>
+      <c r="BO16" s="44"/>
+      <c r="BP16" s="44" t="s">
+        <v>815</v>
+      </c>
+      <c r="BQ16" s="44"/>
+      <c r="BR16" s="44"/>
+      <c r="BS16" s="44"/>
+      <c r="BT16" s="44"/>
+      <c r="BU16" s="44"/>
+      <c r="BV16" s="44"/>
+      <c r="BW16" s="24"/>
+    </row>
+    <row r="17" spans="2:88" ht="15">
+      <c r="B17" s="12" t="s">
+        <v>971</v>
+      </c>
+      <c r="AL17" s="27" t="s">
+        <v>816</v>
+      </c>
+      <c r="AM17" s="23"/>
+      <c r="AN17" s="23"/>
+      <c r="AO17" s="23"/>
+      <c r="AP17" s="23"/>
+      <c r="AQ17" s="23"/>
+      <c r="AR17" s="23"/>
+      <c r="AS17" s="23"/>
+      <c r="AT17" s="23"/>
+      <c r="AU17" s="23"/>
+      <c r="AV17" s="23"/>
+      <c r="AW17" s="23"/>
+      <c r="AX17" s="23"/>
+      <c r="AY17" s="23"/>
+      <c r="AZ17" s="23"/>
+      <c r="BA17" s="23"/>
+      <c r="BB17" s="23"/>
+      <c r="BC17" s="24"/>
+      <c r="BE17" s="21"/>
+      <c r="BF17" s="23"/>
+      <c r="BG17" s="23"/>
+      <c r="BH17" s="23"/>
+      <c r="BI17" s="23"/>
+      <c r="BJ17" s="23"/>
+      <c r="BK17" s="23"/>
+      <c r="BL17" s="23"/>
+      <c r="BM17" s="23"/>
+      <c r="BN17" s="23"/>
+      <c r="BO17" s="23"/>
+      <c r="BP17" s="23"/>
+      <c r="BQ17" s="23"/>
+      <c r="BR17" s="23"/>
+      <c r="BS17" s="23"/>
+      <c r="BT17" s="23"/>
+      <c r="BU17" s="23"/>
+      <c r="BV17" s="23"/>
+      <c r="BW17" s="24"/>
+    </row>
+    <row r="18" spans="2:88" ht="15" customHeight="1">
+      <c r="B18" s="13" t="s">
+        <v>772</v>
+      </c>
+      <c r="AL18" s="21"/>
+      <c r="AM18" s="23"/>
+      <c r="AN18" s="32" t="s">
+        <v>817</v>
+      </c>
+      <c r="AO18" s="23"/>
+      <c r="AP18" s="23"/>
+      <c r="AQ18" s="23"/>
+      <c r="AR18" s="23"/>
+      <c r="AS18" s="23"/>
+      <c r="AT18" s="23"/>
+      <c r="AU18" s="23"/>
+      <c r="AV18" s="23"/>
+      <c r="AW18" s="23"/>
+      <c r="AX18" s="23"/>
+      <c r="AY18" s="23"/>
+      <c r="AZ18" s="23"/>
+      <c r="BA18" s="23"/>
+      <c r="BB18" s="23"/>
+      <c r="BC18" s="24"/>
+      <c r="BE18" s="34" t="s">
+        <v>972</v>
+      </c>
+      <c r="BF18" s="23"/>
+      <c r="BG18" s="23"/>
+      <c r="BH18" s="23"/>
+      <c r="BI18" s="23"/>
+      <c r="BJ18" s="23"/>
+      <c r="BK18" s="23"/>
+      <c r="BL18" s="23"/>
+      <c r="BM18" s="23"/>
+      <c r="BN18" s="23"/>
+      <c r="BO18" s="23"/>
+      <c r="BP18" s="23"/>
+      <c r="BQ18" s="23"/>
+      <c r="BR18" s="23"/>
+      <c r="BS18" s="23"/>
+      <c r="BT18" s="23"/>
+      <c r="BU18" s="23"/>
+      <c r="BV18" s="23"/>
+      <c r="BW18" s="24"/>
+    </row>
+    <row r="19" spans="2:88" ht="14.25" customHeight="1" thickBot="1">
+      <c r="AL19" s="21"/>
+      <c r="AM19" s="23"/>
+      <c r="AN19" s="32" t="s">
+        <v>818</v>
+      </c>
+      <c r="AO19" s="23"/>
+      <c r="AP19" s="23"/>
+      <c r="AQ19" s="23"/>
+      <c r="AR19" s="23"/>
+      <c r="AS19" s="23"/>
+      <c r="AT19" s="23"/>
+      <c r="AU19" s="23"/>
+      <c r="AV19" s="23"/>
+      <c r="AW19" s="23"/>
+      <c r="AX19" s="23"/>
+      <c r="AY19" s="23"/>
+      <c r="AZ19" s="23"/>
+      <c r="BA19" s="23"/>
+      <c r="BB19" s="23"/>
+      <c r="BC19" s="24"/>
+      <c r="BE19" s="35" t="s">
+        <v>874</v>
+      </c>
+      <c r="BF19" s="30"/>
+      <c r="BG19" s="30"/>
+      <c r="BH19" s="30"/>
+      <c r="BI19" s="30"/>
+      <c r="BJ19" s="30"/>
+      <c r="BK19" s="30"/>
+      <c r="BL19" s="30"/>
+      <c r="BM19" s="30"/>
+      <c r="BN19" s="30"/>
+      <c r="BO19" s="30"/>
+      <c r="BP19" s="30"/>
+      <c r="BQ19" s="30"/>
+      <c r="BR19" s="30"/>
+      <c r="BS19" s="30"/>
+      <c r="BT19" s="30"/>
+      <c r="BU19" s="30"/>
+      <c r="BV19" s="30"/>
+      <c r="BW19" s="31"/>
+    </row>
+    <row r="20" spans="2:88" ht="15" customHeight="1">
+      <c r="B20" s="10" t="s">
         <v>859</v>
       </c>
-      <c r="AL6" s="25"/>
-      <c r="AM6" s="26" t="s">
+      <c r="AL20" s="21"/>
+      <c r="AM20" s="23"/>
+      <c r="AN20" s="32" t="s">
+        <v>819</v>
+      </c>
+      <c r="AO20" s="23"/>
+      <c r="AP20" s="23"/>
+      <c r="AQ20" s="23"/>
+      <c r="AR20" s="23"/>
+      <c r="AS20" s="23"/>
+      <c r="AT20" s="23"/>
+      <c r="AU20" s="23"/>
+      <c r="AV20" s="23"/>
+      <c r="AW20" s="23"/>
+      <c r="AX20" s="23"/>
+      <c r="AY20" s="23"/>
+      <c r="AZ20" s="23"/>
+      <c r="BA20" s="23"/>
+      <c r="BB20" s="23"/>
+      <c r="BC20" s="24"/>
+    </row>
+    <row r="21" spans="2:88" ht="14.25" customHeight="1" thickBot="1">
+      <c r="B21" s="12" t="s">
+        <v>973</v>
+      </c>
+      <c r="AL21" s="36" t="s">
+        <v>974</v>
+      </c>
+      <c r="AM21" s="23"/>
+      <c r="AN21" s="23"/>
+      <c r="AO21" s="23"/>
+      <c r="AP21" s="23"/>
+      <c r="AQ21" s="23"/>
+      <c r="AR21" s="23"/>
+      <c r="AS21" s="23"/>
+      <c r="AT21" s="23"/>
+      <c r="AU21" s="23"/>
+      <c r="AV21" s="23"/>
+      <c r="AW21" s="23"/>
+      <c r="AX21" s="23"/>
+      <c r="AY21" s="23"/>
+      <c r="AZ21" s="23"/>
+      <c r="BA21" s="23"/>
+      <c r="BB21" s="23"/>
+      <c r="BC21" s="24"/>
+    </row>
+    <row r="22" spans="2:88" ht="15">
+      <c r="B22" s="12" t="s">
+        <v>975</v>
+      </c>
+      <c r="AL22" s="27" t="s">
+        <v>820</v>
+      </c>
+      <c r="AM22" s="23"/>
+      <c r="AN22" s="23"/>
+      <c r="AO22" s="23"/>
+      <c r="AP22" s="23"/>
+      <c r="AQ22" s="23"/>
+      <c r="AR22" s="23"/>
+      <c r="AS22" s="23"/>
+      <c r="AT22" s="23"/>
+      <c r="AU22" s="23"/>
+      <c r="AV22" s="23"/>
+      <c r="AW22" s="23"/>
+      <c r="AX22" s="23"/>
+      <c r="AY22" s="23"/>
+      <c r="AZ22" s="23"/>
+      <c r="BA22" s="23"/>
+      <c r="BB22" s="23"/>
+      <c r="BC22" s="24"/>
+      <c r="BH22" s="18" t="s">
+        <v>869</v>
+      </c>
+      <c r="BI22" s="19"/>
+      <c r="BJ22" s="19"/>
+      <c r="BK22" s="19"/>
+      <c r="BL22" s="19"/>
+      <c r="BM22" s="19"/>
+      <c r="BN22" s="19"/>
+      <c r="BO22" s="19"/>
+      <c r="BP22" s="19"/>
+      <c r="BQ22" s="19"/>
+      <c r="BR22" s="19"/>
+      <c r="BS22" s="19"/>
+      <c r="BT22" s="19"/>
+      <c r="BU22" s="19"/>
+      <c r="BV22" s="19"/>
+      <c r="BW22" s="19"/>
+      <c r="BX22" s="19"/>
+      <c r="BY22" s="19"/>
+      <c r="BZ22" s="19"/>
+      <c r="CA22" s="19"/>
+      <c r="CB22" s="19"/>
+      <c r="CC22" s="19"/>
+      <c r="CD22" s="19"/>
+      <c r="CE22" s="19"/>
+      <c r="CF22" s="19"/>
+      <c r="CG22" s="19"/>
+      <c r="CH22" s="19"/>
+      <c r="CI22" s="19"/>
+      <c r="CJ22" s="20"/>
+    </row>
+    <row r="23" spans="2:88" ht="15">
+      <c r="B23" s="12" t="s">
+        <v>976</v>
+      </c>
+      <c r="AL23" s="34" t="s">
+        <v>977</v>
+      </c>
+      <c r="AM23" s="23"/>
+      <c r="AN23" s="23"/>
+      <c r="AO23" s="23"/>
+      <c r="AP23" s="23"/>
+      <c r="AQ23" s="23"/>
+      <c r="AR23" s="23"/>
+      <c r="AS23" s="23"/>
+      <c r="AT23" s="23"/>
+      <c r="AU23" s="23"/>
+      <c r="AV23" s="23"/>
+      <c r="AW23" s="23"/>
+      <c r="AX23" s="23"/>
+      <c r="AY23" s="23"/>
+      <c r="AZ23" s="23"/>
+      <c r="BA23" s="23"/>
+      <c r="BB23" s="23"/>
+      <c r="BC23" s="24"/>
+      <c r="BH23" s="48" t="s">
+        <v>837</v>
+      </c>
+      <c r="BI23" s="23"/>
+      <c r="BJ23" s="23"/>
+      <c r="BK23" s="23"/>
+      <c r="BL23" s="23"/>
+      <c r="BM23" s="23"/>
+      <c r="BN23" s="23"/>
+      <c r="BO23" s="23"/>
+      <c r="BP23" s="23"/>
+      <c r="BQ23" s="23"/>
+      <c r="BR23" s="23"/>
+      <c r="BS23" s="23"/>
+      <c r="BT23" s="23"/>
+      <c r="BU23" s="23"/>
+      <c r="BV23" s="23"/>
+      <c r="BW23" s="23"/>
+      <c r="BX23" s="23"/>
+      <c r="BY23" s="23"/>
+      <c r="BZ23" s="23"/>
+      <c r="CA23" s="23"/>
+      <c r="CB23" s="23"/>
+      <c r="CC23" s="23"/>
+      <c r="CD23" s="23"/>
+      <c r="CE23" s="23"/>
+      <c r="CF23" s="23"/>
+      <c r="CG23" s="23"/>
+      <c r="CH23" s="23"/>
+      <c r="CI23" s="23"/>
+      <c r="CJ23" s="24"/>
+    </row>
+    <row r="24" spans="2:88" ht="15" thickBot="1">
+      <c r="AL24" s="29" t="s">
+        <v>978</v>
+      </c>
+      <c r="AM24" s="30"/>
+      <c r="AN24" s="30"/>
+      <c r="AO24" s="30"/>
+      <c r="AP24" s="30"/>
+      <c r="AQ24" s="30"/>
+      <c r="AR24" s="30"/>
+      <c r="AS24" s="30"/>
+      <c r="AT24" s="30"/>
+      <c r="AU24" s="30"/>
+      <c r="AV24" s="30"/>
+      <c r="AW24" s="30"/>
+      <c r="AX24" s="30"/>
+      <c r="AY24" s="30"/>
+      <c r="AZ24" s="30"/>
+      <c r="BA24" s="30"/>
+      <c r="BB24" s="30"/>
+      <c r="BC24" s="31"/>
+      <c r="BH24" s="28" t="s">
+        <v>838</v>
+      </c>
+      <c r="BI24" s="23"/>
+      <c r="BJ24" s="23"/>
+      <c r="BK24" s="23"/>
+      <c r="BL24" s="23"/>
+      <c r="BM24" s="23"/>
+      <c r="BN24" s="23"/>
+      <c r="BO24" s="23"/>
+      <c r="BP24" s="23"/>
+      <c r="BQ24" s="23"/>
+      <c r="BR24" s="23"/>
+      <c r="BS24" s="23"/>
+      <c r="BT24" s="23"/>
+      <c r="BU24" s="23"/>
+      <c r="BV24" s="23"/>
+      <c r="BW24" s="23"/>
+      <c r="BX24" s="23"/>
+      <c r="BY24" s="23"/>
+      <c r="BZ24" s="23"/>
+      <c r="CA24" s="23"/>
+      <c r="CB24" s="23"/>
+      <c r="CC24" s="23"/>
+      <c r="CD24" s="23"/>
+      <c r="CE24" s="23"/>
+      <c r="CF24" s="23"/>
+      <c r="CG24" s="23"/>
+      <c r="CH24" s="23"/>
+      <c r="CI24" s="23"/>
+      <c r="CJ24" s="24"/>
+    </row>
+    <row r="25" spans="2:88" ht="15.75" thickBot="1">
+      <c r="B25" s="10" t="s">
+        <v>860</v>
+      </c>
+      <c r="AL25" s="14"/>
+      <c r="BH25" s="36" t="s">
+        <v>979</v>
+      </c>
+      <c r="BI25" s="23"/>
+      <c r="BJ25" s="23"/>
+      <c r="BK25" s="23"/>
+      <c r="BL25" s="23"/>
+      <c r="BM25" s="23"/>
+      <c r="BN25" s="23"/>
+      <c r="BO25" s="23"/>
+      <c r="BP25" s="23"/>
+      <c r="BQ25" s="23"/>
+      <c r="BR25" s="23"/>
+      <c r="BS25" s="23"/>
+      <c r="BT25" s="23"/>
+      <c r="BU25" s="23"/>
+      <c r="BV25" s="23"/>
+      <c r="BW25" s="23"/>
+      <c r="BX25" s="23"/>
+      <c r="BY25" s="23"/>
+      <c r="BZ25" s="23"/>
+      <c r="CA25" s="23"/>
+      <c r="CB25" s="23"/>
+      <c r="CC25" s="23"/>
+      <c r="CD25" s="23"/>
+      <c r="CE25" s="23"/>
+      <c r="CF25" s="23"/>
+      <c r="CG25" s="23"/>
+      <c r="CH25" s="23"/>
+      <c r="CI25" s="23"/>
+      <c r="CJ25" s="24"/>
+    </row>
+    <row r="26" spans="2:88" ht="15">
+      <c r="B26" s="13" t="s">
+        <v>773</v>
+      </c>
+      <c r="AL26" s="18" t="s">
+        <v>866</v>
+      </c>
+      <c r="AM26" s="19"/>
+      <c r="AN26" s="19"/>
+      <c r="AO26" s="19"/>
+      <c r="AP26" s="19"/>
+      <c r="AQ26" s="19"/>
+      <c r="AR26" s="19"/>
+      <c r="AS26" s="19"/>
+      <c r="AT26" s="19"/>
+      <c r="AU26" s="19"/>
+      <c r="AV26" s="19"/>
+      <c r="AW26" s="19"/>
+      <c r="AX26" s="19"/>
+      <c r="AY26" s="19"/>
+      <c r="AZ26" s="19"/>
+      <c r="BA26" s="19"/>
+      <c r="BB26" s="19"/>
+      <c r="BC26" s="19"/>
+      <c r="BD26" s="19"/>
+      <c r="BE26" s="19"/>
+      <c r="BF26" s="20"/>
+      <c r="BH26" s="27" t="s">
+        <v>839</v>
+      </c>
+      <c r="BI26" s="23"/>
+      <c r="BJ26" s="23"/>
+      <c r="BK26" s="23"/>
+      <c r="BL26" s="23"/>
+      <c r="BM26" s="23"/>
+      <c r="BN26" s="23"/>
+      <c r="BO26" s="23"/>
+      <c r="BP26" s="23"/>
+      <c r="BQ26" s="23"/>
+      <c r="BR26" s="23"/>
+      <c r="BS26" s="23"/>
+      <c r="BT26" s="23"/>
+      <c r="BU26" s="23"/>
+      <c r="BV26" s="23"/>
+      <c r="BW26" s="23"/>
+      <c r="BX26" s="23"/>
+      <c r="BY26" s="23"/>
+      <c r="BZ26" s="23"/>
+      <c r="CA26" s="23"/>
+      <c r="CB26" s="23"/>
+      <c r="CC26" s="23"/>
+      <c r="CD26" s="23"/>
+      <c r="CE26" s="23"/>
+      <c r="CF26" s="23"/>
+      <c r="CG26" s="23"/>
+      <c r="CH26" s="23"/>
+      <c r="CI26" s="23"/>
+      <c r="CJ26" s="24"/>
+    </row>
+    <row r="27" spans="2:88" ht="15">
+      <c r="B27" s="13" t="s">
+        <v>980</v>
+      </c>
+      <c r="AL27" s="27" t="s">
+        <v>821</v>
+      </c>
+      <c r="AM27" s="23"/>
+      <c r="AN27" s="23"/>
+      <c r="AO27" s="23"/>
+      <c r="AP27" s="23"/>
+      <c r="AQ27" s="23"/>
+      <c r="AR27" s="23"/>
+      <c r="AS27" s="23"/>
+      <c r="AT27" s="23"/>
+      <c r="AU27" s="23"/>
+      <c r="AV27" s="23"/>
+      <c r="AW27" s="23"/>
+      <c r="AX27" s="23"/>
+      <c r="AY27" s="23"/>
+      <c r="AZ27" s="23"/>
+      <c r="BA27" s="23"/>
+      <c r="BB27" s="23"/>
+      <c r="BC27" s="23"/>
+      <c r="BD27" s="23"/>
+      <c r="BE27" s="23"/>
+      <c r="BF27" s="24"/>
+      <c r="BH27" s="28" t="s">
+        <v>840</v>
+      </c>
+      <c r="BI27" s="23"/>
+      <c r="BJ27" s="23"/>
+      <c r="BK27" s="23"/>
+      <c r="BL27" s="23"/>
+      <c r="BM27" s="23"/>
+      <c r="BN27" s="23"/>
+      <c r="BO27" s="23"/>
+      <c r="BP27" s="23"/>
+      <c r="BQ27" s="23"/>
+      <c r="BR27" s="23"/>
+      <c r="BS27" s="23"/>
+      <c r="BT27" s="23"/>
+      <c r="BU27" s="23"/>
+      <c r="BV27" s="23"/>
+      <c r="BW27" s="23"/>
+      <c r="BX27" s="23"/>
+      <c r="BY27" s="23"/>
+      <c r="BZ27" s="23"/>
+      <c r="CA27" s="23"/>
+      <c r="CB27" s="23"/>
+      <c r="CC27" s="23"/>
+      <c r="CD27" s="23"/>
+      <c r="CE27" s="23"/>
+      <c r="CF27" s="23"/>
+      <c r="CG27" s="23"/>
+      <c r="CH27" s="23"/>
+      <c r="CI27" s="23"/>
+      <c r="CJ27" s="24"/>
+    </row>
+    <row r="28" spans="2:88" ht="15.75" thickBot="1">
+      <c r="B28" s="13" t="s">
+        <v>981</v>
+      </c>
+      <c r="AL28" s="21"/>
+      <c r="AM28" s="43" t="s">
+        <v>806</v>
+      </c>
+      <c r="AN28" s="43"/>
+      <c r="AO28" s="43"/>
+      <c r="AP28" s="43" t="s">
+        <v>822</v>
+      </c>
+      <c r="AQ28" s="43"/>
+      <c r="AR28" s="43"/>
+      <c r="AS28" s="43"/>
+      <c r="AT28" s="43"/>
+      <c r="AU28" s="43"/>
+      <c r="AV28" s="43"/>
+      <c r="AW28" s="43"/>
+      <c r="AX28" s="43" t="s">
+        <v>823</v>
+      </c>
+      <c r="AY28" s="43"/>
+      <c r="AZ28" s="43"/>
+      <c r="BA28" s="43"/>
+      <c r="BB28" s="43" t="s">
+        <v>824</v>
+      </c>
+      <c r="BC28" s="43"/>
+      <c r="BD28" s="43"/>
+      <c r="BE28" s="43"/>
+      <c r="BF28" s="24"/>
+      <c r="BH28" s="29" t="s">
+        <v>841</v>
+      </c>
+      <c r="BI28" s="30"/>
+      <c r="BJ28" s="30"/>
+      <c r="BK28" s="30"/>
+      <c r="BL28" s="30"/>
+      <c r="BM28" s="30"/>
+      <c r="BN28" s="30"/>
+      <c r="BO28" s="30"/>
+      <c r="BP28" s="30"/>
+      <c r="BQ28" s="30"/>
+      <c r="BR28" s="30"/>
+      <c r="BS28" s="30"/>
+      <c r="BT28" s="30"/>
+      <c r="BU28" s="30"/>
+      <c r="BV28" s="30"/>
+      <c r="BW28" s="30"/>
+      <c r="BX28" s="30"/>
+      <c r="BY28" s="30"/>
+      <c r="BZ28" s="30"/>
+      <c r="CA28" s="30"/>
+      <c r="CB28" s="30"/>
+      <c r="CC28" s="30"/>
+      <c r="CD28" s="30"/>
+      <c r="CE28" s="30"/>
+      <c r="CF28" s="30"/>
+      <c r="CG28" s="30"/>
+      <c r="CH28" s="30"/>
+      <c r="CI28" s="30"/>
+      <c r="CJ28" s="31"/>
+    </row>
+    <row r="29" spans="2:88" ht="15" thickBot="1">
+      <c r="AL29" s="21"/>
+      <c r="AM29" s="45" t="s">
+        <v>825</v>
+      </c>
+      <c r="AN29" s="45"/>
+      <c r="AO29" s="45"/>
+      <c r="AP29" s="44" t="s">
+        <v>982</v>
+      </c>
+      <c r="AQ29" s="44"/>
+      <c r="AR29" s="44"/>
+      <c r="AS29" s="44"/>
+      <c r="AT29" s="44"/>
+      <c r="AU29" s="44"/>
+      <c r="AV29" s="44"/>
+      <c r="AW29" s="44"/>
+      <c r="AX29" s="44" t="s">
+        <v>826</v>
+      </c>
+      <c r="AY29" s="44"/>
+      <c r="AZ29" s="44"/>
+      <c r="BA29" s="44"/>
+      <c r="BB29" s="45" t="s">
+        <v>827</v>
+      </c>
+      <c r="BC29" s="45"/>
+      <c r="BD29" s="45"/>
+      <c r="BE29" s="45"/>
+      <c r="BF29" s="24"/>
+    </row>
+    <row r="30" spans="2:88" ht="15">
+      <c r="B30" s="10" t="s">
+        <v>774</v>
+      </c>
+      <c r="AL30" s="21"/>
+      <c r="AM30" s="45" t="s">
+        <v>828</v>
+      </c>
+      <c r="AN30" s="45"/>
+      <c r="AO30" s="45"/>
+      <c r="AP30" s="44" t="s">
+        <v>829</v>
+      </c>
+      <c r="AQ30" s="44"/>
+      <c r="AR30" s="44"/>
+      <c r="AS30" s="44"/>
+      <c r="AT30" s="44"/>
+      <c r="AU30" s="44"/>
+      <c r="AV30" s="44"/>
+      <c r="AW30" s="44"/>
+      <c r="AX30" s="44" t="s">
+        <v>830</v>
+      </c>
+      <c r="AY30" s="44"/>
+      <c r="AZ30" s="44"/>
+      <c r="BA30" s="44"/>
+      <c r="BB30" s="45" t="s">
+        <v>831</v>
+      </c>
+      <c r="BC30" s="45"/>
+      <c r="BD30" s="45"/>
+      <c r="BE30" s="45"/>
+      <c r="BF30" s="24"/>
+      <c r="BH30" s="18" t="s">
+        <v>842</v>
+      </c>
+      <c r="BI30" s="19"/>
+      <c r="BJ30" s="19"/>
+      <c r="BK30" s="19"/>
+      <c r="BL30" s="19"/>
+      <c r="BM30" s="19"/>
+      <c r="BN30" s="19"/>
+      <c r="BO30" s="19"/>
+      <c r="BP30" s="19"/>
+      <c r="BQ30" s="19"/>
+      <c r="BR30" s="19"/>
+      <c r="BS30" s="19"/>
+      <c r="BT30" s="19"/>
+      <c r="BU30" s="19"/>
+      <c r="BV30" s="19"/>
+      <c r="BW30" s="19"/>
+      <c r="BX30" s="19"/>
+      <c r="BY30" s="19"/>
+      <c r="BZ30" s="19"/>
+      <c r="CA30" s="19"/>
+      <c r="CB30" s="19"/>
+      <c r="CC30" s="20"/>
+    </row>
+    <row r="31" spans="2:88" ht="15">
+      <c r="B31" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="AL31" s="21"/>
+      <c r="AM31" s="45" t="s">
+        <v>831</v>
+      </c>
+      <c r="AN31" s="45"/>
+      <c r="AO31" s="45"/>
+      <c r="AP31" s="44" t="s">
+        <v>832</v>
+      </c>
+      <c r="AQ31" s="44"/>
+      <c r="AR31" s="44"/>
+      <c r="AS31" s="44"/>
+      <c r="AT31" s="44"/>
+      <c r="AU31" s="44"/>
+      <c r="AV31" s="44"/>
+      <c r="AW31" s="44"/>
+      <c r="AX31" s="44" t="s">
+        <v>830</v>
+      </c>
+      <c r="AY31" s="44"/>
+      <c r="AZ31" s="44"/>
+      <c r="BA31" s="44"/>
+      <c r="BB31" s="45" t="s">
+        <v>833</v>
+      </c>
+      <c r="BC31" s="45"/>
+      <c r="BD31" s="45"/>
+      <c r="BE31" s="45"/>
+      <c r="BF31" s="24"/>
+      <c r="BH31" s="27" t="s">
+        <v>843</v>
+      </c>
+      <c r="BI31" s="23"/>
+      <c r="BJ31" s="23"/>
+      <c r="BK31" s="23"/>
+      <c r="BL31" s="23"/>
+      <c r="BM31" s="23"/>
+      <c r="BN31" s="23"/>
+      <c r="BO31" s="23"/>
+      <c r="BP31" s="23"/>
+      <c r="BQ31" s="23"/>
+      <c r="BR31" s="23"/>
+      <c r="BS31" s="23"/>
+      <c r="BT31" s="23"/>
+      <c r="BU31" s="23"/>
+      <c r="BV31" s="23"/>
+      <c r="BW31" s="23"/>
+      <c r="BX31" s="23"/>
+      <c r="BY31" s="23"/>
+      <c r="BZ31" s="23"/>
+      <c r="CA31" s="23"/>
+      <c r="CB31" s="23"/>
+      <c r="CC31" s="24"/>
+    </row>
+    <row r="32" spans="2:88" ht="15">
+      <c r="B32" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="AL32" s="27" t="s">
+        <v>834</v>
+      </c>
+      <c r="AM32" s="23"/>
+      <c r="AN32" s="23"/>
+      <c r="AO32" s="23"/>
+      <c r="AP32" s="23"/>
+      <c r="AQ32" s="23"/>
+      <c r="AR32" s="23"/>
+      <c r="AS32" s="23"/>
+      <c r="AT32" s="23"/>
+      <c r="AU32" s="23"/>
+      <c r="AV32" s="23"/>
+      <c r="AW32" s="23"/>
+      <c r="AX32" s="23"/>
+      <c r="AY32" s="23"/>
+      <c r="AZ32" s="23"/>
+      <c r="BA32" s="23"/>
+      <c r="BB32" s="23"/>
+      <c r="BC32" s="23"/>
+      <c r="BD32" s="23"/>
+      <c r="BE32" s="23"/>
+      <c r="BF32" s="24"/>
+      <c r="BH32" s="34" t="s">
+        <v>844</v>
+      </c>
+      <c r="BI32" s="23"/>
+      <c r="BJ32" s="23"/>
+      <c r="BK32" s="23"/>
+      <c r="BL32" s="23"/>
+      <c r="BM32" s="23"/>
+      <c r="BN32" s="23"/>
+      <c r="BO32" s="23"/>
+      <c r="BP32" s="23"/>
+      <c r="BQ32" s="23"/>
+      <c r="BR32" s="23"/>
+      <c r="BS32" s="23"/>
+      <c r="BT32" s="23"/>
+      <c r="BU32" s="23"/>
+      <c r="BV32" s="23"/>
+      <c r="BW32" s="23"/>
+      <c r="BX32" s="23"/>
+      <c r="BY32" s="23"/>
+      <c r="BZ32" s="23"/>
+      <c r="CA32" s="23"/>
+      <c r="CB32" s="23"/>
+      <c r="CC32" s="24"/>
+    </row>
+    <row r="33" spans="2:81" ht="15">
+      <c r="C33" s="42" t="s">
+        <v>875</v>
+      </c>
+      <c r="AL33" s="28" t="s">
+        <v>835</v>
+      </c>
+      <c r="AM33" s="23"/>
+      <c r="AN33" s="23"/>
+      <c r="AO33" s="23"/>
+      <c r="AP33" s="23"/>
+      <c r="AQ33" s="23"/>
+      <c r="AR33" s="23"/>
+      <c r="AS33" s="23"/>
+      <c r="AT33" s="23"/>
+      <c r="AU33" s="23"/>
+      <c r="AV33" s="23"/>
+      <c r="AW33" s="23"/>
+      <c r="AX33" s="23"/>
+      <c r="AY33" s="23"/>
+      <c r="AZ33" s="23"/>
+      <c r="BA33" s="23"/>
+      <c r="BB33" s="23"/>
+      <c r="BC33" s="23"/>
+      <c r="BD33" s="23"/>
+      <c r="BE33" s="23"/>
+      <c r="BF33" s="24"/>
+      <c r="BH33" s="38" t="s">
+        <v>983</v>
+      </c>
+      <c r="BI33" s="23"/>
+      <c r="BJ33" s="23"/>
+      <c r="BK33" s="23"/>
+      <c r="BL33" s="23"/>
+      <c r="BM33" s="23"/>
+      <c r="BN33" s="23"/>
+      <c r="BO33" s="23"/>
+      <c r="BP33" s="23"/>
+      <c r="BQ33" s="23"/>
+      <c r="BR33" s="23"/>
+      <c r="BS33" s="23"/>
+      <c r="BT33" s="23"/>
+      <c r="BU33" s="23"/>
+      <c r="BV33" s="23"/>
+      <c r="BW33" s="23"/>
+      <c r="BX33" s="23"/>
+      <c r="BY33" s="23"/>
+      <c r="BZ33" s="23"/>
+      <c r="CA33" s="23"/>
+      <c r="CB33" s="23"/>
+      <c r="CC33" s="24"/>
+    </row>
+    <row r="34" spans="2:81" ht="15" thickBot="1">
+      <c r="AL34" s="37" t="s">
+        <v>836</v>
+      </c>
+      <c r="AM34" s="30"/>
+      <c r="AN34" s="30"/>
+      <c r="AO34" s="30"/>
+      <c r="AP34" s="30"/>
+      <c r="AQ34" s="30"/>
+      <c r="AR34" s="30"/>
+      <c r="AS34" s="30"/>
+      <c r="AT34" s="30"/>
+      <c r="AU34" s="30"/>
+      <c r="AV34" s="30"/>
+      <c r="AW34" s="30"/>
+      <c r="AX34" s="30"/>
+      <c r="AY34" s="30"/>
+      <c r="AZ34" s="30"/>
+      <c r="BA34" s="30"/>
+      <c r="BB34" s="30"/>
+      <c r="BC34" s="30"/>
+      <c r="BD34" s="30"/>
+      <c r="BE34" s="30"/>
+      <c r="BF34" s="31"/>
+      <c r="BH34" s="38" t="s">
+        <v>984</v>
+      </c>
+      <c r="BI34" s="23"/>
+      <c r="BJ34" s="23"/>
+      <c r="BK34" s="23"/>
+      <c r="BL34" s="23"/>
+      <c r="BM34" s="23"/>
+      <c r="BN34" s="23"/>
+      <c r="BO34" s="23"/>
+      <c r="BP34" s="23"/>
+      <c r="BQ34" s="23"/>
+      <c r="BR34" s="23"/>
+      <c r="BS34" s="23"/>
+      <c r="BT34" s="23"/>
+      <c r="BU34" s="23"/>
+      <c r="BV34" s="23"/>
+      <c r="BW34" s="23"/>
+      <c r="BX34" s="23"/>
+      <c r="BY34" s="23"/>
+      <c r="BZ34" s="23"/>
+      <c r="CA34" s="23"/>
+      <c r="CB34" s="23"/>
+      <c r="CC34" s="24"/>
+    </row>
+    <row r="35" spans="2:81" ht="15">
+      <c r="BH35" s="27" t="s">
+        <v>845</v>
+      </c>
+      <c r="BI35" s="23"/>
+      <c r="BJ35" s="23"/>
+      <c r="BK35" s="23"/>
+      <c r="BL35" s="23"/>
+      <c r="BM35" s="23"/>
+      <c r="BN35" s="23"/>
+      <c r="BO35" s="23"/>
+      <c r="BP35" s="23"/>
+      <c r="BQ35" s="23"/>
+      <c r="BR35" s="23"/>
+      <c r="BS35" s="23"/>
+      <c r="BT35" s="23"/>
+      <c r="BU35" s="23"/>
+      <c r="BV35" s="23"/>
+      <c r="BW35" s="23"/>
+      <c r="BX35" s="23"/>
+      <c r="BY35" s="23"/>
+      <c r="BZ35" s="23"/>
+      <c r="CA35" s="23"/>
+      <c r="CB35" s="23"/>
+      <c r="CC35" s="24"/>
+    </row>
+    <row r="36" spans="2:81" ht="15">
+      <c r="B36" s="46" t="s">
+        <v>776</v>
+      </c>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="BH36" s="28" t="s">
+        <v>846</v>
+      </c>
+      <c r="BI36" s="23"/>
+      <c r="BJ36" s="23"/>
+      <c r="BK36" s="23"/>
+      <c r="BL36" s="23"/>
+      <c r="BM36" s="23"/>
+      <c r="BN36" s="23"/>
+      <c r="BO36" s="23"/>
+      <c r="BP36" s="23"/>
+      <c r="BQ36" s="23"/>
+      <c r="BR36" s="23"/>
+      <c r="BS36" s="23"/>
+      <c r="BT36" s="23"/>
+      <c r="BU36" s="23"/>
+      <c r="BV36" s="23"/>
+      <c r="BW36" s="23"/>
+      <c r="BX36" s="23"/>
+      <c r="BY36" s="23"/>
+      <c r="BZ36" s="23"/>
+      <c r="CA36" s="23"/>
+      <c r="CB36" s="23"/>
+      <c r="CC36" s="24"/>
+    </row>
+    <row r="37" spans="2:81" ht="15">
+      <c r="C37" s="10" t="s">
+        <v>862</v>
+      </c>
+      <c r="BH37" s="27" t="s">
+        <v>847</v>
+      </c>
+      <c r="BI37" s="23"/>
+      <c r="BJ37" s="23"/>
+      <c r="BK37" s="23"/>
+      <c r="BL37" s="23"/>
+      <c r="BM37" s="23"/>
+      <c r="BN37" s="23"/>
+      <c r="BO37" s="23"/>
+      <c r="BP37" s="23"/>
+      <c r="BQ37" s="23"/>
+      <c r="BR37" s="23"/>
+      <c r="BS37" s="23"/>
+      <c r="BT37" s="23"/>
+      <c r="BU37" s="23"/>
+      <c r="BV37" s="23"/>
+      <c r="BW37" s="23"/>
+      <c r="BX37" s="23"/>
+      <c r="BY37" s="23"/>
+      <c r="BZ37" s="23"/>
+      <c r="CA37" s="23"/>
+      <c r="CB37" s="23"/>
+      <c r="CC37" s="24"/>
+    </row>
+    <row r="38" spans="2:81" ht="15">
+      <c r="C38" s="12" t="s">
+        <v>985</v>
+      </c>
+      <c r="BH38" s="41" t="s">
+        <v>848</v>
+      </c>
+      <c r="BI38" s="40"/>
+      <c r="BJ38" s="40"/>
+      <c r="BK38" s="40"/>
+      <c r="BL38" s="40"/>
+      <c r="BM38" s="40"/>
+      <c r="BN38" s="40"/>
+      <c r="BO38" s="40"/>
+      <c r="BP38" s="40"/>
+      <c r="BQ38" s="40"/>
+      <c r="BR38" s="40"/>
+      <c r="BS38" s="40"/>
+      <c r="BT38" s="40"/>
+      <c r="BU38" s="40"/>
+      <c r="BV38" s="23"/>
+      <c r="BW38" s="23"/>
+      <c r="BX38" s="23"/>
+      <c r="BY38" s="23"/>
+      <c r="BZ38" s="23"/>
+      <c r="CA38" s="23"/>
+      <c r="CB38" s="23"/>
+      <c r="CC38" s="24"/>
+    </row>
+    <row r="39" spans="2:81" ht="15" thickBot="1">
+      <c r="C39" s="12" t="s">
+        <v>986</v>
+      </c>
+      <c r="BH39" s="39" t="s">
+        <v>849</v>
+      </c>
+      <c r="BI39" s="40"/>
+      <c r="BJ39" s="40"/>
+      <c r="BK39" s="40"/>
+      <c r="BL39" s="40"/>
+      <c r="BM39" s="40"/>
+      <c r="BN39" s="40"/>
+      <c r="BO39" s="40"/>
+      <c r="BP39" s="40"/>
+      <c r="BQ39" s="40"/>
+      <c r="BR39" s="40"/>
+      <c r="BS39" s="40"/>
+      <c r="BT39" s="40"/>
+      <c r="BU39" s="40"/>
+      <c r="BV39" s="23"/>
+      <c r="BW39" s="23"/>
+      <c r="BX39" s="23"/>
+      <c r="BY39" s="23"/>
+      <c r="BZ39" s="23"/>
+      <c r="CA39" s="23"/>
+      <c r="CB39" s="23"/>
+      <c r="CC39" s="24"/>
+    </row>
+    <row r="40" spans="2:81" ht="15">
+      <c r="C40" s="10" t="s">
+        <v>777</v>
+      </c>
+      <c r="AC40" s="18" t="s">
+        <v>862</v>
+      </c>
+      <c r="AD40" s="19"/>
+      <c r="AE40" s="19"/>
+      <c r="AF40" s="19"/>
+      <c r="AG40" s="19"/>
+      <c r="AH40" s="19"/>
+      <c r="AI40" s="19"/>
+      <c r="AJ40" s="19"/>
+      <c r="AK40" s="19"/>
+      <c r="AL40" s="19"/>
+      <c r="AM40" s="19"/>
+      <c r="AN40" s="19"/>
+      <c r="AO40" s="19"/>
+      <c r="AP40" s="19"/>
+      <c r="AQ40" s="19"/>
+      <c r="AR40" s="19"/>
+      <c r="AS40" s="19"/>
+      <c r="AT40" s="19"/>
+      <c r="AU40" s="19"/>
+      <c r="AV40" s="19"/>
+      <c r="AW40" s="20"/>
+      <c r="BH40" s="28" t="s">
+        <v>850</v>
+      </c>
+      <c r="BI40" s="23"/>
+      <c r="BJ40" s="23"/>
+      <c r="BK40" s="23"/>
+      <c r="BL40" s="23"/>
+      <c r="BM40" s="23"/>
+      <c r="BN40" s="23"/>
+      <c r="BO40" s="23"/>
+      <c r="BP40" s="23"/>
+      <c r="BQ40" s="23"/>
+      <c r="BR40" s="23"/>
+      <c r="BS40" s="23"/>
+      <c r="BT40" s="23"/>
+      <c r="BU40" s="23"/>
+      <c r="BV40" s="23"/>
+      <c r="BW40" s="23"/>
+      <c r="BX40" s="23"/>
+      <c r="BY40" s="23"/>
+      <c r="BZ40" s="23"/>
+      <c r="CA40" s="23"/>
+      <c r="CB40" s="23"/>
+      <c r="CC40" s="24"/>
+    </row>
+    <row r="41" spans="2:81" ht="15">
+      <c r="C41" s="13" t="s">
+        <v>987</v>
+      </c>
+      <c r="AC41" s="27" t="s">
+        <v>876</v>
+      </c>
+      <c r="AD41" s="23"/>
+      <c r="AE41" s="23"/>
+      <c r="AF41" s="23"/>
+      <c r="AG41" s="23"/>
+      <c r="AH41" s="23"/>
+      <c r="AI41" s="23"/>
+      <c r="AJ41" s="23"/>
+      <c r="AK41" s="23"/>
+      <c r="AL41" s="23"/>
+      <c r="AM41" s="23"/>
+      <c r="AN41" s="23"/>
+      <c r="AO41" s="23"/>
+      <c r="AP41" s="23"/>
+      <c r="AQ41" s="23"/>
+      <c r="AR41" s="23"/>
+      <c r="AS41" s="23"/>
+      <c r="AT41" s="23"/>
+      <c r="AU41" s="23"/>
+      <c r="AV41" s="23"/>
+      <c r="AW41" s="24"/>
+      <c r="BH41" s="28" t="s">
+        <v>851</v>
+      </c>
+      <c r="BI41" s="23"/>
+      <c r="BJ41" s="23"/>
+      <c r="BK41" s="23"/>
+      <c r="BL41" s="23"/>
+      <c r="BM41" s="23"/>
+      <c r="BN41" s="23"/>
+      <c r="BO41" s="23"/>
+      <c r="BP41" s="23"/>
+      <c r="BQ41" s="23"/>
+      <c r="BR41" s="23"/>
+      <c r="BS41" s="23"/>
+      <c r="BT41" s="23"/>
+      <c r="BU41" s="23"/>
+      <c r="BV41" s="23"/>
+      <c r="BW41" s="23"/>
+      <c r="BX41" s="23"/>
+      <c r="BY41" s="23"/>
+      <c r="BZ41" s="23"/>
+      <c r="CA41" s="23"/>
+      <c r="CB41" s="23"/>
+      <c r="CC41" s="24"/>
+    </row>
+    <row r="42" spans="2:81" ht="15">
+      <c r="D42" s="15" t="s">
+        <v>778</v>
+      </c>
+      <c r="AC42" s="21"/>
+      <c r="AD42" s="51" t="s">
+        <v>988</v>
+      </c>
+      <c r="AE42" s="23"/>
+      <c r="AF42" s="23"/>
+      <c r="AG42" s="23"/>
+      <c r="AH42" s="23"/>
+      <c r="AI42" s="23"/>
+      <c r="AJ42" s="23"/>
+      <c r="AK42" s="23"/>
+      <c r="AL42" s="23"/>
+      <c r="AM42" s="23"/>
+      <c r="AN42" s="23"/>
+      <c r="AO42" s="23"/>
+      <c r="AP42" s="23"/>
+      <c r="AQ42" s="23"/>
+      <c r="AR42" s="23"/>
+      <c r="AS42" s="23"/>
+      <c r="AT42" s="23"/>
+      <c r="AU42" s="23"/>
+      <c r="AV42" s="23"/>
+      <c r="AW42" s="24"/>
+      <c r="BH42" s="28" t="s">
+        <v>852</v>
+      </c>
+      <c r="BI42" s="23"/>
+      <c r="BJ42" s="23"/>
+      <c r="BK42" s="23"/>
+      <c r="BL42" s="23"/>
+      <c r="BM42" s="23"/>
+      <c r="BN42" s="23"/>
+      <c r="BO42" s="23"/>
+      <c r="BP42" s="23"/>
+      <c r="BQ42" s="23"/>
+      <c r="BR42" s="23"/>
+      <c r="BS42" s="23"/>
+      <c r="BT42" s="23"/>
+      <c r="BU42" s="23"/>
+      <c r="BV42" s="23"/>
+      <c r="BW42" s="23"/>
+      <c r="BX42" s="23"/>
+      <c r="BY42" s="23"/>
+      <c r="BZ42" s="23"/>
+      <c r="CA42" s="23"/>
+      <c r="CB42" s="23"/>
+      <c r="CC42" s="24"/>
+    </row>
+    <row r="43" spans="2:81">
+      <c r="D43" s="13" t="s">
+        <v>779</v>
+      </c>
+      <c r="AC43" s="34"/>
+      <c r="AD43" s="23"/>
+      <c r="AE43" s="52" t="s">
+        <v>877</v>
+      </c>
+      <c r="AF43" s="23"/>
+      <c r="AG43" s="23"/>
+      <c r="AH43" s="23"/>
+      <c r="AI43" s="23"/>
+      <c r="AJ43" s="23"/>
+      <c r="AK43" s="23"/>
+      <c r="AL43" s="23"/>
+      <c r="AM43" s="23"/>
+      <c r="AN43" s="23"/>
+      <c r="AO43" s="23"/>
+      <c r="AP43" s="23"/>
+      <c r="AQ43" s="23"/>
+      <c r="AR43" s="23"/>
+      <c r="AS43" s="23"/>
+      <c r="AT43" s="23"/>
+      <c r="AU43" s="23"/>
+      <c r="AV43" s="23"/>
+      <c r="AW43" s="24"/>
+      <c r="BH43" s="28" t="s">
+        <v>853</v>
+      </c>
+      <c r="BI43" s="23"/>
+      <c r="BJ43" s="23"/>
+      <c r="BK43" s="23"/>
+      <c r="BL43" s="23"/>
+      <c r="BM43" s="23"/>
+      <c r="BN43" s="23"/>
+      <c r="BO43" s="23"/>
+      <c r="BP43" s="23"/>
+      <c r="BQ43" s="23"/>
+      <c r="BR43" s="23"/>
+      <c r="BS43" s="23"/>
+      <c r="BT43" s="23"/>
+      <c r="BU43" s="23"/>
+      <c r="BV43" s="23"/>
+      <c r="BW43" s="23"/>
+      <c r="BX43" s="23"/>
+      <c r="BY43" s="23"/>
+      <c r="BZ43" s="23"/>
+      <c r="CA43" s="23"/>
+      <c r="CB43" s="23"/>
+      <c r="CC43" s="24"/>
+    </row>
+    <row r="44" spans="2:81" ht="15">
+      <c r="C44" s="10" t="s">
+        <v>780</v>
+      </c>
+      <c r="AC44" s="21"/>
+      <c r="AD44" s="53" t="s">
+        <v>878</v>
+      </c>
+      <c r="AE44" s="23"/>
+      <c r="AF44" s="23"/>
+      <c r="AG44" s="23"/>
+      <c r="AH44" s="23"/>
+      <c r="AI44" s="23"/>
+      <c r="AJ44" s="23"/>
+      <c r="AK44" s="23"/>
+      <c r="AL44" s="23"/>
+      <c r="AM44" s="23"/>
+      <c r="AN44" s="23"/>
+      <c r="AO44" s="23"/>
+      <c r="AP44" s="23"/>
+      <c r="AQ44" s="23"/>
+      <c r="AR44" s="23"/>
+      <c r="AS44" s="23"/>
+      <c r="AT44" s="23"/>
+      <c r="AU44" s="23"/>
+      <c r="AV44" s="23"/>
+      <c r="AW44" s="24"/>
+      <c r="BH44" s="28" t="s">
+        <v>854</v>
+      </c>
+      <c r="BI44" s="23"/>
+      <c r="BJ44" s="23"/>
+      <c r="BK44" s="23"/>
+      <c r="BL44" s="23"/>
+      <c r="BM44" s="23"/>
+      <c r="BN44" s="23"/>
+      <c r="BO44" s="23"/>
+      <c r="BP44" s="23"/>
+      <c r="BQ44" s="23"/>
+      <c r="BR44" s="23"/>
+      <c r="BS44" s="23"/>
+      <c r="BT44" s="23"/>
+      <c r="BU44" s="23"/>
+      <c r="BV44" s="23"/>
+      <c r="BW44" s="23"/>
+      <c r="BX44" s="23"/>
+      <c r="BY44" s="23"/>
+      <c r="BZ44" s="23"/>
+      <c r="CA44" s="23"/>
+      <c r="CB44" s="23"/>
+      <c r="CC44" s="24"/>
+    </row>
+    <row r="45" spans="2:81" ht="15" thickBot="1">
+      <c r="C45" s="12" t="s">
+        <v>989</v>
+      </c>
+      <c r="AC45" s="34"/>
+      <c r="AD45" s="23"/>
+      <c r="AE45" s="52" t="s">
+        <v>879</v>
+      </c>
+      <c r="AF45" s="23"/>
+      <c r="AG45" s="23"/>
+      <c r="AH45" s="23"/>
+      <c r="AI45" s="23"/>
+      <c r="AJ45" s="23"/>
+      <c r="AK45" s="23"/>
+      <c r="AL45" s="23"/>
+      <c r="AM45" s="23"/>
+      <c r="AN45" s="23"/>
+      <c r="AO45" s="23"/>
+      <c r="AP45" s="23"/>
+      <c r="AQ45" s="23"/>
+      <c r="AR45" s="23"/>
+      <c r="AS45" s="23"/>
+      <c r="AT45" s="23"/>
+      <c r="AU45" s="23"/>
+      <c r="AV45" s="23"/>
+      <c r="AW45" s="24"/>
+      <c r="BH45" s="29" t="s">
+        <v>990</v>
+      </c>
+      <c r="BI45" s="30"/>
+      <c r="BJ45" s="30"/>
+      <c r="BK45" s="30"/>
+      <c r="BL45" s="30"/>
+      <c r="BM45" s="30"/>
+      <c r="BN45" s="30"/>
+      <c r="BO45" s="30"/>
+      <c r="BP45" s="30"/>
+      <c r="BQ45" s="30"/>
+      <c r="BR45" s="30"/>
+      <c r="BS45" s="30"/>
+      <c r="BT45" s="30"/>
+      <c r="BU45" s="30"/>
+      <c r="BV45" s="30"/>
+      <c r="BW45" s="30"/>
+      <c r="BX45" s="30"/>
+      <c r="BY45" s="30"/>
+      <c r="BZ45" s="30"/>
+      <c r="CA45" s="30"/>
+      <c r="CB45" s="30"/>
+      <c r="CC45" s="31"/>
+    </row>
+    <row r="46" spans="2:81" ht="15.75" thickBot="1">
+      <c r="C46" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="AC46" s="21"/>
+      <c r="AD46" s="51" t="s">
+        <v>996</v>
+      </c>
+      <c r="AE46" s="23"/>
+      <c r="AF46" s="23"/>
+      <c r="AG46" s="23"/>
+      <c r="AH46" s="23"/>
+      <c r="AI46" s="23"/>
+      <c r="AJ46" s="23"/>
+      <c r="AK46" s="23"/>
+      <c r="AL46" s="23"/>
+      <c r="AM46" s="23"/>
+      <c r="AN46" s="23"/>
+      <c r="AO46" s="23"/>
+      <c r="AP46" s="23"/>
+      <c r="AQ46" s="23"/>
+      <c r="AR46" s="23"/>
+      <c r="AS46" s="23"/>
+      <c r="AT46" s="23"/>
+      <c r="AU46" s="23"/>
+      <c r="AV46" s="23"/>
+      <c r="AW46" s="24"/>
+    </row>
+    <row r="47" spans="2:81" ht="15">
+      <c r="C47" s="12" t="s">
+        <v>992</v>
+      </c>
+      <c r="AC47" s="34"/>
+      <c r="AD47" s="23"/>
+      <c r="AE47" s="52" t="s">
+        <v>880</v>
+      </c>
+      <c r="AF47" s="23"/>
+      <c r="AG47" s="23"/>
+      <c r="AH47" s="23"/>
+      <c r="AI47" s="23"/>
+      <c r="AJ47" s="23"/>
+      <c r="AK47" s="23"/>
+      <c r="AL47" s="23"/>
+      <c r="AM47" s="23"/>
+      <c r="AN47" s="23"/>
+      <c r="AO47" s="23"/>
+      <c r="AP47" s="23"/>
+      <c r="AQ47" s="23"/>
+      <c r="AR47" s="23"/>
+      <c r="AS47" s="23"/>
+      <c r="AT47" s="23"/>
+      <c r="AU47" s="23"/>
+      <c r="AV47" s="23"/>
+      <c r="AW47" s="24"/>
+      <c r="AZ47" s="18" t="s">
+        <v>885</v>
+      </c>
+      <c r="BA47" s="19"/>
+      <c r="BB47" s="19"/>
+      <c r="BC47" s="19"/>
+      <c r="BD47" s="19"/>
+      <c r="BE47" s="19"/>
+      <c r="BF47" s="19"/>
+      <c r="BG47" s="19"/>
+      <c r="BH47" s="19"/>
+      <c r="BI47" s="19"/>
+      <c r="BJ47" s="19"/>
+      <c r="BK47" s="19"/>
+      <c r="BL47" s="19"/>
+      <c r="BM47" s="19"/>
+      <c r="BN47" s="19"/>
+      <c r="BO47" s="19"/>
+      <c r="BP47" s="19"/>
+      <c r="BQ47" s="19"/>
+      <c r="BR47" s="19"/>
+      <c r="BS47" s="19"/>
+      <c r="BT47" s="19"/>
+      <c r="BU47" s="19"/>
+      <c r="BV47" s="19"/>
+      <c r="BW47" s="19"/>
+      <c r="BX47" s="19"/>
+      <c r="BY47" s="19"/>
+      <c r="BZ47" s="19"/>
+      <c r="CA47" s="20"/>
+    </row>
+    <row r="48" spans="2:81" ht="15">
+      <c r="AC48" s="21"/>
+      <c r="AD48" s="54" t="s">
+        <v>997</v>
+      </c>
+      <c r="AE48" s="23"/>
+      <c r="AF48" s="23"/>
+      <c r="AG48" s="23"/>
+      <c r="AH48" s="23"/>
+      <c r="AI48" s="23"/>
+      <c r="AJ48" s="23"/>
+      <c r="AK48" s="23"/>
+      <c r="AL48" s="23"/>
+      <c r="AM48" s="23"/>
+      <c r="AN48" s="23"/>
+      <c r="AO48" s="23"/>
+      <c r="AP48" s="23"/>
+      <c r="AQ48" s="23"/>
+      <c r="AR48" s="23"/>
+      <c r="AS48" s="23"/>
+      <c r="AT48" s="23"/>
+      <c r="AU48" s="23"/>
+      <c r="AV48" s="23"/>
+      <c r="AW48" s="24"/>
+      <c r="AZ48" s="58" t="s">
+        <v>1007</v>
+      </c>
+      <c r="BA48" s="23"/>
+      <c r="BB48" s="23"/>
+      <c r="BC48" s="23"/>
+      <c r="BD48" s="23"/>
+      <c r="BE48" s="23"/>
+      <c r="BF48" s="23"/>
+      <c r="BG48" s="23"/>
+      <c r="BH48" s="23"/>
+      <c r="BI48" s="23"/>
+      <c r="BJ48" s="23"/>
+      <c r="BK48" s="23"/>
+      <c r="BL48" s="23"/>
+      <c r="BM48" s="23"/>
+      <c r="BN48" s="23"/>
+      <c r="BO48" s="23"/>
+      <c r="BP48" s="23"/>
+      <c r="BQ48" s="23"/>
+      <c r="BR48" s="23"/>
+      <c r="BS48" s="23"/>
+      <c r="BT48" s="23"/>
+      <c r="BU48" s="23"/>
+      <c r="BV48" s="23"/>
+      <c r="BW48" s="23"/>
+      <c r="BX48" s="23"/>
+      <c r="BY48" s="23"/>
+      <c r="BZ48" s="23"/>
+      <c r="CA48" s="24"/>
+    </row>
+    <row r="49" spans="2:79" ht="15">
+      <c r="C49" s="10" t="s">
+        <v>781</v>
+      </c>
+      <c r="AC49" s="34"/>
+      <c r="AD49" s="23"/>
+      <c r="AE49" s="52" t="s">
+        <v>881</v>
+      </c>
+      <c r="AF49" s="23"/>
+      <c r="AG49" s="23"/>
+      <c r="AH49" s="23"/>
+      <c r="AI49" s="23"/>
+      <c r="AJ49" s="23"/>
+      <c r="AK49" s="23"/>
+      <c r="AL49" s="23"/>
+      <c r="AM49" s="23"/>
+      <c r="AN49" s="23"/>
+      <c r="AO49" s="23"/>
+      <c r="AP49" s="23"/>
+      <c r="AQ49" s="23"/>
+      <c r="AR49" s="23"/>
+      <c r="AS49" s="23"/>
+      <c r="AT49" s="23"/>
+      <c r="AU49" s="23"/>
+      <c r="AV49" s="23"/>
+      <c r="AW49" s="24"/>
+      <c r="AZ49" s="34"/>
+      <c r="BA49" s="52" t="s">
+        <v>886</v>
+      </c>
+      <c r="BB49" s="23"/>
+      <c r="BC49" s="23"/>
+      <c r="BD49" s="23"/>
+      <c r="BE49" s="23"/>
+      <c r="BF49" s="23"/>
+      <c r="BG49" s="23"/>
+      <c r="BH49" s="23"/>
+      <c r="BI49" s="23"/>
+      <c r="BJ49" s="23"/>
+      <c r="BK49" s="23"/>
+      <c r="BL49" s="23"/>
+      <c r="BM49" s="23"/>
+      <c r="BN49" s="23"/>
+      <c r="BO49" s="23"/>
+      <c r="BP49" s="23"/>
+      <c r="BQ49" s="23"/>
+      <c r="BR49" s="23"/>
+      <c r="BS49" s="23"/>
+      <c r="BT49" s="23"/>
+      <c r="BU49" s="23"/>
+      <c r="BV49" s="23"/>
+      <c r="BW49" s="23"/>
+      <c r="BX49" s="23"/>
+      <c r="BY49" s="23"/>
+      <c r="BZ49" s="23"/>
+      <c r="CA49" s="24"/>
+    </row>
+    <row r="50" spans="2:79" ht="15">
+      <c r="C50" s="12" t="s">
+        <v>993</v>
+      </c>
+      <c r="AC50" s="21"/>
+      <c r="AD50" s="22" t="s">
+        <v>1006</v>
+      </c>
+      <c r="AE50" s="23"/>
+      <c r="AF50" s="23"/>
+      <c r="AG50" s="23"/>
+      <c r="AH50" s="23"/>
+      <c r="AI50" s="23"/>
+      <c r="AJ50" s="23"/>
+      <c r="AK50" s="23"/>
+      <c r="AL50" s="23"/>
+      <c r="AM50" s="23"/>
+      <c r="AN50" s="23"/>
+      <c r="AO50" s="23"/>
+      <c r="AP50" s="23"/>
+      <c r="AQ50" s="23"/>
+      <c r="AR50" s="23"/>
+      <c r="AS50" s="23"/>
+      <c r="AT50" s="23"/>
+      <c r="AU50" s="23"/>
+      <c r="AV50" s="23"/>
+      <c r="AW50" s="24"/>
+      <c r="AZ50" s="21"/>
+      <c r="BA50" s="52" t="s">
+        <v>887</v>
+      </c>
+      <c r="BB50" s="23"/>
+      <c r="BC50" s="23"/>
+      <c r="BD50" s="23"/>
+      <c r="BE50" s="23"/>
+      <c r="BF50" s="23"/>
+      <c r="BG50" s="23"/>
+      <c r="BH50" s="23"/>
+      <c r="BI50" s="23"/>
+      <c r="BJ50" s="23"/>
+      <c r="BK50" s="23"/>
+      <c r="BL50" s="23"/>
+      <c r="BM50" s="23"/>
+      <c r="BN50" s="23"/>
+      <c r="BO50" s="23"/>
+      <c r="BP50" s="23"/>
+      <c r="BQ50" s="23"/>
+      <c r="BR50" s="23"/>
+      <c r="BS50" s="23"/>
+      <c r="BT50" s="23"/>
+      <c r="BU50" s="23"/>
+      <c r="BV50" s="23"/>
+      <c r="BW50" s="23"/>
+      <c r="BX50" s="23"/>
+      <c r="BY50" s="23"/>
+      <c r="BZ50" s="23"/>
+      <c r="CA50" s="24"/>
+    </row>
+    <row r="51" spans="2:79" ht="16.5" customHeight="1">
+      <c r="C51" s="12" t="s">
+        <v>994</v>
+      </c>
+      <c r="AC51" s="34"/>
+      <c r="AD51" s="55"/>
+      <c r="AE51" s="52" t="s">
+        <v>882</v>
+      </c>
+      <c r="AF51" s="23"/>
+      <c r="AG51" s="23"/>
+      <c r="AH51" s="23"/>
+      <c r="AI51" s="23"/>
+      <c r="AJ51" s="23"/>
+      <c r="AK51" s="23"/>
+      <c r="AL51" s="23"/>
+      <c r="AM51" s="23"/>
+      <c r="AN51" s="23"/>
+      <c r="AO51" s="23"/>
+      <c r="AP51" s="23"/>
+      <c r="AQ51" s="23"/>
+      <c r="AR51" s="23"/>
+      <c r="AS51" s="23"/>
+      <c r="AT51" s="23"/>
+      <c r="AU51" s="23"/>
+      <c r="AV51" s="23"/>
+      <c r="AW51" s="24"/>
+      <c r="AZ51" s="21"/>
+      <c r="BA51" s="52" t="s">
+        <v>888</v>
+      </c>
+      <c r="BB51" s="23"/>
+      <c r="BC51" s="23"/>
+      <c r="BD51" s="23"/>
+      <c r="BE51" s="23"/>
+      <c r="BF51" s="23"/>
+      <c r="BG51" s="23"/>
+      <c r="BH51" s="23"/>
+      <c r="BI51" s="23"/>
+      <c r="BJ51" s="23"/>
+      <c r="BK51" s="23"/>
+      <c r="BL51" s="23"/>
+      <c r="BM51" s="23"/>
+      <c r="BN51" s="23"/>
+      <c r="BO51" s="23"/>
+      <c r="BP51" s="23"/>
+      <c r="BQ51" s="23"/>
+      <c r="BR51" s="23"/>
+      <c r="BS51" s="23"/>
+      <c r="BT51" s="23"/>
+      <c r="BU51" s="23"/>
+      <c r="BV51" s="23"/>
+      <c r="BW51" s="23"/>
+      <c r="BX51" s="23"/>
+      <c r="BY51" s="23"/>
+      <c r="BZ51" s="23"/>
+      <c r="CA51" s="24"/>
+    </row>
+    <row r="52" spans="2:79" ht="14.25" customHeight="1">
+      <c r="C52" s="12" t="s">
+        <v>995</v>
+      </c>
+      <c r="AC52" s="21"/>
+      <c r="AD52" s="23"/>
+      <c r="AE52" s="52" t="s">
+        <v>883</v>
+      </c>
+      <c r="AF52" s="23"/>
+      <c r="AG52" s="23"/>
+      <c r="AH52" s="23"/>
+      <c r="AI52" s="23"/>
+      <c r="AJ52" s="23"/>
+      <c r="AK52" s="23"/>
+      <c r="AL52" s="23"/>
+      <c r="AM52" s="23"/>
+      <c r="AN52" s="23"/>
+      <c r="AO52" s="23"/>
+      <c r="AP52" s="23"/>
+      <c r="AQ52" s="23"/>
+      <c r="AR52" s="23"/>
+      <c r="AS52" s="23"/>
+      <c r="AT52" s="23"/>
+      <c r="AU52" s="23"/>
+      <c r="AV52" s="23"/>
+      <c r="AW52" s="24"/>
+      <c r="AZ52" s="59" t="s">
+        <v>889</v>
+      </c>
+      <c r="BA52" s="23"/>
+      <c r="BB52" s="23"/>
+      <c r="BC52" s="23"/>
+      <c r="BD52" s="23"/>
+      <c r="BE52" s="23"/>
+      <c r="BF52" s="23"/>
+      <c r="BG52" s="23"/>
+      <c r="BH52" s="23"/>
+      <c r="BI52" s="23"/>
+      <c r="BJ52" s="23"/>
+      <c r="BK52" s="23"/>
+      <c r="BL52" s="23"/>
+      <c r="BM52" s="23"/>
+      <c r="BN52" s="23"/>
+      <c r="BO52" s="23"/>
+      <c r="BP52" s="23"/>
+      <c r="BQ52" s="23"/>
+      <c r="BR52" s="23"/>
+      <c r="BS52" s="23"/>
+      <c r="BT52" s="23"/>
+      <c r="BU52" s="23"/>
+      <c r="BV52" s="23"/>
+      <c r="BW52" s="23"/>
+      <c r="BX52" s="23"/>
+      <c r="BY52" s="23"/>
+      <c r="BZ52" s="23"/>
+      <c r="CA52" s="24"/>
+    </row>
+    <row r="53" spans="2:79" ht="16.5" customHeight="1" thickBot="1">
+      <c r="AC53" s="56"/>
+      <c r="AD53" s="30"/>
+      <c r="AE53" s="57" t="s">
+        <v>884</v>
+      </c>
+      <c r="AF53" s="30"/>
+      <c r="AG53" s="30"/>
+      <c r="AH53" s="30"/>
+      <c r="AI53" s="30"/>
+      <c r="AJ53" s="30"/>
+      <c r="AK53" s="30"/>
+      <c r="AL53" s="30"/>
+      <c r="AM53" s="30"/>
+      <c r="AN53" s="30"/>
+      <c r="AO53" s="30"/>
+      <c r="AP53" s="30"/>
+      <c r="AQ53" s="30"/>
+      <c r="AR53" s="30"/>
+      <c r="AS53" s="30"/>
+      <c r="AT53" s="30"/>
+      <c r="AU53" s="30"/>
+      <c r="AV53" s="30"/>
+      <c r="AW53" s="31"/>
+      <c r="AZ53" s="34"/>
+      <c r="BA53" s="52" t="s">
+        <v>890</v>
+      </c>
+      <c r="BB53" s="23"/>
+      <c r="BC53" s="23"/>
+      <c r="BD53" s="23"/>
+      <c r="BE53" s="23"/>
+      <c r="BF53" s="23"/>
+      <c r="BG53" s="23"/>
+      <c r="BH53" s="23"/>
+      <c r="BI53" s="23"/>
+      <c r="BJ53" s="23"/>
+      <c r="BK53" s="23"/>
+      <c r="BL53" s="23"/>
+      <c r="BM53" s="23"/>
+      <c r="BN53" s="23"/>
+      <c r="BO53" s="23"/>
+      <c r="BP53" s="23"/>
+      <c r="BQ53" s="23"/>
+      <c r="BR53" s="23"/>
+      <c r="BS53" s="23"/>
+      <c r="BT53" s="23"/>
+      <c r="BU53" s="23"/>
+      <c r="BV53" s="23"/>
+      <c r="BW53" s="23"/>
+      <c r="BX53" s="23"/>
+      <c r="BY53" s="23"/>
+      <c r="BZ53" s="23"/>
+      <c r="CA53" s="24"/>
+    </row>
+    <row r="54" spans="2:79" ht="15">
+      <c r="C54" s="10" t="s">
+        <v>782</v>
+      </c>
+      <c r="AL54" s="13"/>
+      <c r="AZ54" s="21"/>
+      <c r="BA54" s="52" t="s">
+        <v>891</v>
+      </c>
+      <c r="BB54" s="23"/>
+      <c r="BC54" s="23"/>
+      <c r="BD54" s="23"/>
+      <c r="BE54" s="23"/>
+      <c r="BF54" s="23"/>
+      <c r="BG54" s="23"/>
+      <c r="BH54" s="23"/>
+      <c r="BI54" s="23"/>
+      <c r="BJ54" s="23"/>
+      <c r="BK54" s="23"/>
+      <c r="BL54" s="23"/>
+      <c r="BM54" s="23"/>
+      <c r="BN54" s="23"/>
+      <c r="BO54" s="23"/>
+      <c r="BP54" s="23"/>
+      <c r="BQ54" s="23"/>
+      <c r="BR54" s="23"/>
+      <c r="BS54" s="23"/>
+      <c r="BT54" s="23"/>
+      <c r="BU54" s="23"/>
+      <c r="BV54" s="23"/>
+      <c r="BW54" s="23"/>
+      <c r="BX54" s="23"/>
+      <c r="BY54" s="23"/>
+      <c r="BZ54" s="23"/>
+      <c r="CA54" s="24"/>
+    </row>
+    <row r="55" spans="2:79">
+      <c r="C55" s="13" t="s">
+        <v>783</v>
+      </c>
+      <c r="AZ55" s="21"/>
+      <c r="BA55" s="52" t="s">
+        <v>892</v>
+      </c>
+      <c r="BB55" s="23"/>
+      <c r="BC55" s="23"/>
+      <c r="BD55" s="23"/>
+      <c r="BE55" s="23"/>
+      <c r="BF55" s="23"/>
+      <c r="BG55" s="23"/>
+      <c r="BH55" s="23"/>
+      <c r="BI55" s="23"/>
+      <c r="BJ55" s="23"/>
+      <c r="BK55" s="23"/>
+      <c r="BL55" s="23"/>
+      <c r="BM55" s="23"/>
+      <c r="BN55" s="23"/>
+      <c r="BO55" s="23"/>
+      <c r="BP55" s="23"/>
+      <c r="BQ55" s="23"/>
+      <c r="BR55" s="23"/>
+      <c r="BS55" s="23"/>
+      <c r="BT55" s="23"/>
+      <c r="BU55" s="23"/>
+      <c r="BV55" s="23"/>
+      <c r="BW55" s="23"/>
+      <c r="BX55" s="23"/>
+      <c r="BY55" s="23"/>
+      <c r="BZ55" s="23"/>
+      <c r="CA55" s="24"/>
+    </row>
+    <row r="56" spans="2:79">
+      <c r="E56" s="15" t="s">
+        <v>784</v>
+      </c>
+      <c r="AZ56" s="58" t="s">
+        <v>1008</v>
+      </c>
+      <c r="BA56" s="23"/>
+      <c r="BB56" s="23"/>
+      <c r="BC56" s="23"/>
+      <c r="BD56" s="23"/>
+      <c r="BE56" s="23"/>
+      <c r="BF56" s="23"/>
+      <c r="BG56" s="23"/>
+      <c r="BH56" s="23"/>
+      <c r="BI56" s="23"/>
+      <c r="BJ56" s="23"/>
+      <c r="BK56" s="23"/>
+      <c r="BL56" s="23"/>
+      <c r="BM56" s="23"/>
+      <c r="BN56" s="23"/>
+      <c r="BO56" s="23"/>
+      <c r="BP56" s="23"/>
+      <c r="BQ56" s="23"/>
+      <c r="BR56" s="23"/>
+      <c r="BS56" s="23"/>
+      <c r="BT56" s="23"/>
+      <c r="BU56" s="23"/>
+      <c r="BV56" s="23"/>
+      <c r="BW56" s="23"/>
+      <c r="BX56" s="23"/>
+      <c r="BY56" s="23"/>
+      <c r="BZ56" s="23"/>
+      <c r="CA56" s="24"/>
+    </row>
+    <row r="57" spans="2:79">
+      <c r="C57" s="13" t="s">
+        <v>785</v>
+      </c>
+      <c r="AC57" s="13"/>
+      <c r="AZ57" s="34"/>
+      <c r="BA57" s="52" t="s">
+        <v>893</v>
+      </c>
+      <c r="BB57" s="23"/>
+      <c r="BC57" s="23"/>
+      <c r="BD57" s="23"/>
+      <c r="BE57" s="23"/>
+      <c r="BF57" s="23"/>
+      <c r="BG57" s="23"/>
+      <c r="BH57" s="23"/>
+      <c r="BI57" s="23"/>
+      <c r="BJ57" s="23"/>
+      <c r="BK57" s="23"/>
+      <c r="BL57" s="23"/>
+      <c r="BM57" s="23"/>
+      <c r="BN57" s="23"/>
+      <c r="BO57" s="23"/>
+      <c r="BP57" s="23"/>
+      <c r="BQ57" s="23"/>
+      <c r="BR57" s="23"/>
+      <c r="BS57" s="23"/>
+      <c r="BT57" s="23"/>
+      <c r="BU57" s="23"/>
+      <c r="BV57" s="23"/>
+      <c r="BW57" s="23"/>
+      <c r="BX57" s="23"/>
+      <c r="BY57" s="23"/>
+      <c r="BZ57" s="23"/>
+      <c r="CA57" s="24"/>
+    </row>
+    <row r="58" spans="2:79" ht="15" thickBot="1">
+      <c r="C58" s="13"/>
+      <c r="AZ58" s="56"/>
+      <c r="BA58" s="57" t="s">
+        <v>894</v>
+      </c>
+      <c r="BB58" s="30"/>
+      <c r="BC58" s="30"/>
+      <c r="BD58" s="30"/>
+      <c r="BE58" s="30"/>
+      <c r="BF58" s="30"/>
+      <c r="BG58" s="30"/>
+      <c r="BH58" s="30"/>
+      <c r="BI58" s="30"/>
+      <c r="BJ58" s="30"/>
+      <c r="BK58" s="30"/>
+      <c r="BL58" s="30"/>
+      <c r="BM58" s="30"/>
+      <c r="BN58" s="30"/>
+      <c r="BO58" s="30"/>
+      <c r="BP58" s="30"/>
+      <c r="BQ58" s="30"/>
+      <c r="BR58" s="30"/>
+      <c r="BS58" s="30"/>
+      <c r="BT58" s="30"/>
+      <c r="BU58" s="30"/>
+      <c r="BV58" s="30"/>
+      <c r="BW58" s="30"/>
+      <c r="BX58" s="30"/>
+      <c r="BY58" s="30"/>
+      <c r="BZ58" s="30"/>
+      <c r="CA58" s="31"/>
+    </row>
+    <row r="59" spans="2:79" ht="15.75" thickBot="1">
+      <c r="B59" s="46" t="s">
+        <v>786</v>
+      </c>
+      <c r="C59" s="47"/>
+      <c r="D59" s="47"/>
+      <c r="E59" s="47"/>
+      <c r="F59" s="47"/>
+      <c r="G59" s="47"/>
+      <c r="AC59" s="13"/>
+    </row>
+    <row r="60" spans="2:79" ht="15">
+      <c r="B60" s="10" t="s">
+        <v>865</v>
+      </c>
+      <c r="AN60" s="18" t="s">
+        <v>777</v>
+      </c>
+      <c r="AO60" s="19"/>
+      <c r="AP60" s="19"/>
+      <c r="AQ60" s="19"/>
+      <c r="AR60" s="19"/>
+      <c r="AS60" s="19"/>
+      <c r="AT60" s="19"/>
+      <c r="AU60" s="19"/>
+      <c r="AV60" s="19"/>
+      <c r="AW60" s="19"/>
+      <c r="AX60" s="19"/>
+      <c r="AY60" s="19"/>
+      <c r="AZ60" s="19"/>
+      <c r="BA60" s="19"/>
+      <c r="BB60" s="19"/>
+      <c r="BC60" s="19"/>
+      <c r="BD60" s="19"/>
+      <c r="BE60" s="19"/>
+      <c r="BF60" s="19"/>
+      <c r="BG60" s="19"/>
+      <c r="BH60" s="19"/>
+      <c r="BI60" s="19"/>
+      <c r="BJ60" s="20"/>
+    </row>
+    <row r="61" spans="2:79" ht="15">
+      <c r="B61" s="13" t="s">
+        <v>787</v>
+      </c>
+      <c r="AN61" s="27" t="s">
+        <v>876</v>
+      </c>
+      <c r="AO61" s="23"/>
+      <c r="AP61" s="23"/>
+      <c r="AQ61" s="23"/>
+      <c r="AR61" s="23"/>
+      <c r="AS61" s="23"/>
+      <c r="AT61" s="23"/>
+      <c r="AU61" s="23"/>
+      <c r="AV61" s="23"/>
+      <c r="AW61" s="23"/>
+      <c r="AX61" s="23"/>
+      <c r="AY61" s="23"/>
+      <c r="AZ61" s="23"/>
+      <c r="BA61" s="23"/>
+      <c r="BB61" s="23"/>
+      <c r="BC61" s="23"/>
+      <c r="BD61" s="23"/>
+      <c r="BE61" s="23"/>
+      <c r="BF61" s="23"/>
+      <c r="BG61" s="23"/>
+      <c r="BH61" s="23"/>
+      <c r="BI61" s="23"/>
+      <c r="BJ61" s="24"/>
+    </row>
+    <row r="62" spans="2:79" ht="15">
+      <c r="B62" s="13" t="s">
+        <v>788</v>
+      </c>
+      <c r="AN62" s="60" t="s">
+        <v>895</v>
+      </c>
+      <c r="AO62" s="23"/>
+      <c r="AP62" s="23"/>
+      <c r="AQ62" s="23"/>
+      <c r="AR62" s="23"/>
+      <c r="AS62" s="23"/>
+      <c r="AT62" s="23"/>
+      <c r="AU62" s="23"/>
+      <c r="AV62" s="23"/>
+      <c r="AW62" s="23"/>
+      <c r="AX62" s="23"/>
+      <c r="AY62" s="23"/>
+      <c r="AZ62" s="23"/>
+      <c r="BA62" s="23"/>
+      <c r="BB62" s="23"/>
+      <c r="BC62" s="23"/>
+      <c r="BD62" s="23"/>
+      <c r="BE62" s="23"/>
+      <c r="BF62" s="23"/>
+      <c r="BG62" s="23"/>
+      <c r="BH62" s="23"/>
+      <c r="BI62" s="23"/>
+      <c r="BJ62" s="24"/>
+    </row>
+    <row r="63" spans="2:79" ht="20.25" customHeight="1">
+      <c r="B63" s="10" t="s">
+        <v>867</v>
+      </c>
+      <c r="AN63" s="34"/>
+      <c r="AO63" s="52" t="s">
+        <v>896</v>
+      </c>
+      <c r="AP63" s="23"/>
+      <c r="AQ63" s="23"/>
+      <c r="AR63" s="23"/>
+      <c r="AS63" s="23"/>
+      <c r="AT63" s="23"/>
+      <c r="AU63" s="23"/>
+      <c r="AV63" s="23"/>
+      <c r="AW63" s="23"/>
+      <c r="AX63" s="23"/>
+      <c r="AY63" s="23"/>
+      <c r="AZ63" s="23"/>
+      <c r="BA63" s="23"/>
+      <c r="BB63" s="23"/>
+      <c r="BC63" s="23"/>
+      <c r="BD63" s="23"/>
+      <c r="BE63" s="23"/>
+      <c r="BF63" s="23"/>
+      <c r="BG63" s="23"/>
+      <c r="BH63" s="23"/>
+      <c r="BI63" s="23"/>
+      <c r="BJ63" s="24"/>
+    </row>
+    <row r="64" spans="2:79" ht="21.75" customHeight="1">
+      <c r="B64" s="13" t="s">
+        <v>789</v>
+      </c>
+      <c r="AN64" s="60" t="s">
+        <v>998</v>
+      </c>
+      <c r="AO64" s="23"/>
+      <c r="AP64" s="23"/>
+      <c r="AQ64" s="23"/>
+      <c r="AR64" s="23"/>
+      <c r="AS64" s="23"/>
+      <c r="AT64" s="23"/>
+      <c r="AU64" s="23"/>
+      <c r="AV64" s="23"/>
+      <c r="AW64" s="61"/>
+      <c r="AX64" s="23"/>
+      <c r="AY64" s="23"/>
+      <c r="AZ64" s="23"/>
+      <c r="BA64" s="23"/>
+      <c r="BB64" s="23"/>
+      <c r="BC64" s="23"/>
+      <c r="BD64" s="23"/>
+      <c r="BE64" s="23"/>
+      <c r="BF64" s="23"/>
+      <c r="BG64" s="23"/>
+      <c r="BH64" s="23"/>
+      <c r="BI64" s="23"/>
+      <c r="BJ64" s="24"/>
+    </row>
+    <row r="65" spans="2:62">
+      <c r="C65" s="15" t="s">
+        <v>790</v>
+      </c>
+      <c r="AN65" s="34"/>
+      <c r="AO65" s="52" t="s">
+        <v>897</v>
+      </c>
+      <c r="AP65" s="23"/>
+      <c r="AQ65" s="23"/>
+      <c r="AR65" s="23"/>
+      <c r="AS65" s="23"/>
+      <c r="AT65" s="23"/>
+      <c r="AU65" s="23"/>
+      <c r="AV65" s="23"/>
+      <c r="AW65" s="23"/>
+      <c r="AX65" s="23"/>
+      <c r="AY65" s="23"/>
+      <c r="AZ65" s="23"/>
+      <c r="BA65" s="23"/>
+      <c r="BB65" s="23"/>
+      <c r="BC65" s="23"/>
+      <c r="BD65" s="23"/>
+      <c r="BE65" s="23"/>
+      <c r="BF65" s="23"/>
+      <c r="BG65" s="23"/>
+      <c r="BH65" s="23"/>
+      <c r="BI65" s="23"/>
+      <c r="BJ65" s="24"/>
+    </row>
+    <row r="66" spans="2:62" ht="15">
+      <c r="C66" s="15"/>
+      <c r="AN66" s="60" t="s">
+        <v>999</v>
+      </c>
+      <c r="AO66" s="23"/>
+      <c r="AP66" s="23"/>
+      <c r="AQ66" s="23"/>
+      <c r="AR66" s="23"/>
+      <c r="AS66" s="23"/>
+      <c r="AT66" s="23"/>
+      <c r="AU66" s="23"/>
+      <c r="AV66" s="23"/>
+      <c r="AW66" s="62"/>
+      <c r="AX66" s="62"/>
+      <c r="AY66" s="62"/>
+      <c r="AZ66" s="23"/>
+      <c r="BA66" s="23"/>
+      <c r="BB66" s="23"/>
+      <c r="BC66" s="23"/>
+      <c r="BD66" s="23"/>
+      <c r="BE66" s="23"/>
+      <c r="BF66" s="23"/>
+      <c r="BG66" s="23"/>
+      <c r="BH66" s="23"/>
+      <c r="BI66" s="23"/>
+      <c r="BJ66" s="24"/>
+    </row>
+    <row r="67" spans="2:62" ht="15">
+      <c r="B67" s="10" t="s">
+        <v>868</v>
+      </c>
+      <c r="AN67" s="34"/>
+      <c r="AO67" s="52" t="s">
+        <v>898</v>
+      </c>
+      <c r="AP67" s="23"/>
+      <c r="AQ67" s="23"/>
+      <c r="AR67" s="23"/>
+      <c r="AS67" s="23"/>
+      <c r="AT67" s="23"/>
+      <c r="AU67" s="23"/>
+      <c r="AV67" s="23"/>
+      <c r="AW67" s="62"/>
+      <c r="AX67" s="62"/>
+      <c r="AY67" s="62"/>
+      <c r="AZ67" s="23"/>
+      <c r="BA67" s="23"/>
+      <c r="BB67" s="23"/>
+      <c r="BC67" s="23"/>
+      <c r="BD67" s="23"/>
+      <c r="BE67" s="23"/>
+      <c r="BF67" s="23"/>
+      <c r="BG67" s="23"/>
+      <c r="BH67" s="23"/>
+      <c r="BI67" s="23"/>
+      <c r="BJ67" s="24"/>
+    </row>
+    <row r="68" spans="2:62">
+      <c r="B68" s="13" t="s">
+        <v>791</v>
+      </c>
+      <c r="AN68" s="21"/>
+      <c r="AO68" s="52" t="s">
+        <v>899</v>
+      </c>
+      <c r="AP68" s="23"/>
+      <c r="AQ68" s="23"/>
+      <c r="AR68" s="23"/>
+      <c r="AS68" s="23"/>
+      <c r="AT68" s="23"/>
+      <c r="AU68" s="23"/>
+      <c r="AV68" s="23"/>
+      <c r="AW68" s="63"/>
+      <c r="AX68" s="62"/>
+      <c r="AY68" s="62"/>
+      <c r="AZ68" s="23"/>
+      <c r="BA68" s="23"/>
+      <c r="BB68" s="23"/>
+      <c r="BC68" s="23"/>
+      <c r="BD68" s="23"/>
+      <c r="BE68" s="23"/>
+      <c r="BF68" s="23"/>
+      <c r="BG68" s="23"/>
+      <c r="BH68" s="23"/>
+      <c r="BI68" s="23"/>
+      <c r="BJ68" s="24"/>
+    </row>
+    <row r="69" spans="2:62">
+      <c r="B69" s="13" t="s">
+        <v>792</v>
+      </c>
+      <c r="AN69" s="21"/>
+      <c r="AO69" s="52" t="s">
+        <v>900</v>
+      </c>
+      <c r="AP69" s="23"/>
+      <c r="AQ69" s="23"/>
+      <c r="AR69" s="23"/>
+      <c r="AS69" s="23"/>
+      <c r="AT69" s="23"/>
+      <c r="AU69" s="23"/>
+      <c r="AV69" s="23"/>
+      <c r="AW69" s="62"/>
+      <c r="AX69" s="63"/>
+      <c r="AY69" s="62"/>
+      <c r="AZ69" s="23"/>
+      <c r="BA69" s="23"/>
+      <c r="BB69" s="23"/>
+      <c r="BC69" s="23"/>
+      <c r="BD69" s="23"/>
+      <c r="BE69" s="23"/>
+      <c r="BF69" s="23"/>
+      <c r="BG69" s="23"/>
+      <c r="BH69" s="23"/>
+      <c r="BI69" s="23"/>
+      <c r="BJ69" s="24"/>
+    </row>
+    <row r="70" spans="2:62">
+      <c r="B70" s="15" t="s">
+        <v>793</v>
+      </c>
+      <c r="AN70" s="21"/>
+      <c r="AO70" s="52" t="s">
+        <v>901</v>
+      </c>
+      <c r="AP70" s="23"/>
+      <c r="AQ70" s="23"/>
+      <c r="AR70" s="23"/>
+      <c r="AS70" s="23"/>
+      <c r="AT70" s="23"/>
+      <c r="AU70" s="23"/>
+      <c r="AV70" s="23"/>
+      <c r="AW70" s="23"/>
+      <c r="AX70" s="23"/>
+      <c r="AY70" s="23"/>
+      <c r="AZ70" s="23"/>
+      <c r="BA70" s="23"/>
+      <c r="BB70" s="23"/>
+      <c r="BC70" s="23"/>
+      <c r="BD70" s="23"/>
+      <c r="BE70" s="23"/>
+      <c r="BF70" s="23"/>
+      <c r="BG70" s="23"/>
+      <c r="BH70" s="23"/>
+      <c r="BI70" s="23"/>
+      <c r="BJ70" s="24"/>
+    </row>
+    <row r="71" spans="2:62">
+      <c r="AN71" s="21"/>
+      <c r="AO71" s="23"/>
+      <c r="AP71" s="23"/>
+      <c r="AQ71" s="23"/>
+      <c r="AR71" s="23"/>
+      <c r="AS71" s="23"/>
+      <c r="AT71" s="23"/>
+      <c r="AU71" s="23"/>
+      <c r="AV71" s="23"/>
+      <c r="AW71" s="23"/>
+      <c r="AX71" s="23"/>
+      <c r="AY71" s="23"/>
+      <c r="AZ71" s="23"/>
+      <c r="BA71" s="23"/>
+      <c r="BB71" s="23"/>
+      <c r="BC71" s="23"/>
+      <c r="BD71" s="23"/>
+      <c r="BE71" s="23"/>
+      <c r="BF71" s="23"/>
+      <c r="BG71" s="23"/>
+      <c r="BH71" s="23"/>
+      <c r="BI71" s="23"/>
+      <c r="BJ71" s="24"/>
+    </row>
+    <row r="72" spans="2:62" ht="15">
+      <c r="B72" s="10" t="s">
+        <v>870</v>
+      </c>
+      <c r="AN72" s="27" t="s">
+        <v>885</v>
+      </c>
+      <c r="AO72" s="23"/>
+      <c r="AP72" s="23"/>
+      <c r="AQ72" s="23"/>
+      <c r="AR72" s="23"/>
+      <c r="AS72" s="23"/>
+      <c r="AT72" s="23"/>
+      <c r="AU72" s="23"/>
+      <c r="AV72" s="23"/>
+      <c r="AW72" s="23"/>
+      <c r="AX72" s="23"/>
+      <c r="AY72" s="23"/>
+      <c r="AZ72" s="23"/>
+      <c r="BA72" s="23"/>
+      <c r="BB72" s="23"/>
+      <c r="BC72" s="23"/>
+      <c r="BD72" s="23"/>
+      <c r="BE72" s="23"/>
+      <c r="BF72" s="23"/>
+      <c r="BG72" s="23"/>
+      <c r="BH72" s="23"/>
+      <c r="BI72" s="23"/>
+      <c r="BJ72" s="24"/>
+    </row>
+    <row r="73" spans="2:62" ht="15">
+      <c r="B73" s="13" t="s">
+        <v>794</v>
+      </c>
+      <c r="AN73" s="64" t="s">
+        <v>902</v>
+      </c>
+      <c r="AO73" s="23"/>
+      <c r="AP73" s="23"/>
+      <c r="AQ73" s="23"/>
+      <c r="AR73" s="23"/>
+      <c r="AS73" s="23"/>
+      <c r="AT73" s="23"/>
+      <c r="AU73" s="23"/>
+      <c r="AV73" s="23"/>
+      <c r="AW73" s="23"/>
+      <c r="AX73" s="23"/>
+      <c r="AY73" s="23"/>
+      <c r="AZ73" s="23"/>
+      <c r="BA73" s="23"/>
+      <c r="BB73" s="23"/>
+      <c r="BC73" s="23"/>
+      <c r="BD73" s="23"/>
+      <c r="BE73" s="23"/>
+      <c r="BF73" s="23"/>
+      <c r="BG73" s="23"/>
+      <c r="BH73" s="23"/>
+      <c r="BI73" s="23"/>
+      <c r="BJ73" s="24"/>
+    </row>
+    <row r="74" spans="2:62">
+      <c r="B74" s="13" t="s">
+        <v>871</v>
+      </c>
+      <c r="AN74" s="34"/>
+      <c r="AO74" s="52" t="s">
+        <v>903</v>
+      </c>
+      <c r="AP74" s="23"/>
+      <c r="AQ74" s="23"/>
+      <c r="AR74" s="23"/>
+      <c r="AS74" s="23"/>
+      <c r="AT74" s="23"/>
+      <c r="AU74" s="23"/>
+      <c r="AV74" s="23"/>
+      <c r="AW74" s="23"/>
+      <c r="AX74" s="23"/>
+      <c r="AY74" s="23"/>
+      <c r="AZ74" s="23"/>
+      <c r="BA74" s="23"/>
+      <c r="BB74" s="23"/>
+      <c r="BC74" s="23"/>
+      <c r="BD74" s="23"/>
+      <c r="BE74" s="23"/>
+      <c r="BF74" s="23"/>
+      <c r="BG74" s="23"/>
+      <c r="BH74" s="23"/>
+      <c r="BI74" s="23"/>
+      <c r="BJ74" s="24"/>
+    </row>
+    <row r="75" spans="2:62">
+      <c r="B75" s="15" t="s">
+        <v>795</v>
+      </c>
+      <c r="AN75" s="21"/>
+      <c r="AO75" s="52" t="s">
+        <v>904</v>
+      </c>
+      <c r="AP75" s="23"/>
+      <c r="AQ75" s="23"/>
+      <c r="AR75" s="23"/>
+      <c r="AS75" s="23"/>
+      <c r="AT75" s="23"/>
+      <c r="AU75" s="23"/>
+      <c r="AV75" s="23"/>
+      <c r="AW75" s="23"/>
+      <c r="AX75" s="23"/>
+      <c r="AY75" s="23"/>
+      <c r="AZ75" s="23"/>
+      <c r="BA75" s="23"/>
+      <c r="BB75" s="23"/>
+      <c r="BC75" s="23"/>
+      <c r="BD75" s="23"/>
+      <c r="BE75" s="23"/>
+      <c r="BF75" s="23"/>
+      <c r="BG75" s="23"/>
+      <c r="BH75" s="23"/>
+      <c r="BI75" s="23"/>
+      <c r="BJ75" s="24"/>
+    </row>
+    <row r="76" spans="2:62" ht="15">
+      <c r="B76" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="AL76" s="13"/>
+      <c r="AN76" s="64" t="s">
+        <v>1009</v>
+      </c>
+      <c r="AO76" s="23"/>
+      <c r="AP76" s="23"/>
+      <c r="AQ76" s="23"/>
+      <c r="AR76" s="23"/>
+      <c r="AS76" s="23"/>
+      <c r="AT76" s="23"/>
+      <c r="AU76" s="23"/>
+      <c r="AV76" s="23"/>
+      <c r="AW76" s="23"/>
+      <c r="AX76" s="23"/>
+      <c r="AY76" s="23"/>
+      <c r="AZ76" s="23"/>
+      <c r="BA76" s="23"/>
+      <c r="BB76" s="23"/>
+      <c r="BC76" s="23"/>
+      <c r="BD76" s="23"/>
+      <c r="BE76" s="23"/>
+      <c r="BF76" s="23"/>
+      <c r="BG76" s="23"/>
+      <c r="BH76" s="23"/>
+      <c r="BI76" s="23"/>
+      <c r="BJ76" s="24"/>
+    </row>
+    <row r="77" spans="2:62" ht="15" thickBot="1">
+      <c r="AN77" s="29"/>
+      <c r="AO77" s="57" t="s">
+        <v>905</v>
+      </c>
+      <c r="AP77" s="30"/>
+      <c r="AQ77" s="30"/>
+      <c r="AR77" s="30"/>
+      <c r="AS77" s="30"/>
+      <c r="AT77" s="30"/>
+      <c r="AU77" s="30"/>
+      <c r="AV77" s="30"/>
+      <c r="AW77" s="30"/>
+      <c r="AX77" s="30"/>
+      <c r="AY77" s="30"/>
+      <c r="AZ77" s="30"/>
+      <c r="BA77" s="30"/>
+      <c r="BB77" s="30"/>
+      <c r="BC77" s="30"/>
+      <c r="BD77" s="30"/>
+      <c r="BE77" s="30"/>
+      <c r="BF77" s="30"/>
+      <c r="BG77" s="30"/>
+      <c r="BH77" s="30"/>
+      <c r="BI77" s="30"/>
+      <c r="BJ77" s="31"/>
+    </row>
+    <row r="106" spans="29:29" ht="15">
+      <c r="AC106" s="10" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="108" spans="29:29" ht="15">
+      <c r="AC108" s="10" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="109" spans="29:29">
+      <c r="AC109" s="13"/>
+    </row>
+    <row r="110" spans="29:29" ht="15">
+      <c r="AC110" s="49" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="111" spans="29:29">
+      <c r="AC111" s="13"/>
+    </row>
+    <row r="112" spans="29:29">
+      <c r="AC112" s="12" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="113" spans="29:29">
+      <c r="AC113" s="13"/>
+    </row>
+    <row r="114" spans="29:29" ht="15">
+      <c r="AC114" s="49" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="115" spans="29:29">
+      <c r="AC115" s="13"/>
+    </row>
+    <row r="116" spans="29:29">
+      <c r="AC116" s="12" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="117" spans="29:29">
+      <c r="AC117" s="12" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="118" spans="29:29">
+      <c r="AC118" s="13"/>
+    </row>
+    <row r="119" spans="29:29" ht="15">
+      <c r="AC119" s="49" t="s">
         <v>910</v>
       </c>
-      <c r="AN6" s="27"/>
-      <c r="AO6" s="27"/>
-      <c r="AP6" s="27"/>
-      <c r="AQ6" s="27"/>
-      <c r="AR6" s="27"/>
-      <c r="AS6" s="27"/>
-      <c r="AT6" s="27"/>
-      <c r="AU6" s="27"/>
-      <c r="AV6" s="27"/>
-      <c r="AW6" s="27"/>
-      <c r="AX6" s="27"/>
-      <c r="AY6" s="27"/>
-      <c r="AZ6" s="27"/>
-      <c r="BA6" s="27"/>
-      <c r="BB6" s="27"/>
-      <c r="BC6" s="28"/>
-      <c r="BE6" s="37" t="s">
+    </row>
+    <row r="120" spans="29:29">
+      <c r="AC120" s="13"/>
+    </row>
+    <row r="121" spans="29:29">
+      <c r="AC121" s="12" t="s">
         <v>911</v>
       </c>
-      <c r="BF6" s="27"/>
-      <c r="BG6" s="27"/>
-      <c r="BH6" s="27"/>
-      <c r="BI6" s="27"/>
-      <c r="BJ6" s="27"/>
-      <c r="BK6" s="27"/>
-      <c r="BL6" s="27"/>
-      <c r="BM6" s="27"/>
-      <c r="BN6" s="27"/>
-      <c r="BO6" s="27"/>
-      <c r="BP6" s="27"/>
-      <c r="BQ6" s="27"/>
-      <c r="BR6" s="27"/>
-      <c r="BS6" s="27"/>
-      <c r="BT6" s="27"/>
-      <c r="BU6" s="27"/>
-      <c r="BV6" s="27"/>
-      <c r="BW6" s="28"/>
-    </row>
-    <row r="7" spans="2:75">
-      <c r="B7" s="13" t="s">
-        <v>860</v>
-      </c>
-      <c r="AL7" s="25"/>
-      <c r="AM7" s="29" t="s">
-        <v>799</v>
-      </c>
-      <c r="AN7" s="27"/>
-      <c r="AO7" s="27"/>
-      <c r="AP7" s="27"/>
-      <c r="AQ7" s="27"/>
-      <c r="AR7" s="27"/>
-      <c r="AS7" s="27"/>
-      <c r="AT7" s="27"/>
-      <c r="AU7" s="27"/>
-      <c r="AV7" s="27"/>
-      <c r="AW7" s="27"/>
-      <c r="AX7" s="27"/>
-      <c r="AY7" s="27"/>
-      <c r="AZ7" s="27"/>
-      <c r="BA7" s="27"/>
-      <c r="BB7" s="27"/>
-      <c r="BC7" s="28"/>
-      <c r="BE7" s="25"/>
-      <c r="BF7" s="36" t="s">
-        <v>804</v>
-      </c>
-      <c r="BG7" s="27"/>
-      <c r="BH7" s="27"/>
-      <c r="BI7" s="27"/>
-      <c r="BJ7" s="27"/>
-      <c r="BK7" s="27"/>
-      <c r="BL7" s="27"/>
-      <c r="BM7" s="27"/>
-      <c r="BN7" s="27"/>
-      <c r="BO7" s="27"/>
-      <c r="BP7" s="27"/>
-      <c r="BQ7" s="27"/>
-      <c r="BR7" s="27"/>
-      <c r="BS7" s="27"/>
-      <c r="BT7" s="27"/>
-      <c r="BU7" s="27"/>
-      <c r="BV7" s="27"/>
-      <c r="BW7" s="28"/>
-    </row>
-    <row r="8" spans="2:75">
-      <c r="B8" s="13" t="s">
-        <v>861</v>
-      </c>
-      <c r="AL8" s="25"/>
-      <c r="AM8" s="30" t="s">
-        <v>873</v>
-      </c>
-      <c r="AN8" s="27"/>
-      <c r="AO8" s="27"/>
-      <c r="AP8" s="27"/>
-      <c r="AQ8" s="27"/>
-      <c r="AR8" s="27"/>
-      <c r="AS8" s="27"/>
-      <c r="AT8" s="27"/>
-      <c r="AU8" s="27"/>
-      <c r="AV8" s="27"/>
-      <c r="AW8" s="27"/>
-      <c r="AX8" s="27"/>
-      <c r="AY8" s="27"/>
-      <c r="AZ8" s="27"/>
-      <c r="BA8" s="27"/>
-      <c r="BB8" s="27"/>
-      <c r="BC8" s="28"/>
-      <c r="BE8" s="25"/>
-      <c r="BF8" s="36" t="s">
-        <v>805</v>
-      </c>
-      <c r="BG8" s="27"/>
-      <c r="BH8" s="27"/>
-      <c r="BI8" s="27"/>
-      <c r="BJ8" s="27"/>
-      <c r="BK8" s="27"/>
-      <c r="BL8" s="27"/>
-      <c r="BM8" s="27"/>
-      <c r="BN8" s="27"/>
-      <c r="BO8" s="27"/>
-      <c r="BP8" s="27"/>
-      <c r="BQ8" s="27"/>
-      <c r="BR8" s="27"/>
-      <c r="BS8" s="27"/>
-      <c r="BT8" s="27"/>
-      <c r="BU8" s="27"/>
-      <c r="BV8" s="27"/>
-      <c r="BW8" s="28"/>
-    </row>
-    <row r="9" spans="2:75" ht="15">
-      <c r="AL9" s="25"/>
-      <c r="AM9" s="30" t="s">
-        <v>875</v>
-      </c>
-      <c r="AN9" s="27"/>
-      <c r="AO9" s="27"/>
-      <c r="AP9" s="27"/>
-      <c r="AQ9" s="27"/>
-      <c r="AR9" s="27"/>
-      <c r="AS9" s="27"/>
-      <c r="AT9" s="27"/>
-      <c r="AU9" s="27"/>
-      <c r="AV9" s="27"/>
-      <c r="AW9" s="27"/>
-      <c r="AX9" s="27"/>
-      <c r="AY9" s="27"/>
-      <c r="AZ9" s="27"/>
-      <c r="BA9" s="27"/>
-      <c r="BB9" s="27"/>
-      <c r="BC9" s="28"/>
-      <c r="BE9" s="31" t="s">
-        <v>806</v>
-      </c>
-      <c r="BF9" s="27"/>
-      <c r="BG9" s="27"/>
-      <c r="BH9" s="27"/>
-      <c r="BI9" s="27"/>
-      <c r="BJ9" s="27"/>
-      <c r="BK9" s="27"/>
-      <c r="BL9" s="27"/>
-      <c r="BM9" s="27"/>
-      <c r="BN9" s="27"/>
-      <c r="BO9" s="27"/>
-      <c r="BP9" s="27"/>
-      <c r="BQ9" s="27"/>
-      <c r="BR9" s="27"/>
-      <c r="BS9" s="27"/>
-      <c r="BT9" s="27"/>
-      <c r="BU9" s="27"/>
-      <c r="BV9" s="27"/>
-      <c r="BW9" s="28"/>
-    </row>
-    <row r="10" spans="2:75" ht="15.75" thickBot="1">
-      <c r="B10" s="11" t="s">
-        <v>862</v>
-      </c>
-      <c r="AL10" s="25"/>
-      <c r="AM10" s="29" t="s">
-        <v>878</v>
-      </c>
-      <c r="AN10" s="27"/>
-      <c r="AO10" s="27"/>
-      <c r="AP10" s="27"/>
-      <c r="AQ10" s="27"/>
-      <c r="AR10" s="27"/>
-      <c r="AS10" s="27"/>
-      <c r="AT10" s="27"/>
-      <c r="AU10" s="27"/>
-      <c r="AV10" s="27"/>
-      <c r="AW10" s="27"/>
-      <c r="AX10" s="27"/>
-      <c r="AY10" s="27"/>
-      <c r="AZ10" s="27"/>
-      <c r="BA10" s="27"/>
-      <c r="BB10" s="27"/>
-      <c r="BC10" s="28"/>
-      <c r="BE10" s="33" t="s">
+    </row>
+    <row r="122" spans="29:29">
+      <c r="AC122" s="13"/>
+    </row>
+    <row r="123" spans="29:29" ht="15">
+      <c r="AC123" s="49" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="124" spans="29:29">
+      <c r="AC124" s="13"/>
+    </row>
+    <row r="125" spans="29:29">
+      <c r="AC125" s="12" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="127" spans="29:29" ht="15">
+      <c r="AC127" s="10" t="s">
         <v>885</v>
       </c>
-      <c r="BF10" s="34"/>
-      <c r="BG10" s="34"/>
-      <c r="BH10" s="34"/>
-      <c r="BI10" s="34"/>
-      <c r="BJ10" s="34"/>
-      <c r="BK10" s="34"/>
-      <c r="BL10" s="34"/>
-      <c r="BM10" s="34"/>
-      <c r="BN10" s="34"/>
-      <c r="BO10" s="34"/>
-      <c r="BP10" s="34"/>
-      <c r="BQ10" s="34"/>
-      <c r="BR10" s="34"/>
-      <c r="BS10" s="34"/>
-      <c r="BT10" s="34"/>
-      <c r="BU10" s="34"/>
-      <c r="BV10" s="34"/>
-      <c r="BW10" s="35"/>
-    </row>
-    <row r="11" spans="2:75" ht="15.75" thickBot="1">
-      <c r="B11" s="13" t="s">
-        <v>863</v>
-      </c>
-      <c r="AL11" s="31" t="s">
-        <v>800</v>
-      </c>
-      <c r="AM11" s="27"/>
-      <c r="AN11" s="27"/>
-      <c r="AO11" s="27"/>
-      <c r="AP11" s="27"/>
-      <c r="AQ11" s="27"/>
-      <c r="AR11" s="27"/>
-      <c r="AS11" s="27"/>
-      <c r="AT11" s="27"/>
-      <c r="AU11" s="27"/>
-      <c r="AV11" s="27"/>
-      <c r="AW11" s="27"/>
-      <c r="AX11" s="27"/>
-      <c r="AY11" s="27"/>
-      <c r="AZ11" s="27"/>
-      <c r="BA11" s="27"/>
-      <c r="BB11" s="27"/>
-      <c r="BC11" s="28"/>
-    </row>
-    <row r="12" spans="2:75" ht="15">
-      <c r="B12" s="13" t="s">
-        <v>864</v>
-      </c>
-      <c r="AL12" s="32" t="s">
-        <v>801</v>
-      </c>
-      <c r="AM12" s="27"/>
-      <c r="AN12" s="27"/>
-      <c r="AO12" s="27"/>
-      <c r="AP12" s="27"/>
-      <c r="AQ12" s="27"/>
-      <c r="AR12" s="27"/>
-      <c r="AS12" s="27"/>
-      <c r="AT12" s="27"/>
-      <c r="AU12" s="27"/>
-      <c r="AV12" s="27"/>
-      <c r="AW12" s="27"/>
-      <c r="AX12" s="27"/>
-      <c r="AY12" s="27"/>
-      <c r="AZ12" s="27"/>
-      <c r="BA12" s="27"/>
-      <c r="BB12" s="27"/>
-      <c r="BC12" s="28"/>
-      <c r="BE12" s="22" t="s">
-        <v>886</v>
-      </c>
-      <c r="BF12" s="23"/>
-      <c r="BG12" s="23"/>
-      <c r="BH12" s="23"/>
-      <c r="BI12" s="23"/>
-      <c r="BJ12" s="23"/>
-      <c r="BK12" s="23"/>
-      <c r="BL12" s="23"/>
-      <c r="BM12" s="23"/>
-      <c r="BN12" s="23"/>
-      <c r="BO12" s="23"/>
-      <c r="BP12" s="23"/>
-      <c r="BQ12" s="23"/>
-      <c r="BR12" s="23"/>
-      <c r="BS12" s="23"/>
-      <c r="BT12" s="23"/>
-      <c r="BU12" s="23"/>
-      <c r="BV12" s="23"/>
-      <c r="BW12" s="24"/>
-    </row>
-    <row r="13" spans="2:75" ht="15">
-      <c r="B13" s="13" t="s">
-        <v>865</v>
-      </c>
-      <c r="AL13" s="32" t="s">
-        <v>802</v>
-      </c>
-      <c r="AM13" s="27"/>
-      <c r="AN13" s="27"/>
-      <c r="AO13" s="27"/>
-      <c r="AP13" s="27"/>
-      <c r="AQ13" s="27"/>
-      <c r="AR13" s="27"/>
-      <c r="AS13" s="27"/>
-      <c r="AT13" s="27"/>
-      <c r="AU13" s="27"/>
-      <c r="AV13" s="27"/>
-      <c r="AW13" s="27"/>
-      <c r="AX13" s="27"/>
-      <c r="AY13" s="27"/>
-      <c r="AZ13" s="27"/>
-      <c r="BA13" s="27"/>
-      <c r="BB13" s="27"/>
-      <c r="BC13" s="28"/>
-      <c r="BE13" s="25"/>
-      <c r="BF13" s="40" t="s">
-        <v>807</v>
-      </c>
-      <c r="BG13" s="40"/>
-      <c r="BH13" s="40"/>
-      <c r="BI13" s="40"/>
-      <c r="BJ13" s="40" t="s">
-        <v>808</v>
-      </c>
-      <c r="BK13" s="40"/>
-      <c r="BL13" s="40"/>
-      <c r="BM13" s="40"/>
-      <c r="BN13" s="40"/>
-      <c r="BO13" s="40"/>
-      <c r="BP13" s="40" t="s">
-        <v>809</v>
-      </c>
-      <c r="BQ13" s="40"/>
-      <c r="BR13" s="40"/>
-      <c r="BS13" s="40"/>
-      <c r="BT13" s="40"/>
-      <c r="BU13" s="40"/>
-      <c r="BV13" s="40"/>
-      <c r="BW13" s="28"/>
-    </row>
-    <row r="14" spans="2:75" ht="15.75" thickBot="1">
-      <c r="AL14" s="33" t="s">
-        <v>880</v>
-      </c>
-      <c r="AM14" s="34"/>
-      <c r="AN14" s="34"/>
-      <c r="AO14" s="34"/>
-      <c r="AP14" s="34"/>
-      <c r="AQ14" s="34"/>
-      <c r="AR14" s="34"/>
-      <c r="AS14" s="34"/>
-      <c r="AT14" s="34"/>
-      <c r="AU14" s="34"/>
-      <c r="AV14" s="34"/>
-      <c r="AW14" s="34"/>
-      <c r="AX14" s="34"/>
-      <c r="AY14" s="34"/>
-      <c r="AZ14" s="34"/>
-      <c r="BA14" s="34"/>
-      <c r="BB14" s="34"/>
-      <c r="BC14" s="35"/>
-      <c r="BE14" s="25"/>
-      <c r="BF14" s="42" t="s">
-        <v>810</v>
-      </c>
-      <c r="BG14" s="42"/>
-      <c r="BH14" s="42"/>
-      <c r="BI14" s="42"/>
-      <c r="BJ14" s="41" t="s">
-        <v>811</v>
-      </c>
-      <c r="BK14" s="41"/>
-      <c r="BL14" s="41"/>
-      <c r="BM14" s="41"/>
-      <c r="BN14" s="41"/>
-      <c r="BO14" s="41"/>
-      <c r="BP14" s="41" t="s">
-        <v>811</v>
-      </c>
-      <c r="BQ14" s="41"/>
-      <c r="BR14" s="41"/>
-      <c r="BS14" s="41"/>
-      <c r="BT14" s="41"/>
-      <c r="BU14" s="41"/>
-      <c r="BV14" s="41"/>
-      <c r="BW14" s="28"/>
-    </row>
-    <row r="15" spans="2:75" ht="15.75" thickBot="1">
-      <c r="B15" s="11" t="s">
-        <v>866</v>
-      </c>
-      <c r="AL15" s="14"/>
-      <c r="BE15" s="25"/>
-      <c r="BF15" s="42" t="s">
-        <v>812</v>
-      </c>
-      <c r="BG15" s="42"/>
-      <c r="BH15" s="42"/>
-      <c r="BI15" s="42"/>
-      <c r="BJ15" s="41" t="s">
-        <v>813</v>
-      </c>
-      <c r="BK15" s="41"/>
-      <c r="BL15" s="41"/>
-      <c r="BM15" s="41"/>
-      <c r="BN15" s="41"/>
-      <c r="BO15" s="41"/>
-      <c r="BP15" s="41" t="s">
-        <v>814</v>
-      </c>
-      <c r="BQ15" s="41"/>
-      <c r="BR15" s="41"/>
-      <c r="BS15" s="41"/>
-      <c r="BT15" s="41"/>
-      <c r="BU15" s="41"/>
-      <c r="BV15" s="41"/>
-      <c r="BW15" s="28"/>
-    </row>
-    <row r="16" spans="2:75" ht="15">
-      <c r="B16" s="13" t="s">
-        <v>867</v>
-      </c>
-      <c r="AL16" s="22" t="s">
-        <v>892</v>
-      </c>
-      <c r="AM16" s="23"/>
-      <c r="AN16" s="23"/>
-      <c r="AO16" s="23"/>
-      <c r="AP16" s="23"/>
-      <c r="AQ16" s="23"/>
-      <c r="AR16" s="23"/>
-      <c r="AS16" s="23"/>
-      <c r="AT16" s="23"/>
-      <c r="AU16" s="23"/>
-      <c r="AV16" s="23"/>
-      <c r="AW16" s="23"/>
-      <c r="AX16" s="23"/>
-      <c r="AY16" s="23"/>
-      <c r="AZ16" s="23"/>
-      <c r="BA16" s="23"/>
-      <c r="BB16" s="23"/>
-      <c r="BC16" s="24"/>
-      <c r="BE16" s="25"/>
-      <c r="BF16" s="42" t="s">
-        <v>815</v>
-      </c>
-      <c r="BG16" s="42"/>
-      <c r="BH16" s="42"/>
-      <c r="BI16" s="42"/>
-      <c r="BJ16" s="41" t="s">
-        <v>816</v>
-      </c>
-      <c r="BK16" s="41"/>
-      <c r="BL16" s="41"/>
-      <c r="BM16" s="41"/>
-      <c r="BN16" s="41"/>
-      <c r="BO16" s="41"/>
-      <c r="BP16" s="41" t="s">
-        <v>816</v>
-      </c>
-      <c r="BQ16" s="41"/>
-      <c r="BR16" s="41"/>
-      <c r="BS16" s="41"/>
-      <c r="BT16" s="41"/>
-      <c r="BU16" s="41"/>
-      <c r="BV16" s="41"/>
-      <c r="BW16" s="28"/>
-    </row>
-    <row r="17" spans="2:88" ht="15">
-      <c r="B17" s="13" t="s">
-        <v>868</v>
-      </c>
-      <c r="AL17" s="31" t="s">
-        <v>817</v>
-      </c>
-      <c r="AM17" s="27"/>
-      <c r="AN17" s="27"/>
-      <c r="AO17" s="27"/>
-      <c r="AP17" s="27"/>
-      <c r="AQ17" s="27"/>
-      <c r="AR17" s="27"/>
-      <c r="AS17" s="27"/>
-      <c r="AT17" s="27"/>
-      <c r="AU17" s="27"/>
-      <c r="AV17" s="27"/>
-      <c r="AW17" s="27"/>
-      <c r="AX17" s="27"/>
-      <c r="AY17" s="27"/>
-      <c r="AZ17" s="27"/>
-      <c r="BA17" s="27"/>
-      <c r="BB17" s="27"/>
-      <c r="BC17" s="28"/>
-      <c r="BE17" s="25"/>
-      <c r="BF17" s="27"/>
-      <c r="BG17" s="27"/>
-      <c r="BH17" s="27"/>
-      <c r="BI17" s="27"/>
-      <c r="BJ17" s="27"/>
-      <c r="BK17" s="27"/>
-      <c r="BL17" s="27"/>
-      <c r="BM17" s="27"/>
-      <c r="BN17" s="27"/>
-      <c r="BO17" s="27"/>
-      <c r="BP17" s="27"/>
-      <c r="BQ17" s="27"/>
-      <c r="BR17" s="27"/>
-      <c r="BS17" s="27"/>
-      <c r="BT17" s="27"/>
-      <c r="BU17" s="27"/>
-      <c r="BV17" s="27"/>
-      <c r="BW17" s="28"/>
-    </row>
-    <row r="18" spans="2:88" ht="15" customHeight="1">
-      <c r="B18" s="14" t="s">
-        <v>772</v>
-      </c>
-      <c r="AL18" s="25"/>
-      <c r="AM18" s="27"/>
-      <c r="AN18" s="36" t="s">
-        <v>818</v>
-      </c>
-      <c r="AO18" s="27"/>
-      <c r="AP18" s="27"/>
-      <c r="AQ18" s="27"/>
-      <c r="AR18" s="27"/>
-      <c r="AS18" s="27"/>
-      <c r="AT18" s="27"/>
-      <c r="AU18" s="27"/>
-      <c r="AV18" s="27"/>
-      <c r="AW18" s="27"/>
-      <c r="AX18" s="27"/>
-      <c r="AY18" s="27"/>
-      <c r="AZ18" s="27"/>
-      <c r="BA18" s="27"/>
-      <c r="BB18" s="27"/>
-      <c r="BC18" s="28"/>
-      <c r="BE18" s="38" t="s">
-        <v>889</v>
-      </c>
-      <c r="BF18" s="27"/>
-      <c r="BG18" s="27"/>
-      <c r="BH18" s="27"/>
-      <c r="BI18" s="27"/>
-      <c r="BJ18" s="27"/>
-      <c r="BK18" s="27"/>
-      <c r="BL18" s="27"/>
-      <c r="BM18" s="27"/>
-      <c r="BN18" s="27"/>
-      <c r="BO18" s="27"/>
-      <c r="BP18" s="27"/>
-      <c r="BQ18" s="27"/>
-      <c r="BR18" s="27"/>
-      <c r="BS18" s="27"/>
-      <c r="BT18" s="27"/>
-      <c r="BU18" s="27"/>
-      <c r="BV18" s="27"/>
-      <c r="BW18" s="28"/>
-    </row>
-    <row r="19" spans="2:88" ht="14.25" customHeight="1" thickBot="1">
-      <c r="AL19" s="25"/>
-      <c r="AM19" s="27"/>
-      <c r="AN19" s="36" t="s">
-        <v>819</v>
-      </c>
-      <c r="AO19" s="27"/>
-      <c r="AP19" s="27"/>
-      <c r="AQ19" s="27"/>
-      <c r="AR19" s="27"/>
-      <c r="AS19" s="27"/>
-      <c r="AT19" s="27"/>
-      <c r="AU19" s="27"/>
-      <c r="AV19" s="27"/>
-      <c r="AW19" s="27"/>
-      <c r="AX19" s="27"/>
-      <c r="AY19" s="27"/>
-      <c r="AZ19" s="27"/>
-      <c r="BA19" s="27"/>
-      <c r="BB19" s="27"/>
-      <c r="BC19" s="28"/>
-      <c r="BE19" s="39" t="s">
-        <v>912</v>
-      </c>
-      <c r="BF19" s="34"/>
-      <c r="BG19" s="34"/>
-      <c r="BH19" s="34"/>
-      <c r="BI19" s="34"/>
-      <c r="BJ19" s="34"/>
-      <c r="BK19" s="34"/>
-      <c r="BL19" s="34"/>
-      <c r="BM19" s="34"/>
-      <c r="BN19" s="34"/>
-      <c r="BO19" s="34"/>
-      <c r="BP19" s="34"/>
-      <c r="BQ19" s="34"/>
-      <c r="BR19" s="34"/>
-      <c r="BS19" s="34"/>
-      <c r="BT19" s="34"/>
-      <c r="BU19" s="34"/>
-      <c r="BV19" s="34"/>
-      <c r="BW19" s="35"/>
-    </row>
-    <row r="20" spans="2:88" ht="15" customHeight="1">
-      <c r="B20" s="11" t="s">
-        <v>869</v>
-      </c>
-      <c r="AL20" s="25"/>
-      <c r="AM20" s="27"/>
-      <c r="AN20" s="36" t="s">
-        <v>820</v>
-      </c>
-      <c r="AO20" s="27"/>
-      <c r="AP20" s="27"/>
-      <c r="AQ20" s="27"/>
-      <c r="AR20" s="27"/>
-      <c r="AS20" s="27"/>
-      <c r="AT20" s="27"/>
-      <c r="AU20" s="27"/>
-      <c r="AV20" s="27"/>
-      <c r="AW20" s="27"/>
-      <c r="AX20" s="27"/>
-      <c r="AY20" s="27"/>
-      <c r="AZ20" s="27"/>
-      <c r="BA20" s="27"/>
-      <c r="BB20" s="27"/>
-      <c r="BC20" s="28"/>
-    </row>
-    <row r="21" spans="2:88" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B21" s="13" t="s">
-        <v>870</v>
-      </c>
-      <c r="AL21" s="43" t="s">
-        <v>895</v>
-      </c>
-      <c r="AM21" s="27"/>
-      <c r="AN21" s="27"/>
-      <c r="AO21" s="27"/>
-      <c r="AP21" s="27"/>
-      <c r="AQ21" s="27"/>
-      <c r="AR21" s="27"/>
-      <c r="AS21" s="27"/>
-      <c r="AT21" s="27"/>
-      <c r="AU21" s="27"/>
-      <c r="AV21" s="27"/>
-      <c r="AW21" s="27"/>
-      <c r="AX21" s="27"/>
-      <c r="AY21" s="27"/>
-      <c r="AZ21" s="27"/>
-      <c r="BA21" s="27"/>
-      <c r="BB21" s="27"/>
-      <c r="BC21" s="28"/>
-    </row>
-    <row r="22" spans="2:88" ht="15">
-      <c r="B22" s="13" t="s">
-        <v>871</v>
-      </c>
-      <c r="AL22" s="31" t="s">
-        <v>821</v>
-      </c>
-      <c r="AM22" s="27"/>
-      <c r="AN22" s="27"/>
-      <c r="AO22" s="27"/>
-      <c r="AP22" s="27"/>
-      <c r="AQ22" s="27"/>
-      <c r="AR22" s="27"/>
-      <c r="AS22" s="27"/>
-      <c r="AT22" s="27"/>
-      <c r="AU22" s="27"/>
-      <c r="AV22" s="27"/>
-      <c r="AW22" s="27"/>
-      <c r="AX22" s="27"/>
-      <c r="AY22" s="27"/>
-      <c r="AZ22" s="27"/>
-      <c r="BA22" s="27"/>
-      <c r="BB22" s="27"/>
-      <c r="BC22" s="28"/>
-      <c r="BH22" s="22" t="s">
-        <v>903</v>
-      </c>
-      <c r="BI22" s="23"/>
-      <c r="BJ22" s="23"/>
-      <c r="BK22" s="23"/>
-      <c r="BL22" s="23"/>
-      <c r="BM22" s="23"/>
-      <c r="BN22" s="23"/>
-      <c r="BO22" s="23"/>
-      <c r="BP22" s="23"/>
-      <c r="BQ22" s="23"/>
-      <c r="BR22" s="23"/>
-      <c r="BS22" s="23"/>
-      <c r="BT22" s="23"/>
-      <c r="BU22" s="23"/>
-      <c r="BV22" s="23"/>
-      <c r="BW22" s="23"/>
-      <c r="BX22" s="23"/>
-      <c r="BY22" s="23"/>
-      <c r="BZ22" s="23"/>
-      <c r="CA22" s="23"/>
-      <c r="CB22" s="23"/>
-      <c r="CC22" s="23"/>
-      <c r="CD22" s="23"/>
-      <c r="CE22" s="23"/>
-      <c r="CF22" s="23"/>
-      <c r="CG22" s="23"/>
-      <c r="CH22" s="23"/>
-      <c r="CI22" s="23"/>
-      <c r="CJ22" s="24"/>
-    </row>
-    <row r="23" spans="2:88" ht="15">
-      <c r="B23" s="13" t="s">
-        <v>872</v>
-      </c>
-      <c r="AL23" s="38" t="s">
-        <v>896</v>
-      </c>
-      <c r="AM23" s="27"/>
-      <c r="AN23" s="27"/>
-      <c r="AO23" s="27"/>
-      <c r="AP23" s="27"/>
-      <c r="AQ23" s="27"/>
-      <c r="AR23" s="27"/>
-      <c r="AS23" s="27"/>
-      <c r="AT23" s="27"/>
-      <c r="AU23" s="27"/>
-      <c r="AV23" s="27"/>
-      <c r="AW23" s="27"/>
-      <c r="AX23" s="27"/>
-      <c r="AY23" s="27"/>
-      <c r="AZ23" s="27"/>
-      <c r="BA23" s="27"/>
-      <c r="BB23" s="27"/>
-      <c r="BC23" s="28"/>
-      <c r="BH23" s="31" t="s">
-        <v>838</v>
-      </c>
-      <c r="BI23" s="27"/>
-      <c r="BJ23" s="27"/>
-      <c r="BK23" s="27"/>
-      <c r="BL23" s="27"/>
-      <c r="BM23" s="27"/>
-      <c r="BN23" s="27"/>
-      <c r="BO23" s="27"/>
-      <c r="BP23" s="27"/>
-      <c r="BQ23" s="27"/>
-      <c r="BR23" s="27"/>
-      <c r="BS23" s="27"/>
-      <c r="BT23" s="27"/>
-      <c r="BU23" s="27"/>
-      <c r="BV23" s="27"/>
-      <c r="BW23" s="27"/>
-      <c r="BX23" s="27"/>
-      <c r="BY23" s="27"/>
-      <c r="BZ23" s="27"/>
-      <c r="CA23" s="27"/>
-      <c r="CB23" s="27"/>
-      <c r="CC23" s="27"/>
-      <c r="CD23" s="27"/>
-      <c r="CE23" s="27"/>
-      <c r="CF23" s="27"/>
-      <c r="CG23" s="27"/>
-      <c r="CH23" s="27"/>
-      <c r="CI23" s="27"/>
-      <c r="CJ23" s="28"/>
-    </row>
-    <row r="24" spans="2:88" ht="15" thickBot="1">
-      <c r="AL24" s="33" t="s">
-        <v>897</v>
-      </c>
-      <c r="AM24" s="34"/>
-      <c r="AN24" s="34"/>
-      <c r="AO24" s="34"/>
-      <c r="AP24" s="34"/>
-      <c r="AQ24" s="34"/>
-      <c r="AR24" s="34"/>
-      <c r="AS24" s="34"/>
-      <c r="AT24" s="34"/>
-      <c r="AU24" s="34"/>
-      <c r="AV24" s="34"/>
-      <c r="AW24" s="34"/>
-      <c r="AX24" s="34"/>
-      <c r="AY24" s="34"/>
-      <c r="AZ24" s="34"/>
-      <c r="BA24" s="34"/>
-      <c r="BB24" s="34"/>
-      <c r="BC24" s="35"/>
-      <c r="BH24" s="32" t="s">
-        <v>839</v>
-      </c>
-      <c r="BI24" s="27"/>
-      <c r="BJ24" s="27"/>
-      <c r="BK24" s="27"/>
-      <c r="BL24" s="27"/>
-      <c r="BM24" s="27"/>
-      <c r="BN24" s="27"/>
-      <c r="BO24" s="27"/>
-      <c r="BP24" s="27"/>
-      <c r="BQ24" s="27"/>
-      <c r="BR24" s="27"/>
-      <c r="BS24" s="27"/>
-      <c r="BT24" s="27"/>
-      <c r="BU24" s="27"/>
-      <c r="BV24" s="27"/>
-      <c r="BW24" s="27"/>
-      <c r="BX24" s="27"/>
-      <c r="BY24" s="27"/>
-      <c r="BZ24" s="27"/>
-      <c r="CA24" s="27"/>
-      <c r="CB24" s="27"/>
-      <c r="CC24" s="27"/>
-      <c r="CD24" s="27"/>
-      <c r="CE24" s="27"/>
-      <c r="CF24" s="27"/>
-      <c r="CG24" s="27"/>
-      <c r="CH24" s="27"/>
-      <c r="CI24" s="27"/>
-      <c r="CJ24" s="28"/>
-    </row>
-    <row r="25" spans="2:88" ht="15.75" thickBot="1">
-      <c r="B25" s="11" t="s">
-        <v>874</v>
-      </c>
-      <c r="AL25" s="15"/>
-      <c r="BH25" s="43" t="s">
-        <v>905</v>
-      </c>
-      <c r="BI25" s="27"/>
-      <c r="BJ25" s="27"/>
-      <c r="BK25" s="27"/>
-      <c r="BL25" s="27"/>
-      <c r="BM25" s="27"/>
-      <c r="BN25" s="27"/>
-      <c r="BO25" s="27"/>
-      <c r="BP25" s="27"/>
-      <c r="BQ25" s="27"/>
-      <c r="BR25" s="27"/>
-      <c r="BS25" s="27"/>
-      <c r="BT25" s="27"/>
-      <c r="BU25" s="27"/>
-      <c r="BV25" s="27"/>
-      <c r="BW25" s="27"/>
-      <c r="BX25" s="27"/>
-      <c r="BY25" s="27"/>
-      <c r="BZ25" s="27"/>
-      <c r="CA25" s="27"/>
-      <c r="CB25" s="27"/>
-      <c r="CC25" s="27"/>
-      <c r="CD25" s="27"/>
-      <c r="CE25" s="27"/>
-      <c r="CF25" s="27"/>
-      <c r="CG25" s="27"/>
-      <c r="CH25" s="27"/>
-      <c r="CI25" s="27"/>
-      <c r="CJ25" s="28"/>
-    </row>
-    <row r="26" spans="2:88" ht="15">
-      <c r="B26" s="14" t="s">
-        <v>773</v>
-      </c>
-      <c r="AL26" s="22" t="s">
-        <v>899</v>
-      </c>
-      <c r="AM26" s="23"/>
-      <c r="AN26" s="23"/>
-      <c r="AO26" s="23"/>
-      <c r="AP26" s="23"/>
-      <c r="AQ26" s="23"/>
-      <c r="AR26" s="23"/>
-      <c r="AS26" s="23"/>
-      <c r="AT26" s="23"/>
-      <c r="AU26" s="23"/>
-      <c r="AV26" s="23"/>
-      <c r="AW26" s="23"/>
-      <c r="AX26" s="23"/>
-      <c r="AY26" s="23"/>
-      <c r="AZ26" s="23"/>
-      <c r="BA26" s="23"/>
-      <c r="BB26" s="23"/>
-      <c r="BC26" s="23"/>
-      <c r="BD26" s="23"/>
-      <c r="BE26" s="23"/>
-      <c r="BF26" s="24"/>
-      <c r="BH26" s="31" t="s">
-        <v>840</v>
-      </c>
-      <c r="BI26" s="27"/>
-      <c r="BJ26" s="27"/>
-      <c r="BK26" s="27"/>
-      <c r="BL26" s="27"/>
-      <c r="BM26" s="27"/>
-      <c r="BN26" s="27"/>
-      <c r="BO26" s="27"/>
-      <c r="BP26" s="27"/>
-      <c r="BQ26" s="27"/>
-      <c r="BR26" s="27"/>
-      <c r="BS26" s="27"/>
-      <c r="BT26" s="27"/>
-      <c r="BU26" s="27"/>
-      <c r="BV26" s="27"/>
-      <c r="BW26" s="27"/>
-      <c r="BX26" s="27"/>
-      <c r="BY26" s="27"/>
-      <c r="BZ26" s="27"/>
-      <c r="CA26" s="27"/>
-      <c r="CB26" s="27"/>
-      <c r="CC26" s="27"/>
-      <c r="CD26" s="27"/>
-      <c r="CE26" s="27"/>
-      <c r="CF26" s="27"/>
-      <c r="CG26" s="27"/>
-      <c r="CH26" s="27"/>
-      <c r="CI26" s="27"/>
-      <c r="CJ26" s="28"/>
-    </row>
-    <row r="27" spans="2:88" ht="15">
-      <c r="B27" s="14" t="s">
+    </row>
+    <row r="128" spans="29:29">
+      <c r="AC128" s="13"/>
+    </row>
+    <row r="129" spans="29:29" ht="15">
+      <c r="AC129" s="49" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="130" spans="29:29">
+      <c r="AC130" s="13"/>
+    </row>
+    <row r="131" spans="29:29">
+      <c r="AC131" s="12" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="132" spans="29:29">
+      <c r="AC132" s="12" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="133" spans="29:29">
+      <c r="AC133" s="13"/>
+    </row>
+    <row r="134" spans="29:29" ht="15">
+      <c r="AC134" s="49" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="135" spans="29:29">
+      <c r="AC135" s="13"/>
+    </row>
+    <row r="136" spans="29:29">
+      <c r="AC136" s="12" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="140" spans="29:29" ht="15">
+      <c r="AC140" s="10" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="142" spans="29:29" ht="15">
+      <c r="AC142" s="10" t="s">
         <v>876</v>
       </c>
-      <c r="AL27" s="31" t="s">
-        <v>822</v>
-      </c>
-      <c r="AM27" s="27"/>
-      <c r="AN27" s="27"/>
-      <c r="AO27" s="27"/>
-      <c r="AP27" s="27"/>
-      <c r="AQ27" s="27"/>
-      <c r="AR27" s="27"/>
-      <c r="AS27" s="27"/>
-      <c r="AT27" s="27"/>
-      <c r="AU27" s="27"/>
-      <c r="AV27" s="27"/>
-      <c r="AW27" s="27"/>
-      <c r="AX27" s="27"/>
-      <c r="AY27" s="27"/>
-      <c r="AZ27" s="27"/>
-      <c r="BA27" s="27"/>
-      <c r="BB27" s="27"/>
-      <c r="BC27" s="27"/>
-      <c r="BD27" s="27"/>
-      <c r="BE27" s="27"/>
-      <c r="BF27" s="28"/>
-      <c r="BH27" s="32" t="s">
-        <v>841</v>
-      </c>
-      <c r="BI27" s="27"/>
-      <c r="BJ27" s="27"/>
-      <c r="BK27" s="27"/>
-      <c r="BL27" s="27"/>
-      <c r="BM27" s="27"/>
-      <c r="BN27" s="27"/>
-      <c r="BO27" s="27"/>
-      <c r="BP27" s="27"/>
-      <c r="BQ27" s="27"/>
-      <c r="BR27" s="27"/>
-      <c r="BS27" s="27"/>
-      <c r="BT27" s="27"/>
-      <c r="BU27" s="27"/>
-      <c r="BV27" s="27"/>
-      <c r="BW27" s="27"/>
-      <c r="BX27" s="27"/>
-      <c r="BY27" s="27"/>
-      <c r="BZ27" s="27"/>
-      <c r="CA27" s="27"/>
-      <c r="CB27" s="27"/>
-      <c r="CC27" s="27"/>
-      <c r="CD27" s="27"/>
-      <c r="CE27" s="27"/>
-      <c r="CF27" s="27"/>
-      <c r="CG27" s="27"/>
-      <c r="CH27" s="27"/>
-      <c r="CI27" s="27"/>
-      <c r="CJ27" s="28"/>
-    </row>
-    <row r="28" spans="2:88" ht="15.75" thickBot="1">
-      <c r="B28" s="14" t="s">
-        <v>877</v>
-      </c>
-      <c r="AL28" s="25"/>
-      <c r="AM28" s="40" t="s">
-        <v>807</v>
-      </c>
-      <c r="AN28" s="40"/>
-      <c r="AO28" s="40"/>
-      <c r="AP28" s="40" t="s">
-        <v>823</v>
-      </c>
-      <c r="AQ28" s="40"/>
-      <c r="AR28" s="40"/>
-      <c r="AS28" s="40"/>
-      <c r="AT28" s="40"/>
-      <c r="AU28" s="40"/>
-      <c r="AV28" s="40"/>
-      <c r="AW28" s="40"/>
-      <c r="AX28" s="40" t="s">
-        <v>824</v>
-      </c>
-      <c r="AY28" s="40"/>
-      <c r="AZ28" s="40"/>
-      <c r="BA28" s="40"/>
-      <c r="BB28" s="40" t="s">
-        <v>825</v>
-      </c>
-      <c r="BC28" s="40"/>
-      <c r="BD28" s="40"/>
-      <c r="BE28" s="40"/>
-      <c r="BF28" s="28"/>
-      <c r="BH28" s="33" t="s">
-        <v>842</v>
-      </c>
-      <c r="BI28" s="34"/>
-      <c r="BJ28" s="34"/>
-      <c r="BK28" s="34"/>
-      <c r="BL28" s="34"/>
-      <c r="BM28" s="34"/>
-      <c r="BN28" s="34"/>
-      <c r="BO28" s="34"/>
-      <c r="BP28" s="34"/>
-      <c r="BQ28" s="34"/>
-      <c r="BR28" s="34"/>
-      <c r="BS28" s="34"/>
-      <c r="BT28" s="34"/>
-      <c r="BU28" s="34"/>
-      <c r="BV28" s="34"/>
-      <c r="BW28" s="34"/>
-      <c r="BX28" s="34"/>
-      <c r="BY28" s="34"/>
-      <c r="BZ28" s="34"/>
-      <c r="CA28" s="34"/>
-      <c r="CB28" s="34"/>
-      <c r="CC28" s="34"/>
-      <c r="CD28" s="34"/>
-      <c r="CE28" s="34"/>
-      <c r="CF28" s="34"/>
-      <c r="CG28" s="34"/>
-      <c r="CH28" s="34"/>
-      <c r="CI28" s="34"/>
-      <c r="CJ28" s="35"/>
-    </row>
-    <row r="29" spans="2:88" ht="15" thickBot="1">
-      <c r="AL29" s="25"/>
-      <c r="AM29" s="42" t="s">
-        <v>826</v>
-      </c>
-      <c r="AN29" s="42"/>
-      <c r="AO29" s="42"/>
-      <c r="AP29" s="41" t="s">
+    </row>
+    <row r="143" spans="29:29">
+      <c r="AC143" s="13"/>
+    </row>
+    <row r="144" spans="29:29" ht="15">
+      <c r="AC144" s="49" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="145" spans="29:29">
+      <c r="AC145" s="13"/>
+    </row>
+    <row r="146" spans="29:29">
+      <c r="AC146" s="12" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="147" spans="29:29">
+      <c r="AC147" s="12" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="148" spans="29:29">
+      <c r="AC148" s="13"/>
+    </row>
+    <row r="149" spans="29:29" ht="15">
+      <c r="AC149" s="49" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="150" spans="29:29">
+      <c r="AC150" s="13"/>
+    </row>
+    <row r="151" spans="29:29">
+      <c r="AC151" s="12" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="152" spans="29:29">
+      <c r="AC152" s="13"/>
+    </row>
+    <row r="153" spans="29:29" ht="15">
+      <c r="AC153" s="49" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="154" spans="29:29">
+      <c r="AC154" s="13"/>
+    </row>
+    <row r="155" spans="29:29">
+      <c r="AC155" s="12" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="157" spans="29:29" ht="15">
+      <c r="AC157" s="10" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="158" spans="29:29">
+      <c r="AC158" s="13"/>
+    </row>
+    <row r="159" spans="29:29" ht="15">
+      <c r="AC159" s="49" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="160" spans="29:29">
+      <c r="AC160" s="13"/>
+    </row>
+    <row r="161" spans="29:29">
+      <c r="AC161" s="12" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="162" spans="29:29">
+      <c r="AC162" s="13"/>
+    </row>
+    <row r="163" spans="29:29" ht="15">
+      <c r="AC163" s="49" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="167" spans="29:29" ht="15">
+      <c r="AC167" s="10" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="169" spans="29:29" ht="15">
+      <c r="AC169" s="10" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="170" spans="29:29">
+      <c r="AC170" s="13"/>
+    </row>
+    <row r="171" spans="29:29" ht="15">
+      <c r="AC171" s="49" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="172" spans="29:29">
+      <c r="AC172" s="13"/>
+    </row>
+    <row r="173" spans="29:29">
+      <c r="AC173" s="12" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="174" spans="29:29">
+      <c r="AC174" s="12" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="175" spans="29:29">
+      <c r="AC175" s="13"/>
+    </row>
+    <row r="176" spans="29:29" ht="15">
+      <c r="AC176" s="49" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="177" spans="29:29">
+      <c r="AC177" s="13"/>
+    </row>
+    <row r="178" spans="29:29">
+      <c r="AC178" s="12" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="179" spans="29:29">
+      <c r="AC179" s="12" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="180" spans="29:29">
+      <c r="AC180" s="13"/>
+    </row>
+    <row r="181" spans="29:29" ht="15">
+      <c r="AC181" s="49" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="182" spans="29:29">
+      <c r="AC182" s="13"/>
+    </row>
+    <row r="183" spans="29:29">
+      <c r="AC183" s="12" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="185" spans="29:29" ht="15">
+      <c r="AC185" s="10" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="186" spans="29:29">
+      <c r="AC186" s="13"/>
+    </row>
+    <row r="187" spans="29:29" ht="15">
+      <c r="AC187" s="49" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="188" spans="29:29">
+      <c r="AC188" s="13"/>
+    </row>
+    <row r="189" spans="29:29" ht="15">
+      <c r="AC189" s="49" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="190" spans="29:29">
+      <c r="AC190" s="13"/>
+    </row>
+    <row r="191" spans="29:29">
+      <c r="AC191" s="12" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="192" spans="29:29">
+      <c r="AC192" s="12" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="193" spans="29:29">
+      <c r="AC193" s="12" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="194" spans="29:29">
+      <c r="AC194" s="12" t="s">
         <v>901</v>
       </c>
-      <c r="AQ29" s="41"/>
-      <c r="AR29" s="41"/>
-      <c r="AS29" s="41"/>
-      <c r="AT29" s="41"/>
-      <c r="AU29" s="41"/>
-      <c r="AV29" s="41"/>
-      <c r="AW29" s="41"/>
-      <c r="AX29" s="41" t="s">
-        <v>827</v>
-      </c>
-      <c r="AY29" s="41"/>
-      <c r="AZ29" s="41"/>
-      <c r="BA29" s="41"/>
-      <c r="BB29" s="42" t="s">
-        <v>828</v>
-      </c>
-      <c r="BC29" s="42"/>
-      <c r="BD29" s="42"/>
-      <c r="BE29" s="42"/>
-      <c r="BF29" s="28"/>
-    </row>
-    <row r="30" spans="2:88" ht="15">
-      <c r="B30" s="11" t="s">
-        <v>774</v>
-      </c>
-      <c r="AL30" s="25"/>
-      <c r="AM30" s="42" t="s">
-        <v>829</v>
-      </c>
-      <c r="AN30" s="42"/>
-      <c r="AO30" s="42"/>
-      <c r="AP30" s="41" t="s">
-        <v>830</v>
-      </c>
-      <c r="AQ30" s="41"/>
-      <c r="AR30" s="41"/>
-      <c r="AS30" s="41"/>
-      <c r="AT30" s="41"/>
-      <c r="AU30" s="41"/>
-      <c r="AV30" s="41"/>
-      <c r="AW30" s="41"/>
-      <c r="AX30" s="41" t="s">
-        <v>831</v>
-      </c>
-      <c r="AY30" s="41"/>
-      <c r="AZ30" s="41"/>
-      <c r="BA30" s="41"/>
-      <c r="BB30" s="42" t="s">
-        <v>832</v>
-      </c>
-      <c r="BC30" s="42"/>
-      <c r="BD30" s="42"/>
-      <c r="BE30" s="42"/>
-      <c r="BF30" s="28"/>
-      <c r="BH30" s="22" t="s">
-        <v>843</v>
-      </c>
-      <c r="BI30" s="23"/>
-      <c r="BJ30" s="23"/>
-      <c r="BK30" s="23"/>
-      <c r="BL30" s="23"/>
-      <c r="BM30" s="23"/>
-      <c r="BN30" s="23"/>
-      <c r="BO30" s="23"/>
-      <c r="BP30" s="23"/>
-      <c r="BQ30" s="23"/>
-      <c r="BR30" s="23"/>
-      <c r="BS30" s="23"/>
-      <c r="BT30" s="23"/>
-      <c r="BU30" s="23"/>
-      <c r="BV30" s="23"/>
-      <c r="BW30" s="23"/>
-      <c r="BX30" s="23"/>
-      <c r="BY30" s="23"/>
-      <c r="BZ30" s="23"/>
-      <c r="CA30" s="23"/>
-      <c r="CB30" s="23"/>
-      <c r="CC30" s="24"/>
-    </row>
-    <row r="31" spans="2:88" ht="15">
-      <c r="B31" s="10" t="s">
-        <v>775</v>
-      </c>
-      <c r="AL31" s="25"/>
-      <c r="AM31" s="42" t="s">
-        <v>832</v>
-      </c>
-      <c r="AN31" s="42"/>
-      <c r="AO31" s="42"/>
-      <c r="AP31" s="41" t="s">
-        <v>833</v>
-      </c>
-      <c r="AQ31" s="41"/>
-      <c r="AR31" s="41"/>
-      <c r="AS31" s="41"/>
-      <c r="AT31" s="41"/>
-      <c r="AU31" s="41"/>
-      <c r="AV31" s="41"/>
-      <c r="AW31" s="41"/>
-      <c r="AX31" s="41" t="s">
-        <v>831</v>
-      </c>
-      <c r="AY31" s="41"/>
-      <c r="AZ31" s="41"/>
-      <c r="BA31" s="41"/>
-      <c r="BB31" s="42" t="s">
-        <v>834</v>
-      </c>
-      <c r="BC31" s="42"/>
-      <c r="BD31" s="42"/>
-      <c r="BE31" s="42"/>
-      <c r="BF31" s="28"/>
-      <c r="BH31" s="31" t="s">
-        <v>844</v>
-      </c>
-      <c r="BI31" s="27"/>
-      <c r="BJ31" s="27"/>
-      <c r="BK31" s="27"/>
-      <c r="BL31" s="27"/>
-      <c r="BM31" s="27"/>
-      <c r="BN31" s="27"/>
-      <c r="BO31" s="27"/>
-      <c r="BP31" s="27"/>
-      <c r="BQ31" s="27"/>
-      <c r="BR31" s="27"/>
-      <c r="BS31" s="27"/>
-      <c r="BT31" s="27"/>
-      <c r="BU31" s="27"/>
-      <c r="BV31" s="27"/>
-      <c r="BW31" s="27"/>
-      <c r="BX31" s="27"/>
-      <c r="BY31" s="27"/>
-      <c r="BZ31" s="27"/>
-      <c r="CA31" s="27"/>
-      <c r="CB31" s="27"/>
-      <c r="CC31" s="28"/>
-    </row>
-    <row r="32" spans="2:88" ht="15">
-      <c r="B32" s="10" t="s">
-        <v>879</v>
-      </c>
-      <c r="AL32" s="31" t="s">
-        <v>835</v>
-      </c>
-      <c r="AM32" s="27"/>
-      <c r="AN32" s="27"/>
-      <c r="AO32" s="27"/>
-      <c r="AP32" s="27"/>
-      <c r="AQ32" s="27"/>
-      <c r="AR32" s="27"/>
-      <c r="AS32" s="27"/>
-      <c r="AT32" s="27"/>
-      <c r="AU32" s="27"/>
-      <c r="AV32" s="27"/>
-      <c r="AW32" s="27"/>
-      <c r="AX32" s="27"/>
-      <c r="AY32" s="27"/>
-      <c r="AZ32" s="27"/>
-      <c r="BA32" s="27"/>
-      <c r="BB32" s="27"/>
-      <c r="BC32" s="27"/>
-      <c r="BD32" s="27"/>
-      <c r="BE32" s="27"/>
-      <c r="BF32" s="28"/>
-      <c r="BH32" s="38" t="s">
-        <v>845</v>
-      </c>
-      <c r="BI32" s="27"/>
-      <c r="BJ32" s="27"/>
-      <c r="BK32" s="27"/>
-      <c r="BL32" s="27"/>
-      <c r="BM32" s="27"/>
-      <c r="BN32" s="27"/>
-      <c r="BO32" s="27"/>
-      <c r="BP32" s="27"/>
-      <c r="BQ32" s="27"/>
-      <c r="BR32" s="27"/>
-      <c r="BS32" s="27"/>
-      <c r="BT32" s="27"/>
-      <c r="BU32" s="27"/>
-      <c r="BV32" s="27"/>
-      <c r="BW32" s="27"/>
-      <c r="BX32" s="27"/>
-      <c r="BY32" s="27"/>
-      <c r="BZ32" s="27"/>
-      <c r="CA32" s="27"/>
-      <c r="CB32" s="27"/>
-      <c r="CC32" s="28"/>
-    </row>
-    <row r="33" spans="2:81" ht="15">
-      <c r="C33" s="49" t="s">
-        <v>913</v>
-      </c>
-      <c r="AL33" s="32" t="s">
-        <v>836</v>
-      </c>
-      <c r="AM33" s="27"/>
-      <c r="AN33" s="27"/>
-      <c r="AO33" s="27"/>
-      <c r="AP33" s="27"/>
-      <c r="AQ33" s="27"/>
-      <c r="AR33" s="27"/>
-      <c r="AS33" s="27"/>
-      <c r="AT33" s="27"/>
-      <c r="AU33" s="27"/>
-      <c r="AV33" s="27"/>
-      <c r="AW33" s="27"/>
-      <c r="AX33" s="27"/>
-      <c r="AY33" s="27"/>
-      <c r="AZ33" s="27"/>
-      <c r="BA33" s="27"/>
-      <c r="BB33" s="27"/>
-      <c r="BC33" s="27"/>
-      <c r="BD33" s="27"/>
-      <c r="BE33" s="27"/>
-      <c r="BF33" s="28"/>
-      <c r="BH33" s="45" t="s">
-        <v>907</v>
-      </c>
-      <c r="BI33" s="27"/>
-      <c r="BJ33" s="27"/>
-      <c r="BK33" s="27"/>
-      <c r="BL33" s="27"/>
-      <c r="BM33" s="27"/>
-      <c r="BN33" s="27"/>
-      <c r="BO33" s="27"/>
-      <c r="BP33" s="27"/>
-      <c r="BQ33" s="27"/>
-      <c r="BR33" s="27"/>
-      <c r="BS33" s="27"/>
-      <c r="BT33" s="27"/>
-      <c r="BU33" s="27"/>
-      <c r="BV33" s="27"/>
-      <c r="BW33" s="27"/>
-      <c r="BX33" s="27"/>
-      <c r="BY33" s="27"/>
-      <c r="BZ33" s="27"/>
-      <c r="CA33" s="27"/>
-      <c r="CB33" s="27"/>
-      <c r="CC33" s="28"/>
-    </row>
-    <row r="34" spans="2:81" ht="15" thickBot="1">
-      <c r="AL34" s="44" t="s">
-        <v>837</v>
-      </c>
-      <c r="AM34" s="34"/>
-      <c r="AN34" s="34"/>
-      <c r="AO34" s="34"/>
-      <c r="AP34" s="34"/>
-      <c r="AQ34" s="34"/>
-      <c r="AR34" s="34"/>
-      <c r="AS34" s="34"/>
-      <c r="AT34" s="34"/>
-      <c r="AU34" s="34"/>
-      <c r="AV34" s="34"/>
-      <c r="AW34" s="34"/>
-      <c r="AX34" s="34"/>
-      <c r="AY34" s="34"/>
-      <c r="AZ34" s="34"/>
-      <c r="BA34" s="34"/>
-      <c r="BB34" s="34"/>
-      <c r="BC34" s="34"/>
-      <c r="BD34" s="34"/>
-      <c r="BE34" s="34"/>
-      <c r="BF34" s="35"/>
-      <c r="BH34" s="45" t="s">
-        <v>908</v>
-      </c>
-      <c r="BI34" s="27"/>
-      <c r="BJ34" s="27"/>
-      <c r="BK34" s="27"/>
-      <c r="BL34" s="27"/>
-      <c r="BM34" s="27"/>
-      <c r="BN34" s="27"/>
-      <c r="BO34" s="27"/>
-      <c r="BP34" s="27"/>
-      <c r="BQ34" s="27"/>
-      <c r="BR34" s="27"/>
-      <c r="BS34" s="27"/>
-      <c r="BT34" s="27"/>
-      <c r="BU34" s="27"/>
-      <c r="BV34" s="27"/>
-      <c r="BW34" s="27"/>
-      <c r="BX34" s="27"/>
-      <c r="BY34" s="27"/>
-      <c r="BZ34" s="27"/>
-      <c r="CA34" s="27"/>
-      <c r="CB34" s="27"/>
-      <c r="CC34" s="28"/>
-    </row>
-    <row r="35" spans="2:81" ht="15">
-      <c r="BH35" s="31" t="s">
-        <v>846</v>
-      </c>
-      <c r="BI35" s="27"/>
-      <c r="BJ35" s="27"/>
-      <c r="BK35" s="27"/>
-      <c r="BL35" s="27"/>
-      <c r="BM35" s="27"/>
-      <c r="BN35" s="27"/>
-      <c r="BO35" s="27"/>
-      <c r="BP35" s="27"/>
-      <c r="BQ35" s="27"/>
-      <c r="BR35" s="27"/>
-      <c r="BS35" s="27"/>
-      <c r="BT35" s="27"/>
-      <c r="BU35" s="27"/>
-      <c r="BV35" s="27"/>
-      <c r="BW35" s="27"/>
-      <c r="BX35" s="27"/>
-      <c r="BY35" s="27"/>
-      <c r="BZ35" s="27"/>
-      <c r="CA35" s="27"/>
-      <c r="CB35" s="27"/>
-      <c r="CC35" s="28"/>
-    </row>
-    <row r="36" spans="2:81" ht="15">
-      <c r="B36" s="11" t="s">
-        <v>776</v>
-      </c>
-      <c r="BH36" s="32" t="s">
-        <v>847</v>
-      </c>
-      <c r="BI36" s="27"/>
-      <c r="BJ36" s="27"/>
-      <c r="BK36" s="27"/>
-      <c r="BL36" s="27"/>
-      <c r="BM36" s="27"/>
-      <c r="BN36" s="27"/>
-      <c r="BO36" s="27"/>
-      <c r="BP36" s="27"/>
-      <c r="BQ36" s="27"/>
-      <c r="BR36" s="27"/>
-      <c r="BS36" s="27"/>
-      <c r="BT36" s="27"/>
-      <c r="BU36" s="27"/>
-      <c r="BV36" s="27"/>
-      <c r="BW36" s="27"/>
-      <c r="BX36" s="27"/>
-      <c r="BY36" s="27"/>
-      <c r="BZ36" s="27"/>
-      <c r="CA36" s="27"/>
-      <c r="CB36" s="27"/>
-      <c r="CC36" s="28"/>
-    </row>
-    <row r="37" spans="2:81" ht="15">
-      <c r="BH37" s="31" t="s">
-        <v>848</v>
-      </c>
-      <c r="BI37" s="27"/>
-      <c r="BJ37" s="27"/>
-      <c r="BK37" s="27"/>
-      <c r="BL37" s="27"/>
-      <c r="BM37" s="27"/>
-      <c r="BN37" s="27"/>
-      <c r="BO37" s="27"/>
-      <c r="BP37" s="27"/>
-      <c r="BQ37" s="27"/>
-      <c r="BR37" s="27"/>
-      <c r="BS37" s="27"/>
-      <c r="BT37" s="27"/>
-      <c r="BU37" s="27"/>
-      <c r="BV37" s="27"/>
-      <c r="BW37" s="27"/>
-      <c r="BX37" s="27"/>
-      <c r="BY37" s="27"/>
-      <c r="BZ37" s="27"/>
-      <c r="CA37" s="27"/>
-      <c r="CB37" s="27"/>
-      <c r="CC37" s="28"/>
-    </row>
-    <row r="38" spans="2:81" ht="15">
-      <c r="B38" s="11" t="s">
-        <v>881</v>
-      </c>
-      <c r="BH38" s="48" t="s">
-        <v>849</v>
-      </c>
-      <c r="BI38" s="47"/>
-      <c r="BJ38" s="47"/>
-      <c r="BK38" s="47"/>
-      <c r="BL38" s="47"/>
-      <c r="BM38" s="47"/>
-      <c r="BN38" s="47"/>
-      <c r="BO38" s="47"/>
-      <c r="BP38" s="47"/>
-      <c r="BQ38" s="47"/>
-      <c r="BR38" s="47"/>
-      <c r="BS38" s="47"/>
-      <c r="BT38" s="47"/>
-      <c r="BU38" s="47"/>
-      <c r="BV38" s="27"/>
-      <c r="BW38" s="27"/>
-      <c r="BX38" s="27"/>
-      <c r="BY38" s="27"/>
-      <c r="BZ38" s="27"/>
-      <c r="CA38" s="27"/>
-      <c r="CB38" s="27"/>
-      <c r="CC38" s="28"/>
-    </row>
-    <row r="39" spans="2:81">
-      <c r="B39" s="14"/>
-      <c r="BH39" s="46" t="s">
-        <v>850</v>
-      </c>
-      <c r="BI39" s="47"/>
-      <c r="BJ39" s="47"/>
-      <c r="BK39" s="47"/>
-      <c r="BL39" s="47"/>
-      <c r="BM39" s="47"/>
-      <c r="BN39" s="47"/>
-      <c r="BO39" s="47"/>
-      <c r="BP39" s="47"/>
-      <c r="BQ39" s="47"/>
-      <c r="BR39" s="47"/>
-      <c r="BS39" s="47"/>
-      <c r="BT39" s="47"/>
-      <c r="BU39" s="47"/>
-      <c r="BV39" s="27"/>
-      <c r="BW39" s="27"/>
-      <c r="BX39" s="27"/>
-      <c r="BY39" s="27"/>
-      <c r="BZ39" s="27"/>
-      <c r="CA39" s="27"/>
-      <c r="CB39" s="27"/>
-      <c r="CC39" s="28"/>
-    </row>
-    <row r="40" spans="2:81">
-      <c r="B40" s="13" t="s">
-        <v>882</v>
-      </c>
-      <c r="BH40" s="32" t="s">
-        <v>851</v>
-      </c>
-      <c r="BI40" s="27"/>
-      <c r="BJ40" s="27"/>
-      <c r="BK40" s="27"/>
-      <c r="BL40" s="27"/>
-      <c r="BM40" s="27"/>
-      <c r="BN40" s="27"/>
-      <c r="BO40" s="27"/>
-      <c r="BP40" s="27"/>
-      <c r="BQ40" s="27"/>
-      <c r="BR40" s="27"/>
-      <c r="BS40" s="27"/>
-      <c r="BT40" s="27"/>
-      <c r="BU40" s="27"/>
-      <c r="BV40" s="27"/>
-      <c r="BW40" s="27"/>
-      <c r="BX40" s="27"/>
-      <c r="BY40" s="27"/>
-      <c r="BZ40" s="27"/>
-      <c r="CA40" s="27"/>
-      <c r="CB40" s="27"/>
-      <c r="CC40" s="28"/>
-    </row>
-    <row r="41" spans="2:81">
-      <c r="B41" s="14"/>
-      <c r="BH41" s="32" t="s">
-        <v>852</v>
-      </c>
-      <c r="BI41" s="27"/>
-      <c r="BJ41" s="27"/>
-      <c r="BK41" s="27"/>
-      <c r="BL41" s="27"/>
-      <c r="BM41" s="27"/>
-      <c r="BN41" s="27"/>
-      <c r="BO41" s="27"/>
-      <c r="BP41" s="27"/>
-      <c r="BQ41" s="27"/>
-      <c r="BR41" s="27"/>
-      <c r="BS41" s="27"/>
-      <c r="BT41" s="27"/>
-      <c r="BU41" s="27"/>
-      <c r="BV41" s="27"/>
-      <c r="BW41" s="27"/>
-      <c r="BX41" s="27"/>
-      <c r="BY41" s="27"/>
-      <c r="BZ41" s="27"/>
-      <c r="CA41" s="27"/>
-      <c r="CB41" s="27"/>
-      <c r="CC41" s="28"/>
-    </row>
-    <row r="42" spans="2:81">
-      <c r="B42" s="13" t="s">
-        <v>883</v>
-      </c>
-      <c r="BH42" s="32" t="s">
-        <v>853</v>
-      </c>
-      <c r="BI42" s="27"/>
-      <c r="BJ42" s="27"/>
-      <c r="BK42" s="27"/>
-      <c r="BL42" s="27"/>
-      <c r="BM42" s="27"/>
-      <c r="BN42" s="27"/>
-      <c r="BO42" s="27"/>
-      <c r="BP42" s="27"/>
-      <c r="BQ42" s="27"/>
-      <c r="BR42" s="27"/>
-      <c r="BS42" s="27"/>
-      <c r="BT42" s="27"/>
-      <c r="BU42" s="27"/>
-      <c r="BV42" s="27"/>
-      <c r="BW42" s="27"/>
-      <c r="BX42" s="27"/>
-      <c r="BY42" s="27"/>
-      <c r="BZ42" s="27"/>
-      <c r="CA42" s="27"/>
-      <c r="CB42" s="27"/>
-      <c r="CC42" s="28"/>
-    </row>
-    <row r="43" spans="2:81">
-      <c r="BH43" s="32" t="s">
-        <v>854</v>
-      </c>
-      <c r="BI43" s="27"/>
-      <c r="BJ43" s="27"/>
-      <c r="BK43" s="27"/>
-      <c r="BL43" s="27"/>
-      <c r="BM43" s="27"/>
-      <c r="BN43" s="27"/>
-      <c r="BO43" s="27"/>
-      <c r="BP43" s="27"/>
-      <c r="BQ43" s="27"/>
-      <c r="BR43" s="27"/>
-      <c r="BS43" s="27"/>
-      <c r="BT43" s="27"/>
-      <c r="BU43" s="27"/>
-      <c r="BV43" s="27"/>
-      <c r="BW43" s="27"/>
-      <c r="BX43" s="27"/>
-      <c r="BY43" s="27"/>
-      <c r="BZ43" s="27"/>
-      <c r="CA43" s="27"/>
-      <c r="CB43" s="27"/>
-      <c r="CC43" s="28"/>
-    </row>
-    <row r="44" spans="2:81" ht="15">
-      <c r="B44" s="11" t="s">
-        <v>777</v>
-      </c>
-      <c r="BH44" s="32" t="s">
-        <v>855</v>
-      </c>
-      <c r="BI44" s="27"/>
-      <c r="BJ44" s="27"/>
-      <c r="BK44" s="27"/>
-      <c r="BL44" s="27"/>
-      <c r="BM44" s="27"/>
-      <c r="BN44" s="27"/>
-      <c r="BO44" s="27"/>
-      <c r="BP44" s="27"/>
-      <c r="BQ44" s="27"/>
-      <c r="BR44" s="27"/>
-      <c r="BS44" s="27"/>
-      <c r="BT44" s="27"/>
-      <c r="BU44" s="27"/>
-      <c r="BV44" s="27"/>
-      <c r="BW44" s="27"/>
-      <c r="BX44" s="27"/>
-      <c r="BY44" s="27"/>
-      <c r="BZ44" s="27"/>
-      <c r="CA44" s="27"/>
-      <c r="CB44" s="27"/>
-      <c r="CC44" s="28"/>
-    </row>
-    <row r="45" spans="2:81" ht="15" thickBot="1">
-      <c r="B45" s="14"/>
-      <c r="BH45" s="33" t="s">
-        <v>909</v>
-      </c>
-      <c r="BI45" s="34"/>
-      <c r="BJ45" s="34"/>
-      <c r="BK45" s="34"/>
-      <c r="BL45" s="34"/>
-      <c r="BM45" s="34"/>
-      <c r="BN45" s="34"/>
-      <c r="BO45" s="34"/>
-      <c r="BP45" s="34"/>
-      <c r="BQ45" s="34"/>
-      <c r="BR45" s="34"/>
-      <c r="BS45" s="34"/>
-      <c r="BT45" s="34"/>
-      <c r="BU45" s="34"/>
-      <c r="BV45" s="34"/>
-      <c r="BW45" s="34"/>
-      <c r="BX45" s="34"/>
-      <c r="BY45" s="34"/>
-      <c r="BZ45" s="34"/>
-      <c r="CA45" s="34"/>
-      <c r="CB45" s="34"/>
-      <c r="CC45" s="35"/>
-    </row>
-    <row r="46" spans="2:81">
-      <c r="B46" s="14" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="48" spans="2:81">
-      <c r="B48" s="16" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="49" spans="2:38">
-      <c r="B49" s="14"/>
-    </row>
-    <row r="50" spans="2:38">
-      <c r="B50" s="14" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="51" spans="2:38" ht="16.5" customHeight="1"/>
-    <row r="52" spans="2:38" ht="14.25" customHeight="1">
-      <c r="B52" s="11" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="53" spans="2:38" ht="15.75" customHeight="1">
-      <c r="B53" s="14"/>
-    </row>
-    <row r="54" spans="2:38" ht="16.5" customHeight="1">
-      <c r="B54" s="13" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="55" spans="2:38" ht="16.5" customHeight="1">
-      <c r="B55" s="14"/>
-    </row>
-    <row r="56" spans="2:38">
-      <c r="B56" s="13" t="s">
-        <v>888</v>
-      </c>
-      <c r="AL56" s="14"/>
-    </row>
-    <row r="57" spans="2:38">
-      <c r="B57" s="14"/>
-    </row>
-    <row r="58" spans="2:38">
-      <c r="B58" s="13" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="60" spans="2:38" ht="15">
-      <c r="B60" s="11" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="61" spans="2:38">
-      <c r="B61" s="14"/>
-    </row>
-    <row r="62" spans="2:38">
-      <c r="B62" s="13" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="63" spans="2:38">
-      <c r="B63" s="14"/>
-    </row>
-    <row r="64" spans="2:38">
-      <c r="B64" s="13" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="65" spans="2:38">
-      <c r="B65" s="14"/>
-    </row>
-    <row r="66" spans="2:38">
-      <c r="B66" s="13" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="68" spans="2:38" ht="15">
-      <c r="B68" s="11" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="69" spans="2:38">
-      <c r="B69" s="14"/>
-    </row>
-    <row r="70" spans="2:38">
-      <c r="B70" s="14" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="72" spans="2:38">
-      <c r="B72" s="16" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="73" spans="2:38">
-      <c r="B73" s="14"/>
-    </row>
-    <row r="74" spans="2:38">
-      <c r="B74" s="14" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="76" spans="2:38">
-      <c r="AL76" s="14"/>
-    </row>
-    <row r="78" spans="2:38" ht="15">
-      <c r="B78" s="11" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="80" spans="2:38" ht="15">
-      <c r="B80" s="11" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2">
-      <c r="B81" s="14"/>
-    </row>
-    <row r="82" spans="2:2">
-      <c r="B82" s="14" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2">
-      <c r="B83" s="14"/>
-    </row>
-    <row r="84" spans="2:2">
-      <c r="B84" s="14" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2" ht="18.75" customHeight="1"/>
-    <row r="86" spans="2:2" ht="20.25" customHeight="1">
-      <c r="B86" s="11" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2" ht="24.75" customHeight="1">
-      <c r="B87" s="14"/>
-    </row>
-    <row r="88" spans="2:2" ht="21.75" customHeight="1">
-      <c r="B88" s="14" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2">
-      <c r="B90" s="16" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="92" spans="2:2" ht="15">
-      <c r="B92" s="11" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="93" spans="2:2">
-      <c r="B93" s="14"/>
-    </row>
-    <row r="94" spans="2:2">
-      <c r="B94" s="14" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2">
-      <c r="B95" s="14"/>
-    </row>
-    <row r="96" spans="2:2">
-      <c r="B96" s="14" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="98" spans="2:38">
-      <c r="B98" s="16" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="100" spans="2:38" ht="15">
-      <c r="B100" s="11" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="101" spans="2:38">
-      <c r="B101" s="14"/>
-    </row>
-    <row r="102" spans="2:38">
-      <c r="B102" s="14" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="103" spans="2:38">
-      <c r="B103" s="14"/>
-    </row>
-    <row r="104" spans="2:38">
-      <c r="B104" s="14" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="106" spans="2:38">
-      <c r="B106" s="16" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="107" spans="2:38">
-      <c r="B107" s="14"/>
-    </row>
-    <row r="108" spans="2:38">
-      <c r="B108" s="14" t="s">
-        <v>796</v>
-      </c>
-      <c r="AL108" s="14"/>
-    </row>
-    <row r="112" spans="2:38">
-      <c r="B112" s="12" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="132" spans="38:40" ht="15">
-      <c r="AL132" s="11"/>
-    </row>
-    <row r="134" spans="38:40" ht="15">
-      <c r="AL134" s="9"/>
-      <c r="AM134" s="9"/>
-      <c r="AN134" s="9"/>
-    </row>
-    <row r="135" spans="38:40">
-      <c r="AL135" s="18"/>
-      <c r="AM135" s="17"/>
-      <c r="AN135" s="18"/>
-    </row>
-    <row r="136" spans="38:40">
-      <c r="AL136" s="18"/>
-      <c r="AM136" s="18"/>
-      <c r="AN136" s="18"/>
-    </row>
-    <row r="137" spans="38:40">
-      <c r="AL137" s="18"/>
-      <c r="AM137" s="18"/>
-      <c r="AN137" s="18"/>
-    </row>
-    <row r="138" spans="38:40">
-      <c r="AL138" s="17"/>
-      <c r="AM138" s="18"/>
-      <c r="AN138" s="18"/>
-    </row>
-    <row r="139" spans="38:40">
-      <c r="AL139" s="18"/>
-      <c r="AM139" s="17"/>
-      <c r="AN139" s="18"/>
+    </row>
+    <row r="195" spans="29:29">
+      <c r="AC195" s="12" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="199" spans="29:29" ht="15">
+      <c r="AC199" s="10" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="200" spans="29:29">
+      <c r="AC200" s="13"/>
+    </row>
+    <row r="201" spans="29:29" ht="15">
+      <c r="AC201" s="49" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="202" spans="29:29">
+      <c r="AC202" s="13"/>
+    </row>
+    <row r="203" spans="29:29">
+      <c r="AC203" s="12" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="204" spans="29:29">
+      <c r="AC204" s="12" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="205" spans="29:29">
+      <c r="AC205" s="13"/>
+    </row>
+    <row r="206" spans="29:29" ht="15">
+      <c r="AC206" s="49" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="207" spans="29:29">
+      <c r="AC207" s="13"/>
+    </row>
+    <row r="208" spans="29:29">
+      <c r="AC208" s="12" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="209" spans="29:29">
+      <c r="AC209" s="12" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="210" spans="29:29">
+      <c r="AC210" s="13"/>
+    </row>
+    <row r="211" spans="29:29" ht="15">
+      <c r="AC211" s="49" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="212" spans="29:29">
+      <c r="AC212" s="13"/>
+    </row>
+    <row r="213" spans="29:29">
+      <c r="AC213" s="12" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="214" spans="29:29">
+      <c r="AC214" s="13"/>
+    </row>
+    <row r="215" spans="29:29" ht="15">
+      <c r="AC215" s="49" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="216" spans="29:29">
+      <c r="AC216" s="13"/>
+    </row>
+    <row r="217" spans="29:29">
+      <c r="AC217" s="12" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="218" spans="29:29">
+      <c r="AC218" s="12" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="219" spans="29:29">
+      <c r="AC219" s="13"/>
+    </row>
+    <row r="220" spans="29:29" ht="15">
+      <c r="AC220" s="49" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="221" spans="29:29">
+      <c r="AC221" s="13"/>
+    </row>
+    <row r="222" spans="29:29">
+      <c r="AC222" s="12" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="223" spans="29:29">
+      <c r="AC223" s="12" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="224" spans="29:29">
+      <c r="AC224" s="12" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="225" spans="29:29">
+      <c r="AC225" s="12" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="226" spans="29:29">
+      <c r="AC226" s="12" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="227" spans="29:29">
+      <c r="AC227" s="13"/>
+    </row>
+    <row r="228" spans="29:29" ht="15">
+      <c r="AC228" s="49" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="229" spans="29:29">
+      <c r="AC229" s="13"/>
+    </row>
+    <row r="230" spans="29:29">
+      <c r="AC230" s="12" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="231" spans="29:29">
+      <c r="AC231" s="12" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="232" spans="29:29">
+      <c r="AC232" s="12" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="236" spans="29:29">
+      <c r="AC236" s="11" t="s">
+        <v>957</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="AX28:BA28"/>
-    <mergeCell ref="AX29:BA29"/>
-    <mergeCell ref="AX30:BA30"/>
-    <mergeCell ref="AX31:BA31"/>
-    <mergeCell ref="BB28:BE28"/>
-    <mergeCell ref="BB29:BE29"/>
-    <mergeCell ref="BB30:BE30"/>
-    <mergeCell ref="BB31:BE31"/>
-    <mergeCell ref="AM28:AO28"/>
-    <mergeCell ref="AM29:AO29"/>
-    <mergeCell ref="AM30:AO30"/>
-    <mergeCell ref="AM31:AO31"/>
-    <mergeCell ref="AP28:AW28"/>
-    <mergeCell ref="AP29:AW29"/>
-    <mergeCell ref="AP30:AW30"/>
-    <mergeCell ref="AP31:AW31"/>
     <mergeCell ref="BP13:BV13"/>
     <mergeCell ref="BP14:BV14"/>
     <mergeCell ref="BP15:BV15"/>
@@ -17937,6 +20123,22 @@
     <mergeCell ref="BJ14:BO14"/>
     <mergeCell ref="BJ15:BO15"/>
     <mergeCell ref="BJ16:BO16"/>
+    <mergeCell ref="AM28:AO28"/>
+    <mergeCell ref="AM29:AO29"/>
+    <mergeCell ref="AM30:AO30"/>
+    <mergeCell ref="AM31:AO31"/>
+    <mergeCell ref="AP28:AW28"/>
+    <mergeCell ref="AP29:AW29"/>
+    <mergeCell ref="AP30:AW30"/>
+    <mergeCell ref="AP31:AW31"/>
+    <mergeCell ref="AX28:BA28"/>
+    <mergeCell ref="AX29:BA29"/>
+    <mergeCell ref="AX30:BA30"/>
+    <mergeCell ref="AX31:BA31"/>
+    <mergeCell ref="BB28:BE28"/>
+    <mergeCell ref="BB29:BE29"/>
+    <mergeCell ref="BB30:BE30"/>
+    <mergeCell ref="BB31:BE31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Kỹ Thuật lập trình/C/C.xlsx
+++ b/Kỹ Thuật lập trình/C/C.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Linux\Kỹ Thuật lập trình\C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7ADE7F7-E5CA-4FF1-A454-8DAC3C949E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD52719F-6779-408F-9892-C63E7C3B7817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D515FE12-8DDF-4954-9F3B-744B83BED5E7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D515FE12-8DDF-4954-9F3B-744B83BED5E7}"/>
   </bookViews>
   <sheets>
     <sheet name="CheckList C" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="1419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="1419">
   <si>
     <t>🔧 TOOLS &amp; ENVIRONMENT</t>
   </si>
@@ -12201,9 +12201,6 @@
     <t>#include &lt;threads.h&gt;</t>
   </si>
   <si>
-    <t>_Thread_local int tls_counter = 0;</t>
-  </si>
-  <si>
     <t>int thread_function(void* arg) {</t>
   </si>
   <si>
@@ -12441,9 +12438,6 @@
     <t>void demonstrate_shadowing() {</t>
   </si>
   <si>
-    <t xml:space="preserve">    int global_var = 200;  // Shadows global variable</t>
-  </si>
-  <si>
     <t xml:space="preserve">    printf("Local: %d\n", global_var);    // 200</t>
   </si>
   <si>
@@ -12663,12 +12657,6 @@
     <t>Rodata Segment (Read-only Data):</t>
   </si>
   <si>
-    <t>const int readonly_global = 42;        // Rodata segment</t>
-  </si>
-  <si>
-    <t>static const char* string_literals = "Hello";  // Rodata</t>
-  </si>
-  <si>
     <t>void rodata_example() {</t>
   </si>
   <si>
@@ -12921,9 +12909,6 @@
     <t>Careful với global variables</t>
   </si>
   <si>
-    <t>Những kiến thức này tạo nền tảng vững chắc cho lập trình C chuyên nghiệp và hiệu quả.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Từ khóa </t>
     </r>
@@ -13029,12 +13014,86 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
+      <t>static</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cho internal linkage</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tránh </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>register</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong modern C</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Biến </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="8" tint="0.39997558519241921"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>static</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="8" tint="0.39997558519241921"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> được khởi tạo đúng 1 lần duy nhất, và giá trị khởi tạo đó phải được xác định trước khi chương trình chạy.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sử dụng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
       <t>_Thread_local</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="163"/>
@@ -13045,7 +13104,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
       <t>thread_local</t>
@@ -13053,7 +13112,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
         <family val="2"/>
         <charset val="163"/>
@@ -13064,50 +13123,79 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Sử dụng </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>static</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> cho internal linkage</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Tránh </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>register</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> trong modern C</t>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="163"/>
+      </rPr>
+      <t>_Thread_local</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> int tls_counter = 0;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    int global_var = 200;  // </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Shadows global variable</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="163"/>
+      </rPr>
+      <t>const</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> int readonly_global = 42;        // Rodata segment</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">static </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+        <charset val="163"/>
+      </rPr>
+      <t>const</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t xml:space="preserve"> char* string_literals = "Hello";  // Rodata</t>
     </r>
   </si>
 </sst>
@@ -13115,7 +13203,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13250,14 +13338,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="163"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
@@ -13272,8 +13352,49 @@
       <color rgb="FFFF0000"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="8" tint="0.39997558519241921"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="8" tint="0.39997558519241921"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="163"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -13289,6 +13410,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -13437,7 +13576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -13585,15 +13724,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -13655,6 +13785,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13670,6 +13841,148 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>75</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>84</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Speech Bubble: Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC843C6F-D0EA-FE40-08FC-037976B62D86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17287875" y="4038600"/>
+          <a:ext cx="2076450" cy="1095375"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -90099"/>
+            <a:gd name="adj2" fmla="val 42114"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Trong </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="1"/>
+            <a:t>file-scope</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t> hoặc </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="1"/>
+            <a:t>function-scope</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>, một biến static phải được </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="1"/>
+            <a:t>khởi tạo bằng một constant expression</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>"Constant expression" nghĩa là một biểu thức có thể tính được tại </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="1"/>
+            <a:t>compile-time</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>Nhưng get_value() là một </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="1"/>
+            <a:t>function call</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>, chỉ có thể thực hiện tại </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="1"/>
+            <a:t>runtime</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>, không phải hằng số → </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800" b="1"/>
+            <a:t>không hợp lệ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="vi-VN" sz="800"/>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="vi-VN" sz="800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19398,29 +19711,29 @@
       <c r="BB13" s="23"/>
       <c r="BC13" s="24"/>
       <c r="BE13" s="21"/>
-      <c r="BF13" s="61" t="s">
+      <c r="BF13" s="84" t="s">
         <v>806</v>
       </c>
-      <c r="BG13" s="61"/>
-      <c r="BH13" s="61"/>
-      <c r="BI13" s="61"/>
-      <c r="BJ13" s="61" t="s">
+      <c r="BG13" s="84"/>
+      <c r="BH13" s="84"/>
+      <c r="BI13" s="84"/>
+      <c r="BJ13" s="84" t="s">
         <v>807</v>
       </c>
-      <c r="BK13" s="61"/>
-      <c r="BL13" s="61"/>
-      <c r="BM13" s="61"/>
-      <c r="BN13" s="61"/>
-      <c r="BO13" s="61"/>
-      <c r="BP13" s="61" t="s">
+      <c r="BK13" s="84"/>
+      <c r="BL13" s="84"/>
+      <c r="BM13" s="84"/>
+      <c r="BN13" s="84"/>
+      <c r="BO13" s="84"/>
+      <c r="BP13" s="84" t="s">
         <v>808</v>
       </c>
-      <c r="BQ13" s="61"/>
-      <c r="BR13" s="61"/>
-      <c r="BS13" s="61"/>
-      <c r="BT13" s="61"/>
-      <c r="BU13" s="61"/>
-      <c r="BV13" s="61"/>
+      <c r="BQ13" s="84"/>
+      <c r="BR13" s="84"/>
+      <c r="BS13" s="84"/>
+      <c r="BT13" s="84"/>
+      <c r="BU13" s="84"/>
+      <c r="BV13" s="84"/>
       <c r="BW13" s="24"/>
     </row>
     <row r="14" spans="2:75" ht="15.75" thickBot="1">
@@ -19445,29 +19758,29 @@
       <c r="BB14" s="30"/>
       <c r="BC14" s="31"/>
       <c r="BE14" s="21"/>
-      <c r="BF14" s="63" t="s">
+      <c r="BF14" s="86" t="s">
         <v>809</v>
       </c>
-      <c r="BG14" s="63"/>
-      <c r="BH14" s="63"/>
-      <c r="BI14" s="63"/>
-      <c r="BJ14" s="62" t="s">
+      <c r="BG14" s="86"/>
+      <c r="BH14" s="86"/>
+      <c r="BI14" s="86"/>
+      <c r="BJ14" s="85" t="s">
         <v>810</v>
       </c>
-      <c r="BK14" s="62"/>
-      <c r="BL14" s="62"/>
-      <c r="BM14" s="62"/>
-      <c r="BN14" s="62"/>
-      <c r="BO14" s="62"/>
-      <c r="BP14" s="62" t="s">
+      <c r="BK14" s="85"/>
+      <c r="BL14" s="85"/>
+      <c r="BM14" s="85"/>
+      <c r="BN14" s="85"/>
+      <c r="BO14" s="85"/>
+      <c r="BP14" s="85" t="s">
         <v>810</v>
       </c>
-      <c r="BQ14" s="62"/>
-      <c r="BR14" s="62"/>
-      <c r="BS14" s="62"/>
-      <c r="BT14" s="62"/>
-      <c r="BU14" s="62"/>
-      <c r="BV14" s="62"/>
+      <c r="BQ14" s="85"/>
+      <c r="BR14" s="85"/>
+      <c r="BS14" s="85"/>
+      <c r="BT14" s="85"/>
+      <c r="BU14" s="85"/>
+      <c r="BV14" s="85"/>
       <c r="BW14" s="24"/>
     </row>
     <row r="15" spans="2:75" ht="15.75" thickBot="1">
@@ -19476,29 +19789,29 @@
       </c>
       <c r="AL15" s="13"/>
       <c r="BE15" s="21"/>
-      <c r="BF15" s="63" t="s">
+      <c r="BF15" s="86" t="s">
         <v>811</v>
       </c>
-      <c r="BG15" s="63"/>
-      <c r="BH15" s="63"/>
-      <c r="BI15" s="63"/>
-      <c r="BJ15" s="62" t="s">
+      <c r="BG15" s="86"/>
+      <c r="BH15" s="86"/>
+      <c r="BI15" s="86"/>
+      <c r="BJ15" s="85" t="s">
         <v>812</v>
       </c>
-      <c r="BK15" s="62"/>
-      <c r="BL15" s="62"/>
-      <c r="BM15" s="62"/>
-      <c r="BN15" s="62"/>
-      <c r="BO15" s="62"/>
-      <c r="BP15" s="62" t="s">
+      <c r="BK15" s="85"/>
+      <c r="BL15" s="85"/>
+      <c r="BM15" s="85"/>
+      <c r="BN15" s="85"/>
+      <c r="BO15" s="85"/>
+      <c r="BP15" s="85" t="s">
         <v>813</v>
       </c>
-      <c r="BQ15" s="62"/>
-      <c r="BR15" s="62"/>
-      <c r="BS15" s="62"/>
-      <c r="BT15" s="62"/>
-      <c r="BU15" s="62"/>
-      <c r="BV15" s="62"/>
+      <c r="BQ15" s="85"/>
+      <c r="BR15" s="85"/>
+      <c r="BS15" s="85"/>
+      <c r="BT15" s="85"/>
+      <c r="BU15" s="85"/>
+      <c r="BV15" s="85"/>
       <c r="BW15" s="24"/>
     </row>
     <row r="16" spans="2:75" ht="15">
@@ -19526,29 +19839,29 @@
       <c r="BB16" s="19"/>
       <c r="BC16" s="20"/>
       <c r="BE16" s="21"/>
-      <c r="BF16" s="63" t="s">
+      <c r="BF16" s="86" t="s">
         <v>814</v>
       </c>
-      <c r="BG16" s="63"/>
-      <c r="BH16" s="63"/>
-      <c r="BI16" s="63"/>
-      <c r="BJ16" s="62" t="s">
+      <c r="BG16" s="86"/>
+      <c r="BH16" s="86"/>
+      <c r="BI16" s="86"/>
+      <c r="BJ16" s="85" t="s">
         <v>815</v>
       </c>
-      <c r="BK16" s="62"/>
-      <c r="BL16" s="62"/>
-      <c r="BM16" s="62"/>
-      <c r="BN16" s="62"/>
-      <c r="BO16" s="62"/>
-      <c r="BP16" s="62" t="s">
+      <c r="BK16" s="85"/>
+      <c r="BL16" s="85"/>
+      <c r="BM16" s="85"/>
+      <c r="BN16" s="85"/>
+      <c r="BO16" s="85"/>
+      <c r="BP16" s="85" t="s">
         <v>815</v>
       </c>
-      <c r="BQ16" s="62"/>
-      <c r="BR16" s="62"/>
-      <c r="BS16" s="62"/>
-      <c r="BT16" s="62"/>
-      <c r="BU16" s="62"/>
-      <c r="BV16" s="62"/>
+      <c r="BQ16" s="85"/>
+      <c r="BR16" s="85"/>
+      <c r="BS16" s="85"/>
+      <c r="BT16" s="85"/>
+      <c r="BU16" s="85"/>
+      <c r="BV16" s="85"/>
       <c r="BW16" s="24"/>
     </row>
     <row r="17" spans="2:88" ht="15">
@@ -20059,33 +20372,33 @@
         <v>962</v>
       </c>
       <c r="AL28" s="21"/>
-      <c r="AM28" s="61" t="s">
+      <c r="AM28" s="84" t="s">
         <v>806</v>
       </c>
-      <c r="AN28" s="61"/>
-      <c r="AO28" s="61"/>
-      <c r="AP28" s="61" t="s">
+      <c r="AN28" s="84"/>
+      <c r="AO28" s="84"/>
+      <c r="AP28" s="84" t="s">
         <v>822</v>
       </c>
-      <c r="AQ28" s="61"/>
-      <c r="AR28" s="61"/>
-      <c r="AS28" s="61"/>
-      <c r="AT28" s="61"/>
-      <c r="AU28" s="61"/>
-      <c r="AV28" s="61"/>
-      <c r="AW28" s="61"/>
-      <c r="AX28" s="61" t="s">
+      <c r="AQ28" s="84"/>
+      <c r="AR28" s="84"/>
+      <c r="AS28" s="84"/>
+      <c r="AT28" s="84"/>
+      <c r="AU28" s="84"/>
+      <c r="AV28" s="84"/>
+      <c r="AW28" s="84"/>
+      <c r="AX28" s="84" t="s">
         <v>823</v>
       </c>
-      <c r="AY28" s="61"/>
-      <c r="AZ28" s="61"/>
-      <c r="BA28" s="61"/>
-      <c r="BB28" s="61" t="s">
+      <c r="AY28" s="84"/>
+      <c r="AZ28" s="84"/>
+      <c r="BA28" s="84"/>
+      <c r="BB28" s="84" t="s">
         <v>824</v>
       </c>
-      <c r="BC28" s="61"/>
-      <c r="BD28" s="61"/>
-      <c r="BE28" s="61"/>
+      <c r="BC28" s="84"/>
+      <c r="BD28" s="84"/>
+      <c r="BE28" s="84"/>
       <c r="BF28" s="24"/>
       <c r="BH28" s="29" t="s">
         <v>841</v>
@@ -20121,33 +20434,33 @@
     </row>
     <row r="29" spans="2:88" ht="15" thickBot="1">
       <c r="AL29" s="21"/>
-      <c r="AM29" s="63" t="s">
+      <c r="AM29" s="86" t="s">
         <v>825</v>
       </c>
-      <c r="AN29" s="63"/>
-      <c r="AO29" s="63"/>
-      <c r="AP29" s="62" t="s">
+      <c r="AN29" s="86"/>
+      <c r="AO29" s="86"/>
+      <c r="AP29" s="85" t="s">
         <v>963</v>
       </c>
-      <c r="AQ29" s="62"/>
-      <c r="AR29" s="62"/>
-      <c r="AS29" s="62"/>
-      <c r="AT29" s="62"/>
-      <c r="AU29" s="62"/>
-      <c r="AV29" s="62"/>
-      <c r="AW29" s="62"/>
-      <c r="AX29" s="62" t="s">
+      <c r="AQ29" s="85"/>
+      <c r="AR29" s="85"/>
+      <c r="AS29" s="85"/>
+      <c r="AT29" s="85"/>
+      <c r="AU29" s="85"/>
+      <c r="AV29" s="85"/>
+      <c r="AW29" s="85"/>
+      <c r="AX29" s="85" t="s">
         <v>826</v>
       </c>
-      <c r="AY29" s="62"/>
-      <c r="AZ29" s="62"/>
-      <c r="BA29" s="62"/>
-      <c r="BB29" s="63" t="s">
+      <c r="AY29" s="85"/>
+      <c r="AZ29" s="85"/>
+      <c r="BA29" s="85"/>
+      <c r="BB29" s="86" t="s">
         <v>827</v>
       </c>
-      <c r="BC29" s="63"/>
-      <c r="BD29" s="63"/>
-      <c r="BE29" s="63"/>
+      <c r="BC29" s="86"/>
+      <c r="BD29" s="86"/>
+      <c r="BE29" s="86"/>
       <c r="BF29" s="24"/>
     </row>
     <row r="30" spans="2:88" ht="15">
@@ -20155,33 +20468,33 @@
         <v>774</v>
       </c>
       <c r="AL30" s="21"/>
-      <c r="AM30" s="63" t="s">
+      <c r="AM30" s="86" t="s">
         <v>828</v>
       </c>
-      <c r="AN30" s="63"/>
-      <c r="AO30" s="63"/>
-      <c r="AP30" s="62" t="s">
+      <c r="AN30" s="86"/>
+      <c r="AO30" s="86"/>
+      <c r="AP30" s="85" t="s">
         <v>829</v>
       </c>
-      <c r="AQ30" s="62"/>
-      <c r="AR30" s="62"/>
-      <c r="AS30" s="62"/>
-      <c r="AT30" s="62"/>
-      <c r="AU30" s="62"/>
-      <c r="AV30" s="62"/>
-      <c r="AW30" s="62"/>
-      <c r="AX30" s="62" t="s">
+      <c r="AQ30" s="85"/>
+      <c r="AR30" s="85"/>
+      <c r="AS30" s="85"/>
+      <c r="AT30" s="85"/>
+      <c r="AU30" s="85"/>
+      <c r="AV30" s="85"/>
+      <c r="AW30" s="85"/>
+      <c r="AX30" s="85" t="s">
         <v>830</v>
       </c>
-      <c r="AY30" s="62"/>
-      <c r="AZ30" s="62"/>
-      <c r="BA30" s="62"/>
-      <c r="BB30" s="63" t="s">
+      <c r="AY30" s="85"/>
+      <c r="AZ30" s="85"/>
+      <c r="BA30" s="85"/>
+      <c r="BB30" s="86" t="s">
         <v>831</v>
       </c>
-      <c r="BC30" s="63"/>
-      <c r="BD30" s="63"/>
-      <c r="BE30" s="63"/>
+      <c r="BC30" s="86"/>
+      <c r="BD30" s="86"/>
+      <c r="BE30" s="86"/>
       <c r="BF30" s="24"/>
       <c r="BH30" s="18" t="s">
         <v>842</v>
@@ -20213,33 +20526,33 @@
         <v>775</v>
       </c>
       <c r="AL31" s="21"/>
-      <c r="AM31" s="63" t="s">
+      <c r="AM31" s="86" t="s">
         <v>831</v>
       </c>
-      <c r="AN31" s="63"/>
-      <c r="AO31" s="63"/>
-      <c r="AP31" s="62" t="s">
+      <c r="AN31" s="86"/>
+      <c r="AO31" s="86"/>
+      <c r="AP31" s="85" t="s">
         <v>832</v>
       </c>
-      <c r="AQ31" s="62"/>
-      <c r="AR31" s="62"/>
-      <c r="AS31" s="62"/>
-      <c r="AT31" s="62"/>
-      <c r="AU31" s="62"/>
-      <c r="AV31" s="62"/>
-      <c r="AW31" s="62"/>
-      <c r="AX31" s="62" t="s">
+      <c r="AQ31" s="85"/>
+      <c r="AR31" s="85"/>
+      <c r="AS31" s="85"/>
+      <c r="AT31" s="85"/>
+      <c r="AU31" s="85"/>
+      <c r="AV31" s="85"/>
+      <c r="AW31" s="85"/>
+      <c r="AX31" s="85" t="s">
         <v>830</v>
       </c>
-      <c r="AY31" s="62"/>
-      <c r="AZ31" s="62"/>
-      <c r="BA31" s="62"/>
-      <c r="BB31" s="63" t="s">
+      <c r="AY31" s="85"/>
+      <c r="AZ31" s="85"/>
+      <c r="BA31" s="85"/>
+      <c r="BB31" s="86" t="s">
         <v>833</v>
       </c>
-      <c r="BC31" s="63"/>
-      <c r="BD31" s="63"/>
-      <c r="BE31" s="63"/>
+      <c r="BC31" s="86"/>
+      <c r="BD31" s="86"/>
+      <c r="BE31" s="86"/>
       <c r="BF31" s="24"/>
       <c r="BH31" s="27" t="s">
         <v>843</v>
@@ -21079,11 +21392,11 @@
       <c r="CA49" s="24"/>
     </row>
     <row r="50" spans="2:79" ht="15">
-      <c r="C50" s="64" t="s">
+      <c r="C50" s="61" t="s">
         <v>986</v>
       </c>
-      <c r="D50" s="65"/>
-      <c r="E50" s="65"/>
+      <c r="D50" s="62"/>
+      <c r="E50" s="62"/>
       <c r="AC50" s="21"/>
       <c r="AD50" s="22" t="s">
         <v>982</v>
@@ -21139,17 +21452,17 @@
       <c r="CA50" s="24"/>
     </row>
     <row r="51" spans="2:79" ht="16.5" customHeight="1">
-      <c r="C51" s="64" t="s">
+      <c r="C51" s="61" t="s">
         <v>987</v>
       </c>
-      <c r="D51" s="65"/>
-      <c r="E51" s="65"/>
+      <c r="D51" s="62"/>
+      <c r="E51" s="62"/>
       <c r="AC51" s="34"/>
       <c r="AD51" s="51"/>
-      <c r="AE51" s="66" t="s">
+      <c r="AE51" s="63" t="s">
         <v>882</v>
       </c>
-      <c r="AF51" s="67"/>
+      <c r="AF51" s="64"/>
       <c r="AG51" s="23"/>
       <c r="AH51" s="23"/>
       <c r="AI51" s="23"/>
@@ -21199,17 +21512,17 @@
       <c r="CA51" s="24"/>
     </row>
     <row r="52" spans="2:79" ht="14.25" customHeight="1">
-      <c r="C52" s="64" t="s">
+      <c r="C52" s="61" t="s">
         <v>988</v>
       </c>
-      <c r="D52" s="65"/>
-      <c r="E52" s="65"/>
+      <c r="D52" s="62"/>
+      <c r="E52" s="62"/>
       <c r="AC52" s="21"/>
       <c r="AD52" s="23"/>
-      <c r="AE52" s="66" t="s">
+      <c r="AE52" s="63" t="s">
         <v>883</v>
       </c>
-      <c r="AF52" s="67"/>
+      <c r="AF52" s="64"/>
       <c r="AG52" s="23"/>
       <c r="AH52" s="23"/>
       <c r="AI52" s="23"/>
@@ -21261,10 +21574,10 @@
     <row r="53" spans="2:79" ht="16.5" customHeight="1" thickBot="1">
       <c r="AC53" s="52"/>
       <c r="AD53" s="30"/>
-      <c r="AE53" s="68" t="s">
+      <c r="AE53" s="65" t="s">
         <v>884</v>
       </c>
-      <c r="AF53" s="69"/>
+      <c r="AF53" s="66"/>
       <c r="AG53" s="30"/>
       <c r="AH53" s="30"/>
       <c r="AI53" s="30"/>
@@ -22910,7 +23223,7 @@
       <c r="BW90" s="24"/>
     </row>
     <row r="91" spans="3:75" ht="15">
-      <c r="C91" s="76" t="s">
+      <c r="C91" s="73" t="s">
         <v>1055</v>
       </c>
       <c r="D91" s="23"/>
@@ -23082,7 +23395,7 @@
       <c r="X93" s="23"/>
       <c r="Y93" s="23"/>
       <c r="Z93" s="24"/>
-      <c r="AE93" s="75" t="s">
+      <c r="AE93" s="72" t="s">
         <v>981</v>
       </c>
       <c r="AF93" s="30"/>
@@ -23129,7 +23442,7 @@
       <c r="BW93" s="24"/>
     </row>
     <row r="94" spans="3:75" ht="15">
-      <c r="C94" s="76" t="s">
+      <c r="C94" s="73" t="s">
         <v>916</v>
       </c>
       <c r="D94" s="23"/>
@@ -23452,7 +23765,7 @@
       <c r="BZ99" s="24"/>
     </row>
     <row r="100" spans="3:78" ht="15">
-      <c r="C100" s="77" t="s">
+      <c r="C100" s="74" t="s">
         <v>1056</v>
       </c>
       <c r="D100" s="23"/>
@@ -23479,7 +23792,7 @@
       <c r="Y100" s="23"/>
       <c r="Z100" s="23"/>
       <c r="AA100" s="24"/>
-      <c r="AC100" s="77" t="s">
+      <c r="AC100" s="74" t="s">
         <v>1057</v>
       </c>
       <c r="AD100" s="23"/>
@@ -23561,7 +23874,7 @@
       <c r="Y101" s="23"/>
       <c r="Z101" s="23"/>
       <c r="AA101" s="24"/>
-      <c r="AC101" s="85" t="s">
+      <c r="AC101" s="82" t="s">
         <v>1058</v>
       </c>
       <c r="AD101" s="23"/>
@@ -23616,7 +23929,7 @@
       <c r="BZ101" s="24"/>
     </row>
     <row r="102" spans="3:78" ht="15">
-      <c r="C102" s="78" t="s">
+      <c r="C102" s="75" t="s">
         <v>1020</v>
       </c>
       <c r="D102" s="23"/>
@@ -23698,7 +24011,7 @@
       <c r="BZ102" s="24"/>
     </row>
     <row r="103" spans="3:78" ht="15">
-      <c r="C103" s="78" t="s">
+      <c r="C103" s="75" t="s">
         <v>1021</v>
       </c>
       <c r="D103" s="23"/>
@@ -23780,7 +24093,7 @@
       <c r="BZ103" s="24"/>
     </row>
     <row r="104" spans="3:78">
-      <c r="C104" s="79" t="s">
+      <c r="C104" s="76" t="s">
         <v>1022</v>
       </c>
       <c r="D104" s="23"/>
@@ -23862,7 +24175,7 @@
       <c r="BZ104" s="24"/>
     </row>
     <row r="105" spans="3:78" ht="15">
-      <c r="C105" s="79" t="s">
+      <c r="C105" s="76" t="s">
         <v>1023</v>
       </c>
       <c r="D105" s="23"/>
@@ -23944,7 +24257,7 @@
       <c r="BZ105" s="24"/>
     </row>
     <row r="106" spans="3:78">
-      <c r="C106" s="79" t="s">
+      <c r="C106" s="76" t="s">
         <v>1024</v>
       </c>
       <c r="D106" s="23"/>
@@ -23971,7 +24284,7 @@
       <c r="Y106" s="23"/>
       <c r="Z106" s="23"/>
       <c r="AA106" s="24"/>
-      <c r="AC106" s="81" t="s">
+      <c r="AC106" s="78" t="s">
         <v>1034</v>
       </c>
       <c r="AD106" s="23"/>
@@ -24377,7 +24690,7 @@
       <c r="Y111" s="23"/>
       <c r="Z111" s="23"/>
       <c r="AA111" s="24"/>
-      <c r="AC111" s="83" t="s">
+      <c r="AC111" s="80" t="s">
         <v>1001</v>
       </c>
       <c r="AD111" s="30"/>
@@ -24432,7 +24745,7 @@
       <c r="BZ111" s="24"/>
     </row>
     <row r="112" spans="3:78" ht="15">
-      <c r="C112" s="80" t="s">
+      <c r="C112" s="77" t="s">
         <v>1026</v>
       </c>
       <c r="D112" s="23"/>
@@ -24514,7 +24827,7 @@
       <c r="Y113" s="23"/>
       <c r="Z113" s="23"/>
       <c r="AA113" s="24"/>
-      <c r="BC113" s="81" t="s">
+      <c r="BC113" s="78" t="s">
         <v>1042</v>
       </c>
       <c r="BD113" s="23"/>
@@ -24624,7 +24937,7 @@
       <c r="Y115" s="23"/>
       <c r="Z115" s="23"/>
       <c r="AA115" s="24"/>
-      <c r="BC115" s="84" t="s">
+      <c r="BC115" s="81" t="s">
         <v>1044</v>
       </c>
       <c r="BD115" s="30"/>
@@ -24652,7 +24965,7 @@
       <c r="BZ115" s="31"/>
     </row>
     <row r="116" spans="3:78" ht="15.75" thickBot="1">
-      <c r="C116" s="80" t="s">
+      <c r="C116" s="77" t="s">
         <v>1027</v>
       </c>
       <c r="D116" s="23"/>
@@ -24681,7 +24994,7 @@
       <c r="AA116" s="24"/>
     </row>
     <row r="117" spans="3:78" ht="15">
-      <c r="C117" s="81" t="s">
+      <c r="C117" s="78" t="s">
         <v>1028</v>
       </c>
       <c r="D117" s="23"/>
@@ -24739,7 +25052,7 @@
       <c r="BC117" s="20"/>
     </row>
     <row r="118" spans="3:78" ht="15">
-      <c r="C118" s="81" t="s">
+      <c r="C118" s="78" t="s">
         <v>1029</v>
       </c>
       <c r="D118" s="23"/>
@@ -24855,7 +25168,7 @@
       <c r="BC119" s="24"/>
     </row>
     <row r="120" spans="3:78" ht="15.75" thickBot="1">
-      <c r="C120" s="82" t="s">
+      <c r="C120" s="79" t="s">
         <v>997</v>
       </c>
       <c r="D120" s="30"/>
@@ -25007,7 +25320,7 @@
     </row>
     <row r="124" spans="3:78">
       <c r="AC124" s="21"/>
-      <c r="AD124" s="86"/>
+      <c r="AD124" s="83"/>
       <c r="AE124" s="23"/>
       <c r="AF124" s="23"/>
       <c r="AG124" s="23"/>
@@ -25188,7 +25501,7 @@
       <c r="BC129" s="24"/>
     </row>
     <row r="130" spans="29:55">
-      <c r="AC130" s="81" t="s">
+      <c r="AC130" s="78" t="s">
         <v>1049</v>
       </c>
       <c r="AD130" s="23"/>
@@ -25467,7 +25780,7 @@
       <c r="BC138" s="24"/>
     </row>
     <row r="139" spans="29:55">
-      <c r="AC139" s="81" t="s">
+      <c r="AC139" s="78" t="s">
         <v>1053</v>
       </c>
       <c r="AD139" s="23"/>
@@ -25498,7 +25811,7 @@
       <c r="BC139" s="24"/>
     </row>
     <row r="140" spans="29:55" ht="15" thickBot="1">
-      <c r="AC140" s="84" t="s">
+      <c r="AC140" s="81" t="s">
         <v>1054</v>
       </c>
       <c r="AD140" s="30"/>
@@ -25532,53 +25845,37 @@
       <c r="C189" s="10"/>
     </row>
     <row r="191" spans="3:6" ht="15">
-      <c r="C191" s="71"/>
-      <c r="D191" s="71"/>
-      <c r="E191" s="71"/>
-      <c r="F191" s="71"/>
+      <c r="C191" s="68"/>
+      <c r="D191" s="68"/>
+      <c r="E191" s="68"/>
+      <c r="F191" s="68"/>
     </row>
     <row r="192" spans="3:6">
-      <c r="C192" s="73"/>
-      <c r="D192" s="74"/>
-      <c r="E192" s="74"/>
-      <c r="F192" s="74"/>
+      <c r="C192" s="70"/>
+      <c r="D192" s="71"/>
+      <c r="E192" s="71"/>
+      <c r="F192" s="71"/>
     </row>
     <row r="193" spans="3:6">
-      <c r="C193" s="73"/>
-      <c r="D193" s="74"/>
-      <c r="E193" s="74"/>
-      <c r="F193" s="74"/>
+      <c r="C193" s="70"/>
+      <c r="D193" s="71"/>
+      <c r="E193" s="71"/>
+      <c r="F193" s="71"/>
     </row>
     <row r="194" spans="3:6">
-      <c r="C194" s="73"/>
-      <c r="D194" s="74"/>
-      <c r="E194" s="74"/>
-      <c r="F194" s="74"/>
+      <c r="C194" s="70"/>
+      <c r="D194" s="71"/>
+      <c r="E194" s="71"/>
+      <c r="F194" s="71"/>
     </row>
     <row r="195" spans="3:6">
-      <c r="C195" s="73"/>
-      <c r="D195" s="74"/>
-      <c r="E195" s="74"/>
-      <c r="F195" s="74"/>
+      <c r="C195" s="70"/>
+      <c r="D195" s="71"/>
+      <c r="E195" s="71"/>
+      <c r="F195" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="AX28:BA28"/>
-    <mergeCell ref="AX29:BA29"/>
-    <mergeCell ref="AX30:BA30"/>
-    <mergeCell ref="AX31:BA31"/>
-    <mergeCell ref="BB28:BE28"/>
-    <mergeCell ref="BB29:BE29"/>
-    <mergeCell ref="BB30:BE30"/>
-    <mergeCell ref="BB31:BE31"/>
-    <mergeCell ref="AM28:AO28"/>
-    <mergeCell ref="AM29:AO29"/>
-    <mergeCell ref="AM30:AO30"/>
-    <mergeCell ref="AM31:AO31"/>
-    <mergeCell ref="AP28:AW28"/>
-    <mergeCell ref="AP29:AW29"/>
-    <mergeCell ref="AP30:AW30"/>
-    <mergeCell ref="AP31:AW31"/>
     <mergeCell ref="BP13:BV13"/>
     <mergeCell ref="BP14:BV14"/>
     <mergeCell ref="BP15:BV15"/>
@@ -25591,6 +25888,22 @@
     <mergeCell ref="BJ14:BO14"/>
     <mergeCell ref="BJ15:BO15"/>
     <mergeCell ref="BJ16:BO16"/>
+    <mergeCell ref="AM28:AO28"/>
+    <mergeCell ref="AM29:AO29"/>
+    <mergeCell ref="AM30:AO30"/>
+    <mergeCell ref="AM31:AO31"/>
+    <mergeCell ref="AP28:AW28"/>
+    <mergeCell ref="AP29:AW29"/>
+    <mergeCell ref="AP30:AW30"/>
+    <mergeCell ref="AP31:AW31"/>
+    <mergeCell ref="AX28:BA28"/>
+    <mergeCell ref="AX29:BA29"/>
+    <mergeCell ref="AX30:BA30"/>
+    <mergeCell ref="AX31:BA31"/>
+    <mergeCell ref="BB28:BE28"/>
+    <mergeCell ref="BB29:BE29"/>
+    <mergeCell ref="BB30:BE30"/>
+    <mergeCell ref="BB31:BE31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -25599,2524 +25912,2468 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD678391-01EC-4BBB-A4FC-EBED70F213C9}">
-  <dimension ref="B1:B623"/>
+  <dimension ref="A1:BU211"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="16384" width="3" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" ht="15">
+    <row r="1" spans="1:70" ht="15">
       <c r="B1" s="10" t="s">
         <v>1059</v>
       </c>
     </row>
-    <row r="3" spans="2:2" ht="15">
-      <c r="B3" s="10" t="s">
+    <row r="2" spans="1:70" ht="15" thickBot="1"/>
+    <row r="3" spans="1:70" s="16" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A3" s="95"/>
+      <c r="B3" s="96" t="s">
         <v>1060</v>
       </c>
     </row>
-    <row r="5" spans="2:2" ht="15">
-      <c r="B5" s="10" t="s">
+    <row r="4" spans="1:70" ht="15">
+      <c r="B4" s="43" t="s">
         <v>1061</v>
       </c>
-    </row>
-    <row r="7" spans="2:2" ht="15">
-      <c r="B7" s="70" t="s">
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="W4" s="43" t="s">
+        <v>1076</v>
+      </c>
+      <c r="X4" s="44"/>
+      <c r="Y4" s="44"/>
+      <c r="Z4" s="44"/>
+      <c r="AA4" s="44"/>
+      <c r="AB4" s="44"/>
+      <c r="AC4" s="44"/>
+      <c r="AD4" s="44"/>
+      <c r="AQ4" s="43" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AR4" s="44"/>
+      <c r="AS4" s="44"/>
+      <c r="AT4" s="44"/>
+      <c r="AU4" s="44"/>
+      <c r="AV4" s="44"/>
+      <c r="AW4" s="44"/>
+      <c r="AY4" s="93" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="5" spans="1:70" ht="15">
+      <c r="B5" s="67" t="s">
         <v>1062</v>
       </c>
-    </row>
-    <row r="8" spans="2:2">
-      <c r="B8" s="13"/>
-    </row>
-    <row r="9" spans="2:2">
-      <c r="B9" s="13" t="s">
+      <c r="W5" s="87" t="s">
+        <v>1062</v>
+      </c>
+      <c r="X5" s="62"/>
+      <c r="AQ5" s="89" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AR5" s="90"/>
+      <c r="AS5" s="90"/>
+      <c r="AT5" s="90"/>
+      <c r="AU5" s="90"/>
+      <c r="AV5" s="90"/>
+      <c r="AW5" s="90"/>
+      <c r="AX5" s="90"/>
+      <c r="BJ5" s="89" t="s">
+        <v>1119</v>
+      </c>
+      <c r="BK5" s="90"/>
+      <c r="BL5" s="90"/>
+      <c r="BM5" s="90"/>
+      <c r="BN5" s="90"/>
+      <c r="BO5" s="90"/>
+      <c r="BP5" s="90"/>
+      <c r="BQ5" s="90"/>
+      <c r="BR5" s="90"/>
+    </row>
+    <row r="6" spans="1:70" ht="15">
+      <c r="B6" s="13" t="s">
+        <v>1407</v>
+      </c>
+      <c r="W6" s="88" t="s">
+        <v>1077</v>
+      </c>
+      <c r="X6" s="62"/>
+      <c r="AQ6" s="87" t="s">
+        <v>1062</v>
+      </c>
+      <c r="BJ6" s="87" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="7" spans="1:70">
+      <c r="B7" s="13" t="s">
+        <v>1408</v>
+      </c>
+      <c r="W7" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="X7" s="62"/>
+      <c r="AQ7" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="BJ7" s="9" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:70" ht="15">
+      <c r="B8" s="13" t="s">
+        <v>1409</v>
+      </c>
+      <c r="W8" s="88" t="s">
+        <v>1079</v>
+      </c>
+      <c r="X8" s="62"/>
+      <c r="AQ8" s="9" t="s">
+        <v>1098</v>
+      </c>
+      <c r="BJ8" s="9" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:70">
+      <c r="B9" s="15" t="s">
+        <v>1063</v>
+      </c>
+      <c r="AQ9" s="9" t="s">
+        <v>1099</v>
+      </c>
+      <c r="BJ9" s="9" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:70">
+      <c r="B10" s="15" t="s">
+        <v>1064</v>
+      </c>
+      <c r="W10" s="15" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="11" spans="1:70">
+      <c r="B11" s="15" t="s">
+        <v>1065</v>
+      </c>
+      <c r="W11" s="15" t="s">
+        <v>1081</v>
+      </c>
+      <c r="AQ11" s="15" t="s">
+        <v>1100</v>
+      </c>
+      <c r="BJ11" s="15" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:70">
+      <c r="B12" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="W12" s="15" t="s">
+        <v>1082</v>
+      </c>
+      <c r="AQ12" s="15" t="s">
+        <v>1101</v>
+      </c>
+      <c r="BJ12" s="15" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:70">
+      <c r="W13" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AQ13" s="15" t="s">
+        <v>1102</v>
+      </c>
+      <c r="BJ13" s="69"/>
+    </row>
+    <row r="14" spans="1:70" ht="15">
+      <c r="B14" s="67" t="s">
+        <v>1066</v>
+      </c>
+      <c r="W14" s="15" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AQ14" s="15" t="s">
+        <v>1103</v>
+      </c>
+      <c r="BJ14" s="15" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:70">
+      <c r="B15" s="13" t="s">
+        <v>1067</v>
+      </c>
+      <c r="W15" s="15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AQ15" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BJ15" s="15" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:70">
+      <c r="B16" s="13" t="s">
+        <v>1068</v>
+      </c>
+      <c r="W16" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AQ16" s="69"/>
+      <c r="BJ16" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="17" spans="2:62">
+      <c r="B17" s="13" t="s">
+        <v>1069</v>
+      </c>
+      <c r="W17" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AQ17" s="15" t="s">
+        <v>1104</v>
+      </c>
+      <c r="BJ17" s="69"/>
+    </row>
+    <row r="18" spans="2:62">
+      <c r="B18" s="13" t="s">
+        <v>1070</v>
+      </c>
+      <c r="W18" s="15" t="s">
+        <v>1087</v>
+      </c>
+      <c r="AQ18" s="15" t="s">
+        <v>1105</v>
+      </c>
+      <c r="BJ18" s="15" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="19" spans="2:62">
+      <c r="W19" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AQ19" s="15" t="s">
+        <v>1106</v>
+      </c>
+      <c r="BJ19" s="15" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="20" spans="2:62" ht="15">
+      <c r="B20" s="67" t="s">
+        <v>1071</v>
+      </c>
+      <c r="AQ20" s="15" t="s">
+        <v>1107</v>
+      </c>
+      <c r="BJ20" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="21" spans="2:62" ht="15">
+      <c r="B21" s="15" t="s">
+        <v>1072</v>
+      </c>
+      <c r="W21" s="67" t="s">
+        <v>1088</v>
+      </c>
+      <c r="AQ21" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="22" spans="2:62">
+      <c r="B22" s="15" t="s">
+        <v>1073</v>
+      </c>
+      <c r="W22" s="13" t="s">
+        <v>1410</v>
+      </c>
+      <c r="BJ22" s="15" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="23" spans="2:62" ht="15">
+      <c r="B23" s="15" t="s">
+        <v>1074</v>
+      </c>
+      <c r="W23" s="13" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AQ23" s="67" t="s">
+        <v>1108</v>
+      </c>
+      <c r="BJ23" s="15" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="24" spans="2:62">
+      <c r="B24" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="W24" s="13" t="s">
+        <v>1090</v>
+      </c>
+      <c r="AQ24" s="15" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="25" spans="2:62" ht="15">
+      <c r="B25" s="15" t="s">
+        <v>1075</v>
+      </c>
+      <c r="AQ25" s="15" t="s">
+        <v>1110</v>
+      </c>
+      <c r="BJ25" s="67" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="26" spans="2:62" ht="15">
+      <c r="W26" s="67" t="s">
+        <v>1091</v>
+      </c>
+      <c r="AQ26" s="15" t="s">
+        <v>1111</v>
+      </c>
+      <c r="BJ26" s="91" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="27" spans="2:62">
+      <c r="W27" s="15" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AQ27" s="15" t="s">
+        <v>1103</v>
+      </c>
+      <c r="BJ27" s="91" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="28" spans="2:62">
+      <c r="W28" s="15" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AQ28" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BJ28" s="92"/>
+    </row>
+    <row r="29" spans="2:62">
+      <c r="W29" s="15" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AQ29" s="69"/>
+      <c r="BJ29" s="91" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="30" spans="2:62">
+      <c r="W30" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AQ30" s="15" t="s">
+        <v>1112</v>
+      </c>
+      <c r="BJ30" s="91" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="31" spans="2:62">
+      <c r="AQ31" s="15" t="s">
+        <v>1113</v>
+      </c>
+      <c r="BJ31" s="91" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="32" spans="2:62">
+      <c r="AQ32" s="15" t="s">
+        <v>1110</v>
+      </c>
+      <c r="BJ32" s="69"/>
+    </row>
+    <row r="33" spans="2:62" ht="15">
+      <c r="B33" s="43" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="U33" s="43" t="s">
+        <v>1168</v>
+      </c>
+      <c r="V33" s="44"/>
+      <c r="W33" s="44"/>
+      <c r="X33" s="44"/>
+      <c r="Y33" s="44"/>
+      <c r="Z33" s="44"/>
+      <c r="AA33" s="44"/>
+      <c r="AB33" s="44"/>
+      <c r="AC33" s="44"/>
+      <c r="AD33" s="44"/>
+      <c r="AE33" s="44"/>
+      <c r="AF33" s="44"/>
+      <c r="AQ33" s="15" t="s">
+        <v>1114</v>
+      </c>
+      <c r="BJ33" s="15" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="34" spans="2:62" ht="15">
+      <c r="B34" s="87" t="s">
+        <v>1062</v>
+      </c>
+      <c r="U34" s="87" t="s">
+        <v>1062</v>
+      </c>
+      <c r="V34" s="62"/>
+      <c r="AQ34" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="BJ34" s="15" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="35" spans="2:62">
+      <c r="B35" s="9" t="s">
+        <v>1140</v>
+      </c>
+      <c r="U35" s="9" t="s">
+        <v>1169</v>
+      </c>
+      <c r="V35" s="62"/>
+      <c r="AQ35" s="15" t="s">
+        <v>1115</v>
+      </c>
+      <c r="BJ35" s="15" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="36" spans="2:62">
+      <c r="B36" s="9" t="s">
+        <v>1141</v>
+      </c>
+      <c r="U36" s="9" t="s">
+        <v>1414</v>
+      </c>
+      <c r="V36" s="62"/>
+      <c r="AQ36" s="15" t="s">
+        <v>1102</v>
+      </c>
+      <c r="BJ36" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="37" spans="2:62">
+      <c r="B37" s="9" t="s">
+        <v>1142</v>
+      </c>
+      <c r="AQ37" s="15" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="38" spans="2:62">
+      <c r="B38" s="15" t="s">
+        <v>1143</v>
+      </c>
+      <c r="U38" s="15" t="s">
+        <v>1170</v>
+      </c>
+      <c r="AQ38" s="15" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="39" spans="2:62">
+      <c r="B39" s="15" t="s">
+        <v>1144</v>
+      </c>
+      <c r="U39" s="69"/>
+      <c r="AQ39" s="15" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="40" spans="2:62" ht="15">
+      <c r="B40" s="15" t="s">
+        <v>1145</v>
+      </c>
+      <c r="U40" s="94" t="s">
+        <v>1415</v>
+      </c>
+      <c r="AQ40" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="41" spans="2:62">
+      <c r="B41" s="69"/>
+      <c r="U41" s="69"/>
+    </row>
+    <row r="42" spans="2:62">
+      <c r="B42" s="15" t="s">
+        <v>1146</v>
+      </c>
+      <c r="U42" s="15" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="43" spans="2:62">
+      <c r="B43" s="15" t="s">
+        <v>1147</v>
+      </c>
+      <c r="U43" s="15" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="44" spans="2:62">
+      <c r="B44" s="15" t="s">
+        <v>1148</v>
+      </c>
+      <c r="U44" s="15" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="45" spans="2:62">
+      <c r="B45" s="15" t="s">
+        <v>1149</v>
+      </c>
+      <c r="U45" s="15" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="46" spans="2:62">
+      <c r="B46" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="U46" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="47" spans="2:62">
+      <c r="B47" s="69"/>
+      <c r="U47" s="69"/>
+    </row>
+    <row r="48" spans="2:62">
+      <c r="B48" s="15" t="s">
+        <v>1150</v>
+      </c>
+      <c r="U48" s="15" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="49" spans="2:21">
+      <c r="B49" s="15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="U49" s="15" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="50" spans="2:21">
+      <c r="B50" s="15" t="s">
+        <v>1152</v>
+      </c>
+      <c r="U50" s="15" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="51" spans="2:21">
+      <c r="B51" s="15" t="s">
+        <v>1153</v>
+      </c>
+      <c r="U51" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="52" spans="2:21">
+      <c r="B52" s="15" t="s">
+        <v>1154</v>
+      </c>
+      <c r="U52" s="15" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="53" spans="2:21">
+      <c r="B53" s="15" t="s">
+        <v>1155</v>
+      </c>
+      <c r="U53" s="15" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="54" spans="2:21">
+      <c r="B54" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="U54" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="55" spans="2:21">
+      <c r="U55" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="56" spans="2:21" ht="15">
+      <c r="B56" s="67" t="s">
+        <v>1156</v>
+      </c>
+      <c r="U56" s="15" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="57" spans="2:21">
+      <c r="B57" s="15" t="s">
+        <v>1123</v>
+      </c>
+      <c r="U57" s="15" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="58" spans="2:21">
+      <c r="B58" s="15" t="s">
+        <v>1157</v>
+      </c>
+      <c r="U58" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="59" spans="2:21">
+      <c r="B59" s="15" t="s">
+        <v>1158</v>
+      </c>
+      <c r="U59" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="60" spans="2:21">
+      <c r="B60" s="69"/>
+    </row>
+    <row r="61" spans="2:21" ht="15">
+      <c r="B61" s="15" t="s">
+        <v>1129</v>
+      </c>
+      <c r="U61" s="67" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="62" spans="2:21">
+      <c r="B62" s="15" t="s">
+        <v>1159</v>
+      </c>
+      <c r="U62" s="15" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="63" spans="2:21">
+      <c r="U63" s="15" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="64" spans="2:21" ht="15">
+      <c r="B64" s="67" t="s">
+        <v>1160</v>
+      </c>
+      <c r="U64" s="69"/>
+    </row>
+    <row r="65" spans="1:21">
+      <c r="B65" s="15" t="s">
+        <v>1161</v>
+      </c>
+      <c r="U65" s="15" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21">
+      <c r="B66" s="91" t="s">
+        <v>1162</v>
+      </c>
+      <c r="U66" s="15" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21">
+      <c r="B67" s="69"/>
+      <c r="U67" s="15" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21">
+      <c r="B68" s="15" t="s">
+        <v>1163</v>
+      </c>
+      <c r="U68" s="15" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21">
+      <c r="U69" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" ht="15">
+      <c r="B70" s="67" t="s">
+        <v>1164</v>
+      </c>
+      <c r="U70" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21">
+      <c r="B71" s="15" t="s">
+        <v>1161</v>
+      </c>
+      <c r="U71" s="69"/>
+    </row>
+    <row r="72" spans="1:21">
+      <c r="B72" s="15" t="s">
+        <v>1165</v>
+      </c>
+      <c r="U72" s="15" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21">
+      <c r="B73" s="69"/>
+      <c r="U73" s="15" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21">
+      <c r="B74" s="15" t="s">
+        <v>1166</v>
+      </c>
+      <c r="U74" s="15" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21">
+      <c r="B75" s="15" t="s">
+        <v>1167</v>
+      </c>
+      <c r="U75" s="15" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21">
+      <c r="U76" s="15" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21">
+      <c r="U77" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21">
+      <c r="U78" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" ht="15" thickBot="1"/>
+    <row r="80" spans="1:21" s="16" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A80" s="95"/>
+      <c r="B80" s="96" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="81" spans="2:73" ht="15">
+      <c r="B81" s="43" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C81" s="44"/>
+      <c r="D81" s="44"/>
+      <c r="E81" s="44"/>
+      <c r="F81" s="44"/>
+      <c r="G81" s="44"/>
+      <c r="H81" s="44"/>
+      <c r="I81" s="44"/>
+      <c r="J81" s="44"/>
+      <c r="U81" s="43" t="s">
+        <v>1213</v>
+      </c>
+      <c r="V81" s="44"/>
+      <c r="W81" s="44"/>
+      <c r="X81" s="44"/>
+      <c r="Y81" s="44"/>
+      <c r="Z81" s="44"/>
+      <c r="AA81" s="44"/>
+      <c r="AB81" s="44"/>
+      <c r="AC81" s="44"/>
+      <c r="AD81" s="44"/>
+      <c r="AN81" s="43" t="s">
+        <v>1229</v>
+      </c>
+      <c r="AO81" s="44"/>
+      <c r="AP81" s="44"/>
+      <c r="AQ81" s="44"/>
+      <c r="AR81" s="44"/>
+      <c r="AS81" s="44"/>
+      <c r="AT81" s="44"/>
+      <c r="AU81" s="44"/>
+      <c r="AV81" s="44"/>
+      <c r="AW81" s="44"/>
+      <c r="BE81" s="43" t="s">
+        <v>1246</v>
+      </c>
+      <c r="BF81" s="44"/>
+      <c r="BG81" s="44"/>
+      <c r="BH81" s="44"/>
+      <c r="BI81" s="44"/>
+      <c r="BJ81" s="44"/>
+      <c r="BK81" s="44"/>
+      <c r="BL81" s="44"/>
+      <c r="BM81" s="44"/>
+      <c r="BN81" s="44"/>
+    </row>
+    <row r="82" spans="2:73" ht="15">
+      <c r="B82" s="97" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C82" s="98"/>
+      <c r="D82" s="98"/>
+      <c r="E82" s="98"/>
+      <c r="U82" s="97" t="s">
+        <v>1214</v>
+      </c>
+      <c r="V82" s="98"/>
+      <c r="W82" s="98"/>
+      <c r="X82" s="98"/>
+      <c r="Y82" s="98"/>
+      <c r="Z82" s="98"/>
+      <c r="AN82" s="97" t="s">
+        <v>1230</v>
+      </c>
+      <c r="AO82" s="98"/>
+      <c r="AP82" s="98"/>
+      <c r="AQ82" s="98"/>
+      <c r="AR82" s="98"/>
+      <c r="AS82" s="98"/>
+      <c r="AT82" s="98"/>
+      <c r="AU82" s="98"/>
+      <c r="AV82" s="98"/>
+      <c r="BE82" s="97" t="s">
+        <v>1247</v>
+      </c>
+      <c r="BF82" s="98"/>
+      <c r="BG82" s="98"/>
+      <c r="BH82" s="98"/>
+      <c r="BI82" s="98"/>
+      <c r="BJ82" s="98"/>
+    </row>
+    <row r="83" spans="2:73">
+      <c r="B83" s="15" t="s">
+        <v>1194</v>
+      </c>
+      <c r="AN83" s="15" t="s">
+        <v>1231</v>
+      </c>
+      <c r="BE83" s="15" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="84" spans="2:73">
+      <c r="B84" s="15" t="s">
+        <v>1195</v>
+      </c>
+      <c r="U84" s="15" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AN84" s="15" t="s">
+        <v>1232</v>
+      </c>
+      <c r="BE84" s="69"/>
+    </row>
+    <row r="85" spans="2:73">
+      <c r="B85" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="U85" s="15" t="s">
+        <v>1215</v>
+      </c>
+      <c r="AN85" s="15" t="s">
+        <v>1233</v>
+      </c>
+      <c r="BE85" s="15" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="86" spans="2:73">
+      <c r="B86" s="15" t="s">
+        <v>1196</v>
+      </c>
+      <c r="U86" s="15" t="s">
+        <v>1216</v>
+      </c>
+      <c r="AN86" s="15" t="s">
+        <v>1234</v>
+      </c>
+      <c r="BE86" s="15" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="87" spans="2:73">
+      <c r="B87" s="15" t="s">
+        <v>1197</v>
+      </c>
+      <c r="U87" s="15" t="s">
+        <v>1217</v>
+      </c>
+      <c r="AN87" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BE87" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="88" spans="2:73">
+      <c r="B88" s="15" t="s">
+        <v>1198</v>
+      </c>
+      <c r="U88" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AN88" s="69"/>
+      <c r="BE88" s="15" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="89" spans="2:73">
+      <c r="B89" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="U89" s="69"/>
+      <c r="AN89" s="15" t="s">
+        <v>1235</v>
+      </c>
+      <c r="BE89" s="91" t="s">
+        <v>1251</v>
+      </c>
+      <c r="BF89" s="62"/>
+      <c r="BG89" s="62"/>
+      <c r="BH89" s="62"/>
+      <c r="BI89" s="62"/>
+      <c r="BJ89" s="62"/>
+      <c r="BK89" s="62"/>
+      <c r="BL89" s="62"/>
+      <c r="BM89" s="62"/>
+      <c r="BN89" s="62"/>
+      <c r="BO89" s="62"/>
+      <c r="BP89" s="62"/>
+      <c r="BQ89" s="62"/>
+      <c r="BR89" s="62"/>
+      <c r="BS89" s="62"/>
+      <c r="BT89" s="62"/>
+      <c r="BU89" s="62"/>
+    </row>
+    <row r="90" spans="2:73">
+      <c r="B90" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="U90" s="15" t="s">
+        <v>1129</v>
+      </c>
+      <c r="AN90" s="15" t="s">
+        <v>1236</v>
+      </c>
+      <c r="BE90" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="91" spans="2:73">
+      <c r="B91" s="15" t="s">
+        <v>1199</v>
+      </c>
+      <c r="U91" s="15" t="s">
+        <v>1218</v>
+      </c>
+      <c r="AN91" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BE91" s="15" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="92" spans="2:73">
+      <c r="B92" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="U92" s="15" t="s">
+        <v>1219</v>
+      </c>
+      <c r="BE92" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="93" spans="2:73" ht="15">
+      <c r="B93" s="15" t="s">
+        <v>1200</v>
+      </c>
+      <c r="U93" s="69"/>
+      <c r="AN93" s="97" t="s">
+        <v>1237</v>
+      </c>
+      <c r="AO93" s="98"/>
+      <c r="AP93" s="98"/>
+      <c r="AQ93" s="98"/>
+      <c r="AR93" s="98"/>
+    </row>
+    <row r="94" spans="2:73" ht="15">
+      <c r="B94" s="15" t="s">
+        <v>1201</v>
+      </c>
+      <c r="U94" s="15" t="s">
+        <v>1220</v>
+      </c>
+      <c r="AN94" s="15" t="s">
+        <v>1238</v>
+      </c>
+      <c r="BE94" s="97" t="s">
+        <v>1253</v>
+      </c>
+      <c r="BF94" s="98"/>
+      <c r="BG94" s="98"/>
+      <c r="BH94" s="98"/>
+      <c r="BI94" s="98"/>
+      <c r="BJ94" s="98"/>
+      <c r="BK94" s="98"/>
+    </row>
+    <row r="95" spans="2:73">
+      <c r="B95" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="U95" s="15" t="s">
+        <v>1221</v>
+      </c>
+      <c r="AN95" s="15" t="s">
+        <v>1239</v>
+      </c>
+      <c r="BE95" s="15" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="96" spans="2:73">
+      <c r="B96" s="15" t="s">
+        <v>1202</v>
+      </c>
+      <c r="U96" s="15" t="s">
+        <v>1222</v>
+      </c>
+      <c r="AN96" s="15" t="s">
+        <v>1240</v>
+      </c>
+      <c r="BE96" s="69"/>
+    </row>
+    <row r="97" spans="2:57">
+      <c r="B97" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="U97" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AN97" s="15" t="s">
+        <v>1241</v>
+      </c>
+      <c r="BE97" s="15" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="98" spans="2:57">
+      <c r="AN98" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BE98" s="15" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="99" spans="2:57" ht="15">
+      <c r="B99" s="97" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C99" s="98"/>
+      <c r="D99" s="98"/>
+      <c r="E99" s="98"/>
+      <c r="U99" s="97" t="s">
+        <v>1223</v>
+      </c>
+      <c r="V99" s="98"/>
+      <c r="W99" s="98"/>
+      <c r="X99" s="98"/>
+      <c r="Y99" s="98"/>
+      <c r="AN99" s="69"/>
+      <c r="BE99" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="100" spans="2:57">
+      <c r="B100" s="15" t="s">
+        <v>1204</v>
+      </c>
+      <c r="AN100" s="15" t="s">
+        <v>1242</v>
+      </c>
+      <c r="BE100" s="15" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="101" spans="2:57">
+      <c r="B101" s="15" t="s">
+        <v>1205</v>
+      </c>
+      <c r="U101" s="15" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AN101" s="15" t="s">
+        <v>1243</v>
+      </c>
+      <c r="BE101" s="15" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="102" spans="2:57">
+      <c r="B102" s="15" t="s">
+        <v>1206</v>
+      </c>
+      <c r="U102" s="15" t="s">
+        <v>1224</v>
+      </c>
+      <c r="AN102" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BE102" s="15" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="103" spans="2:57">
+      <c r="B103" s="69"/>
+      <c r="U103" s="15" t="s">
+        <v>1225</v>
+      </c>
+      <c r="AN103" s="69"/>
+      <c r="BE103" s="15" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="104" spans="2:57">
+      <c r="B104" s="15" t="s">
+        <v>1207</v>
+      </c>
+      <c r="U104" s="15" t="s">
+        <v>1226</v>
+      </c>
+      <c r="AN104" s="15" t="s">
+        <v>1244</v>
+      </c>
+      <c r="BE104" s="15" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="105" spans="2:57">
+      <c r="B105" s="15" t="s">
+        <v>1208</v>
+      </c>
+      <c r="U105" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AN105" s="15" t="s">
+        <v>1245</v>
+      </c>
+      <c r="BE105" s="15" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="106" spans="2:57">
+      <c r="B106" s="15" t="s">
+        <v>1209</v>
+      </c>
+      <c r="U106" s="69"/>
+      <c r="AN106" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BE106" s="15" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="107" spans="2:57">
+      <c r="B107" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="U107" s="15" t="s">
+        <v>1129</v>
+      </c>
+      <c r="BE107" s="15" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="108" spans="2:57">
+      <c r="B108" s="69"/>
+      <c r="U108" s="15" t="s">
+        <v>1227</v>
+      </c>
+      <c r="BE108" s="15" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="109" spans="2:57">
+      <c r="B109" s="15" t="s">
+        <v>1210</v>
+      </c>
+      <c r="U109" s="15" t="s">
+        <v>1228</v>
+      </c>
+      <c r="BE109" s="15" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="110" spans="2:57">
+      <c r="B110" s="15" t="s">
+        <v>1211</v>
+      </c>
+      <c r="BE110" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="111" spans="2:57">
+      <c r="B111" s="15" t="s">
+        <v>1212</v>
+      </c>
+      <c r="BE111" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="112" spans="2:57">
+      <c r="B112" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BE112" s="15" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="113" spans="1:53" ht="15" thickBot="1"/>
+    <row r="114" spans="1:53" s="16" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A114" s="95"/>
+      <c r="B114" s="96" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="115" spans="1:53" ht="15">
+      <c r="B115" s="43" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C115" s="44"/>
+      <c r="D115" s="44"/>
+      <c r="E115" s="44"/>
+      <c r="F115" s="44"/>
+      <c r="G115" s="44"/>
+      <c r="H115" s="44"/>
+      <c r="I115" s="44"/>
+      <c r="J115" s="44"/>
+      <c r="Y115" s="43" t="s">
+        <v>1298</v>
+      </c>
+      <c r="Z115" s="44"/>
+      <c r="AA115" s="44"/>
+      <c r="AB115" s="44"/>
+      <c r="AC115" s="44"/>
+      <c r="AD115" s="44"/>
+      <c r="AE115" s="44"/>
+      <c r="AF115" s="44"/>
+      <c r="AG115" s="44"/>
+      <c r="AH115" s="44"/>
+      <c r="AQ115" s="43" t="s">
+        <v>1315</v>
+      </c>
+      <c r="AR115" s="44"/>
+      <c r="AS115" s="44"/>
+      <c r="AT115" s="44"/>
+      <c r="AU115" s="44"/>
+      <c r="AV115" s="44"/>
+      <c r="AW115" s="44"/>
+      <c r="AX115" s="44"/>
+      <c r="AY115" s="44"/>
+      <c r="AZ115" s="44"/>
+      <c r="BA115" s="44"/>
+    </row>
+    <row r="116" spans="1:53" ht="15">
+      <c r="B116" s="97" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C116" s="98"/>
+      <c r="D116" s="98"/>
+      <c r="E116" s="98"/>
+      <c r="F116" s="98"/>
+      <c r="Y116" s="97" t="s">
+        <v>1299</v>
+      </c>
+      <c r="Z116" s="98"/>
+      <c r="AA116" s="98"/>
+      <c r="AB116" s="98"/>
+      <c r="AC116" s="98"/>
+      <c r="AD116" s="98"/>
+      <c r="AE116" s="98"/>
+      <c r="AF116" s="98"/>
+      <c r="AG116" s="98"/>
+      <c r="AH116" s="98"/>
+      <c r="AQ116" s="97" t="s">
+        <v>1316</v>
+      </c>
+      <c r="AR116" s="98"/>
+      <c r="AS116" s="98"/>
+      <c r="AT116" s="98"/>
+      <c r="AU116" s="98"/>
+    </row>
+    <row r="117" spans="1:53">
+      <c r="B117" s="15" t="s">
+        <v>1270</v>
+      </c>
+      <c r="Y117" s="15" t="s">
+        <v>1300</v>
+      </c>
+      <c r="AQ117" s="15" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="118" spans="1:53">
+      <c r="B118" s="15" t="s">
+        <v>1271</v>
+      </c>
+      <c r="Y118" s="15" t="s">
+        <v>1301</v>
+      </c>
+      <c r="AQ118" s="15" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="119" spans="1:53">
+      <c r="B119" s="15" t="s">
+        <v>1272</v>
+      </c>
+      <c r="Y119" s="15" t="s">
+        <v>1302</v>
+      </c>
+      <c r="AQ119" s="15" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="120" spans="1:53">
+      <c r="B120" s="15" t="s">
+        <v>1273</v>
+      </c>
+      <c r="Y120" s="15" t="s">
+        <v>1303</v>
+      </c>
+      <c r="AQ120" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="121" spans="1:53">
+      <c r="B121" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Y121" s="69"/>
+      <c r="AQ121" s="69"/>
+    </row>
+    <row r="122" spans="1:53">
+      <c r="B122" s="15" t="s">
+        <v>1274</v>
+      </c>
+      <c r="Y122" s="15" t="s">
+        <v>1304</v>
+      </c>
+      <c r="AQ122" s="15" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="123" spans="1:53">
+      <c r="B123" s="15" t="s">
+        <v>1275</v>
+      </c>
+      <c r="Y123" s="91" t="s">
+        <v>1305</v>
+      </c>
+      <c r="Z123" s="62"/>
+      <c r="AA123" s="62"/>
+      <c r="AB123" s="62"/>
+      <c r="AC123" s="62"/>
+      <c r="AD123" s="62"/>
+      <c r="AE123" s="62"/>
+      <c r="AF123" s="62"/>
+      <c r="AG123" s="62"/>
+      <c r="AH123" s="62"/>
+      <c r="AI123" s="62"/>
+      <c r="AJ123" s="62"/>
+      <c r="AK123" s="62"/>
+      <c r="AL123" s="62"/>
+      <c r="AM123" s="62"/>
+      <c r="AQ123" s="15" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="124" spans="1:53" ht="15">
+      <c r="B124" s="15" t="s">
+        <v>1276</v>
+      </c>
+      <c r="Y124" s="99" t="s">
+        <v>1306</v>
+      </c>
+      <c r="Z124" s="62"/>
+      <c r="AA124" s="62"/>
+      <c r="AB124" s="62"/>
+      <c r="AC124" s="62"/>
+      <c r="AD124" s="62"/>
+      <c r="AE124" s="62"/>
+      <c r="AF124" s="62"/>
+      <c r="AG124" s="62"/>
+      <c r="AH124" s="62"/>
+      <c r="AI124" s="62"/>
+      <c r="AJ124" s="62"/>
+      <c r="AK124" s="62"/>
+      <c r="AL124" s="62"/>
+      <c r="AM124" s="62"/>
+    </row>
+    <row r="125" spans="1:53" ht="15">
+      <c r="B125" s="15" t="s">
+        <v>1277</v>
+      </c>
+      <c r="Y125" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AQ125" s="97" t="s">
+        <v>1322</v>
+      </c>
+      <c r="AR125" s="98"/>
+      <c r="AS125" s="98"/>
+      <c r="AT125" s="98"/>
+      <c r="AU125" s="98"/>
+      <c r="AV125" s="98"/>
+      <c r="AW125" s="98"/>
+      <c r="AX125" s="98"/>
+      <c r="AY125" s="98"/>
+      <c r="AZ125" s="98"/>
+      <c r="BA125" s="98"/>
+    </row>
+    <row r="126" spans="1:53" ht="15">
+      <c r="B126" s="15" t="s">
+        <v>1278</v>
+      </c>
+      <c r="AQ126" s="100" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="127" spans="1:53" ht="15">
+      <c r="B127" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="Y127" s="97" t="s">
+        <v>1307</v>
+      </c>
+      <c r="Z127" s="98"/>
+      <c r="AA127" s="98"/>
+      <c r="AB127" s="98"/>
+      <c r="AC127" s="98"/>
+      <c r="AD127" s="98"/>
+      <c r="AE127" s="98"/>
+      <c r="AF127" s="98"/>
+      <c r="AG127" s="98"/>
+      <c r="AH127" s="98"/>
+      <c r="AI127" s="98"/>
+      <c r="AQ127" s="91" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="128" spans="1:53">
+      <c r="Y128" s="15" t="s">
+        <v>1308</v>
+      </c>
+      <c r="AQ128" s="69"/>
+    </row>
+    <row r="129" spans="2:58" ht="15">
+      <c r="B129" s="97" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C129" s="98"/>
+      <c r="D129" s="98"/>
+      <c r="E129" s="98"/>
+      <c r="F129" s="98"/>
+      <c r="Y129" s="15" t="s">
+        <v>1309</v>
+      </c>
+      <c r="AQ129" s="15" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="130" spans="2:58">
+      <c r="B130" s="15" t="s">
+        <v>1280</v>
+      </c>
+      <c r="Y130" s="15" t="s">
+        <v>1310</v>
+      </c>
+      <c r="AQ130" s="15" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="131" spans="2:58">
+      <c r="B131" s="15" t="s">
+        <v>1281</v>
+      </c>
+      <c r="Y131" s="15" t="s">
+        <v>1311</v>
+      </c>
+      <c r="AQ131" s="15" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="132" spans="2:58">
+      <c r="B132" s="15" t="s">
+        <v>1282</v>
+      </c>
+      <c r="Y132" s="69"/>
+      <c r="AQ132" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="133" spans="2:58" ht="15">
+      <c r="B133" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Y133" s="15" t="s">
+        <v>1312</v>
+      </c>
+      <c r="AQ133" s="99" t="s">
+        <v>1326</v>
+      </c>
+      <c r="AR133" s="87"/>
+      <c r="AS133" s="87"/>
+      <c r="AT133" s="87"/>
+      <c r="AU133" s="87"/>
+      <c r="AV133" s="87"/>
+      <c r="AW133" s="87"/>
+      <c r="AX133" s="87"/>
+      <c r="AY133" s="87"/>
+      <c r="AZ133" s="87"/>
+      <c r="BA133" s="87"/>
+      <c r="BB133" s="87"/>
+      <c r="BC133" s="87"/>
+      <c r="BD133" s="87"/>
+      <c r="BE133" s="87"/>
+      <c r="BF133" s="87"/>
+    </row>
+    <row r="134" spans="2:58" ht="15">
+      <c r="B134" s="15" t="s">
+        <v>1283</v>
+      </c>
+      <c r="Y134" s="91" t="s">
+        <v>1313</v>
+      </c>
+      <c r="Z134" s="62"/>
+      <c r="AA134" s="62"/>
+      <c r="AB134" s="62"/>
+      <c r="AC134" s="62"/>
+      <c r="AD134" s="62"/>
+      <c r="AE134" s="62"/>
+      <c r="AF134" s="62"/>
+      <c r="AG134" s="62"/>
+      <c r="AH134" s="62"/>
+      <c r="AI134" s="62"/>
+      <c r="AJ134" s="62"/>
+      <c r="AK134" s="62"/>
+      <c r="AL134" s="62"/>
+      <c r="AM134" s="62"/>
+      <c r="AQ134" s="99" t="s">
+        <v>1327</v>
+      </c>
+      <c r="AR134" s="87"/>
+      <c r="AS134" s="87"/>
+      <c r="AT134" s="87"/>
+      <c r="AU134" s="87"/>
+      <c r="AV134" s="87"/>
+      <c r="AW134" s="87"/>
+      <c r="AX134" s="87"/>
+      <c r="AY134" s="87"/>
+      <c r="AZ134" s="87"/>
+      <c r="BA134" s="87"/>
+      <c r="BB134" s="87"/>
+      <c r="BC134" s="87"/>
+      <c r="BD134" s="87"/>
+      <c r="BE134" s="87"/>
+      <c r="BF134" s="87"/>
+    </row>
+    <row r="135" spans="2:58" ht="15">
+      <c r="B135" s="15" t="s">
+        <v>1284</v>
+      </c>
+      <c r="Y135" s="99" t="s">
+        <v>1314</v>
+      </c>
+      <c r="Z135" s="62"/>
+      <c r="AA135" s="62"/>
+      <c r="AB135" s="62"/>
+      <c r="AC135" s="62"/>
+      <c r="AD135" s="62"/>
+      <c r="AE135" s="62"/>
+      <c r="AF135" s="62"/>
+      <c r="AG135" s="62"/>
+      <c r="AH135" s="62"/>
+      <c r="AI135" s="62"/>
+      <c r="AJ135" s="62"/>
+      <c r="AK135" s="62"/>
+      <c r="AL135" s="62"/>
+      <c r="AM135" s="62"/>
+      <c r="AQ135" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="136" spans="2:58">
+      <c r="B136" s="15" t="s">
+        <v>1285</v>
+      </c>
+      <c r="Y136" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AQ136" s="15" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="137" spans="2:58">
+      <c r="B137" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AQ137" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="138" spans="2:58">
+      <c r="B138" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="139" spans="2:58">
+      <c r="B139" s="15" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="140" spans="2:58">
+      <c r="B140" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="141" spans="2:58">
+      <c r="B141" s="15" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="142" spans="2:58">
+      <c r="B142" s="15" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="143" spans="2:58">
+      <c r="B143" s="15" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="144" spans="2:58">
+      <c r="B144" s="15" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="145" spans="2:12">
+      <c r="B145" s="15" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="146" spans="2:12">
+      <c r="B146" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="147" spans="2:12">
+      <c r="B147" s="15" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="148" spans="2:12">
+      <c r="B148" s="15" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="149" spans="2:12">
+      <c r="B149" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="151" spans="2:12" ht="15">
+      <c r="B151" s="97" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C151" s="98"/>
+      <c r="D151" s="98"/>
+      <c r="E151" s="98"/>
+      <c r="F151" s="98"/>
+      <c r="G151" s="98"/>
+      <c r="H151" s="98"/>
+      <c r="I151" s="98"/>
+    </row>
+    <row r="152" spans="2:12">
+      <c r="B152" s="15" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="153" spans="2:12">
+      <c r="B153" s="15" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="154" spans="2:12">
+      <c r="B154" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="155" spans="2:12">
+      <c r="B155" s="15" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="156" spans="2:12">
+      <c r="B156" s="15" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="157" spans="2:12">
+      <c r="B157" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="158" spans="2:12">
+      <c r="B158" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="160" spans="2:12" ht="15">
+      <c r="B160" s="43" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C160" s="44"/>
+      <c r="D160" s="44"/>
+      <c r="E160" s="44"/>
+      <c r="F160" s="44"/>
+      <c r="G160" s="44"/>
+      <c r="H160" s="44"/>
+      <c r="I160" s="44"/>
+      <c r="J160" s="44"/>
+      <c r="K160" s="44"/>
+      <c r="L160" s="44"/>
+    </row>
+    <row r="161" spans="2:52" ht="15">
+      <c r="B161" s="101" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C161" s="102"/>
+      <c r="D161" s="102"/>
+      <c r="E161" s="102"/>
+      <c r="F161" s="102"/>
+      <c r="G161" s="102"/>
+      <c r="U161" s="101" t="s">
+        <v>1338</v>
+      </c>
+      <c r="V161" s="102"/>
+      <c r="W161" s="102"/>
+      <c r="X161" s="102"/>
+      <c r="Y161" s="102"/>
+      <c r="Z161" s="102"/>
+      <c r="AS161" s="101" t="s">
+        <v>1352</v>
+      </c>
+      <c r="AT161" s="102"/>
+      <c r="AU161" s="102"/>
+      <c r="AV161" s="102"/>
+      <c r="AW161" s="102"/>
+      <c r="AX161" s="102"/>
+    </row>
+    <row r="162" spans="2:52" ht="15">
+      <c r="B162" s="15" t="s">
+        <v>1331</v>
+      </c>
+      <c r="U162" s="15" t="s">
+        <v>1339</v>
+      </c>
+      <c r="AS162" s="99" t="s">
+        <v>1353</v>
+      </c>
+      <c r="AT162" s="87"/>
+      <c r="AU162" s="87"/>
+      <c r="AV162" s="87"/>
+      <c r="AW162" s="87"/>
+      <c r="AX162" s="87"/>
+      <c r="AY162" s="87"/>
+    </row>
+    <row r="163" spans="2:52">
+      <c r="B163" s="15" t="s">
+        <v>1332</v>
+      </c>
+      <c r="U163" s="15" t="s">
+        <v>1340</v>
+      </c>
+      <c r="AS163" s="15" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="164" spans="2:52">
+      <c r="B164" s="69"/>
+      <c r="U164" s="15" t="s">
+        <v>1341</v>
+      </c>
+      <c r="AS164" s="15" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="165" spans="2:52">
+      <c r="B165" s="15" t="s">
+        <v>1333</v>
+      </c>
+      <c r="U165" s="15" t="s">
+        <v>1342</v>
+      </c>
+      <c r="AS165" s="15" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="166" spans="2:52">
+      <c r="B166" s="15" t="s">
+        <v>1334</v>
+      </c>
+      <c r="U166" s="15" t="s">
+        <v>1343</v>
+      </c>
+      <c r="AS166" s="69"/>
+    </row>
+    <row r="167" spans="2:52" ht="15">
+      <c r="B167" s="15" t="s">
+        <v>1335</v>
+      </c>
+      <c r="U167" s="99" t="s">
+        <v>1341</v>
+      </c>
+      <c r="V167" s="87"/>
+      <c r="W167" s="87"/>
+      <c r="X167" s="87"/>
+      <c r="Y167" s="87"/>
+      <c r="Z167" s="87"/>
+      <c r="AS167" s="99" t="s">
+        <v>1356</v>
+      </c>
+      <c r="AT167" s="87"/>
+      <c r="AU167" s="87"/>
+      <c r="AV167" s="87"/>
+      <c r="AW167" s="87"/>
+      <c r="AX167" s="87"/>
+      <c r="AY167" s="87"/>
+      <c r="AZ167" s="87"/>
+    </row>
+    <row r="168" spans="2:52">
+      <c r="B168" s="15" t="s">
+        <v>1336</v>
+      </c>
+      <c r="U168" s="15" t="s">
+        <v>1344</v>
+      </c>
+      <c r="AS168" s="15" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="169" spans="2:52">
+      <c r="B169" s="15" t="s">
+        <v>1337</v>
+      </c>
+      <c r="U169" s="15" t="s">
+        <v>1345</v>
+      </c>
+      <c r="AS169" s="15" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="170" spans="2:52">
+      <c r="B170" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="U170" s="69"/>
+      <c r="AS170" s="15" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="171" spans="2:52">
+      <c r="U171" s="15" t="s">
+        <v>1346</v>
+      </c>
+      <c r="AS171" s="15" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="172" spans="2:52">
+      <c r="U172" s="15" t="s">
+        <v>1342</v>
+      </c>
+      <c r="AS172" s="15" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="173" spans="2:52">
+      <c r="U173" s="15" t="s">
+        <v>1340</v>
+      </c>
+      <c r="AS173" s="69"/>
+    </row>
+    <row r="174" spans="2:52" ht="15">
+      <c r="U174" s="15" t="s">
+        <v>1343</v>
+      </c>
+      <c r="AS174" s="99" t="s">
+        <v>1362</v>
+      </c>
+      <c r="AT174" s="87"/>
+      <c r="AU174" s="87"/>
+      <c r="AV174" s="87"/>
+      <c r="AW174" s="87"/>
+      <c r="AX174" s="87"/>
+      <c r="AY174" s="87"/>
+      <c r="AZ174" s="87"/>
+    </row>
+    <row r="175" spans="2:52" ht="15">
+      <c r="U175" s="99" t="s">
+        <v>1347</v>
+      </c>
+      <c r="V175" s="87"/>
+      <c r="W175" s="87"/>
+      <c r="X175" s="87"/>
+      <c r="Y175" s="87"/>
+      <c r="Z175" s="87"/>
+      <c r="AS175" s="15" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="176" spans="2:52">
+      <c r="U176" s="15" t="s">
+        <v>1344</v>
+      </c>
+      <c r="AS176" s="15" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="177" spans="1:47">
+      <c r="U177" s="15" t="s">
+        <v>1348</v>
+      </c>
+      <c r="AS177" s="15" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="178" spans="1:47">
+      <c r="U178" s="69"/>
+      <c r="AS178" s="15" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="179" spans="1:47">
+      <c r="U179" s="15" t="s">
+        <v>1349</v>
+      </c>
+      <c r="AS179" s="15" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="180" spans="1:47">
+      <c r="U180" s="15" t="s">
+        <v>1350</v>
+      </c>
+      <c r="AS180" s="15" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="181" spans="1:47">
+      <c r="U181" s="15" t="s">
+        <v>1351</v>
+      </c>
+      <c r="AS181" s="15" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="182" spans="1:47">
+      <c r="U182" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="183" spans="1:47" ht="15" thickBot="1"/>
+    <row r="184" spans="1:47" s="16" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A184" s="95"/>
+      <c r="B184" s="96" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="185" spans="1:47" ht="15">
+      <c r="B185" s="43" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C185" s="44"/>
+      <c r="D185" s="44"/>
+      <c r="E185" s="44"/>
+      <c r="F185" s="44"/>
+      <c r="G185" s="44"/>
+      <c r="H185" s="44"/>
+      <c r="I185" s="44"/>
+      <c r="T185" s="43" t="s">
+        <v>1374</v>
+      </c>
+      <c r="U185" s="44"/>
+      <c r="V185" s="44"/>
+      <c r="W185" s="44"/>
+      <c r="X185" s="44"/>
+      <c r="Y185" s="44"/>
+      <c r="Z185" s="44"/>
+      <c r="AM185" s="43" t="s">
+        <v>1381</v>
+      </c>
+      <c r="AN185" s="44"/>
+      <c r="AO185" s="44"/>
+      <c r="AP185" s="44"/>
+      <c r="AQ185" s="44"/>
+      <c r="AR185" s="44"/>
+      <c r="AS185" s="44"/>
+      <c r="AT185" s="44"/>
+      <c r="AU185" s="44"/>
+    </row>
+    <row r="186" spans="1:47">
+      <c r="B186" s="15" t="s">
+        <v>1368</v>
+      </c>
+      <c r="T186" s="15" t="s">
+        <v>1375</v>
+      </c>
+      <c r="AM186" s="15" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="187" spans="1:47">
+      <c r="B187" s="15" t="s">
+        <v>1369</v>
+      </c>
+      <c r="T187" s="15" t="s">
+        <v>1376</v>
+      </c>
+      <c r="AM187" s="69"/>
+    </row>
+    <row r="188" spans="1:47">
+      <c r="B188" s="15" t="s">
+        <v>1370</v>
+      </c>
+      <c r="T188" s="15" t="s">
+        <v>1377</v>
+      </c>
+      <c r="AM188" s="15" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="189" spans="1:47">
+      <c r="B189" s="15" t="s">
+        <v>1371</v>
+      </c>
+      <c r="T189" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AM189" s="15" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="190" spans="1:47">
+      <c r="B190" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="T190" s="69"/>
+      <c r="AM190" s="15" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="191" spans="1:47">
+      <c r="B191" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="T191" s="15" t="s">
+        <v>1378</v>
+      </c>
+      <c r="AM191" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="192" spans="1:47">
+      <c r="B192" s="15" t="s">
+        <v>1372</v>
+      </c>
+      <c r="T192" s="15" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="193" spans="1:44">
+      <c r="B193" s="15" t="s">
+        <v>1373</v>
+      </c>
+      <c r="T193" s="15" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="194" spans="1:44">
+      <c r="B194" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="T194" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="196" spans="1:44" ht="15">
+      <c r="B196" s="43" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C196" s="44"/>
+      <c r="D196" s="44"/>
+      <c r="E196" s="44"/>
+      <c r="F196" s="44"/>
+      <c r="G196" s="44"/>
+      <c r="H196" s="44"/>
+      <c r="I196" s="44"/>
+      <c r="J196" s="44"/>
+      <c r="K196" s="44"/>
+      <c r="L196" s="44"/>
+      <c r="T196" s="43" t="s">
+        <v>1390</v>
+      </c>
+      <c r="U196" s="44"/>
+      <c r="V196" s="44"/>
+      <c r="W196" s="44"/>
+      <c r="X196" s="44"/>
+      <c r="Y196" s="44"/>
+      <c r="Z196" s="44"/>
+      <c r="AA196" s="44"/>
+      <c r="AB196" s="44"/>
+      <c r="AC196" s="44"/>
+    </row>
+    <row r="197" spans="1:44">
+      <c r="B197" s="15" t="s">
+        <v>1161</v>
+      </c>
+      <c r="T197" s="15" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="198" spans="1:44">
+      <c r="B198" s="15" t="s">
+        <v>1387</v>
+      </c>
+      <c r="T198" s="69"/>
+    </row>
+    <row r="199" spans="1:44">
+      <c r="B199" s="15" t="s">
+        <v>1388</v>
+      </c>
+      <c r="T199" s="15" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="200" spans="1:44">
+      <c r="B200" s="69"/>
+      <c r="T200" s="15" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="201" spans="1:44">
+      <c r="B201" s="91" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C201" s="62"/>
+      <c r="D201" s="62"/>
+      <c r="E201" s="62"/>
+      <c r="F201" s="62"/>
+      <c r="G201" s="62"/>
+      <c r="H201" s="62"/>
+      <c r="I201" s="62"/>
+      <c r="J201" s="62"/>
+      <c r="K201" s="62"/>
+      <c r="L201" s="62"/>
+      <c r="M201" s="62"/>
+      <c r="N201" s="62"/>
+      <c r="T201" s="15" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="202" spans="1:44">
+      <c r="B202" s="91" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C202" s="62"/>
+      <c r="D202" s="62"/>
+      <c r="E202" s="62"/>
+      <c r="F202" s="62"/>
+      <c r="G202" s="62"/>
+      <c r="H202" s="62"/>
+      <c r="I202" s="62"/>
+      <c r="J202" s="62"/>
+      <c r="K202" s="62"/>
+      <c r="L202" s="62"/>
+      <c r="M202" s="62"/>
+      <c r="N202" s="62"/>
+      <c r="T202" s="15" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="203" spans="1:44">
+      <c r="B203" s="91" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C203" s="62"/>
+      <c r="D203" s="62"/>
+      <c r="E203" s="62"/>
+      <c r="F203" s="62"/>
+      <c r="G203" s="62"/>
+      <c r="H203" s="62"/>
+      <c r="I203" s="62"/>
+      <c r="J203" s="62"/>
+      <c r="K203" s="62"/>
+      <c r="L203" s="62"/>
+      <c r="M203" s="62"/>
+      <c r="N203" s="62"/>
+      <c r="T203" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="204" spans="1:44" ht="15" thickBot="1"/>
+    <row r="205" spans="1:44" s="16" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A205" s="95"/>
+      <c r="B205" s="96" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="206" spans="1:44" ht="15" thickBot="1"/>
+    <row r="207" spans="1:44" ht="15">
+      <c r="B207" s="18" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C207" s="19"/>
+      <c r="D207" s="19"/>
+      <c r="E207" s="19"/>
+      <c r="F207" s="19"/>
+      <c r="G207" s="19"/>
+      <c r="H207" s="19"/>
+      <c r="I207" s="19"/>
+      <c r="J207" s="19"/>
+      <c r="K207" s="19"/>
+      <c r="L207" s="20"/>
+      <c r="R207" s="18" t="s">
+        <v>1397</v>
+      </c>
+      <c r="S207" s="19"/>
+      <c r="T207" s="19"/>
+      <c r="U207" s="19"/>
+      <c r="V207" s="19"/>
+      <c r="W207" s="19"/>
+      <c r="X207" s="19"/>
+      <c r="Y207" s="19"/>
+      <c r="Z207" s="19"/>
+      <c r="AA207" s="19"/>
+      <c r="AB207" s="20"/>
+      <c r="AH207" s="18" t="s">
+        <v>1402</v>
+      </c>
+      <c r="AI207" s="19"/>
+      <c r="AJ207" s="19"/>
+      <c r="AK207" s="19"/>
+      <c r="AL207" s="19"/>
+      <c r="AM207" s="19"/>
+      <c r="AN207" s="19"/>
+      <c r="AO207" s="19"/>
+      <c r="AP207" s="19"/>
+      <c r="AQ207" s="19"/>
+      <c r="AR207" s="20"/>
+    </row>
+    <row r="208" spans="1:44">
+      <c r="B208" s="34" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C208" s="23"/>
+      <c r="D208" s="23"/>
+      <c r="E208" s="23"/>
+      <c r="F208" s="23"/>
+      <c r="G208" s="23"/>
+      <c r="H208" s="23"/>
+      <c r="I208" s="23"/>
+      <c r="J208" s="23"/>
+      <c r="K208" s="23"/>
+      <c r="L208" s="24"/>
+      <c r="R208" s="34" t="s">
+        <v>1398</v>
+      </c>
+      <c r="S208" s="23"/>
+      <c r="T208" s="23"/>
+      <c r="U208" s="23"/>
+      <c r="V208" s="23"/>
+      <c r="W208" s="23"/>
+      <c r="X208" s="23"/>
+      <c r="Y208" s="23"/>
+      <c r="Z208" s="23"/>
+      <c r="AA208" s="23"/>
+      <c r="AB208" s="24"/>
+      <c r="AH208" s="34" t="s">
+        <v>1403</v>
+      </c>
+      <c r="AI208" s="23"/>
+      <c r="AJ208" s="23"/>
+      <c r="AK208" s="23"/>
+      <c r="AL208" s="23"/>
+      <c r="AM208" s="23"/>
+      <c r="AN208" s="23"/>
+      <c r="AO208" s="23"/>
+      <c r="AP208" s="23"/>
+      <c r="AQ208" s="23"/>
+      <c r="AR208" s="24"/>
+    </row>
+    <row r="209" spans="2:44">
+      <c r="B209" s="34" t="s">
         <v>1412</v>
       </c>
-    </row>
-    <row r="10" spans="2:2">
-      <c r="B10" s="13" t="s">
-        <v>1413</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" s="13" t="s">
-        <v>1414</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="15" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="15" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2">
-      <c r="B15" s="15" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2">
-      <c r="B16" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" ht="15">
-      <c r="B18" s="70" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="13"/>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="13" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" s="13" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="13" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23" s="13" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" ht="15">
-      <c r="B25" s="70" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27" s="15" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="15" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="15" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2">
-      <c r="B30" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2">
-      <c r="B31" s="15" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" ht="15">
-      <c r="B33" s="10" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" ht="15">
-      <c r="B35" s="70" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="13"/>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="13" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38" s="13" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39" s="13" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2">
-      <c r="B41" s="15" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2">
-      <c r="B42" s="15" t="s">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2">
-      <c r="B43" s="15" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2">
-      <c r="B44" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2">
-      <c r="B45" s="15" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2">
-      <c r="B46" s="15" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2">
-      <c r="B47" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2">
-      <c r="B48" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2">
-      <c r="B49" s="15" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2">
-      <c r="B50" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" ht="15">
-      <c r="B52" s="70" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" s="13"/>
-    </row>
-    <row r="54" spans="2:2">
-      <c r="B54" s="13" t="s">
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2">
-      <c r="B55" s="13" t="s">
-        <v>1089</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2">
-      <c r="B56" s="13" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2" ht="15">
-      <c r="B58" s="70" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2">
-      <c r="B60" s="15" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2">
-      <c r="B61" s="15" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="62" spans="2:2">
-      <c r="B62" s="15" t="s">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2">
-      <c r="B63" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" ht="15">
-      <c r="B65" s="10" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" ht="15">
-      <c r="B67" s="10" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2" ht="15">
-      <c r="B69" s="70" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2">
-      <c r="B70" s="13"/>
-    </row>
-    <row r="71" spans="2:2">
-      <c r="B71" s="13" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2">
-      <c r="B72" s="13" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2">
-      <c r="B73" s="13" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2">
-      <c r="B75" s="15" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2">
-      <c r="B76" s="15" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2">
-      <c r="B77" s="15" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2">
-      <c r="B78" s="15" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2">
-      <c r="B79" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2">
-      <c r="B80" s="72"/>
-    </row>
-    <row r="81" spans="2:2">
-      <c r="B81" s="15" t="s">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2">
-      <c r="B82" s="15" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2">
-      <c r="B83" s="15" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2">
-      <c r="B84" s="15" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2">
-      <c r="B85" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2" ht="15">
-      <c r="B87" s="70" t="s">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="89" spans="2:2">
-      <c r="B89" s="15" t="s">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2">
-      <c r="B90" s="15" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="91" spans="2:2">
-      <c r="B91" s="15" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="92" spans="2:2">
-      <c r="B92" s="15" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="93" spans="2:2">
-      <c r="B93" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2">
-      <c r="B94" s="72"/>
-    </row>
-    <row r="95" spans="2:2">
-      <c r="B95" s="15" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2">
-      <c r="B96" s="15" t="s">
-        <v>1113</v>
-      </c>
-    </row>
-    <row r="97" spans="2:2">
-      <c r="B97" s="15" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="98" spans="2:2">
-      <c r="B98" s="15" t="s">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="99" spans="2:2">
-      <c r="B99" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2">
-      <c r="B100" s="15" t="s">
-        <v>1115</v>
-      </c>
-    </row>
-    <row r="101" spans="2:2">
-      <c r="B101" s="15" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="102" spans="2:2">
-      <c r="B102" s="15" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="103" spans="2:2">
-      <c r="B103" s="15" t="s">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="104" spans="2:2">
-      <c r="B104" s="15" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="105" spans="2:2">
-      <c r="B105" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2" ht="15">
-      <c r="B107" s="10" t="s">
-        <v>1119</v>
-      </c>
-    </row>
-    <row r="109" spans="2:2" ht="15">
-      <c r="B109" s="70" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="110" spans="2:2">
-      <c r="B110" s="13"/>
-    </row>
-    <row r="111" spans="2:2">
-      <c r="B111" s="13" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="112" spans="2:2">
-      <c r="B112" s="13" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="113" spans="2:2">
-      <c r="B113" s="13" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="115" spans="2:2">
-      <c r="B115" s="15" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="116" spans="2:2">
-      <c r="B116" s="15" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="117" spans="2:2">
-      <c r="B117" s="72"/>
-    </row>
-    <row r="118" spans="2:2">
-      <c r="B118" s="15" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="119" spans="2:2">
-      <c r="B119" s="15" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="120" spans="2:2">
-      <c r="B120" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="121" spans="2:2">
-      <c r="B121" s="72"/>
-    </row>
-    <row r="122" spans="2:2">
-      <c r="B122" s="15" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="123" spans="2:2">
-      <c r="B123" s="15" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="124" spans="2:2">
-      <c r="B124" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="126" spans="2:2">
-      <c r="B126" s="15" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="127" spans="2:2">
-      <c r="B127" s="15" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="129" spans="2:2" ht="15">
-      <c r="B129" s="70" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="131" spans="2:2">
-      <c r="B131" s="15" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="132" spans="2:2">
-      <c r="B132" s="15" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="133" spans="2:2">
-      <c r="B133" s="72"/>
-    </row>
-    <row r="134" spans="2:2">
-      <c r="B134" s="15" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="135" spans="2:2">
-      <c r="B135" s="15" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="136" spans="2:2">
-      <c r="B136" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="137" spans="2:2">
-      <c r="B137" s="72"/>
-    </row>
-    <row r="138" spans="2:2">
-      <c r="B138" s="15" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="139" spans="2:2">
-      <c r="B139" s="15" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="140" spans="2:2">
-      <c r="B140" s="15" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="141" spans="2:2">
-      <c r="B141" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="143" spans="2:2" ht="15">
-      <c r="B143" s="10" t="s">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="145" spans="2:2" ht="15">
-      <c r="B145" s="70" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="146" spans="2:2">
-      <c r="B146" s="13"/>
-    </row>
-    <row r="147" spans="2:2">
-      <c r="B147" s="13" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="148" spans="2:2">
-      <c r="B148" s="13" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="149" spans="2:2">
-      <c r="B149" s="13" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="151" spans="2:2">
-      <c r="B151" s="15" t="s">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="152" spans="2:2">
-      <c r="B152" s="15" t="s">
-        <v>1144</v>
-      </c>
-    </row>
-    <row r="153" spans="2:2">
-      <c r="B153" s="15" t="s">
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="154" spans="2:2">
-      <c r="B154" s="72"/>
-    </row>
-    <row r="155" spans="2:2">
-      <c r="B155" s="15" t="s">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="156" spans="2:2">
-      <c r="B156" s="15" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="157" spans="2:2">
-      <c r="B157" s="15" t="s">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="158" spans="2:2">
-      <c r="B158" s="15" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="159" spans="2:2">
-      <c r="B159" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="160" spans="2:2">
-      <c r="B160" s="72"/>
-    </row>
-    <row r="161" spans="2:2">
-      <c r="B161" s="15" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="162" spans="2:2">
-      <c r="B162" s="15" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="163" spans="2:2">
-      <c r="B163" s="15" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="164" spans="2:2">
-      <c r="B164" s="15" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="165" spans="2:2">
-      <c r="B165" s="15" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="166" spans="2:2">
-      <c r="B166" s="15" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="167" spans="2:2">
-      <c r="B167" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="169" spans="2:2" ht="15">
-      <c r="B169" s="70" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="171" spans="2:2">
-      <c r="B171" s="15" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="172" spans="2:2">
-      <c r="B172" s="15" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="173" spans="2:2">
-      <c r="B173" s="15" t="s">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="174" spans="2:2">
-      <c r="B174" s="72"/>
-    </row>
-    <row r="175" spans="2:2">
-      <c r="B175" s="15" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="176" spans="2:2">
-      <c r="B176" s="15" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="178" spans="2:2" ht="15">
-      <c r="B178" s="70" t="s">
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="180" spans="2:2">
-      <c r="B180" s="15" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="181" spans="2:2">
-      <c r="B181" s="15" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="182" spans="2:2">
-      <c r="B182" s="72"/>
-    </row>
-    <row r="183" spans="2:2">
-      <c r="B183" s="15" t="s">
-        <v>1163</v>
-      </c>
-    </row>
-    <row r="185" spans="2:2" ht="15">
-      <c r="B185" s="70" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="187" spans="2:2">
-      <c r="B187" s="15" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="188" spans="2:2">
-      <c r="B188" s="15" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="189" spans="2:2">
-      <c r="B189" s="72"/>
-    </row>
-    <row r="190" spans="2:2">
-      <c r="B190" s="15" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="191" spans="2:2">
-      <c r="B191" s="15" t="s">
-        <v>1167</v>
-      </c>
-    </row>
-    <row r="193" spans="2:2" ht="15">
-      <c r="B193" s="10" t="s">
-        <v>1168</v>
-      </c>
-    </row>
-    <row r="195" spans="2:2" ht="15">
-      <c r="B195" s="70" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="196" spans="2:2">
-      <c r="B196" s="13"/>
-    </row>
-    <row r="197" spans="2:2">
-      <c r="B197" s="13" t="s">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="198" spans="2:2">
-      <c r="B198" s="13" t="s">
-        <v>1416</v>
-      </c>
-    </row>
-    <row r="200" spans="2:2">
-      <c r="B200" s="15" t="s">
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="201" spans="2:2">
-      <c r="B201" s="72"/>
-    </row>
-    <row r="202" spans="2:2">
-      <c r="B202" s="15" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="203" spans="2:2">
-      <c r="B203" s="72"/>
-    </row>
-    <row r="204" spans="2:2">
-      <c r="B204" s="15" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="205" spans="2:2">
-      <c r="B205" s="15" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="206" spans="2:2">
-      <c r="B206" s="15" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="207" spans="2:2">
-      <c r="B207" s="15" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="208" spans="2:2">
-      <c r="B208" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="209" spans="2:2">
-      <c r="B209" s="72"/>
-    </row>
-    <row r="210" spans="2:2">
-      <c r="B210" s="15" t="s">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="211" spans="2:2">
-      <c r="B211" s="15" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="212" spans="2:2">
-      <c r="B212" s="15" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="213" spans="2:2">
-      <c r="B213" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="214" spans="2:2">
-      <c r="B214" s="15" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="215" spans="2:2">
-      <c r="B215" s="15" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="216" spans="2:2">
-      <c r="B216" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="217" spans="2:2">
-      <c r="B217" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="218" spans="2:2">
-      <c r="B218" s="15" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="219" spans="2:2">
-      <c r="B219" s="15" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="220" spans="2:2">
-      <c r="B220" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="221" spans="2:2">
-      <c r="B221" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="223" spans="2:2" ht="15">
-      <c r="B223" s="70" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="225" spans="2:2">
-      <c r="B225" s="15" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="226" spans="2:2">
-      <c r="B226" s="15" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="227" spans="2:2">
-      <c r="B227" s="72"/>
-    </row>
-    <row r="228" spans="2:2">
-      <c r="B228" s="15" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="229" spans="2:2">
-      <c r="B229" s="15" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="230" spans="2:2">
-      <c r="B230" s="15" t="s">
-        <v>1185</v>
-      </c>
-    </row>
-    <row r="231" spans="2:2">
-      <c r="B231" s="15" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="232" spans="2:2">
-      <c r="B232" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="233" spans="2:2">
-      <c r="B233" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="234" spans="2:2">
-      <c r="B234" s="72"/>
-    </row>
-    <row r="235" spans="2:2">
-      <c r="B235" s="15" t="s">
-        <v>1187</v>
-      </c>
-    </row>
-    <row r="236" spans="2:2">
-      <c r="B236" s="15" t="s">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="237" spans="2:2">
-      <c r="B237" s="15" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="238" spans="2:2">
-      <c r="B238" s="15" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="239" spans="2:2">
-      <c r="B239" s="15" t="s">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="240" spans="2:2">
-      <c r="B240" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="241" spans="2:2">
-      <c r="B241" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="243" spans="2:2" ht="15">
-      <c r="B243" s="10" t="s">
-        <v>1192</v>
-      </c>
-    </row>
-    <row r="245" spans="2:2" ht="15">
-      <c r="B245" s="10" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="247" spans="2:2" ht="15">
-      <c r="B247" s="70" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="249" spans="2:2">
-      <c r="B249" s="15" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="250" spans="2:2">
-      <c r="B250" s="15" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="251" spans="2:2">
-      <c r="B251" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="252" spans="2:2">
-      <c r="B252" s="15" t="s">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="253" spans="2:2">
-      <c r="B253" s="15" t="s">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="254" spans="2:2">
-      <c r="B254" s="15" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="255" spans="2:2">
-      <c r="B255" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="256" spans="2:2">
-      <c r="B256" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="257" spans="2:2">
-      <c r="B257" s="15" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="258" spans="2:2">
-      <c r="B258" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="259" spans="2:2">
-      <c r="B259" s="15" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="260" spans="2:2">
-      <c r="B260" s="15" t="s">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="261" spans="2:2">
-      <c r="B261" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="262" spans="2:2">
-      <c r="B262" s="15" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="263" spans="2:2">
-      <c r="B263" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="265" spans="2:2" ht="15">
-      <c r="B265" s="70" t="s">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="267" spans="2:2">
-      <c r="B267" s="15" t="s">
-        <v>1205</v>
-      </c>
-    </row>
-    <row r="268" spans="2:2">
-      <c r="B268" s="15" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="269" spans="2:2">
-      <c r="B269" s="15" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="270" spans="2:2">
-      <c r="B270" s="72"/>
-    </row>
-    <row r="271" spans="2:2">
-      <c r="B271" s="15" t="s">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="272" spans="2:2">
-      <c r="B272" s="15" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="273" spans="2:2">
-      <c r="B273" s="15" t="s">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="274" spans="2:2">
-      <c r="B274" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="275" spans="2:2">
-      <c r="B275" s="72"/>
-    </row>
-    <row r="276" spans="2:2">
-      <c r="B276" s="15" t="s">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="277" spans="2:2">
-      <c r="B277" s="15" t="s">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="278" spans="2:2">
-      <c r="B278" s="15" t="s">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="279" spans="2:2">
-      <c r="B279" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="281" spans="2:2" ht="15">
-      <c r="B281" s="10" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="283" spans="2:2" ht="15">
-      <c r="B283" s="70" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="285" spans="2:2">
-      <c r="B285" s="15" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="286" spans="2:2">
-      <c r="B286" s="15" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="287" spans="2:2">
-      <c r="B287" s="15" t="s">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="288" spans="2:2">
-      <c r="B288" s="15" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-    <row r="289" spans="2:2">
-      <c r="B289" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="290" spans="2:2">
-      <c r="B290" s="72"/>
-    </row>
-    <row r="291" spans="2:2">
-      <c r="B291" s="15" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="292" spans="2:2">
-      <c r="B292" s="15" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="293" spans="2:2">
-      <c r="B293" s="15" t="s">
-        <v>1220</v>
-      </c>
-    </row>
-    <row r="294" spans="2:2">
-      <c r="B294" s="72"/>
-    </row>
-    <row r="295" spans="2:2">
-      <c r="B295" s="15" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="296" spans="2:2">
-      <c r="B296" s="15" t="s">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="297" spans="2:2">
-      <c r="B297" s="15" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="298" spans="2:2">
-      <c r="B298" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="300" spans="2:2" ht="15">
-      <c r="B300" s="70" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="302" spans="2:2">
-      <c r="B302" s="15" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="303" spans="2:2">
-      <c r="B303" s="15" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="304" spans="2:2">
-      <c r="B304" s="15" t="s">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="305" spans="2:2">
-      <c r="B305" s="15" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="306" spans="2:2">
-      <c r="B306" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="307" spans="2:2">
-      <c r="B307" s="72"/>
-    </row>
-    <row r="308" spans="2:2">
-      <c r="B308" s="15" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="309" spans="2:2">
-      <c r="B309" s="15" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="310" spans="2:2">
-      <c r="B310" s="15" t="s">
-        <v>1229</v>
-      </c>
-    </row>
-    <row r="312" spans="2:2" ht="15">
-      <c r="B312" s="10" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="314" spans="2:2" ht="15">
-      <c r="B314" s="70" t="s">
-        <v>1231</v>
-      </c>
-    </row>
-    <row r="316" spans="2:2">
-      <c r="B316" s="15" t="s">
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="317" spans="2:2">
-      <c r="B317" s="15" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="318" spans="2:2">
-      <c r="B318" s="15" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="319" spans="2:2">
-      <c r="B319" s="15" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="320" spans="2:2">
-      <c r="B320" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="321" spans="2:2">
-      <c r="B321" s="72"/>
-    </row>
-    <row r="322" spans="2:2">
-      <c r="B322" s="15" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="323" spans="2:2">
-      <c r="B323" s="15" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="324" spans="2:2">
-      <c r="B324" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="326" spans="2:2" ht="15">
-      <c r="B326" s="70" t="s">
-        <v>1238</v>
-      </c>
-    </row>
-    <row r="328" spans="2:2">
-      <c r="B328" s="15" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="329" spans="2:2">
-      <c r="B329" s="15" t="s">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="330" spans="2:2">
-      <c r="B330" s="15" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="331" spans="2:2">
-      <c r="B331" s="15" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="332" spans="2:2">
-      <c r="B332" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="333" spans="2:2">
-      <c r="B333" s="72"/>
-    </row>
-    <row r="334" spans="2:2">
-      <c r="B334" s="15" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="335" spans="2:2">
-      <c r="B335" s="15" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="336" spans="2:2">
-      <c r="B336" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="337" spans="2:2">
-      <c r="B337" s="72"/>
-    </row>
-    <row r="338" spans="2:2">
-      <c r="B338" s="15" t="s">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="339" spans="2:2">
-      <c r="B339" s="15" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="340" spans="2:2">
-      <c r="B340" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="342" spans="2:2" ht="15">
-      <c r="B342" s="10" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="344" spans="2:2" ht="15">
-      <c r="B344" s="70" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="346" spans="2:2">
-      <c r="B346" s="15" t="s">
-        <v>1249</v>
-      </c>
-    </row>
-    <row r="347" spans="2:2">
-      <c r="B347" s="72"/>
-    </row>
-    <row r="348" spans="2:2">
-      <c r="B348" s="15" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="349" spans="2:2">
-      <c r="B349" s="15" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="350" spans="2:2">
-      <c r="B350" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="351" spans="2:2">
-      <c r="B351" s="15" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="352" spans="2:2">
-      <c r="B352" s="15" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="353" spans="2:2">
-      <c r="B353" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="354" spans="2:2">
-      <c r="B354" s="15" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="355" spans="2:2">
-      <c r="B355" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="357" spans="2:2" ht="15">
-      <c r="B357" s="70" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="359" spans="2:2">
-      <c r="B359" s="15" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="360" spans="2:2">
-      <c r="B360" s="72"/>
-    </row>
-    <row r="361" spans="2:2">
-      <c r="B361" s="15" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="362" spans="2:2">
-      <c r="B362" s="15" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="363" spans="2:2">
-      <c r="B363" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="364" spans="2:2">
-      <c r="B364" s="15" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="365" spans="2:2">
-      <c r="B365" s="15" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="366" spans="2:2">
-      <c r="B366" s="15" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="367" spans="2:2">
-      <c r="B367" s="15" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="368" spans="2:2">
-      <c r="B368" s="15" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="369" spans="2:2">
-      <c r="B369" s="15" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="370" spans="2:2">
-      <c r="B370" s="15" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="371" spans="2:2">
-      <c r="B371" s="15" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="372" spans="2:2">
-      <c r="B372" s="15" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="373" spans="2:2">
-      <c r="B373" s="15" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="374" spans="2:2">
-      <c r="B374" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="375" spans="2:2">
-      <c r="B375" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="376" spans="2:2">
-      <c r="B376" s="15" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="377" spans="2:2">
-      <c r="B377" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="379" spans="2:2" ht="15">
-      <c r="B379" s="10" t="s">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="381" spans="2:2" ht="15">
-      <c r="B381" s="10" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="383" spans="2:2" ht="15">
-      <c r="B383" s="70" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="385" spans="2:2">
-      <c r="B385" s="15" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="386" spans="2:2">
-      <c r="B386" s="15" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="387" spans="2:2">
-      <c r="B387" s="15" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="388" spans="2:2">
-      <c r="B388" s="15" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="389" spans="2:2">
-      <c r="B389" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="390" spans="2:2">
-      <c r="B390" s="15" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="391" spans="2:2">
-      <c r="B391" s="15" t="s">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="392" spans="2:2">
-      <c r="B392" s="15" t="s">
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="393" spans="2:2">
-      <c r="B393" s="15" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="394" spans="2:2">
-      <c r="B394" s="15" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="395" spans="2:2">
-      <c r="B395" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="397" spans="2:2" ht="15">
-      <c r="B397" s="70" t="s">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="399" spans="2:2">
-      <c r="B399" s="15" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="400" spans="2:2">
-      <c r="B400" s="15" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="401" spans="2:2">
-      <c r="B401" s="15" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="402" spans="2:2">
-      <c r="B402" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="403" spans="2:2">
-      <c r="B403" s="15" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="404" spans="2:2">
-      <c r="B404" s="15" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="405" spans="2:2">
-      <c r="B405" s="15" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="406" spans="2:2">
-      <c r="B406" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="407" spans="2:2">
-      <c r="B407" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="408" spans="2:2">
-      <c r="B408" s="15" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="409" spans="2:2">
-      <c r="B409" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="410" spans="2:2">
-      <c r="B410" s="15" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="411" spans="2:2">
-      <c r="B411" s="15" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="412" spans="2:2">
-      <c r="B412" s="15" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="413" spans="2:2">
-      <c r="B413" s="15" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="414" spans="2:2">
-      <c r="B414" s="15" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="415" spans="2:2">
-      <c r="B415" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="416" spans="2:2">
-      <c r="B416" s="15" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="417" spans="2:2">
-      <c r="B417" s="15" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="418" spans="2:2">
-      <c r="B418" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="420" spans="2:2" ht="15">
-      <c r="B420" s="70" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="422" spans="2:2">
-      <c r="B422" s="15" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="423" spans="2:2">
-      <c r="B423" s="15" t="s">
-        <v>1297</v>
-      </c>
-    </row>
-    <row r="424" spans="2:2">
-      <c r="B424" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="425" spans="2:2">
-      <c r="B425" s="15" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="426" spans="2:2">
-      <c r="B426" s="15" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="427" spans="2:2">
-      <c r="B427" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="428" spans="2:2">
-      <c r="B428" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="430" spans="2:2" ht="15">
-      <c r="B430" s="10" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="432" spans="2:2" ht="15">
-      <c r="B432" s="70" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="434" spans="2:2">
-      <c r="B434" s="15" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="435" spans="2:2">
-      <c r="B435" s="15" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="436" spans="2:2">
-      <c r="B436" s="15" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="437" spans="2:2">
-      <c r="B437" s="15" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="438" spans="2:2">
-      <c r="B438" s="72"/>
-    </row>
-    <row r="439" spans="2:2">
-      <c r="B439" s="15" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="440" spans="2:2">
-      <c r="B440" s="15" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="441" spans="2:2">
-      <c r="B441" s="15" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="442" spans="2:2">
-      <c r="B442" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="444" spans="2:2" ht="15">
-      <c r="B444" s="70" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="446" spans="2:2">
-      <c r="B446" s="15" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="447" spans="2:2">
-      <c r="B447" s="15" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="448" spans="2:2">
-      <c r="B448" s="15" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="449" spans="2:2">
-      <c r="B449" s="15" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="450" spans="2:2">
-      <c r="B450" s="72"/>
-    </row>
-    <row r="451" spans="2:2">
-      <c r="B451" s="15" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="452" spans="2:2">
-      <c r="B452" s="15" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="453" spans="2:2">
-      <c r="B453" s="15" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="454" spans="2:2">
-      <c r="B454" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="456" spans="2:2" ht="15">
-      <c r="B456" s="10" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="458" spans="2:2" ht="15">
-      <c r="B458" s="70" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="460" spans="2:2">
-      <c r="B460" s="15" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="461" spans="2:2">
-      <c r="B461" s="15" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="462" spans="2:2">
-      <c r="B462" s="15" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="463" spans="2:2">
-      <c r="B463" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="464" spans="2:2">
-      <c r="B464" s="72"/>
-    </row>
-    <row r="465" spans="2:2">
-      <c r="B465" s="15" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="466" spans="2:2">
-      <c r="B466" s="15" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="468" spans="2:2" ht="15">
-      <c r="B468" s="70" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="470" spans="2:2">
-      <c r="B470" s="15" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="471" spans="2:2">
-      <c r="B471" s="15" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="472" spans="2:2">
-      <c r="B472" s="72"/>
-    </row>
-    <row r="473" spans="2:2">
-      <c r="B473" s="15" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="474" spans="2:2">
-      <c r="B474" s="15" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="475" spans="2:2">
-      <c r="B475" s="15" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="476" spans="2:2">
-      <c r="B476" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="477" spans="2:2">
-      <c r="B477" s="15" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="478" spans="2:2">
-      <c r="B478" s="15" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="479" spans="2:2">
-      <c r="B479" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="480" spans="2:2">
-      <c r="B480" s="15" t="s">
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="481" spans="2:2">
-      <c r="B481" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="483" spans="2:2" ht="15">
-      <c r="B483" s="10" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="485" spans="2:2" ht="15">
-      <c r="B485" s="70" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="487" spans="2:2">
-      <c r="B487" s="15" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="488" spans="2:2">
-      <c r="B488" s="15" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="489" spans="2:2">
-      <c r="B489" s="72"/>
-    </row>
-    <row r="490" spans="2:2">
-      <c r="B490" s="15" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="491" spans="2:2">
-      <c r="B491" s="15" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="492" spans="2:2">
-      <c r="B492" s="15" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="493" spans="2:2">
-      <c r="B493" s="15" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="494" spans="2:2">
-      <c r="B494" s="15" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="495" spans="2:2">
-      <c r="B495" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="497" spans="2:2" ht="15">
-      <c r="B497" s="70" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="499" spans="2:2">
-      <c r="B499" s="15" t="s">
-        <v>1343</v>
-      </c>
-    </row>
-    <row r="500" spans="2:2">
-      <c r="B500" s="15" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="501" spans="2:2">
-      <c r="B501" s="15" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="502" spans="2:2">
-      <c r="B502" s="15" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="503" spans="2:2">
-      <c r="B503" s="15" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="504" spans="2:2">
-      <c r="B504" s="15" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="505" spans="2:2">
-      <c r="B505" s="15" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="506" spans="2:2">
-      <c r="B506" s="15" t="s">
-        <v>1349</v>
-      </c>
-    </row>
-    <row r="507" spans="2:2">
-      <c r="B507" s="72"/>
-    </row>
-    <row r="508" spans="2:2">
-      <c r="B508" s="15" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="509" spans="2:2">
-      <c r="B509" s="15" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="510" spans="2:2">
-      <c r="B510" s="15" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="511" spans="2:2">
-      <c r="B511" s="15" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="512" spans="2:2">
-      <c r="B512" s="15" t="s">
-        <v>1351</v>
-      </c>
-    </row>
-    <row r="513" spans="2:2">
-      <c r="B513" s="15" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="514" spans="2:2">
-      <c r="B514" s="15" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="515" spans="2:2">
-      <c r="B515" s="72"/>
-    </row>
-    <row r="516" spans="2:2">
-      <c r="B516" s="15" t="s">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="517" spans="2:2">
-      <c r="B517" s="15" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="518" spans="2:2">
-      <c r="B518" s="15" t="s">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="519" spans="2:2">
-      <c r="B519" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="521" spans="2:2" ht="15">
-      <c r="B521" s="70" t="s">
-        <v>1356</v>
-      </c>
-    </row>
-    <row r="523" spans="2:2">
-      <c r="B523" s="15" t="s">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="524" spans="2:2">
-      <c r="B524" s="15" t="s">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="525" spans="2:2">
-      <c r="B525" s="15" t="s">
-        <v>1359</v>
-      </c>
-    </row>
-    <row r="526" spans="2:2">
-      <c r="B526" s="15" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="527" spans="2:2">
-      <c r="B527" s="72"/>
-    </row>
-    <row r="528" spans="2:2">
-      <c r="B528" s="15" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="529" spans="2:2">
-      <c r="B529" s="15" t="s">
-        <v>1361</v>
-      </c>
-    </row>
-    <row r="530" spans="2:2">
-      <c r="B530" s="15" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="531" spans="2:2">
-      <c r="B531" s="15" t="s">
-        <v>1363</v>
-      </c>
-    </row>
-    <row r="532" spans="2:2">
-      <c r="B532" s="15" t="s">
-        <v>1364</v>
-      </c>
-    </row>
-    <row r="533" spans="2:2">
-      <c r="B533" s="15" t="s">
-        <v>1365</v>
-      </c>
-    </row>
-    <row r="534" spans="2:2">
-      <c r="B534" s="72"/>
-    </row>
-    <row r="535" spans="2:2">
-      <c r="B535" s="15" t="s">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="536" spans="2:2">
-      <c r="B536" s="15" t="s">
-        <v>1367</v>
-      </c>
-    </row>
-    <row r="537" spans="2:2">
-      <c r="B537" s="15" t="s">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="538" spans="2:2">
-      <c r="B538" s="15" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="539" spans="2:2">
-      <c r="B539" s="15" t="s">
-        <v>1363</v>
-      </c>
-    </row>
-    <row r="540" spans="2:2">
-      <c r="B540" s="15" t="s">
-        <v>1364</v>
-      </c>
-    </row>
-    <row r="541" spans="2:2">
-      <c r="B541" s="15" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="542" spans="2:2">
-      <c r="B542" s="15" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="544" spans="2:2" ht="15">
-      <c r="B544" s="10" t="s">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="546" spans="2:2" ht="15">
-      <c r="B546" s="10" t="s">
-        <v>1371</v>
-      </c>
-    </row>
-    <row r="548" spans="2:2">
-      <c r="B548" s="15" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="549" spans="2:2">
-      <c r="B549" s="15" t="s">
-        <v>1373</v>
-      </c>
-    </row>
-    <row r="550" spans="2:2">
-      <c r="B550" s="15" t="s">
-        <v>1374</v>
-      </c>
-    </row>
-    <row r="551" spans="2:2">
-      <c r="B551" s="15" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="552" spans="2:2">
-      <c r="B552" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="553" spans="2:2">
-      <c r="B553" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="554" spans="2:2">
-      <c r="B554" s="15" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="555" spans="2:2">
-      <c r="B555" s="15" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="556" spans="2:2">
-      <c r="B556" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="558" spans="2:2" ht="15">
-      <c r="B558" s="10" t="s">
-        <v>1378</v>
-      </c>
-    </row>
-    <row r="560" spans="2:2">
-      <c r="B560" s="15" t="s">
-        <v>1379</v>
-      </c>
-    </row>
-    <row r="561" spans="2:2">
-      <c r="B561" s="15" t="s">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="562" spans="2:2">
-      <c r="B562" s="15" t="s">
-        <v>1381</v>
-      </c>
-    </row>
-    <row r="563" spans="2:2">
-      <c r="B563" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="564" spans="2:2">
-      <c r="B564" s="72"/>
-    </row>
-    <row r="565" spans="2:2">
-      <c r="B565" s="15" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="566" spans="2:2">
-      <c r="B566" s="15" t="s">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="567" spans="2:2">
-      <c r="B567" s="15" t="s">
-        <v>1384</v>
-      </c>
-    </row>
-    <row r="568" spans="2:2">
-      <c r="B568" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="570" spans="2:2" ht="15">
-      <c r="B570" s="10" t="s">
-        <v>1385</v>
-      </c>
-    </row>
-    <row r="572" spans="2:2">
-      <c r="B572" s="15" t="s">
-        <v>1386</v>
-      </c>
-    </row>
-    <row r="573" spans="2:2">
-      <c r="B573" s="72"/>
-    </row>
-    <row r="574" spans="2:2">
-      <c r="B574" s="15" t="s">
-        <v>1387</v>
-      </c>
-    </row>
-    <row r="575" spans="2:2">
-      <c r="B575" s="15" t="s">
-        <v>1388</v>
-      </c>
-    </row>
-    <row r="576" spans="2:2">
-      <c r="B576" s="15" t="s">
-        <v>1389</v>
-      </c>
-    </row>
-    <row r="577" spans="2:2">
-      <c r="B577" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="579" spans="2:2" ht="15">
-      <c r="B579" s="10" t="s">
-        <v>1390</v>
-      </c>
-    </row>
-    <row r="581" spans="2:2">
-      <c r="B581" s="15" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="582" spans="2:2">
-      <c r="B582" s="15" t="s">
-        <v>1391</v>
-      </c>
-    </row>
-    <row r="583" spans="2:2">
-      <c r="B583" s="15" t="s">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="584" spans="2:2">
-      <c r="B584" s="72"/>
-    </row>
-    <row r="585" spans="2:2">
-      <c r="B585" s="15" t="s">
-        <v>1166</v>
-      </c>
-    </row>
-    <row r="586" spans="2:2">
-      <c r="B586" s="15" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="587" spans="2:2">
-      <c r="B587" s="15" t="s">
-        <v>1393</v>
-      </c>
-    </row>
-    <row r="589" spans="2:2" ht="15">
-      <c r="B589" s="10" t="s">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="591" spans="2:2">
-      <c r="B591" s="15" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="592" spans="2:2">
-      <c r="B592" s="72"/>
-    </row>
-    <row r="593" spans="2:2">
-      <c r="B593" s="15" t="s">
+      <c r="C209" s="23"/>
+      <c r="D209" s="23"/>
+      <c r="E209" s="23"/>
+      <c r="F209" s="23"/>
+      <c r="G209" s="23"/>
+      <c r="H209" s="23"/>
+      <c r="I209" s="23"/>
+      <c r="J209" s="23"/>
+      <c r="K209" s="23"/>
+      <c r="L209" s="24"/>
+      <c r="R209" s="34" t="s">
+        <v>1399</v>
+      </c>
+      <c r="S209" s="23"/>
+      <c r="T209" s="23"/>
+      <c r="U209" s="23"/>
+      <c r="V209" s="23"/>
+      <c r="W209" s="23"/>
+      <c r="X209" s="23"/>
+      <c r="Y209" s="23"/>
+      <c r="Z209" s="23"/>
+      <c r="AA209" s="23"/>
+      <c r="AB209" s="24"/>
+      <c r="AH209" s="34" t="s">
+        <v>1404</v>
+      </c>
+      <c r="AI209" s="23"/>
+      <c r="AJ209" s="23"/>
+      <c r="AK209" s="23"/>
+      <c r="AL209" s="23"/>
+      <c r="AM209" s="23"/>
+      <c r="AN209" s="23"/>
+      <c r="AO209" s="23"/>
+      <c r="AP209" s="23"/>
+      <c r="AQ209" s="23"/>
+      <c r="AR209" s="24"/>
+    </row>
+    <row r="210" spans="2:44">
+      <c r="B210" s="34" t="s">
         <v>1395</v>
       </c>
-    </row>
-    <row r="594" spans="2:2">
-      <c r="B594" s="15" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="595" spans="2:2">
-      <c r="B595" s="15" t="s">
-        <v>1185</v>
-      </c>
-    </row>
-    <row r="596" spans="2:2">
-      <c r="B596" s="15" t="s">
+      <c r="C210" s="23"/>
+      <c r="D210" s="23"/>
+      <c r="E210" s="23"/>
+      <c r="F210" s="23"/>
+      <c r="G210" s="23"/>
+      <c r="H210" s="23"/>
+      <c r="I210" s="23"/>
+      <c r="J210" s="23"/>
+      <c r="K210" s="23"/>
+      <c r="L210" s="24"/>
+      <c r="R210" s="34" t="s">
+        <v>1400</v>
+      </c>
+      <c r="S210" s="23"/>
+      <c r="T210" s="23"/>
+      <c r="U210" s="23"/>
+      <c r="V210" s="23"/>
+      <c r="W210" s="23"/>
+      <c r="X210" s="23"/>
+      <c r="Y210" s="23"/>
+      <c r="Z210" s="23"/>
+      <c r="AA210" s="23"/>
+      <c r="AB210" s="24"/>
+      <c r="AH210" s="34" t="s">
+        <v>1405</v>
+      </c>
+      <c r="AI210" s="23"/>
+      <c r="AJ210" s="23"/>
+      <c r="AK210" s="23"/>
+      <c r="AL210" s="23"/>
+      <c r="AM210" s="23"/>
+      <c r="AN210" s="23"/>
+      <c r="AO210" s="23"/>
+      <c r="AP210" s="23"/>
+      <c r="AQ210" s="23"/>
+      <c r="AR210" s="24"/>
+    </row>
+    <row r="211" spans="2:44" ht="15" thickBot="1">
+      <c r="B211" s="29" t="s">
         <v>1396</v>
       </c>
-    </row>
-    <row r="597" spans="2:2">
-      <c r="B597" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="598" spans="2:2">
-      <c r="B598" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="600" spans="2:2" ht="15">
-      <c r="B600" s="10" t="s">
-        <v>1397</v>
-      </c>
-    </row>
-    <row r="602" spans="2:2" ht="15">
-      <c r="B602" s="10" t="s">
-        <v>1398</v>
-      </c>
-    </row>
-    <row r="603" spans="2:2">
-      <c r="B603" s="13"/>
-    </row>
-    <row r="604" spans="2:2">
-      <c r="B604" s="13" t="s">
-        <v>1417</v>
-      </c>
-    </row>
-    <row r="605" spans="2:2">
-      <c r="B605" s="13" t="s">
-        <v>1418</v>
-      </c>
-    </row>
-    <row r="606" spans="2:2">
-      <c r="B606" s="13" t="s">
-        <v>1399</v>
-      </c>
-    </row>
-    <row r="607" spans="2:2">
-      <c r="B607" s="13" t="s">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="609" spans="2:2" ht="15">
-      <c r="B609" s="10" t="s">
+      <c r="C211" s="30"/>
+      <c r="D211" s="30"/>
+      <c r="E211" s="30"/>
+      <c r="F211" s="30"/>
+      <c r="G211" s="30"/>
+      <c r="H211" s="30"/>
+      <c r="I211" s="30"/>
+      <c r="J211" s="30"/>
+      <c r="K211" s="30"/>
+      <c r="L211" s="31"/>
+      <c r="R211" s="29" t="s">
         <v>1401</v>
       </c>
-    </row>
-    <row r="610" spans="2:2">
-      <c r="B610" s="13"/>
-    </row>
-    <row r="611" spans="2:2">
-      <c r="B611" s="13" t="s">
-        <v>1402</v>
-      </c>
-    </row>
-    <row r="612" spans="2:2">
-      <c r="B612" s="13" t="s">
-        <v>1403</v>
-      </c>
-    </row>
-    <row r="613" spans="2:2">
-      <c r="B613" s="13" t="s">
-        <v>1404</v>
-      </c>
-    </row>
-    <row r="614" spans="2:2">
-      <c r="B614" s="13" t="s">
-        <v>1405</v>
-      </c>
-    </row>
-    <row r="616" spans="2:2" ht="15">
-      <c r="B616" s="10" t="s">
+      <c r="S211" s="30"/>
+      <c r="T211" s="30"/>
+      <c r="U211" s="30"/>
+      <c r="V211" s="30"/>
+      <c r="W211" s="30"/>
+      <c r="X211" s="30"/>
+      <c r="Y211" s="30"/>
+      <c r="Z211" s="30"/>
+      <c r="AA211" s="30"/>
+      <c r="AB211" s="31"/>
+      <c r="AH211" s="29" t="s">
         <v>1406</v>
       </c>
-    </row>
-    <row r="617" spans="2:2">
-      <c r="B617" s="13"/>
-    </row>
-    <row r="618" spans="2:2">
-      <c r="B618" s="13" t="s">
-        <v>1407</v>
-      </c>
-    </row>
-    <row r="619" spans="2:2">
-      <c r="B619" s="13" t="s">
-        <v>1408</v>
-      </c>
-    </row>
-    <row r="620" spans="2:2">
-      <c r="B620" s="13" t="s">
-        <v>1409</v>
-      </c>
-    </row>
-    <row r="621" spans="2:2">
-      <c r="B621" s="13" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="623" spans="2:2">
-      <c r="B623" s="11" t="s">
-        <v>1411</v>
-      </c>
+      <c r="AI211" s="30"/>
+      <c r="AJ211" s="30"/>
+      <c r="AK211" s="30"/>
+      <c r="AL211" s="30"/>
+      <c r="AM211" s="30"/>
+      <c r="AN211" s="30"/>
+      <c r="AO211" s="30"/>
+      <c r="AP211" s="30"/>
+      <c r="AQ211" s="30"/>
+      <c r="AR211" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Kỹ Thuật lập trình/C/C.xlsx
+++ b/Kỹ Thuật lập trình/C/C.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Linux\Kỹ Thuật lập trình\C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD52719F-6779-408F-9892-C63E7C3B7817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8632AB2B-7969-4080-8484-18EFB498E7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D515FE12-8DDF-4954-9F3B-744B83BED5E7}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="CheckList C" sheetId="2" r:id="rId1"/>
     <sheet name="1. Basic Syntax &amp; Data Types" sheetId="3" r:id="rId2"/>
     <sheet name="2. Variables &amp; Storage Classes_x0009_" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="5" r:id="rId4"/>
+    <sheet name="3. Operators &amp; Expressions" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="1419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2448" uniqueCount="2082">
   <si>
     <t>🔧 TOOLS &amp; ENVIRONMENT</t>
   </si>
@@ -13196,6 +13196,2304 @@
         <rFont val="Arial Unicode MS"/>
       </rPr>
       <t xml:space="preserve"> char* string_literals = "Hello";  // Rodata</t>
+    </r>
+  </si>
+  <si>
+    <t>Operators &amp; Expressions trong C - Lý thuyết toàn diện</t>
+  </si>
+  <si>
+    <t>1. Arithmetic Operators</t>
+  </si>
+  <si>
+    <t>1.1 Integer Arithmetic và Overflow</t>
+  </si>
+  <si>
+    <t>Basic Integer Arithmetic:</t>
+  </si>
+  <si>
+    <t>#include &lt;stdio.h&gt;</t>
+  </si>
+  <si>
+    <t>#include &lt;limits.h&gt;</t>
+  </si>
+  <si>
+    <t>void basic_arithmetic() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a = 10, b = 3;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Addition: %d + %d = %d\n", a, b, a + b);      // 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Subtraction: %d - %d = %d\n", a, b, a - b);   // 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Multiplication: %d * %d = %d\n", a, b, a * b); // 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Division: %d / %d = %d\n", a, b, a / b);       // 3 (integer division)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Modulo: %d %% %d = %d\n", a, b, a % b);        // 1</t>
+  </si>
+  <si>
+    <t>Integer Overflow - Signed:</t>
+  </si>
+  <si>
+    <t>void signed_overflow() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int max_int = INT_MAX;  // 2147483647 (32-bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int min_int = INT_MIN;  // -2147483648 (32-bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("INT_MAX: %d\n", max_int);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("INT_MAX + 1: %d\n", max_int + 1);  // UNDEFINED BEHAVIOR!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("INT_MIN: %d\n", min_int);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("INT_MIN - 1: %d\n", min_int - 1);  // UNDEFINED BEHAVIOR!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Multiplication overflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int large = 100000;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Large multiplication: %d\n", large * large);  // Có thể overflow</t>
+  </si>
+  <si>
+    <t>Integer Overflow - Unsigned:</t>
+  </si>
+  <si>
+    <t>void unsigned_overflow() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    unsigned int max_uint = UINT_MAX;  // 4294967295 (32-bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("UINT_MAX: %u\n", max_uint);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("UINT_MAX + 1: %u\n", max_uint + 1);  // 0 (wraps around)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("0 - 1: %u\n", 0u - 1);               // UINT_MAX (wraps around)</t>
+  </si>
+  <si>
+    <t>Safe Overflow Detection:</t>
+  </si>
+  <si>
+    <t>#include &lt;stdbool.h&gt;</t>
+  </si>
+  <si>
+    <t>bool safe_add(int a, int b, int* result) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Check for overflow before performing operation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (a &gt; 0 &amp;&amp; b &gt; 0 &amp;&amp; a &gt; INT_MAX - b) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return false;  // Positive overflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (a &lt; 0 &amp;&amp; b &lt; 0 &amp;&amp; a &lt; INT_MIN - b) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return false;  // Negative overflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    *result = a + b;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return true;</t>
+  </si>
+  <si>
+    <t>bool safe_multiply(int a, int b, int* result) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (a == 0 || b == 0) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        *result = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return true;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (a &gt; 0 &amp;&amp; b &gt; 0 &amp;&amp; a &gt; INT_MAX / b) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (a &lt; 0 &amp;&amp; b &lt; 0 &amp;&amp; a &lt; INT_MAX / b) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if ((a &gt; 0 &amp;&amp; b &lt; 0 &amp;&amp; b &lt; INT_MIN / a) ||</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        (a &lt; 0 &amp;&amp; b &gt; 0 &amp;&amp; a &lt; INT_MIN / b)) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return false;  // Mixed sign overflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    *result = a * b;</t>
+  </si>
+  <si>
+    <t>1.2 Floating-point Arithmetic</t>
+  </si>
+  <si>
+    <t>Floating-point Precision Issues:</t>
+  </si>
+  <si>
+    <t>#include &lt;float.h&gt;</t>
+  </si>
+  <si>
+    <t>#include &lt;math.h&gt;</t>
+  </si>
+  <si>
+    <t>void floating_point_issues() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float f1 = 0.1f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float f2 = 0.2f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float sum = f1 + f2;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("0.1 + 0.2 = %.10f\n", sum);  // Không chính xác bằng 0.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Is equal to 0.3? %s\n", (sum == 0.3f) ? "Yes" : "No");  // No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Comparison with epsilon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float epsilon = FLT_EPSILON;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Using epsilon: %s\n", </t>
+  </si>
+  <si>
+    <t xml:space="preserve">           (fabs(sum - 0.3f) &lt; epsilon) ? "Equal" : "Not equal");</t>
+  </si>
+  <si>
+    <t>Special Floating-point Values:</t>
+  </si>
+  <si>
+    <t>void special_float_values() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float pos_inf = 1.0f / 0.0f;   // Positive infinity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float neg_inf = -1.0f / 0.0f;  // Negative infinity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float nan_val = 0.0f / 0.0f;   // NaN (Not a Number)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Positive infinity: %f\n", pos_inf);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Negative infinity: %f\n", neg_inf);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("NaN: %f\n", nan_val);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Testing special values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Is infinite: %s\n", isinf(pos_inf) ? "Yes" : "No");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Is NaN: %s\n", isnan(nan_val) ? "Yes" : "No");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Is finite: %s\n", isfinite(42.0f) ? "Yes" : "No");</t>
+  </si>
+  <si>
+    <t>Floating-point Arithmetic Gotchas:</t>
+  </si>
+  <si>
+    <t>void floating_point_gotchas() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Loss of precision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float large = 1e20f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float small = 1.0f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Large + small: %.1f\n", large + small);  // small bị "nuốt"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Catastrophic cancellation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float x = 1.0f + 1e-15f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float y = 1.0f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Subtraction: %.20f\n", x - y);  // Mất precision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Associativity issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float a = 1e20f, b = -1e20f, c = 1.0f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("(a + b) + c = %.1f\n", (a + b) + c);  // 1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("a + (b + c) = %.1f\n", a + (b + c));  // 0.0</t>
+  </si>
+  <si>
+    <t>1.3 Modulo Operator với Negative Numbers</t>
+  </si>
+  <si>
+    <t>Modulo Behavior:</t>
+  </si>
+  <si>
+    <t>void modulo_with_negatives() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Positive operands:\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("7 %% 3 = %d\n", 7 % 3);    // 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("8 %% 3 = %d\n", 8 % 3);    // 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("\nNegative dividend:\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("-7 %% 3 = %d\n", -7 % 3);  // -1 (C99+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("-8 %% 3 = %d\n", -8 % 3);  // -2 (C99+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("\nNegative divisor:\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("7 %% -3 = %d\n", 7 % -3);  // 1 (C99+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("8 %% -3 = %d\n", 8 % -3);  // 2 (C99+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("\nBoth negative:\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("-7 %% -3 = %d\n", -7 % -3);  // -1 (C99+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("-8 %% -3 = %d\n", -8 % -3);  // -2 (C99+)</t>
+  </si>
+  <si>
+    <t>Rule trong C99+:</t>
+  </si>
+  <si>
+    <t>void modulo_rule() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Rule: (a/b)*b + a%b == a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a = -7, b = 3;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int quotient = a / b;    // -2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int remainder = a % b;   // -1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("(%d/%d)*%d + %d%%%d = %d + %d = %d\n", </t>
+  </si>
+  <si>
+    <t xml:space="preserve">           a, b, b, a, b, quotient * b, remainder, quotient * b + remainder);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Original a: %d\n", a);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Kết quả: (-2)*3 + (-1) = -6 + (-1) = -7 ✓</t>
+  </si>
+  <si>
+    <t>Portable Modulo Function:</t>
+  </si>
+  <si>
+    <t>// Luôn trả về kết quả positive</t>
+  </si>
+  <si>
+    <t>int positive_mod(int a, int b) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int result = a % b;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return result &lt; 0 ? result + b : result;</t>
+  </si>
+  <si>
+    <t>// Euclidean modulo (mathematical definition)</t>
+  </si>
+  <si>
+    <t>int euclidean_mod(int a, int b) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return result &gt;= 0 ? result : result + (b &lt; 0 ? -b : b);</t>
+  </si>
+  <si>
+    <t>1.4 Bitwise Operations</t>
+  </si>
+  <si>
+    <t>Basic Bitwise Operations:</t>
+  </si>
+  <si>
+    <t>void basic_bitwise() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    unsigned int a = 0xF0;  // 11110000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    unsigned int b = 0x0F;  // 00001111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("a = 0x%02X (%u)\n", a, a);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("b = 0x%02X (%u)\n", b, b);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("a &amp; b = 0x%02X (%u)\n", a &amp; b, a &amp; b);  // 00000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("a | b = 0x%02X (%u)\n", a | b, a | b);  // 11111111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("a ^ b = 0x%02X (%u)\n", a ^ b, a ^ b);  // 11111111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("~a = 0x%02X (%u)\n", ~a, ~a);           // 00001111 (lower 8 bits)</t>
+  </si>
+  <si>
+    <t>Shift Operations:</t>
+  </si>
+  <si>
+    <t>void shift_operations() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    unsigned int value = 0x12;  // 00010010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Original: 0x%02X\n", value);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Left shift by 1: 0x%02X\n", value &lt;&lt; 1);   // 00100100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Left shift by 2: 0x%02X\n", value &lt;&lt; 2);   // 01001000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Right shift by 1: 0x%02X\n", value &gt;&gt; 1);  // 00001001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Right shift by 2: 0x%02X\n", value &gt;&gt; 2);  // 00000100</t>
+  </si>
+  <si>
+    <t>Signed Right Shift (Implementation-defined):</t>
+  </si>
+  <si>
+    <t>void signed_right_shift() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int negative = -8;  // Typically 11111111111111111111111111111000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Negative value: %d\n", negative);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Right shift by 1: %d\n", negative &gt;&gt; 1);  // Arithmetic or logical?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Right shift by 2: %d\n", negative &gt;&gt; 2);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Portable alternative for logical right shift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    unsigned int unsigned_negative = (unsigned int)negative;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Unsigned right shift: %u\n", unsigned_negative &gt;&gt; 1);</t>
+  </si>
+  <si>
+    <t>Practical Bitwise Applications:</t>
+  </si>
+  <si>
+    <t>// Bit manipulation utilities</t>
+  </si>
+  <si>
+    <t>void bit_utilities() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    unsigned int flags = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Set bit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    #define SET_BIT(var, pos) ((var) |= (1U &lt;&lt; (pos)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Clear bit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    #define CLEAR_BIT(var, pos) ((var) &amp;= ~(1U &lt;&lt; (pos)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Toggle bit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    #define TOGGLE_BIT(var, pos) ((var) ^= (1U &lt;&lt; (pos)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Check bit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    #define CHECK_BIT(var, pos) ((var) &amp; (1U &lt;&lt; (pos)))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    SET_BIT(flags, 3);    // Set bit 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    SET_BIT(flags, 7);    // Set bit 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Flags: 0x%02X\n", flags);  // 0x88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Bit 3 set: %s\n", CHECK_BIT(flags, 3) ? "Yes" : "No");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Bit 4 set: %s\n", CHECK_BIT(flags, 4) ? "Yes" : "No");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    TOGGLE_BIT(flags, 3);  // Toggle bit 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("After toggle: 0x%02X\n", flags);  // 0x80</t>
+  </si>
+  <si>
+    <t>Advanced Bitwise Tricks:</t>
+  </si>
+  <si>
+    <t>void bitwise_tricks() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Swap without temporary variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a = 5, b = 10;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Before swap: a=%d, b=%d\n", a, b);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    a ^= b;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    b ^= a;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("After swap: a=%d, b=%d\n", a, b);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Check if power of 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    unsigned int n = 16;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("%u is power of 2: %s\n", n, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">           (n &amp;&amp; !(n &amp; (n - 1))) ? "Yes" : "No");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Count set bits (Brian Kernighan's algorithm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    unsigned int count = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    unsigned int temp = n;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    while (temp) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        temp &amp;= temp - 1;  // Clear lowest set bit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        count++;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Number of set bits in %u: %u\n", n, count);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Isolate rightmost set bit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Rightmost set bit of %u: %u\n", n, n &amp; -n);</t>
+  </si>
+  <si>
+    <t>2. Logical &amp; Relational Operators</t>
+  </si>
+  <si>
+    <t>2.1 Short-circuit Evaluation</t>
+  </si>
+  <si>
+    <t>Logical AND (&amp;&amp;):</t>
+  </si>
+  <si>
+    <t>int expensive_function() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Expensive function called\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return 1;</t>
+  </si>
+  <si>
+    <t>void short_circuit_and() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int x = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Testing: x &amp;&amp; expensive_function()\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (x &amp;&amp; expensive_function()) {  // expensive_function() không được gọi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Both true\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    } else {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("At least one false\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Testing: (x = 1) &amp;&amp; expensive_function()\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if ((x = 1) &amp;&amp; expensive_function()) {  // expensive_function() được gọi</t>
+  </si>
+  <si>
+    <t>Logical OR (||):</t>
+  </si>
+  <si>
+    <t>void short_circuit_or() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int x = 1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Testing: x || expensive_function()\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (x || expensive_function()) {  // expensive_function() không được gọi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("At least one true\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    x = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (x || expensive_function()) {  // expensive_function() được gọi</t>
+  </si>
+  <si>
+    <t>Practical Short-circuit Usage:</t>
+  </si>
+  <si>
+    <t>void practical_short_circuit() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    char* ptr = NULL;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Safe pointer checking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (ptr != NULL &amp;&amp; *ptr != '\0') {  // Không crash nếu ptr == NULL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Valid string: %s\n", ptr);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Array bounds checking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int arr[] = {1, 2, 3, 4, 5};</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int index = 10;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int size = sizeof(arr) / sizeof(arr[0]);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (index &gt;= 0 &amp;&amp; index &lt; size &amp;&amp; arr[index] &gt; 0) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Valid positive element\n");</t>
+  </si>
+  <si>
+    <t>2.2 Comparison Operators</t>
+  </si>
+  <si>
+    <t>Comparison với Different Types:</t>
+  </si>
+  <si>
+    <t>void comparison_types() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a = -1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    unsigned int b = 1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("int a = %d, unsigned b = %u\n", a, b);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("a &lt; b: %s\n", (a &lt; b) ? "true" : "false");  // false! (surprising)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Explanation: a được convert thành unsigned, trở thành very large number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("a as unsigned: %u\n", (unsigned)a);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Safe comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Safe comparison: %s\n", </t>
+  </si>
+  <si>
+    <t xml:space="preserve">           (a &lt; 0 || (unsigned)a &lt; b) ? "true" : "false");</t>
+  </si>
+  <si>
+    <t>Floating-point Comparison:</t>
+  </si>
+  <si>
+    <t>bool float_equal(float a, float b, float epsilon) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return fabs(a - b) &lt; epsilon;</t>
+  </si>
+  <si>
+    <t>bool float_equal_relative(float a, float b, float rel_epsilon) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (a == b) return true;  // Handle exact equality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float diff = fabs(a - b);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float largest = fmax(fabs(a), fabs(b));</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return diff &lt;= rel_epsilon * largest;</t>
+  </si>
+  <si>
+    <t>void floating_comparison() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float a = 0.1f + 0.2f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float b = 0.3f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Direct comparison: %s\n", (a == b) ? "equal" : "not equal");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Epsilon comparison: %s\n", </t>
+  </si>
+  <si>
+    <t xml:space="preserve">           float_equal(a, b, FLT_EPSILON) ? "equal" : "not equal");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Relative comparison: %s\n", </t>
+  </si>
+  <si>
+    <t xml:space="preserve">           float_equal_relative(a, b, 1e-5f) ? "equal" : "not equal");</t>
+  </si>
+  <si>
+    <t>2.3 Ternary Operator</t>
+  </si>
+  <si>
+    <t>Basic Ternary Usage:</t>
+  </si>
+  <si>
+    <t>void basic_ternary() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a = 10, b = 20;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int max = (a &gt; b) ? a : b;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Max: %d\n", max);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Ternary với side effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int x = 5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int result = (x &gt; 0) ? ++x : --x;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Result: %d, x: %d\n", result, x);  // Result: 6, x: 6</t>
+  </si>
+  <si>
+    <t>Nested Ternary (Avoid when possible):</t>
+  </si>
+  <si>
+    <t>void nested_ternary() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int score = 85;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Nested ternary - hard to read</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    char* grade = (score &gt;= 90) ? "A" : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  (score &gt;= 80) ? "B" : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  (score &gt;= 70) ? "C" : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  (score &gt;= 60) ? "D" : "F";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Grade: %s\n", grade);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Better approach with if-else</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    char* better_grade;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (score &gt;= 90) better_grade = "A";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    else if (score &gt;= 80) better_grade = "B";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    else if (score &gt;= 70) better_grade = "C";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    else if (score &gt;= 60) better_grade = "D";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    else better_grade = "F";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Better grade: %s\n", better_grade);</t>
+  </si>
+  <si>
+    <t>Ternary Type Conversion:</t>
+  </si>
+  <si>
+    <t>void ternary_type_conversion() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int i = 10;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float f = 3.14f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Result type is promoted to common type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double result = (i &gt; 5) ? i : f;  // Both operands promoted to double</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Result: %f\n", result);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Potential gotcha with pointers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int* ptr = &amp;i;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void* void_ptr = (ptr != NULL) ? ptr : NULL;  // Common type is void*</t>
+  </si>
+  <si>
+    <t>3. Assignment &amp; Compound Operators</t>
+  </si>
+  <si>
+    <t>3.1 Assignment Operators</t>
+  </si>
+  <si>
+    <t>Basic Assignment:</t>
+  </si>
+  <si>
+    <t>void basic_assignment() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a, b, c;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Chained assignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    a = b = c = 10;  // Right-to-left associativity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("a=%d, b=%d, c=%d\n", a, b, c);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Assignment returns value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int x;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if ((x = 5) &gt; 0) {  // x được assign 5, sau đó compare với 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("x is positive: %d\n", x);</t>
+  </si>
+  <si>
+    <t>Assignment vs Equality:</t>
+  </si>
+  <si>
+    <t>void assignment_vs_equality() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int x = 10;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Common mistake: assignment instead of comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (x = 5) {  // WRONG: assignment, not comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("This will always execute if x=5 is non-zero\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Correct comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (x == 10) {  // Now x is 5 from above assignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("This won't execute\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("x is now %d\n", x);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Yoda conditions to prevent mistake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (5 == x) {  // Compiler error if you write 5 = x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("x equals 5\n");</t>
+  </si>
+  <si>
+    <t>3.2 Compound Assignment Operators</t>
+  </si>
+  <si>
+    <t>Compound Assignment Behavior:</t>
+  </si>
+  <si>
+    <t>void compound_assignment() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a = 10;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    a += 5;    // a = a + 5; → 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    a -= 3;    // a = a - 3; → 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    a *= 2;    // a = a * 2; → 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    a /= 4;    // a = a / 4; → 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    a %= 3;    // a = a % 3; → 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Final value: %d\n", a);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Bitwise compound assignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    unsigned int flags = 0xFF;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    flags &amp;= 0xF0;  // flags = flags &amp; 0xF0; → 0xF0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    flags |= 0x0F;  // flags = flags | 0x0F; → 0xFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    flags ^= 0xAA;  // flags = flags ^ 0xAA; → 0x55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    flags &lt;&lt;= 1;    // flags = flags &lt;&lt; 1;   → 0xAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    flags &gt;&gt;= 2;    // flags = flags &gt;&gt; 2;   → 0x2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Flags: 0x%02X\n", flags);</t>
+  </si>
+  <si>
+    <t>Compound Assignment with Side Effects:</t>
+  </si>
+  <si>
+    <t>int global_index = 0;</t>
+  </si>
+  <si>
+    <t>int array[10] = {0, 1, 2, 3, 4, 5, 6, 7, 8, 9};</t>
+  </si>
+  <si>
+    <t>int get_next_index() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return ++global_index;</t>
+  </si>
+  <si>
+    <t>void compound_side_effects() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Potential issue with side effects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    array[get_next_index()] += array[get_next_index()];</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Undefined behavior: get_next_index() called twice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Order of evaluation is not specified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Safe approach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int index = get_next_index();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    array[index] += array[index];</t>
+  </si>
+  <si>
+    <t>3.3 Increment/Decrement Operators</t>
+  </si>
+  <si>
+    <t>Pre vs Post Increment:</t>
+  </si>
+  <si>
+    <t>void pre_post_increment() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a = 5, b = 5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int x, y;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    x = ++a;  // Pre-increment: a tăng trước, sau đó assign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    y = b++;  // Post-increment: assign trước, sau đó b tăng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Pre-increment: a=%d, x=%d\n", a, x);  // a=6, x=6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Post-increment: b=%d, y=%d\n", b, y);  // b=6, y=5</t>
+  </si>
+  <si>
+    <t>Increment/Decrement với Pointers:</t>
+  </si>
+  <si>
+    <t>void pointer_increment() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int arr[] = {10, 20, 30, 40, 50};</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int* ptr = arr;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("*ptr = %d\n", *ptr);        // 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("*ptr++ = %d\n", *ptr++);    // 10, sau đó ptr tăng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("*ptr = %d\n", *ptr);        // 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("*++ptr = %d\n", *++ptr);    // 30, ptr tăng trước</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("++*ptr = %d\n", ++*ptr);    // 31, value tăng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("*ptr = %d\n", *ptr);        // 31</t>
+  </si>
+  <si>
+    <t>Dangerous Increment/Decrement:</t>
+  </si>
+  <si>
+    <t>void dangerous_increment() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int i = 5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Undefined behavior examples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("%d\n", i++ + ++i);  // UB: i modified twice between sequence points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("%d\n", i++ + i++);  // UB: i modified twice between sequence points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int arr[10];</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int index = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    arr[index++] = index;  // UB: index used and modified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Safe alternatives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int j = 5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int temp1 = j++;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int temp2 = ++j;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Safe: %d\n", temp1 + temp2);</t>
+  </si>
+  <si>
+    <t>3.4 Sequence Points và Undefined Behavior</t>
+  </si>
+  <si>
+    <t>Sequence Points trong C:</t>
+  </si>
+  <si>
+    <t>void sequence_points() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int i = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Sequence points tại:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // 1. Sau toàn bộ expression trong &amp;&amp;, ||</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // 2. Sau toàn bộ expression trong ternary operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // 3. Sau toàn bộ expression trước comma operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // 4. Tại semicolon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // 5. Tại function call (sau evaluate arguments)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Safe: sequence point after &amp;&amp;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (i++ &amp;&amp; i &lt; 10) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Safe: i = %d\n", i);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Safe: sequence point after ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int result = (i++ &gt; 5) ? i : 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Ternary result: %d, i = %d\n", result, i);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Safe: sequence point after comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a = (i++, i * 2);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Comma result: %d, i = %d\n", a, i);</t>
+  </si>
+  <si>
+    <t>Common Undefined Behavior:</t>
+  </si>
+  <si>
+    <t>void undefined_behavior_examples() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int i = 1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // UB: modifying i twice between sequence points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    i = i++;        // UB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    i = ++i;        // UB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    i = i + i++;    // UB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // UB: unspecified order of evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("%d %d\n", i++, i++);  // UB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // UB: modifying and using variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a[10];</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int j = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    a[j] = j++;     // UB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    a[++j] = j;     // UB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int k = 1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int temp = k;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    k = temp + 1;   // Safe equivalent of k = k++</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Safe: %d %d\n", k, k+1);  // Safe</t>
+  </si>
+  <si>
+    <t>4. Operator Precedence &amp; Associativity</t>
+  </si>
+  <si>
+    <t>4.1 Complete Precedence Table</t>
+  </si>
+  <si>
+    <t>// Precedence table (highest to lowest):</t>
+  </si>
+  <si>
+    <t>void precedence_table() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    /*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    1. () [] -&gt; .                    Left-to-right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2. ! ~ ++ -- + - * &amp; (type) sizeof    Right-to-left (unary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    3. * / %                         Left-to-right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    4. + -                           Left-to-right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    5. &lt;&lt; &gt;&gt;                         Left-to-right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    6. &lt; &lt;= &gt; &gt;=                     Left-to-right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    7. == !=                         Left-to-right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    8. &amp;                             Left-to-right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    9. ^                             Left-to-right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    10. |                            Left-to-right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    11. &amp;&amp;                           Left-to-right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    12. ||                           Left-to-right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    13. ?:                           Right-to-left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    14. = += -= *= /= %= &amp;= ^= |= &lt;&lt;= &gt;&gt;= Right-to-left</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    15. ,                            Left-to-right</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    */</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a = 5, b = 3, c = 2;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Precedence examples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("5 + 3 * 2 = %d\n", a + b * c);      // 11, not 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("5 * 3 + 2 = %d\n", a * b + c);      // 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("5 + 3 &lt; 2 * 4 = %d\n", a + b &lt; c * 4); // 0 (false)</t>
+  </si>
+  <si>
+    <t>4.2 Associativity Rules</t>
+  </si>
+  <si>
+    <t>Left-to-right Associativity:</t>
+  </si>
+  <si>
+    <t>void left_associativity() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a = 10, b = 5, c = 2;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Arithmetic operators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("10 - 5 - 2 = %d\n", a - b - c);      // (10 - 5) - 2 = 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("10 / 5 / 2 = %d\n", a / b / c);      // (10 / 5) / 2 = 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Shift operators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("8 &gt;&gt; 1 &gt;&gt; 1 = %d\n", 8 &gt;&gt; 1 &gt;&gt; 1);  // (8 &gt;&gt; 1) &gt;&gt; 1 = 2</t>
+  </si>
+  <si>
+    <t>Right-to-left Associativity:</t>
+  </si>
+  <si>
+    <t>void right_associativity() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a = 1, b = 2, c = 3;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Assignment operators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    a = b = c = 10;  // a = (b = (c = 10))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Ternary operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int result = x &gt; 0 ? x &gt; 10 ? 1 : 2 : 3;  // x &gt; 0 ? (x &gt; 10 ? 1 : 2) : 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Ternary result: %d\n", result);   // 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Unary operators</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int y = 5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("*&amp;y = %d\n", *&amp;y);  // *(&amp;y) = 5</t>
+  </si>
+  <si>
+    <t>4.3 Common Precedence Pitfalls</t>
+  </si>
+  <si>
+    <t>Pitfall 1: Bitwise vs Logical:</t>
+  </si>
+  <si>
+    <t>void bitwise_vs_logical() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int flags = 0x05;  // 0101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Wrong: &amp; has lower precedence than ==</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (flags &amp; 0x01 == 0x01) {  // Parsed as: flags &amp; (0x01 == 0x01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("This might not work as expected\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Correct: use parentheses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if ((flags &amp; 0x01) == 0x01) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Flag is set correctly\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Even better: just check the bit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (flags &amp; 0x01) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Flag is set (simpler)\n");</t>
+  </si>
+  <si>
+    <t>Pitfall 2: Pointer Arithmetic:</t>
+  </si>
+  <si>
+    <t>void pointer_precedence() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Wrong: ++ has higher precedence than *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("*ptr++ = %d\n", *ptr++);  // Prints 1, then ptr advances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("*ptr = %d\n", *ptr);      // Now prints 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ptr = arr;  // Reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Different meaning: increment the value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("++*ptr = %d\n", ++*ptr);  // Increments value at ptr, prints 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("*ptr = %d\n", *ptr);      // Still 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Clear with parentheses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ptr = arr + 1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("*(ptr++) = %d\n", *(ptr++));  // Same as *ptr++</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("(*ptr)++ = %d\n", (*ptr)++);  // Increment value, return old value</t>
+  </si>
+  <si>
+    <t>Pitfall 3: Sizeof Operator:</t>
+  </si>
+  <si>
+    <t>void sizeof_precedence() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // sizeof has high precedence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("sizeof *ptr = %zu\n", sizeof *ptr);        // sizeof(int)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("sizeof(int) * 10 = %zu\n", sizeof(int) * 10);  // 40 (typically)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Careful with expressions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("sizeof arr + 1 = %zu\n", sizeof arr + 1);  // (sizeof arr) + 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("sizeof(arr + 1) = %zu\n", sizeof(arr + 1)); // sizeof(pointer)</t>
+  </si>
+  <si>
+    <t>Pitfall 4: Ternary Operator:</t>
+  </si>
+  <si>
+    <t>void ternary_precedence() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Wrong: assignment has lower precedence than ternary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int max = a &gt; b ? a : b = 0;  // ERROR: can't assign to b in ternary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Wrong: comma has lower precedence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int result = a &gt; b ? a, b : 0;  // Parsed as: (a &gt; b ? a, b) : 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int max_correct = a &gt; b ? a : (b = 0);  // b assigned 0 if a &lt;= b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int result_correct = a &gt; b ? (a, b) : 0;  // comma expression in parentheses</t>
+  </si>
+  <si>
+    <t>Pitfall 5: Mixing Arithmetic and Shift:</t>
+  </si>
+  <si>
+    <t>void arithmetic_shift_precedence() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a = 8, b = 2;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Shift has lower precedence than arithmetic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("a &lt;&lt; b + 1 = %d\n", a &lt;&lt; b + 1);  // a &lt;&lt; (b + 1) = 8 &lt;&lt; 3 = 64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("(a &lt;&lt; b) + 1 = %d\n", (a &lt;&lt; b) + 1);  // (8 &lt;&lt; 2) + 1 = 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Mixing with comparisons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("a &lt;&lt; 1 &gt; b = %d\n", a &lt;&lt; 1 &gt; b);  // (a &lt;&lt; 1) &gt; b = 16 &gt; 2 = 1</t>
+  </si>
+  <si>
+    <t>4.4 Best Practices for Operator Usage</t>
+  </si>
+  <si>
+    <t>Use Parentheses for Clarity:</t>
+  </si>
+  <si>
+    <t>void clarity_examples() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Unclear without parentheses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int result1 = a + b * c - a / b;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Clear with parentheses (same meaning)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int result2 = a + (b * c) - (a / b);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Complex boolean expressions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int x = 5, y = 10, z = 15;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Hard to read</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (x &gt; 0 &amp;&amp; y &gt; x || z &gt; y &amp;&amp; x &lt; z) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Complex condition\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if ((x &gt; 0 &amp;&amp; y &gt; x) || (z &gt; y &amp;&amp; x &lt; z)) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Clear condition\n");</t>
+  </si>
+  <si>
+    <t>Avoid Complex Expressions:</t>
+  </si>
+  <si>
+    <t>void avoid_complex() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int arr[10] = {1, 2, 3, 4, 5, 6, 7, 8, 9, 10};</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Too complex - hard to understand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int bad_result = arr[i++] + arr[++i] * arr[i--] - arr[--i];</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Break it down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int val1 = arr[i++];</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int val2 = arr[++i];</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int val3 = arr[i--];</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int val4 = arr[--i];</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int good_result = val1 + val2 * val3 - val4;</t>
+  </si>
+  <si>
+    <t>5. Advanced Topics và Cạm bẫy</t>
+  </si>
+  <si>
+    <t>5.1 Type Conversion trong Expressions</t>
+  </si>
+  <si>
+    <t>Implicit Type Conversion:</t>
+  </si>
+  <si>
+    <t>void implicit_conversion() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    char c = 100;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    short s = 200;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int i = 300;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    long l = 400L;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double d = 2.718;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Arithmetic conversions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("c + s = %d\n", c + s);        // Both promoted to int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("i + l = %ld\n", i + l);       // i promoted to long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("f + d = %f\n", f + d);        // f promoted to double</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("i + f = %f\n", i + f);        // i converted to float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Surprising conversions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    unsigned int ui = 1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int si = -1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("ui + si = %u\n", ui + si);    // si converted to unsigned!</t>
+  </si>
+  <si>
+    <t>Explicit Type Conversion:</t>
+  </si>
+  <si>
+    <t>void explicit_conversion() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double d = 3.14159;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int i = (int)d;  // Truncation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("d = %f, i = %d\n", d, i);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Pointer conversions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int value = 42;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void* vptr = &amp;value;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int* iptr = (int*)vptr;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("*iptr = %d\n", *iptr);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Dangerous conversions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float f = 1e20f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int dangerous = (int)f;  // Undefined behavior if out of range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Dangerous conversion: %d\n", dangerous);</t>
+  </si>
+  <si>
+    <t>5.2 Operator Overloading Alternatives</t>
+  </si>
+  <si>
+    <t>Function-like Macros:</t>
+  </si>
+  <si>
+    <t>#define MAX(a, b) ((a) &gt; (b) ? (a) : (b))</t>
+  </si>
+  <si>
+    <t>#define MIN(a, b) ((a) &lt; (b) ? (a) : (b))</t>
+  </si>
+  <si>
+    <t>#define ABS(x) ((x) &lt; 0 ? -(x) : (x))</t>
+  </si>
+  <si>
+    <t>void macro_operators() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("MAX(a, b) = %d\n", MAX(a, b));</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("MIN(a, b) = %d\n", MIN(a, b));</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("ABS(-5) = %d\n", ABS(-5));</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Macro gotchas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("MAX(x++, 10) = %d\n", MAX(x++, 10));  // x++ evaluated twice!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("x = %d\n", x);  // x might be 7, not 6!</t>
+  </si>
+  <si>
+    <t>Generic Selections (C11):</t>
+  </si>
+  <si>
+    <t>#define ABS_GENERIC(x) _Generic((x), \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int: abs, \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    long: labs, \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    long long: llabs, \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float: fabsf, \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double: fabs, \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    long double: fabsl \</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    )(x)</t>
+  </si>
+  <si>
+    <t>void generic_example() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int i = -5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    float f = -3.14f;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    double d = -2.718;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("ABS_GENERIC(i) = %d\n", ABS_GENERIC(i));</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("ABS_GENERIC(f) = %f\n", ABS_GENERIC(f));</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("ABS_GENERIC(d) = %f\n", ABS_GENERIC(d));</t>
+  </si>
+  <si>
+    <t>5.3 Performance Considerations</t>
+  </si>
+  <si>
+    <t>Expensive Operations:</t>
+  </si>
+  <si>
+    <t>void performance_tips() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Division is expensive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int quotient = a / b;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int remainder = a % b;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Use div() for both quotient and remainder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    #include &lt;stdlib.h&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    div_t result = div(a, b);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("quotient: %d, remainder: %d\n", result.quot, result.rem);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Multiplication by power of 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int n = 100;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int fast_mult = n &lt;&lt; 3;  // n * 8, faster than n * 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int fast_div = n &gt;&gt; 2;   // n / 4, faster than n / 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // But modern compilers optimize these automatically</t>
+  </si>
+  <si>
+    <t>Short-circuit Optimization:</t>
+  </si>
+  <si>
+    <t>bool expensive_check(int x) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Simulate expensive operation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    for (int i = 0; i &lt; 1000000; i++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        x = x * 2 + 1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return x &gt; 0;</t>
+  </si>
+  <si>
+    <t>void optimization_example() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int quick_value = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Put cheaper conditions first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (quick_value != 0 &amp;&amp; expensive_check(quick_value)) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Both conditions true\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Wrong order - expensive function always called</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (expensive_check(quick_value) &amp;&amp; quick_value != 0) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("This is inefficient\n");</t>
+  </si>
+  <si>
+    <t>5.4 Debugging Operator Issues</t>
+  </si>
+  <si>
+    <t>Common Debugging Techniques:</t>
+  </si>
+  <si>
+    <t>void debugging_operators() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a = 5, b = 10, c = 15;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Use temporary variables to debug complex expressions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int temp1 = a + b;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int temp2 = c - a;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int result = temp1 * temp2;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("temp1 = %d, temp2 = %d, result = %d\n", temp1, temp2, result);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Use assertions for operator assumptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    #include &lt;assert.h&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    assert(a &gt; 0);  // Ensure a is positive before using in division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int division_result = b / a;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Print intermediate values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Before: a=%d, b=%d\n", a, b);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    a += b;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("After a += b: a=%d, b=%d\n", a, b);</t>
+  </si>
+  <si>
+    <t>6. Tóm tắt Best Practices</t>
+  </si>
+  <si>
+    <t>6.1 Operator Usage Guidelines</t>
+  </si>
+  <si>
+    <t>6.2 Common Mistakes to Avoid</t>
+  </si>
+  <si>
+    <t>Hiểu rõ operators và expressions là fundamental để viết C code hiệu quả và bug-free. Những kiến thức này giúp tránh được nhiều pitfalls phổ biến và tối ưu hóa performance.</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Always use parentheses</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> khi không chắc chắn về precedence</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Avoid complex expressions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - chia nhỏ thành multiple statements</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Be careful with side effects</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - tránh modify variable nhiều lần trong cùng expression</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. Use appropriate types</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - tránh unexpected type conversions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5. Test edge cases</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - overflow, underflow, division by zero</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6. Use const</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cho values không thay đổi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>7. Initialize variables</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trước khi sử dụng</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>8. Check return values</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> của functions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. Assignment vs Comparison</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>==</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Bitwise vs Logical</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>&amp;&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>||</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Precedence assumptions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - luôn dùng parentheses</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. Integer overflow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - check bounds trước arithmetic</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5. Floating-point equality</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - sử dụng epsilon comparison</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6. Undefined behavior</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - tránh modify variables nhiều lần</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>7. Side effects trong macros</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - cẩn thận với arguments được evaluate nhiều lần</t>
     </r>
   </si>
 </sst>
@@ -13203,7 +15501,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13393,6 +15691,14 @@
       <name val="Arial Unicode MS"/>
       <charset val="163"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -13576,7 +15882,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -13785,15 +16091,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -13826,6 +16123,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19711,29 +22020,29 @@
       <c r="BB13" s="23"/>
       <c r="BC13" s="24"/>
       <c r="BE13" s="21"/>
-      <c r="BF13" s="84" t="s">
+      <c r="BF13" s="100" t="s">
         <v>806</v>
       </c>
-      <c r="BG13" s="84"/>
-      <c r="BH13" s="84"/>
-      <c r="BI13" s="84"/>
-      <c r="BJ13" s="84" t="s">
+      <c r="BG13" s="100"/>
+      <c r="BH13" s="100"/>
+      <c r="BI13" s="100"/>
+      <c r="BJ13" s="100" t="s">
         <v>807</v>
       </c>
-      <c r="BK13" s="84"/>
-      <c r="BL13" s="84"/>
-      <c r="BM13" s="84"/>
-      <c r="BN13" s="84"/>
-      <c r="BO13" s="84"/>
-      <c r="BP13" s="84" t="s">
+      <c r="BK13" s="100"/>
+      <c r="BL13" s="100"/>
+      <c r="BM13" s="100"/>
+      <c r="BN13" s="100"/>
+      <c r="BO13" s="100"/>
+      <c r="BP13" s="100" t="s">
         <v>808</v>
       </c>
-      <c r="BQ13" s="84"/>
-      <c r="BR13" s="84"/>
-      <c r="BS13" s="84"/>
-      <c r="BT13" s="84"/>
-      <c r="BU13" s="84"/>
-      <c r="BV13" s="84"/>
+      <c r="BQ13" s="100"/>
+      <c r="BR13" s="100"/>
+      <c r="BS13" s="100"/>
+      <c r="BT13" s="100"/>
+      <c r="BU13" s="100"/>
+      <c r="BV13" s="100"/>
       <c r="BW13" s="24"/>
     </row>
     <row r="14" spans="2:75" ht="15.75" thickBot="1">
@@ -19758,29 +22067,29 @@
       <c r="BB14" s="30"/>
       <c r="BC14" s="31"/>
       <c r="BE14" s="21"/>
-      <c r="BF14" s="86" t="s">
+      <c r="BF14" s="102" t="s">
         <v>809</v>
       </c>
-      <c r="BG14" s="86"/>
-      <c r="BH14" s="86"/>
-      <c r="BI14" s="86"/>
-      <c r="BJ14" s="85" t="s">
+      <c r="BG14" s="102"/>
+      <c r="BH14" s="102"/>
+      <c r="BI14" s="102"/>
+      <c r="BJ14" s="101" t="s">
         <v>810</v>
       </c>
-      <c r="BK14" s="85"/>
-      <c r="BL14" s="85"/>
-      <c r="BM14" s="85"/>
-      <c r="BN14" s="85"/>
-      <c r="BO14" s="85"/>
-      <c r="BP14" s="85" t="s">
+      <c r="BK14" s="101"/>
+      <c r="BL14" s="101"/>
+      <c r="BM14" s="101"/>
+      <c r="BN14" s="101"/>
+      <c r="BO14" s="101"/>
+      <c r="BP14" s="101" t="s">
         <v>810</v>
       </c>
-      <c r="BQ14" s="85"/>
-      <c r="BR14" s="85"/>
-      <c r="BS14" s="85"/>
-      <c r="BT14" s="85"/>
-      <c r="BU14" s="85"/>
-      <c r="BV14" s="85"/>
+      <c r="BQ14" s="101"/>
+      <c r="BR14" s="101"/>
+      <c r="BS14" s="101"/>
+      <c r="BT14" s="101"/>
+      <c r="BU14" s="101"/>
+      <c r="BV14" s="101"/>
       <c r="BW14" s="24"/>
     </row>
     <row r="15" spans="2:75" ht="15.75" thickBot="1">
@@ -19789,29 +22098,29 @@
       </c>
       <c r="AL15" s="13"/>
       <c r="BE15" s="21"/>
-      <c r="BF15" s="86" t="s">
+      <c r="BF15" s="102" t="s">
         <v>811</v>
       </c>
-      <c r="BG15" s="86"/>
-      <c r="BH15" s="86"/>
-      <c r="BI15" s="86"/>
-      <c r="BJ15" s="85" t="s">
+      <c r="BG15" s="102"/>
+      <c r="BH15" s="102"/>
+      <c r="BI15" s="102"/>
+      <c r="BJ15" s="101" t="s">
         <v>812</v>
       </c>
-      <c r="BK15" s="85"/>
-      <c r="BL15" s="85"/>
-      <c r="BM15" s="85"/>
-      <c r="BN15" s="85"/>
-      <c r="BO15" s="85"/>
-      <c r="BP15" s="85" t="s">
+      <c r="BK15" s="101"/>
+      <c r="BL15" s="101"/>
+      <c r="BM15" s="101"/>
+      <c r="BN15" s="101"/>
+      <c r="BO15" s="101"/>
+      <c r="BP15" s="101" t="s">
         <v>813</v>
       </c>
-      <c r="BQ15" s="85"/>
-      <c r="BR15" s="85"/>
-      <c r="BS15" s="85"/>
-      <c r="BT15" s="85"/>
-      <c r="BU15" s="85"/>
-      <c r="BV15" s="85"/>
+      <c r="BQ15" s="101"/>
+      <c r="BR15" s="101"/>
+      <c r="BS15" s="101"/>
+      <c r="BT15" s="101"/>
+      <c r="BU15" s="101"/>
+      <c r="BV15" s="101"/>
       <c r="BW15" s="24"/>
     </row>
     <row r="16" spans="2:75" ht="15">
@@ -19839,29 +22148,29 @@
       <c r="BB16" s="19"/>
       <c r="BC16" s="20"/>
       <c r="BE16" s="21"/>
-      <c r="BF16" s="86" t="s">
+      <c r="BF16" s="102" t="s">
         <v>814</v>
       </c>
-      <c r="BG16" s="86"/>
-      <c r="BH16" s="86"/>
-      <c r="BI16" s="86"/>
-      <c r="BJ16" s="85" t="s">
+      <c r="BG16" s="102"/>
+      <c r="BH16" s="102"/>
+      <c r="BI16" s="102"/>
+      <c r="BJ16" s="101" t="s">
         <v>815</v>
       </c>
-      <c r="BK16" s="85"/>
-      <c r="BL16" s="85"/>
-      <c r="BM16" s="85"/>
-      <c r="BN16" s="85"/>
-      <c r="BO16" s="85"/>
-      <c r="BP16" s="85" t="s">
+      <c r="BK16" s="101"/>
+      <c r="BL16" s="101"/>
+      <c r="BM16" s="101"/>
+      <c r="BN16" s="101"/>
+      <c r="BO16" s="101"/>
+      <c r="BP16" s="101" t="s">
         <v>815</v>
       </c>
-      <c r="BQ16" s="85"/>
-      <c r="BR16" s="85"/>
-      <c r="BS16" s="85"/>
-      <c r="BT16" s="85"/>
-      <c r="BU16" s="85"/>
-      <c r="BV16" s="85"/>
+      <c r="BQ16" s="101"/>
+      <c r="BR16" s="101"/>
+      <c r="BS16" s="101"/>
+      <c r="BT16" s="101"/>
+      <c r="BU16" s="101"/>
+      <c r="BV16" s="101"/>
       <c r="BW16" s="24"/>
     </row>
     <row r="17" spans="2:88" ht="15">
@@ -20372,33 +22681,33 @@
         <v>962</v>
       </c>
       <c r="AL28" s="21"/>
-      <c r="AM28" s="84" t="s">
+      <c r="AM28" s="100" t="s">
         <v>806</v>
       </c>
-      <c r="AN28" s="84"/>
-      <c r="AO28" s="84"/>
-      <c r="AP28" s="84" t="s">
+      <c r="AN28" s="100"/>
+      <c r="AO28" s="100"/>
+      <c r="AP28" s="100" t="s">
         <v>822</v>
       </c>
-      <c r="AQ28" s="84"/>
-      <c r="AR28" s="84"/>
-      <c r="AS28" s="84"/>
-      <c r="AT28" s="84"/>
-      <c r="AU28" s="84"/>
-      <c r="AV28" s="84"/>
-      <c r="AW28" s="84"/>
-      <c r="AX28" s="84" t="s">
+      <c r="AQ28" s="100"/>
+      <c r="AR28" s="100"/>
+      <c r="AS28" s="100"/>
+      <c r="AT28" s="100"/>
+      <c r="AU28" s="100"/>
+      <c r="AV28" s="100"/>
+      <c r="AW28" s="100"/>
+      <c r="AX28" s="100" t="s">
         <v>823</v>
       </c>
-      <c r="AY28" s="84"/>
-      <c r="AZ28" s="84"/>
-      <c r="BA28" s="84"/>
-      <c r="BB28" s="84" t="s">
+      <c r="AY28" s="100"/>
+      <c r="AZ28" s="100"/>
+      <c r="BA28" s="100"/>
+      <c r="BB28" s="100" t="s">
         <v>824</v>
       </c>
-      <c r="BC28" s="84"/>
-      <c r="BD28" s="84"/>
-      <c r="BE28" s="84"/>
+      <c r="BC28" s="100"/>
+      <c r="BD28" s="100"/>
+      <c r="BE28" s="100"/>
       <c r="BF28" s="24"/>
       <c r="BH28" s="29" t="s">
         <v>841</v>
@@ -20434,33 +22743,33 @@
     </row>
     <row r="29" spans="2:88" ht="15" thickBot="1">
       <c r="AL29" s="21"/>
-      <c r="AM29" s="86" t="s">
+      <c r="AM29" s="102" t="s">
         <v>825</v>
       </c>
-      <c r="AN29" s="86"/>
-      <c r="AO29" s="86"/>
-      <c r="AP29" s="85" t="s">
+      <c r="AN29" s="102"/>
+      <c r="AO29" s="102"/>
+      <c r="AP29" s="101" t="s">
         <v>963</v>
       </c>
-      <c r="AQ29" s="85"/>
-      <c r="AR29" s="85"/>
-      <c r="AS29" s="85"/>
-      <c r="AT29" s="85"/>
-      <c r="AU29" s="85"/>
-      <c r="AV29" s="85"/>
-      <c r="AW29" s="85"/>
-      <c r="AX29" s="85" t="s">
+      <c r="AQ29" s="101"/>
+      <c r="AR29" s="101"/>
+      <c r="AS29" s="101"/>
+      <c r="AT29" s="101"/>
+      <c r="AU29" s="101"/>
+      <c r="AV29" s="101"/>
+      <c r="AW29" s="101"/>
+      <c r="AX29" s="101" t="s">
         <v>826</v>
       </c>
-      <c r="AY29" s="85"/>
-      <c r="AZ29" s="85"/>
-      <c r="BA29" s="85"/>
-      <c r="BB29" s="86" t="s">
+      <c r="AY29" s="101"/>
+      <c r="AZ29" s="101"/>
+      <c r="BA29" s="101"/>
+      <c r="BB29" s="102" t="s">
         <v>827</v>
       </c>
-      <c r="BC29" s="86"/>
-      <c r="BD29" s="86"/>
-      <c r="BE29" s="86"/>
+      <c r="BC29" s="102"/>
+      <c r="BD29" s="102"/>
+      <c r="BE29" s="102"/>
       <c r="BF29" s="24"/>
     </row>
     <row r="30" spans="2:88" ht="15">
@@ -20468,33 +22777,33 @@
         <v>774</v>
       </c>
       <c r="AL30" s="21"/>
-      <c r="AM30" s="86" t="s">
+      <c r="AM30" s="102" t="s">
         <v>828</v>
       </c>
-      <c r="AN30" s="86"/>
-      <c r="AO30" s="86"/>
-      <c r="AP30" s="85" t="s">
+      <c r="AN30" s="102"/>
+      <c r="AO30" s="102"/>
+      <c r="AP30" s="101" t="s">
         <v>829</v>
       </c>
-      <c r="AQ30" s="85"/>
-      <c r="AR30" s="85"/>
-      <c r="AS30" s="85"/>
-      <c r="AT30" s="85"/>
-      <c r="AU30" s="85"/>
-      <c r="AV30" s="85"/>
-      <c r="AW30" s="85"/>
-      <c r="AX30" s="85" t="s">
+      <c r="AQ30" s="101"/>
+      <c r="AR30" s="101"/>
+      <c r="AS30" s="101"/>
+      <c r="AT30" s="101"/>
+      <c r="AU30" s="101"/>
+      <c r="AV30" s="101"/>
+      <c r="AW30" s="101"/>
+      <c r="AX30" s="101" t="s">
         <v>830</v>
       </c>
-      <c r="AY30" s="85"/>
-      <c r="AZ30" s="85"/>
-      <c r="BA30" s="85"/>
-      <c r="BB30" s="86" t="s">
+      <c r="AY30" s="101"/>
+      <c r="AZ30" s="101"/>
+      <c r="BA30" s="101"/>
+      <c r="BB30" s="102" t="s">
         <v>831</v>
       </c>
-      <c r="BC30" s="86"/>
-      <c r="BD30" s="86"/>
-      <c r="BE30" s="86"/>
+      <c r="BC30" s="102"/>
+      <c r="BD30" s="102"/>
+      <c r="BE30" s="102"/>
       <c r="BF30" s="24"/>
       <c r="BH30" s="18" t="s">
         <v>842</v>
@@ -20526,33 +22835,33 @@
         <v>775</v>
       </c>
       <c r="AL31" s="21"/>
-      <c r="AM31" s="86" t="s">
+      <c r="AM31" s="102" t="s">
         <v>831</v>
       </c>
-      <c r="AN31" s="86"/>
-      <c r="AO31" s="86"/>
-      <c r="AP31" s="85" t="s">
+      <c r="AN31" s="102"/>
+      <c r="AO31" s="102"/>
+      <c r="AP31" s="101" t="s">
         <v>832</v>
       </c>
-      <c r="AQ31" s="85"/>
-      <c r="AR31" s="85"/>
-      <c r="AS31" s="85"/>
-      <c r="AT31" s="85"/>
-      <c r="AU31" s="85"/>
-      <c r="AV31" s="85"/>
-      <c r="AW31" s="85"/>
-      <c r="AX31" s="85" t="s">
+      <c r="AQ31" s="101"/>
+      <c r="AR31" s="101"/>
+      <c r="AS31" s="101"/>
+      <c r="AT31" s="101"/>
+      <c r="AU31" s="101"/>
+      <c r="AV31" s="101"/>
+      <c r="AW31" s="101"/>
+      <c r="AX31" s="101" t="s">
         <v>830</v>
       </c>
-      <c r="AY31" s="85"/>
-      <c r="AZ31" s="85"/>
-      <c r="BA31" s="85"/>
-      <c r="BB31" s="86" t="s">
+      <c r="AY31" s="101"/>
+      <c r="AZ31" s="101"/>
+      <c r="BA31" s="101"/>
+      <c r="BB31" s="102" t="s">
         <v>833</v>
       </c>
-      <c r="BC31" s="86"/>
-      <c r="BD31" s="86"/>
-      <c r="BE31" s="86"/>
+      <c r="BC31" s="102"/>
+      <c r="BD31" s="102"/>
+      <c r="BE31" s="102"/>
       <c r="BF31" s="24"/>
       <c r="BH31" s="27" t="s">
         <v>843</v>
@@ -25876,6 +28185,22 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="AX28:BA28"/>
+    <mergeCell ref="AX29:BA29"/>
+    <mergeCell ref="AX30:BA30"/>
+    <mergeCell ref="AX31:BA31"/>
+    <mergeCell ref="BB28:BE28"/>
+    <mergeCell ref="BB29:BE29"/>
+    <mergeCell ref="BB30:BE30"/>
+    <mergeCell ref="BB31:BE31"/>
+    <mergeCell ref="AM28:AO28"/>
+    <mergeCell ref="AM29:AO29"/>
+    <mergeCell ref="AM30:AO30"/>
+    <mergeCell ref="AM31:AO31"/>
+    <mergeCell ref="AP28:AW28"/>
+    <mergeCell ref="AP29:AW29"/>
+    <mergeCell ref="AP30:AW30"/>
+    <mergeCell ref="AP31:AW31"/>
     <mergeCell ref="BP13:BV13"/>
     <mergeCell ref="BP14:BV14"/>
     <mergeCell ref="BP15:BV15"/>
@@ -25888,22 +28213,6 @@
     <mergeCell ref="BJ14:BO14"/>
     <mergeCell ref="BJ15:BO15"/>
     <mergeCell ref="BJ16:BO16"/>
-    <mergeCell ref="AM28:AO28"/>
-    <mergeCell ref="AM29:AO29"/>
-    <mergeCell ref="AM30:AO30"/>
-    <mergeCell ref="AM31:AO31"/>
-    <mergeCell ref="AP28:AW28"/>
-    <mergeCell ref="AP29:AW29"/>
-    <mergeCell ref="AP30:AW30"/>
-    <mergeCell ref="AP31:AW31"/>
-    <mergeCell ref="AX28:BA28"/>
-    <mergeCell ref="AX29:BA29"/>
-    <mergeCell ref="AX30:BA30"/>
-    <mergeCell ref="AX31:BA31"/>
-    <mergeCell ref="BB28:BE28"/>
-    <mergeCell ref="BB29:BE29"/>
-    <mergeCell ref="BB30:BE30"/>
-    <mergeCell ref="BB31:BE31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -25925,8 +28234,8 @@
     </row>
     <row r="2" spans="1:70" ht="15" thickBot="1"/>
     <row r="3" spans="1:70" s="16" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A3" s="95"/>
-      <c r="B3" s="96" t="s">
+      <c r="A3" s="92"/>
+      <c r="B3" s="93" t="s">
         <v>1060</v>
       </c>
     </row>
@@ -25959,7 +28268,7 @@
       <c r="AU4" s="44"/>
       <c r="AV4" s="44"/>
       <c r="AW4" s="44"/>
-      <c r="AY4" s="93" t="s">
+      <c r="AY4" s="90" t="s">
         <v>1413</v>
       </c>
     </row>
@@ -25967,44 +28276,44 @@
       <c r="B5" s="67" t="s">
         <v>1062</v>
       </c>
-      <c r="W5" s="87" t="s">
+      <c r="W5" s="84" t="s">
         <v>1062</v>
       </c>
       <c r="X5" s="62"/>
-      <c r="AQ5" s="89" t="s">
+      <c r="AQ5" s="86" t="s">
         <v>1096</v>
       </c>
-      <c r="AR5" s="90"/>
-      <c r="AS5" s="90"/>
-      <c r="AT5" s="90"/>
-      <c r="AU5" s="90"/>
-      <c r="AV5" s="90"/>
-      <c r="AW5" s="90"/>
-      <c r="AX5" s="90"/>
-      <c r="BJ5" s="89" t="s">
+      <c r="AR5" s="87"/>
+      <c r="AS5" s="87"/>
+      <c r="AT5" s="87"/>
+      <c r="AU5" s="87"/>
+      <c r="AV5" s="87"/>
+      <c r="AW5" s="87"/>
+      <c r="AX5" s="87"/>
+      <c r="BJ5" s="86" t="s">
         <v>1119</v>
       </c>
-      <c r="BK5" s="90"/>
-      <c r="BL5" s="90"/>
-      <c r="BM5" s="90"/>
-      <c r="BN5" s="90"/>
-      <c r="BO5" s="90"/>
-      <c r="BP5" s="90"/>
-      <c r="BQ5" s="90"/>
-      <c r="BR5" s="90"/>
+      <c r="BK5" s="87"/>
+      <c r="BL5" s="87"/>
+      <c r="BM5" s="87"/>
+      <c r="BN5" s="87"/>
+      <c r="BO5" s="87"/>
+      <c r="BP5" s="87"/>
+      <c r="BQ5" s="87"/>
+      <c r="BR5" s="87"/>
     </row>
     <row r="6" spans="1:70" ht="15">
       <c r="B6" s="13" t="s">
         <v>1407</v>
       </c>
-      <c r="W6" s="88" t="s">
+      <c r="W6" s="85" t="s">
         <v>1077</v>
       </c>
       <c r="X6" s="62"/>
-      <c r="AQ6" s="87" t="s">
+      <c r="AQ6" s="84" t="s">
         <v>1062</v>
       </c>
-      <c r="BJ6" s="87" t="s">
+      <c r="BJ6" s="84" t="s">
         <v>1062</v>
       </c>
     </row>
@@ -26027,7 +28336,7 @@
       <c r="B8" s="13" t="s">
         <v>1409</v>
       </c>
-      <c r="W8" s="88" t="s">
+      <c r="W8" s="85" t="s">
         <v>1079</v>
       </c>
       <c r="X8" s="62"/>
@@ -26247,7 +28556,7 @@
       <c r="AQ26" s="15" t="s">
         <v>1111</v>
       </c>
-      <c r="BJ26" s="91" t="s">
+      <c r="BJ26" s="88" t="s">
         <v>1132</v>
       </c>
     </row>
@@ -26258,7 +28567,7 @@
       <c r="AQ27" s="15" t="s">
         <v>1103</v>
       </c>
-      <c r="BJ27" s="91" t="s">
+      <c r="BJ27" s="88" t="s">
         <v>1133</v>
       </c>
     </row>
@@ -26269,14 +28578,14 @@
       <c r="AQ28" s="15" t="s">
         <v>901</v>
       </c>
-      <c r="BJ28" s="92"/>
+      <c r="BJ28" s="89"/>
     </row>
     <row r="29" spans="2:62">
       <c r="W29" s="15" t="s">
         <v>1094</v>
       </c>
       <c r="AQ29" s="69"/>
-      <c r="BJ29" s="91" t="s">
+      <c r="BJ29" s="88" t="s">
         <v>1134</v>
       </c>
     </row>
@@ -26287,7 +28596,7 @@
       <c r="AQ30" s="15" t="s">
         <v>1112</v>
       </c>
-      <c r="BJ30" s="91" t="s">
+      <c r="BJ30" s="88" t="s">
         <v>1135</v>
       </c>
     </row>
@@ -26295,7 +28604,7 @@
       <c r="AQ31" s="15" t="s">
         <v>1113</v>
       </c>
-      <c r="BJ31" s="91" t="s">
+      <c r="BJ31" s="88" t="s">
         <v>901</v>
       </c>
     </row>
@@ -26336,10 +28645,10 @@
       </c>
     </row>
     <row r="34" spans="2:62" ht="15">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="84" t="s">
         <v>1062</v>
       </c>
-      <c r="U34" s="87" t="s">
+      <c r="U34" s="84" t="s">
         <v>1062</v>
       </c>
       <c r="V34" s="62"/>
@@ -26412,7 +28721,7 @@
       <c r="B40" s="15" t="s">
         <v>1145</v>
       </c>
-      <c r="U40" s="94" t="s">
+      <c r="U40" s="91" t="s">
         <v>1415</v>
       </c>
       <c r="AQ40" s="15" t="s">
@@ -26599,7 +28908,7 @@
       </c>
     </row>
     <row r="66" spans="1:21">
-      <c r="B66" s="91" t="s">
+      <c r="B66" s="88" t="s">
         <v>1162</v>
       </c>
       <c r="U66" s="15" t="s">
@@ -26686,8 +28995,8 @@
     </row>
     <row r="79" spans="1:21" ht="15" thickBot="1"/>
     <row r="80" spans="1:21" s="16" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A80" s="95"/>
-      <c r="B80" s="96" t="s">
+      <c r="A80" s="92"/>
+      <c r="B80" s="93" t="s">
         <v>1191</v>
       </c>
     </row>
@@ -26741,39 +29050,39 @@
       <c r="BN81" s="44"/>
     </row>
     <row r="82" spans="2:73" ht="15">
-      <c r="B82" s="97" t="s">
+      <c r="B82" s="94" t="s">
         <v>1193</v>
       </c>
-      <c r="C82" s="98"/>
-      <c r="D82" s="98"/>
-      <c r="E82" s="98"/>
-      <c r="U82" s="97" t="s">
+      <c r="C82" s="95"/>
+      <c r="D82" s="95"/>
+      <c r="E82" s="95"/>
+      <c r="U82" s="94" t="s">
         <v>1214</v>
       </c>
-      <c r="V82" s="98"/>
-      <c r="W82" s="98"/>
-      <c r="X82" s="98"/>
-      <c r="Y82" s="98"/>
-      <c r="Z82" s="98"/>
-      <c r="AN82" s="97" t="s">
+      <c r="V82" s="95"/>
+      <c r="W82" s="95"/>
+      <c r="X82" s="95"/>
+      <c r="Y82" s="95"/>
+      <c r="Z82" s="95"/>
+      <c r="AN82" s="94" t="s">
         <v>1230</v>
       </c>
-      <c r="AO82" s="98"/>
-      <c r="AP82" s="98"/>
-      <c r="AQ82" s="98"/>
-      <c r="AR82" s="98"/>
-      <c r="AS82" s="98"/>
-      <c r="AT82" s="98"/>
-      <c r="AU82" s="98"/>
-      <c r="AV82" s="98"/>
-      <c r="BE82" s="97" t="s">
+      <c r="AO82" s="95"/>
+      <c r="AP82" s="95"/>
+      <c r="AQ82" s="95"/>
+      <c r="AR82" s="95"/>
+      <c r="AS82" s="95"/>
+      <c r="AT82" s="95"/>
+      <c r="AU82" s="95"/>
+      <c r="AV82" s="95"/>
+      <c r="BE82" s="94" t="s">
         <v>1247</v>
       </c>
-      <c r="BF82" s="98"/>
-      <c r="BG82" s="98"/>
-      <c r="BH82" s="98"/>
-      <c r="BI82" s="98"/>
-      <c r="BJ82" s="98"/>
+      <c r="BF82" s="95"/>
+      <c r="BG82" s="95"/>
+      <c r="BH82" s="95"/>
+      <c r="BI82" s="95"/>
+      <c r="BJ82" s="95"/>
     </row>
     <row r="83" spans="2:73">
       <c r="B83" s="15" t="s">
@@ -26860,7 +29169,7 @@
       <c r="AN89" s="15" t="s">
         <v>1235</v>
       </c>
-      <c r="BE89" s="91" t="s">
+      <c r="BE89" s="88" t="s">
         <v>1251</v>
       </c>
       <c r="BF89" s="62"/>
@@ -26924,13 +29233,13 @@
         <v>1200</v>
       </c>
       <c r="U93" s="69"/>
-      <c r="AN93" s="97" t="s">
+      <c r="AN93" s="94" t="s">
         <v>1237</v>
       </c>
-      <c r="AO93" s="98"/>
-      <c r="AP93" s="98"/>
-      <c r="AQ93" s="98"/>
-      <c r="AR93" s="98"/>
+      <c r="AO93" s="95"/>
+      <c r="AP93" s="95"/>
+      <c r="AQ93" s="95"/>
+      <c r="AR93" s="95"/>
     </row>
     <row r="94" spans="2:73" ht="15">
       <c r="B94" s="15" t="s">
@@ -26942,15 +29251,15 @@
       <c r="AN94" s="15" t="s">
         <v>1238</v>
       </c>
-      <c r="BE94" s="97" t="s">
+      <c r="BE94" s="94" t="s">
         <v>1253</v>
       </c>
-      <c r="BF94" s="98"/>
-      <c r="BG94" s="98"/>
-      <c r="BH94" s="98"/>
-      <c r="BI94" s="98"/>
-      <c r="BJ94" s="98"/>
-      <c r="BK94" s="98"/>
+      <c r="BF94" s="95"/>
+      <c r="BG94" s="95"/>
+      <c r="BH94" s="95"/>
+      <c r="BI94" s="95"/>
+      <c r="BJ94" s="95"/>
+      <c r="BK94" s="95"/>
     </row>
     <row r="95" spans="2:73">
       <c r="B95" s="15" t="s">
@@ -27001,19 +29310,19 @@
       </c>
     </row>
     <row r="99" spans="2:57" ht="15">
-      <c r="B99" s="97" t="s">
+      <c r="B99" s="94" t="s">
         <v>1203</v>
       </c>
-      <c r="C99" s="98"/>
-      <c r="D99" s="98"/>
-      <c r="E99" s="98"/>
-      <c r="U99" s="97" t="s">
+      <c r="C99" s="95"/>
+      <c r="D99" s="95"/>
+      <c r="E99" s="95"/>
+      <c r="U99" s="94" t="s">
         <v>1223</v>
       </c>
-      <c r="V99" s="98"/>
-      <c r="W99" s="98"/>
-      <c r="X99" s="98"/>
-      <c r="Y99" s="98"/>
+      <c r="V99" s="95"/>
+      <c r="W99" s="95"/>
+      <c r="X99" s="95"/>
+      <c r="Y99" s="95"/>
       <c r="AN99" s="69"/>
       <c r="BE99" s="15" t="s">
         <v>1083</v>
@@ -27165,8 +29474,8 @@
     </row>
     <row r="113" spans="1:53" ht="15" thickBot="1"/>
     <row r="114" spans="1:53" s="16" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A114" s="95"/>
-      <c r="B114" s="96" t="s">
+      <c r="A114" s="92"/>
+      <c r="B114" s="93" t="s">
         <v>1267</v>
       </c>
     </row>
@@ -27209,32 +29518,32 @@
       <c r="BA115" s="44"/>
     </row>
     <row r="116" spans="1:53" ht="15">
-      <c r="B116" s="97" t="s">
+      <c r="B116" s="94" t="s">
         <v>1269</v>
       </c>
-      <c r="C116" s="98"/>
-      <c r="D116" s="98"/>
-      <c r="E116" s="98"/>
-      <c r="F116" s="98"/>
-      <c r="Y116" s="97" t="s">
+      <c r="C116" s="95"/>
+      <c r="D116" s="95"/>
+      <c r="E116" s="95"/>
+      <c r="F116" s="95"/>
+      <c r="Y116" s="94" t="s">
         <v>1299</v>
       </c>
-      <c r="Z116" s="98"/>
-      <c r="AA116" s="98"/>
-      <c r="AB116" s="98"/>
-      <c r="AC116" s="98"/>
-      <c r="AD116" s="98"/>
-      <c r="AE116" s="98"/>
-      <c r="AF116" s="98"/>
-      <c r="AG116" s="98"/>
-      <c r="AH116" s="98"/>
-      <c r="AQ116" s="97" t="s">
+      <c r="Z116" s="95"/>
+      <c r="AA116" s="95"/>
+      <c r="AB116" s="95"/>
+      <c r="AC116" s="95"/>
+      <c r="AD116" s="95"/>
+      <c r="AE116" s="95"/>
+      <c r="AF116" s="95"/>
+      <c r="AG116" s="95"/>
+      <c r="AH116" s="95"/>
+      <c r="AQ116" s="94" t="s">
         <v>1316</v>
       </c>
-      <c r="AR116" s="98"/>
-      <c r="AS116" s="98"/>
-      <c r="AT116" s="98"/>
-      <c r="AU116" s="98"/>
+      <c r="AR116" s="95"/>
+      <c r="AS116" s="95"/>
+      <c r="AT116" s="95"/>
+      <c r="AU116" s="95"/>
     </row>
     <row r="117" spans="1:53">
       <c r="B117" s="15" t="s">
@@ -27302,7 +29611,7 @@
       <c r="B123" s="15" t="s">
         <v>1275</v>
       </c>
-      <c r="Y123" s="91" t="s">
+      <c r="Y123" s="88" t="s">
         <v>1305</v>
       </c>
       <c r="Z123" s="62"/>
@@ -27327,7 +29636,7 @@
       <c r="B124" s="15" t="s">
         <v>1276</v>
       </c>
-      <c r="Y124" s="99" t="s">
+      <c r="Y124" s="96" t="s">
         <v>1306</v>
       </c>
       <c r="Z124" s="62"/>
@@ -27352,25 +29661,25 @@
       <c r="Y125" s="15" t="s">
         <v>901</v>
       </c>
-      <c r="AQ125" s="97" t="s">
+      <c r="AQ125" s="94" t="s">
         <v>1322</v>
       </c>
-      <c r="AR125" s="98"/>
-      <c r="AS125" s="98"/>
-      <c r="AT125" s="98"/>
-      <c r="AU125" s="98"/>
-      <c r="AV125" s="98"/>
-      <c r="AW125" s="98"/>
-      <c r="AX125" s="98"/>
-      <c r="AY125" s="98"/>
-      <c r="AZ125" s="98"/>
-      <c r="BA125" s="98"/>
+      <c r="AR125" s="95"/>
+      <c r="AS125" s="95"/>
+      <c r="AT125" s="95"/>
+      <c r="AU125" s="95"/>
+      <c r="AV125" s="95"/>
+      <c r="AW125" s="95"/>
+      <c r="AX125" s="95"/>
+      <c r="AY125" s="95"/>
+      <c r="AZ125" s="95"/>
+      <c r="BA125" s="95"/>
     </row>
     <row r="126" spans="1:53" ht="15">
       <c r="B126" s="15" t="s">
         <v>1278</v>
       </c>
-      <c r="AQ126" s="100" t="s">
+      <c r="AQ126" s="97" t="s">
         <v>1417</v>
       </c>
     </row>
@@ -27378,20 +29687,20 @@
       <c r="B127" s="15" t="s">
         <v>901</v>
       </c>
-      <c r="Y127" s="97" t="s">
+      <c r="Y127" s="94" t="s">
         <v>1307</v>
       </c>
-      <c r="Z127" s="98"/>
-      <c r="AA127" s="98"/>
-      <c r="AB127" s="98"/>
-      <c r="AC127" s="98"/>
-      <c r="AD127" s="98"/>
-      <c r="AE127" s="98"/>
-      <c r="AF127" s="98"/>
-      <c r="AG127" s="98"/>
-      <c r="AH127" s="98"/>
-      <c r="AI127" s="98"/>
-      <c r="AQ127" s="91" t="s">
+      <c r="Z127" s="95"/>
+      <c r="AA127" s="95"/>
+      <c r="AB127" s="95"/>
+      <c r="AC127" s="95"/>
+      <c r="AD127" s="95"/>
+      <c r="AE127" s="95"/>
+      <c r="AF127" s="95"/>
+      <c r="AG127" s="95"/>
+      <c r="AH127" s="95"/>
+      <c r="AI127" s="95"/>
+      <c r="AQ127" s="88" t="s">
         <v>1418</v>
       </c>
     </row>
@@ -27402,13 +29711,13 @@
       <c r="AQ128" s="69"/>
     </row>
     <row r="129" spans="2:58" ht="15">
-      <c r="B129" s="97" t="s">
+      <c r="B129" s="94" t="s">
         <v>1279</v>
       </c>
-      <c r="C129" s="98"/>
-      <c r="D129" s="98"/>
-      <c r="E129" s="98"/>
-      <c r="F129" s="98"/>
+      <c r="C129" s="95"/>
+      <c r="D129" s="95"/>
+      <c r="E129" s="95"/>
+      <c r="F129" s="95"/>
       <c r="Y129" s="15" t="s">
         <v>1309</v>
       </c>
@@ -27454,30 +29763,30 @@
       <c r="Y133" s="15" t="s">
         <v>1312</v>
       </c>
-      <c r="AQ133" s="99" t="s">
+      <c r="AQ133" s="96" t="s">
         <v>1326</v>
       </c>
-      <c r="AR133" s="87"/>
-      <c r="AS133" s="87"/>
-      <c r="AT133" s="87"/>
-      <c r="AU133" s="87"/>
-      <c r="AV133" s="87"/>
-      <c r="AW133" s="87"/>
-      <c r="AX133" s="87"/>
-      <c r="AY133" s="87"/>
-      <c r="AZ133" s="87"/>
-      <c r="BA133" s="87"/>
-      <c r="BB133" s="87"/>
-      <c r="BC133" s="87"/>
-      <c r="BD133" s="87"/>
-      <c r="BE133" s="87"/>
-      <c r="BF133" s="87"/>
+      <c r="AR133" s="84"/>
+      <c r="AS133" s="84"/>
+      <c r="AT133" s="84"/>
+      <c r="AU133" s="84"/>
+      <c r="AV133" s="84"/>
+      <c r="AW133" s="84"/>
+      <c r="AX133" s="84"/>
+      <c r="AY133" s="84"/>
+      <c r="AZ133" s="84"/>
+      <c r="BA133" s="84"/>
+      <c r="BB133" s="84"/>
+      <c r="BC133" s="84"/>
+      <c r="BD133" s="84"/>
+      <c r="BE133" s="84"/>
+      <c r="BF133" s="84"/>
     </row>
     <row r="134" spans="2:58" ht="15">
       <c r="B134" s="15" t="s">
         <v>1283</v>
       </c>
-      <c r="Y134" s="91" t="s">
+      <c r="Y134" s="88" t="s">
         <v>1313</v>
       </c>
       <c r="Z134" s="62"/>
@@ -27494,30 +29803,30 @@
       <c r="AK134" s="62"/>
       <c r="AL134" s="62"/>
       <c r="AM134" s="62"/>
-      <c r="AQ134" s="99" t="s">
+      <c r="AQ134" s="96" t="s">
         <v>1327</v>
       </c>
-      <c r="AR134" s="87"/>
-      <c r="AS134" s="87"/>
-      <c r="AT134" s="87"/>
-      <c r="AU134" s="87"/>
-      <c r="AV134" s="87"/>
-      <c r="AW134" s="87"/>
-      <c r="AX134" s="87"/>
-      <c r="AY134" s="87"/>
-      <c r="AZ134" s="87"/>
-      <c r="BA134" s="87"/>
-      <c r="BB134" s="87"/>
-      <c r="BC134" s="87"/>
-      <c r="BD134" s="87"/>
-      <c r="BE134" s="87"/>
-      <c r="BF134" s="87"/>
+      <c r="AR134" s="84"/>
+      <c r="AS134" s="84"/>
+      <c r="AT134" s="84"/>
+      <c r="AU134" s="84"/>
+      <c r="AV134" s="84"/>
+      <c r="AW134" s="84"/>
+      <c r="AX134" s="84"/>
+      <c r="AY134" s="84"/>
+      <c r="AZ134" s="84"/>
+      <c r="BA134" s="84"/>
+      <c r="BB134" s="84"/>
+      <c r="BC134" s="84"/>
+      <c r="BD134" s="84"/>
+      <c r="BE134" s="84"/>
+      <c r="BF134" s="84"/>
     </row>
     <row r="135" spans="2:58" ht="15">
       <c r="B135" s="15" t="s">
         <v>1284</v>
       </c>
-      <c r="Y135" s="99" t="s">
+      <c r="Y135" s="96" t="s">
         <v>1314</v>
       </c>
       <c r="Z135" s="62"/>
@@ -27618,16 +29927,16 @@
       </c>
     </row>
     <row r="151" spans="2:12" ht="15">
-      <c r="B151" s="97" t="s">
+      <c r="B151" s="94" t="s">
         <v>1293</v>
       </c>
-      <c r="C151" s="98"/>
-      <c r="D151" s="98"/>
-      <c r="E151" s="98"/>
-      <c r="F151" s="98"/>
-      <c r="G151" s="98"/>
-      <c r="H151" s="98"/>
-      <c r="I151" s="98"/>
+      <c r="C151" s="95"/>
+      <c r="D151" s="95"/>
+      <c r="E151" s="95"/>
+      <c r="F151" s="95"/>
+      <c r="G151" s="95"/>
+      <c r="H151" s="95"/>
+      <c r="I151" s="95"/>
     </row>
     <row r="152" spans="2:12">
       <c r="B152" s="15" t="s">
@@ -27680,30 +29989,30 @@
       <c r="L160" s="44"/>
     </row>
     <row r="161" spans="2:52" ht="15">
-      <c r="B161" s="101" t="s">
+      <c r="B161" s="98" t="s">
         <v>1330</v>
       </c>
-      <c r="C161" s="102"/>
-      <c r="D161" s="102"/>
-      <c r="E161" s="102"/>
-      <c r="F161" s="102"/>
-      <c r="G161" s="102"/>
-      <c r="U161" s="101" t="s">
+      <c r="C161" s="99"/>
+      <c r="D161" s="99"/>
+      <c r="E161" s="99"/>
+      <c r="F161" s="99"/>
+      <c r="G161" s="99"/>
+      <c r="U161" s="98" t="s">
         <v>1338</v>
       </c>
-      <c r="V161" s="102"/>
-      <c r="W161" s="102"/>
-      <c r="X161" s="102"/>
-      <c r="Y161" s="102"/>
-      <c r="Z161" s="102"/>
-      <c r="AS161" s="101" t="s">
+      <c r="V161" s="99"/>
+      <c r="W161" s="99"/>
+      <c r="X161" s="99"/>
+      <c r="Y161" s="99"/>
+      <c r="Z161" s="99"/>
+      <c r="AS161" s="98" t="s">
         <v>1352</v>
       </c>
-      <c r="AT161" s="102"/>
-      <c r="AU161" s="102"/>
-      <c r="AV161" s="102"/>
-      <c r="AW161" s="102"/>
-      <c r="AX161" s="102"/>
+      <c r="AT161" s="99"/>
+      <c r="AU161" s="99"/>
+      <c r="AV161" s="99"/>
+      <c r="AW161" s="99"/>
+      <c r="AX161" s="99"/>
     </row>
     <row r="162" spans="2:52" ht="15">
       <c r="B162" s="15" t="s">
@@ -27712,15 +30021,15 @@
       <c r="U162" s="15" t="s">
         <v>1339</v>
       </c>
-      <c r="AS162" s="99" t="s">
+      <c r="AS162" s="96" t="s">
         <v>1353</v>
       </c>
-      <c r="AT162" s="87"/>
-      <c r="AU162" s="87"/>
-      <c r="AV162" s="87"/>
-      <c r="AW162" s="87"/>
-      <c r="AX162" s="87"/>
-      <c r="AY162" s="87"/>
+      <c r="AT162" s="84"/>
+      <c r="AU162" s="84"/>
+      <c r="AV162" s="84"/>
+      <c r="AW162" s="84"/>
+      <c r="AX162" s="84"/>
+      <c r="AY162" s="84"/>
     </row>
     <row r="163" spans="2:52">
       <c r="B163" s="15" t="s">
@@ -27766,24 +30075,24 @@
       <c r="B167" s="15" t="s">
         <v>1335</v>
       </c>
-      <c r="U167" s="99" t="s">
+      <c r="U167" s="96" t="s">
         <v>1341</v>
       </c>
-      <c r="V167" s="87"/>
-      <c r="W167" s="87"/>
-      <c r="X167" s="87"/>
-      <c r="Y167" s="87"/>
-      <c r="Z167" s="87"/>
-      <c r="AS167" s="99" t="s">
+      <c r="V167" s="84"/>
+      <c r="W167" s="84"/>
+      <c r="X167" s="84"/>
+      <c r="Y167" s="84"/>
+      <c r="Z167" s="84"/>
+      <c r="AS167" s="96" t="s">
         <v>1356</v>
       </c>
-      <c r="AT167" s="87"/>
-      <c r="AU167" s="87"/>
-      <c r="AV167" s="87"/>
-      <c r="AW167" s="87"/>
-      <c r="AX167" s="87"/>
-      <c r="AY167" s="87"/>
-      <c r="AZ167" s="87"/>
+      <c r="AT167" s="84"/>
+      <c r="AU167" s="84"/>
+      <c r="AV167" s="84"/>
+      <c r="AW167" s="84"/>
+      <c r="AX167" s="84"/>
+      <c r="AY167" s="84"/>
+      <c r="AZ167" s="84"/>
     </row>
     <row r="168" spans="2:52">
       <c r="B168" s="15" t="s">
@@ -27842,26 +30151,26 @@
       <c r="U174" s="15" t="s">
         <v>1343</v>
       </c>
-      <c r="AS174" s="99" t="s">
+      <c r="AS174" s="96" t="s">
         <v>1362</v>
       </c>
-      <c r="AT174" s="87"/>
-      <c r="AU174" s="87"/>
-      <c r="AV174" s="87"/>
-      <c r="AW174" s="87"/>
-      <c r="AX174" s="87"/>
-      <c r="AY174" s="87"/>
-      <c r="AZ174" s="87"/>
+      <c r="AT174" s="84"/>
+      <c r="AU174" s="84"/>
+      <c r="AV174" s="84"/>
+      <c r="AW174" s="84"/>
+      <c r="AX174" s="84"/>
+      <c r="AY174" s="84"/>
+      <c r="AZ174" s="84"/>
     </row>
     <row r="175" spans="2:52" ht="15">
-      <c r="U175" s="99" t="s">
+      <c r="U175" s="96" t="s">
         <v>1347</v>
       </c>
-      <c r="V175" s="87"/>
-      <c r="W175" s="87"/>
-      <c r="X175" s="87"/>
-      <c r="Y175" s="87"/>
-      <c r="Z175" s="87"/>
+      <c r="V175" s="84"/>
+      <c r="W175" s="84"/>
+      <c r="X175" s="84"/>
+      <c r="Y175" s="84"/>
+      <c r="Z175" s="84"/>
       <c r="AS175" s="15" t="s">
         <v>1363</v>
       </c>
@@ -27919,8 +30228,8 @@
     </row>
     <row r="183" spans="1:47" ht="15" thickBot="1"/>
     <row r="184" spans="1:47" s="16" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A184" s="95"/>
-      <c r="B184" s="96" t="s">
+      <c r="A184" s="92"/>
+      <c r="B184" s="93" t="s">
         <v>1366</v>
       </c>
     </row>
@@ -28098,7 +30407,7 @@
       </c>
     </row>
     <row r="201" spans="1:44">
-      <c r="B201" s="91" t="s">
+      <c r="B201" s="88" t="s">
         <v>1166</v>
       </c>
       <c r="C201" s="62"/>
@@ -28118,7 +30427,7 @@
       </c>
     </row>
     <row r="202" spans="1:44">
-      <c r="B202" s="91" t="s">
+      <c r="B202" s="88" t="s">
         <v>1205</v>
       </c>
       <c r="C202" s="62"/>
@@ -28138,7 +30447,7 @@
       </c>
     </row>
     <row r="203" spans="1:44">
-      <c r="B203" s="91" t="s">
+      <c r="B203" s="88" t="s">
         <v>1389</v>
       </c>
       <c r="C203" s="62"/>
@@ -28159,8 +30468,8 @@
     </row>
     <row r="204" spans="1:44" ht="15" thickBot="1"/>
     <row r="205" spans="1:44" s="16" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A205" s="95"/>
-      <c r="B205" s="96" t="s">
+      <c r="A205" s="92"/>
+      <c r="B205" s="93" t="s">
         <v>1393</v>
       </c>
     </row>
@@ -28379,9 +30688,4311 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E705242-2605-4ED2-A504-13435F2B53FF}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:CB728"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="16384" width="3" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:74" ht="15">
+      <c r="B1" s="10" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="2" spans="1:74" ht="15" thickBot="1"/>
+    <row r="3" spans="1:74" s="16" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A3" s="92"/>
+      <c r="B3" s="93" t="s">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="4" spans="1:74" ht="15">
+      <c r="B4" s="43" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="AA4" s="43" t="s">
+        <v>1469</v>
+      </c>
+      <c r="AB4" s="44"/>
+      <c r="AC4" s="44"/>
+      <c r="AD4" s="44"/>
+      <c r="AE4" s="44"/>
+      <c r="AF4" s="44"/>
+      <c r="AG4" s="44"/>
+      <c r="AH4" s="44"/>
+      <c r="AI4" s="44"/>
+      <c r="AU4" s="43" t="s">
+        <v>1509</v>
+      </c>
+      <c r="AV4" s="44"/>
+      <c r="AW4" s="44"/>
+      <c r="AX4" s="44"/>
+      <c r="AY4" s="44"/>
+      <c r="AZ4" s="44"/>
+      <c r="BA4" s="44"/>
+      <c r="BB4" s="44"/>
+      <c r="BC4" s="44"/>
+      <c r="BD4" s="44"/>
+      <c r="BE4" s="44"/>
+      <c r="BF4" s="44"/>
+      <c r="BG4" s="44"/>
+      <c r="BO4" s="43" t="s">
+        <v>1542</v>
+      </c>
+      <c r="BP4" s="44"/>
+      <c r="BQ4" s="44"/>
+      <c r="BR4" s="44"/>
+      <c r="BS4" s="44"/>
+      <c r="BT4" s="44"/>
+      <c r="BU4" s="44"/>
+    </row>
+    <row r="5" spans="1:74" ht="15">
+      <c r="B5" s="98" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="AA5" s="98" t="s">
+        <v>1470</v>
+      </c>
+      <c r="AB5" s="99"/>
+      <c r="AC5" s="99"/>
+      <c r="AD5" s="99"/>
+      <c r="AE5" s="99"/>
+      <c r="AF5" s="99"/>
+      <c r="AG5" s="99"/>
+      <c r="AH5" s="99"/>
+      <c r="AI5" s="99"/>
+      <c r="AJ5" s="99"/>
+      <c r="AU5" s="98" t="s">
+        <v>1510</v>
+      </c>
+      <c r="AV5" s="99"/>
+      <c r="AW5" s="99"/>
+      <c r="AX5" s="99"/>
+      <c r="AY5" s="99"/>
+      <c r="AZ5" s="99"/>
+      <c r="BO5" s="98" t="s">
+        <v>1543</v>
+      </c>
+      <c r="BP5" s="99"/>
+      <c r="BQ5" s="99"/>
+      <c r="BR5" s="99"/>
+      <c r="BS5" s="99"/>
+      <c r="BT5" s="99"/>
+      <c r="BU5" s="99"/>
+      <c r="BV5" s="99"/>
+    </row>
+    <row r="6" spans="1:74">
+      <c r="B6" s="15" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="7" spans="1:74">
+      <c r="B7" s="15" t="s">
+        <v>1424</v>
+      </c>
+      <c r="AA7" s="15" t="s">
+        <v>1471</v>
+      </c>
+      <c r="AU7" s="15" t="s">
+        <v>1511</v>
+      </c>
+      <c r="BO7" s="15" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="8" spans="1:74">
+      <c r="B8" s="69"/>
+      <c r="AA8" s="15" t="s">
+        <v>1472</v>
+      </c>
+      <c r="AU8" s="15" t="s">
+        <v>1512</v>
+      </c>
+      <c r="BO8" s="15" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="9" spans="1:74">
+      <c r="B9" s="15" t="s">
+        <v>1425</v>
+      </c>
+      <c r="AA9" s="69"/>
+      <c r="AU9" s="15" t="s">
+        <v>1513</v>
+      </c>
+      <c r="BO9" s="15" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="10" spans="1:74">
+      <c r="B10" s="15" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AA10" s="15" t="s">
+        <v>1473</v>
+      </c>
+      <c r="AU10" s="15" t="s">
+        <v>1514</v>
+      </c>
+      <c r="BO10" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="11" spans="1:74">
+      <c r="B11" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AA11" s="15" t="s">
+        <v>1474</v>
+      </c>
+      <c r="AU11" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="BO11" s="15" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="12" spans="1:74">
+      <c r="B12" s="15" t="s">
+        <v>1427</v>
+      </c>
+      <c r="AA12" s="15" t="s">
+        <v>1475</v>
+      </c>
+      <c r="AU12" s="15" t="s">
+        <v>1515</v>
+      </c>
+      <c r="BO12" s="15" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="13" spans="1:74">
+      <c r="B13" s="15" t="s">
+        <v>1428</v>
+      </c>
+      <c r="AA13" s="15" t="s">
+        <v>1476</v>
+      </c>
+      <c r="AU13" s="15" t="s">
+        <v>1516</v>
+      </c>
+      <c r="BO13" s="15" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="14" spans="1:74">
+      <c r="B14" s="15" t="s">
+        <v>1429</v>
+      </c>
+      <c r="AA14" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AU14" s="15" t="s">
+        <v>1517</v>
+      </c>
+      <c r="BO14" s="15" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="15" spans="1:74">
+      <c r="B15" s="15" t="s">
+        <v>1430</v>
+      </c>
+      <c r="AA15" s="88" t="s">
+        <v>1477</v>
+      </c>
+      <c r="AB15" s="62"/>
+      <c r="AC15" s="62"/>
+      <c r="AD15" s="62"/>
+      <c r="AE15" s="62"/>
+      <c r="AF15" s="62"/>
+      <c r="AG15" s="62"/>
+      <c r="AH15" s="62"/>
+      <c r="AI15" s="62"/>
+      <c r="AJ15" s="62"/>
+      <c r="AK15" s="62"/>
+      <c r="AL15" s="62"/>
+      <c r="AM15" s="62"/>
+      <c r="AN15" s="62"/>
+      <c r="AO15" s="62"/>
+      <c r="AP15" s="62"/>
+      <c r="AQ15" s="62"/>
+      <c r="AR15" s="62"/>
+      <c r="AU15" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="BO15" s="15" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="16" spans="1:74">
+      <c r="B16" s="15" t="s">
+        <v>1431</v>
+      </c>
+      <c r="AA16" s="88" t="s">
+        <v>1478</v>
+      </c>
+      <c r="AB16" s="62"/>
+      <c r="AC16" s="62"/>
+      <c r="AD16" s="62"/>
+      <c r="AE16" s="62"/>
+      <c r="AF16" s="62"/>
+      <c r="AG16" s="62"/>
+      <c r="AH16" s="62"/>
+      <c r="AI16" s="62"/>
+      <c r="AJ16" s="62"/>
+      <c r="AK16" s="62"/>
+      <c r="AL16" s="62"/>
+      <c r="AM16" s="62"/>
+      <c r="AN16" s="62"/>
+      <c r="AO16" s="62"/>
+      <c r="AP16" s="62"/>
+      <c r="AQ16" s="62"/>
+      <c r="AR16" s="62"/>
+      <c r="AU16" s="15" t="s">
+        <v>1518</v>
+      </c>
+      <c r="BO16" s="15" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="17" spans="2:80">
+      <c r="B17" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AA17" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AU17" s="15" t="s">
+        <v>1519</v>
+      </c>
+      <c r="BO17" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="18" spans="2:80">
+      <c r="AA18" s="15" t="s">
+        <v>1479</v>
+      </c>
+      <c r="AU18" s="15" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="19" spans="2:80" ht="15">
+      <c r="B19" s="98" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C19" s="99"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="99"/>
+      <c r="I19" s="99"/>
+      <c r="AA19" s="15" t="s">
+        <v>1480</v>
+      </c>
+      <c r="AU19" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="BO19" s="98" t="s">
+        <v>1553</v>
+      </c>
+      <c r="BP19" s="99"/>
+      <c r="BQ19" s="99"/>
+      <c r="BR19" s="99"/>
+      <c r="BS19" s="99"/>
+      <c r="BT19" s="99"/>
+    </row>
+    <row r="20" spans="2:80">
+      <c r="B20" s="15" t="s">
+        <v>1424</v>
+      </c>
+      <c r="AA20" s="15" t="s">
+        <v>1481</v>
+      </c>
+      <c r="AU20" s="15" t="s">
+        <v>1521</v>
+      </c>
+      <c r="BO20" s="15" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="21" spans="2:80">
+      <c r="B21" s="69"/>
+      <c r="AA21" s="15" t="s">
+        <v>1482</v>
+      </c>
+      <c r="AU21" s="15" t="s">
+        <v>1522</v>
+      </c>
+      <c r="BO21" s="15" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="22" spans="2:80">
+      <c r="B22" s="15" t="s">
+        <v>1433</v>
+      </c>
+      <c r="AA22" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AU22" s="15" t="s">
+        <v>1523</v>
+      </c>
+      <c r="BO22" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="23" spans="2:80">
+      <c r="B23" s="15" t="s">
+        <v>1434</v>
+      </c>
+      <c r="AU23" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BO23" s="15" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="24" spans="2:80" ht="15">
+      <c r="B24" s="15" t="s">
+        <v>1435</v>
+      </c>
+      <c r="AA24" s="98" t="s">
+        <v>1483</v>
+      </c>
+      <c r="AB24" s="99"/>
+      <c r="AC24" s="99"/>
+      <c r="AD24" s="99"/>
+      <c r="AE24" s="99"/>
+      <c r="AF24" s="99"/>
+      <c r="AG24" s="99"/>
+      <c r="AH24" s="99"/>
+      <c r="AI24" s="99"/>
+      <c r="AJ24" s="99"/>
+      <c r="BO24" s="15" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="25" spans="2:80" ht="15">
+      <c r="B25" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AA25" s="15" t="s">
+        <v>1472</v>
+      </c>
+      <c r="AU25" s="98" t="s">
+        <v>1524</v>
+      </c>
+      <c r="AV25" s="99"/>
+      <c r="AW25" s="99"/>
+      <c r="AX25" s="99"/>
+      <c r="AY25" s="99"/>
+      <c r="BO25" s="15" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="26" spans="2:80">
+      <c r="B26" s="15" t="s">
+        <v>1436</v>
+      </c>
+      <c r="AA26" s="69"/>
+      <c r="AU26" s="15" t="s">
+        <v>1525</v>
+      </c>
+      <c r="BO26" s="15" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="27" spans="2:80">
+      <c r="B27" s="88" t="s">
+        <v>1437</v>
+      </c>
+      <c r="AA27" s="15" t="s">
+        <v>1484</v>
+      </c>
+      <c r="AU27" s="15" t="s">
+        <v>1526</v>
+      </c>
+      <c r="BO27" s="15" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="28" spans="2:80">
+      <c r="B28" s="15" t="s">
+        <v>1438</v>
+      </c>
+      <c r="AA28" s="88" t="s">
+        <v>1485</v>
+      </c>
+      <c r="AB28" s="62"/>
+      <c r="AU28" s="15" t="s">
+        <v>1527</v>
+      </c>
+      <c r="BO28" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="29" spans="2:80">
+      <c r="B29" s="88" t="s">
+        <v>1439</v>
+      </c>
+      <c r="AA29" s="88" t="s">
+        <v>1486</v>
+      </c>
+      <c r="AB29" s="62"/>
+      <c r="AU29" s="15" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="30" spans="2:80" ht="15">
+      <c r="B30" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AA30" s="88" t="s">
+        <v>1487</v>
+      </c>
+      <c r="AB30" s="62"/>
+      <c r="AU30" s="15" t="s">
+        <v>1529</v>
+      </c>
+      <c r="BO30" s="98" t="s">
+        <v>1561</v>
+      </c>
+      <c r="BP30" s="99"/>
+      <c r="BQ30" s="99"/>
+      <c r="BR30" s="99"/>
+      <c r="BS30" s="99"/>
+      <c r="BT30" s="99"/>
+      <c r="BU30" s="99"/>
+      <c r="BV30" s="99"/>
+      <c r="BW30" s="99"/>
+      <c r="BX30" s="99"/>
+      <c r="BY30" s="99"/>
+      <c r="BZ30" s="99"/>
+      <c r="CA30" s="99"/>
+      <c r="CB30" s="99"/>
+    </row>
+    <row r="31" spans="2:80">
+      <c r="B31" s="15" t="s">
+        <v>1440</v>
+      </c>
+      <c r="AA31" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AU31" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="BO31" s="15" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="32" spans="2:80">
+      <c r="B32" s="15" t="s">
+        <v>1441</v>
+      </c>
+      <c r="AA32" s="15" t="s">
+        <v>1488</v>
+      </c>
+      <c r="AU32" s="15" t="s">
+        <v>1530</v>
+      </c>
+      <c r="BO32" s="15" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="33" spans="2:75">
+      <c r="B33" s="15" t="s">
+        <v>1442</v>
+      </c>
+      <c r="AA33" s="15" t="s">
+        <v>1489</v>
+      </c>
+      <c r="AU33" s="15" t="s">
+        <v>1531</v>
+      </c>
+      <c r="BO33" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="34" spans="2:75">
+      <c r="B34" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AA34" s="15" t="s">
+        <v>1490</v>
+      </c>
+      <c r="AU34" s="15" t="s">
+        <v>1532</v>
+      </c>
+      <c r="BO34" s="15" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="35" spans="2:75">
+      <c r="AA35" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AU35" s="15" t="s">
+        <v>1533</v>
+      </c>
+      <c r="BO35" s="15" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="36" spans="2:75" ht="15">
+      <c r="B36" s="98" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C36" s="99"/>
+      <c r="D36" s="99"/>
+      <c r="E36" s="99"/>
+      <c r="F36" s="99"/>
+      <c r="G36" s="99"/>
+      <c r="H36" s="99"/>
+      <c r="I36" s="99"/>
+      <c r="J36" s="99"/>
+      <c r="AA36" s="15" t="s">
+        <v>1491</v>
+      </c>
+      <c r="AU36" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BO36" s="15" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="37" spans="2:75">
+      <c r="B37" s="15" t="s">
+        <v>1444</v>
+      </c>
+      <c r="AA37" s="15" t="s">
+        <v>1492</v>
+      </c>
+      <c r="BO37" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="38" spans="2:75" ht="15">
+      <c r="B38" s="15" t="s">
+        <v>1445</v>
+      </c>
+      <c r="AA38" s="15" t="s">
+        <v>1493</v>
+      </c>
+      <c r="AU38" s="98" t="s">
+        <v>1534</v>
+      </c>
+      <c r="AV38" s="99"/>
+      <c r="AW38" s="99"/>
+      <c r="AX38" s="99"/>
+      <c r="AY38" s="99"/>
+      <c r="AZ38" s="99"/>
+      <c r="BA38" s="99"/>
+      <c r="BB38" s="99"/>
+      <c r="BO38" s="15" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="39" spans="2:75">
+      <c r="B39" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AA39" s="15" t="s">
+        <v>1494</v>
+      </c>
+      <c r="AU39" s="15" t="s">
+        <v>1535</v>
+      </c>
+      <c r="BO39" s="15" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="40" spans="2:75">
+      <c r="B40" s="15" t="s">
+        <v>1446</v>
+      </c>
+      <c r="AA40" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AU40" s="15" t="s">
+        <v>1536</v>
+      </c>
+      <c r="BO40" s="15" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="41" spans="2:75">
+      <c r="B41" s="88" t="s">
+        <v>1447</v>
+      </c>
+      <c r="AU41" s="15" t="s">
+        <v>1537</v>
+      </c>
+      <c r="BO41" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="42" spans="2:75" ht="15">
+      <c r="B42" s="88" t="s">
+        <v>1448</v>
+      </c>
+      <c r="AA42" s="98" t="s">
+        <v>1495</v>
+      </c>
+      <c r="AB42" s="99"/>
+      <c r="AC42" s="99"/>
+      <c r="AD42" s="99"/>
+      <c r="AE42" s="99"/>
+      <c r="AF42" s="99"/>
+      <c r="AG42" s="99"/>
+      <c r="AH42" s="99"/>
+      <c r="AI42" s="99"/>
+      <c r="AJ42" s="99"/>
+      <c r="AK42" s="99"/>
+      <c r="AU42" s="15" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="43" spans="2:75" ht="15">
+      <c r="B43" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AA43" s="15" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AU43" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BO43" s="98" t="s">
+        <v>1570</v>
+      </c>
+      <c r="BP43" s="99"/>
+      <c r="BQ43" s="99"/>
+      <c r="BR43" s="99"/>
+      <c r="BS43" s="99"/>
+      <c r="BT43" s="99"/>
+      <c r="BU43" s="99"/>
+      <c r="BV43" s="99"/>
+      <c r="BW43" s="99"/>
+    </row>
+    <row r="44" spans="2:75">
+      <c r="AA44" s="15" t="s">
+        <v>1497</v>
+      </c>
+      <c r="AU44" s="69"/>
+      <c r="BO44" s="15" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="45" spans="2:75" ht="15">
+      <c r="B45" s="98" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
+      <c r="F45" s="99"/>
+      <c r="G45" s="99"/>
+      <c r="H45" s="99"/>
+      <c r="I45" s="99"/>
+      <c r="AA45" s="15" t="s">
+        <v>1498</v>
+      </c>
+      <c r="AU45" s="15" t="s">
+        <v>1539</v>
+      </c>
+      <c r="BO45" s="15" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="46" spans="2:75">
+      <c r="B46" s="15" t="s">
+        <v>1450</v>
+      </c>
+      <c r="AA46" s="15" t="s">
+        <v>1499</v>
+      </c>
+      <c r="AU46" s="15" t="s">
+        <v>1540</v>
+      </c>
+      <c r="BO46" s="15" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="47" spans="2:75">
+      <c r="B47" s="69"/>
+      <c r="AA47" s="15" t="s">
+        <v>1500</v>
+      </c>
+      <c r="AU47" s="15" t="s">
+        <v>1537</v>
+      </c>
+      <c r="BO47" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="48" spans="2:75">
+      <c r="B48" s="15" t="s">
+        <v>1451</v>
+      </c>
+      <c r="AA48" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AU48" s="15" t="s">
+        <v>1541</v>
+      </c>
+      <c r="BO48" s="15" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="49" spans="2:67">
+      <c r="B49" s="15" t="s">
+        <v>1452</v>
+      </c>
+      <c r="AA49" s="15" t="s">
+        <v>1501</v>
+      </c>
+      <c r="AU49" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BO49" s="15" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="50" spans="2:67">
+      <c r="B50" s="15" t="s">
+        <v>1453</v>
+      </c>
+      <c r="AA50" s="15" t="s">
+        <v>1502</v>
+      </c>
+      <c r="BO50" s="15" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="51" spans="2:67">
+      <c r="B51" s="15" t="s">
+        <v>1454</v>
+      </c>
+      <c r="AA51" s="15" t="s">
+        <v>1503</v>
+      </c>
+      <c r="BO51" s="15" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="52" spans="2:67">
+      <c r="B52" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AA52" s="15" t="s">
+        <v>1504</v>
+      </c>
+      <c r="BO52" s="15" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="53" spans="2:67">
+      <c r="B53" s="15" t="s">
+        <v>1455</v>
+      </c>
+      <c r="AA53" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="BO53" s="15" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="54" spans="2:67">
+      <c r="B54" s="15" t="s">
+        <v>1456</v>
+      </c>
+      <c r="AA54" s="15" t="s">
+        <v>1505</v>
+      </c>
+      <c r="BO54" s="15" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="55" spans="2:67">
+      <c r="B55" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AA55" s="15" t="s">
+        <v>1506</v>
+      </c>
+      <c r="BO55" s="15" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="56" spans="2:67">
+      <c r="B56" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AA56" s="15" t="s">
+        <v>1507</v>
+      </c>
+      <c r="BO56" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="57" spans="2:67">
+      <c r="B57" s="15" t="s">
+        <v>1457</v>
+      </c>
+      <c r="AA57" s="15" t="s">
+        <v>1508</v>
+      </c>
+      <c r="BO57" s="15" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="58" spans="2:67">
+      <c r="B58" s="15" t="s">
+        <v>1458</v>
+      </c>
+      <c r="AA58" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BO58" s="15" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="59" spans="2:67">
+      <c r="B59" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BO59" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="60" spans="2:67">
+      <c r="B60" s="69"/>
+      <c r="BO60" s="15" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="61" spans="2:67">
+      <c r="B61" s="15" t="s">
+        <v>1459</v>
+      </c>
+      <c r="BO61" s="15" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="62" spans="2:67">
+      <c r="B62" s="15" t="s">
+        <v>1460</v>
+      </c>
+      <c r="BO62" s="15" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="63" spans="2:67">
+      <c r="B63" s="15" t="s">
+        <v>1461</v>
+      </c>
+      <c r="BO63" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="64" spans="2:67">
+      <c r="B64" s="15" t="s">
+        <v>1462</v>
+      </c>
+      <c r="BO64" s="15" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="65" spans="2:74">
+      <c r="B65" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="BO65" s="15" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="66" spans="2:74">
+      <c r="B66" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="BO66" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="67" spans="2:74">
+      <c r="B67" s="15" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="68" spans="2:74" ht="15">
+      <c r="B68" s="15" t="s">
+        <v>1454</v>
+      </c>
+      <c r="BO68" s="98" t="s">
+        <v>1589</v>
+      </c>
+      <c r="BP68" s="99"/>
+      <c r="BQ68" s="99"/>
+      <c r="BR68" s="99"/>
+      <c r="BS68" s="99"/>
+      <c r="BT68" s="99"/>
+      <c r="BU68" s="99"/>
+      <c r="BV68" s="99"/>
+    </row>
+    <row r="69" spans="2:74">
+      <c r="B69" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="BO69" s="15" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="70" spans="2:74">
+      <c r="B70" s="15" t="s">
+        <v>1464</v>
+      </c>
+      <c r="BO70" s="15" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="71" spans="2:74">
+      <c r="B71" s="15" t="s">
+        <v>1456</v>
+      </c>
+      <c r="BO71" s="15" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="72" spans="2:74">
+      <c r="B72" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="BO72" s="15" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="73" spans="2:74">
+      <c r="B73" s="15" t="s">
+        <v>1465</v>
+      </c>
+      <c r="BO73" s="15" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="74" spans="2:74">
+      <c r="B74" s="15" t="s">
+        <v>1466</v>
+      </c>
+      <c r="BO74" s="15" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="75" spans="2:74">
+      <c r="B75" s="15" t="s">
+        <v>1467</v>
+      </c>
+      <c r="BO75" s="15" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="76" spans="2:74">
+      <c r="B76" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="BO76" s="15" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="77" spans="2:74">
+      <c r="B77" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="BO77" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="78" spans="2:74">
+      <c r="B78" s="15" t="s">
+        <v>1468</v>
+      </c>
+      <c r="BO78" s="15" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="79" spans="2:74">
+      <c r="B79" s="15" t="s">
+        <v>1458</v>
+      </c>
+      <c r="BO79" s="15" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="80" spans="2:74">
+      <c r="B80" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BO80" s="15" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="81" spans="1:67">
+      <c r="BO81" s="15" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="82" spans="1:67">
+      <c r="BO82" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="83" spans="1:67">
+      <c r="BO83" s="15" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="84" spans="1:67">
+      <c r="BO84" s="15" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="85" spans="1:67">
+      <c r="BO85" s="15" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="86" spans="1:67">
+      <c r="BO86" s="15" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="87" spans="1:67">
+      <c r="BO87" s="15" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="88" spans="1:67">
+      <c r="BO88" s="15" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="89" spans="1:67">
+      <c r="BO89" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="90" spans="1:67">
+      <c r="BO90" s="15" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="91" spans="1:67">
+      <c r="BO91" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="92" spans="1:67">
+      <c r="BO92" s="15" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="93" spans="1:67">
+      <c r="BO93" s="15" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="94" spans="1:67">
+      <c r="BO94" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="95" spans="1:67" ht="15" thickBot="1"/>
+    <row r="96" spans="1:67" s="16" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A96" s="92"/>
+      <c r="B96" s="93" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="97" spans="2:62" ht="15">
+      <c r="B97" s="43" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C97" s="44"/>
+      <c r="D97" s="44"/>
+      <c r="E97" s="44"/>
+      <c r="F97" s="44"/>
+      <c r="G97" s="44"/>
+      <c r="H97" s="44"/>
+      <c r="I97" s="44"/>
+      <c r="AB97" s="43" t="s">
+        <v>1645</v>
+      </c>
+      <c r="AC97" s="44"/>
+      <c r="AD97" s="44"/>
+      <c r="AE97" s="44"/>
+      <c r="AF97" s="44"/>
+      <c r="AG97" s="44"/>
+      <c r="AH97" s="44"/>
+      <c r="AI97" s="44"/>
+      <c r="AY97" s="43" t="s">
+        <v>1673</v>
+      </c>
+      <c r="AZ97" s="44"/>
+      <c r="BA97" s="44"/>
+      <c r="BB97" s="44"/>
+      <c r="BC97" s="44"/>
+      <c r="BD97" s="44"/>
+      <c r="BE97" s="44"/>
+    </row>
+    <row r="98" spans="2:62" ht="15">
+      <c r="B98" s="98" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C98" s="99"/>
+      <c r="D98" s="99"/>
+      <c r="E98" s="99"/>
+      <c r="F98" s="99"/>
+      <c r="G98" s="99"/>
+      <c r="AB98" s="98" t="s">
+        <v>1646</v>
+      </c>
+      <c r="AC98" s="99"/>
+      <c r="AD98" s="99"/>
+      <c r="AE98" s="99"/>
+      <c r="AF98" s="99"/>
+      <c r="AG98" s="99"/>
+      <c r="AH98" s="99"/>
+      <c r="AI98" s="99"/>
+      <c r="AJ98" s="99"/>
+      <c r="AK98" s="99"/>
+      <c r="AY98" s="98" t="s">
+        <v>1674</v>
+      </c>
+      <c r="AZ98" s="99"/>
+      <c r="BA98" s="99"/>
+      <c r="BB98" s="99"/>
+      <c r="BC98" s="99"/>
+      <c r="BD98" s="99"/>
+      <c r="BE98" s="99"/>
+    </row>
+    <row r="99" spans="2:62">
+      <c r="B99" s="15" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="100" spans="2:62">
+      <c r="B100" s="15" t="s">
+        <v>1614</v>
+      </c>
+      <c r="AB100" s="15" t="s">
+        <v>1647</v>
+      </c>
+      <c r="AY100" s="15" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="101" spans="2:62">
+      <c r="B101" s="15" t="s">
+        <v>1615</v>
+      </c>
+      <c r="AB101" s="15" t="s">
+        <v>1648</v>
+      </c>
+      <c r="AY101" s="15" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="102" spans="2:62">
+      <c r="B102" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AB102" s="15" t="s">
+        <v>1649</v>
+      </c>
+      <c r="AY102" s="15" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="103" spans="2:62">
+      <c r="B103" s="69"/>
+      <c r="AB103" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AY103" s="15" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="104" spans="2:62">
+      <c r="B104" s="15" t="s">
+        <v>1616</v>
+      </c>
+      <c r="AB104" s="15" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AY104" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="105" spans="2:62" ht="15">
+      <c r="B105" s="15" t="s">
+        <v>1617</v>
+      </c>
+      <c r="AB105" s="96" t="s">
+        <v>1651</v>
+      </c>
+      <c r="AY105" s="15" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="106" spans="2:62">
+      <c r="B106" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AB106" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AY106" s="15" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="107" spans="2:62">
+      <c r="B107" s="15" t="s">
+        <v>1618</v>
+      </c>
+      <c r="AB107" s="15" t="s">
+        <v>1652</v>
+      </c>
+      <c r="AY107" s="15" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="108" spans="2:62">
+      <c r="B108" s="88" t="s">
+        <v>1619</v>
+      </c>
+      <c r="AB108" s="15" t="s">
+        <v>1653</v>
+      </c>
+      <c r="AY108" s="15" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="109" spans="2:62">
+      <c r="B109" s="15" t="s">
+        <v>1620</v>
+      </c>
+      <c r="AB109" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AY109" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="110" spans="2:62">
+      <c r="B110" s="15" t="s">
+        <v>1621</v>
+      </c>
+      <c r="AB110" s="15" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="111" spans="2:62" ht="15">
+      <c r="B111" s="15" t="s">
+        <v>1622</v>
+      </c>
+      <c r="AB111" s="88" t="s">
+        <v>1655</v>
+      </c>
+      <c r="AC111" s="62"/>
+      <c r="AD111" s="62"/>
+      <c r="AY111" s="98" t="s">
+        <v>1683</v>
+      </c>
+      <c r="AZ111" s="99"/>
+      <c r="BA111" s="99"/>
+      <c r="BB111" s="99"/>
+      <c r="BC111" s="99"/>
+      <c r="BD111" s="99"/>
+      <c r="BE111" s="99"/>
+      <c r="BF111" s="99"/>
+      <c r="BG111" s="99"/>
+      <c r="BH111" s="99"/>
+      <c r="BI111" s="99"/>
+      <c r="BJ111" s="99"/>
+    </row>
+    <row r="112" spans="2:62">
+      <c r="B112" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AB112" s="88" t="s">
+        <v>1656</v>
+      </c>
+      <c r="AC112" s="62"/>
+      <c r="AD112" s="62"/>
+      <c r="AY112" s="15" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="113" spans="2:55">
+      <c r="B113" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AB113" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AY113" s="15" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="114" spans="2:55">
+      <c r="B114" s="15" t="s">
+        <v>1623</v>
+      </c>
+      <c r="AY114" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="115" spans="2:55" ht="15">
+      <c r="B115" s="88" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AB115" s="98" t="s">
+        <v>1657</v>
+      </c>
+      <c r="AC115" s="99"/>
+      <c r="AD115" s="99"/>
+      <c r="AE115" s="99"/>
+      <c r="AF115" s="99"/>
+      <c r="AG115" s="99"/>
+      <c r="AH115" s="99"/>
+      <c r="AI115" s="99"/>
+      <c r="AJ115" s="99"/>
+      <c r="AY115" s="88" t="s">
+        <v>1686</v>
+      </c>
+      <c r="AZ115" s="62"/>
+      <c r="BA115" s="62"/>
+      <c r="BB115" s="62"/>
+      <c r="BC115" s="62"/>
+    </row>
+    <row r="116" spans="2:55">
+      <c r="B116" s="15" t="s">
+        <v>1620</v>
+      </c>
+      <c r="AB116" s="15" t="s">
+        <v>1471</v>
+      </c>
+      <c r="AY116" s="88" t="s">
+        <v>1687</v>
+      </c>
+      <c r="AZ116" s="62"/>
+      <c r="BA116" s="62"/>
+      <c r="BB116" s="62"/>
+      <c r="BC116" s="62"/>
+    </row>
+    <row r="117" spans="2:55">
+      <c r="B117" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AB117" s="15" t="s">
+        <v>1472</v>
+      </c>
+      <c r="AY117" s="88" t="s">
+        <v>1688</v>
+      </c>
+      <c r="AZ117" s="62"/>
+      <c r="BA117" s="62"/>
+      <c r="BB117" s="62"/>
+      <c r="BC117" s="62"/>
+    </row>
+    <row r="118" spans="2:55">
+      <c r="B118" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AB118" s="69"/>
+      <c r="AY118" s="88" t="s">
+        <v>1689</v>
+      </c>
+      <c r="AZ118" s="62"/>
+      <c r="BA118" s="62"/>
+      <c r="BB118" s="62"/>
+      <c r="BC118" s="62"/>
+    </row>
+    <row r="119" spans="2:55">
+      <c r="AB119" s="88" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AY119" s="88" t="s">
+        <v>1690</v>
+      </c>
+      <c r="AZ119" s="62"/>
+      <c r="BA119" s="62"/>
+      <c r="BB119" s="62"/>
+      <c r="BC119" s="62"/>
+    </row>
+    <row r="120" spans="2:55" ht="15">
+      <c r="B120" s="98" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C120" s="99"/>
+      <c r="D120" s="99"/>
+      <c r="E120" s="99"/>
+      <c r="F120" s="99"/>
+      <c r="AB120" s="88" t="s">
+        <v>1659</v>
+      </c>
+      <c r="AY120" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="121" spans="2:55">
+      <c r="B121" s="15" t="s">
+        <v>1626</v>
+      </c>
+      <c r="AB121" s="88" t="s">
+        <v>901</v>
+      </c>
+      <c r="AY121" s="15" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="122" spans="2:55">
+      <c r="B122" s="15" t="s">
+        <v>1627</v>
+      </c>
+      <c r="AB122" s="69"/>
+      <c r="AY122" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="123" spans="2:55">
+      <c r="B123" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AB123" s="15" t="s">
+        <v>1660</v>
+      </c>
+      <c r="AY123" s="15" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="124" spans="2:55">
+      <c r="B124" s="15" t="s">
+        <v>1628</v>
+      </c>
+      <c r="AB124" s="15" t="s">
+        <v>1661</v>
+      </c>
+      <c r="AY124" s="15" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="125" spans="2:55">
+      <c r="B125" s="88" t="s">
+        <v>1629</v>
+      </c>
+      <c r="AB125" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AY125" s="15" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="126" spans="2:55">
+      <c r="B126" s="15" t="s">
+        <v>1630</v>
+      </c>
+      <c r="AB126" s="15" t="s">
+        <v>1662</v>
+      </c>
+      <c r="AY126" s="15" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="127" spans="2:55">
+      <c r="B127" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AB127" s="15" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AY127" s="15" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="128" spans="2:55">
+      <c r="B128" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AB128" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AY128" s="15" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="129" spans="2:58">
+      <c r="B129" s="15" t="s">
+        <v>1631</v>
+      </c>
+      <c r="AB129" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="AY129" s="15" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="130" spans="2:58">
+      <c r="B130" s="15" t="s">
+        <v>1628</v>
+      </c>
+      <c r="AB130" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AY130" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="131" spans="2:58">
+      <c r="B131" s="88" t="s">
+        <v>1632</v>
+      </c>
+      <c r="AB131" s="69"/>
+      <c r="AY131" s="15" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="132" spans="2:58">
+      <c r="B132" s="15" t="s">
+        <v>1630</v>
+      </c>
+      <c r="AB132" s="15" t="s">
+        <v>1665</v>
+      </c>
+      <c r="AY132" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="133" spans="2:58">
+      <c r="B133" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AB133" s="15" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="134" spans="2:58" ht="15">
+      <c r="B134" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AB134" s="15" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AY134" s="98" t="s">
+        <v>1700</v>
+      </c>
+      <c r="AZ134" s="99"/>
+      <c r="BA134" s="99"/>
+      <c r="BB134" s="99"/>
+      <c r="BC134" s="99"/>
+      <c r="BD134" s="99"/>
+      <c r="BE134" s="99"/>
+      <c r="BF134" s="99"/>
+    </row>
+    <row r="135" spans="2:58">
+      <c r="AB135" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AY135" s="15" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="136" spans="2:58" ht="15">
+      <c r="B136" s="98" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C136" s="99"/>
+      <c r="D136" s="99"/>
+      <c r="E136" s="99"/>
+      <c r="F136" s="99"/>
+      <c r="G136" s="99"/>
+      <c r="H136" s="99"/>
+      <c r="I136" s="99"/>
+      <c r="J136" s="99"/>
+      <c r="AB136" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="AY136" s="15" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="137" spans="2:58">
+      <c r="B137" s="15" t="s">
+        <v>1634</v>
+      </c>
+      <c r="AB137" s="15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="AY137" s="15" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="138" spans="2:58">
+      <c r="B138" s="15" t="s">
+        <v>1635</v>
+      </c>
+      <c r="AB138" s="15" t="s">
+        <v>1670</v>
+      </c>
+      <c r="AY138" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="139" spans="2:58">
+      <c r="B139" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AB139" s="15" t="s">
+        <v>1671</v>
+      </c>
+      <c r="AY139" s="15" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="140" spans="2:58">
+      <c r="B140" s="15" t="s">
+        <v>1636</v>
+      </c>
+      <c r="AB140" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="AY140" s="15" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="141" spans="2:58">
+      <c r="B141" s="15" t="s">
+        <v>1637</v>
+      </c>
+      <c r="AB141" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AY141" s="15" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="142" spans="2:58">
+      <c r="B142" s="15" t="s">
+        <v>1638</v>
+      </c>
+      <c r="AY142" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="143" spans="2:58">
+      <c r="B143" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AY143" s="15" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="144" spans="2:58">
+      <c r="B144" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AY144" s="15" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="145" spans="1:51">
+      <c r="B145" s="15" t="s">
+        <v>1639</v>
+      </c>
+      <c r="AY145" s="15" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="146" spans="1:51">
+      <c r="B146" s="15" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AY146" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="147" spans="1:51">
+      <c r="B147" s="15" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="148" spans="1:51">
+      <c r="B148" s="15" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="149" spans="1:51">
+      <c r="B149" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="150" spans="1:51">
+      <c r="B150" s="15" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="151" spans="1:51">
+      <c r="B151" s="15" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="152" spans="1:51">
+      <c r="B152" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="153" spans="1:51" ht="15" thickBot="1">
+      <c r="B153" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="154" spans="1:51" s="16" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A154" s="92"/>
+      <c r="B154" s="93" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="156" spans="1:51" ht="15">
+      <c r="B156" s="10" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="158" spans="1:51" ht="15">
+      <c r="B158" s="67" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="160" spans="1:51">
+      <c r="B160" s="15" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161" s="15" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2">
+      <c r="B163" s="15" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2">
+      <c r="B164" s="15" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2">
+      <c r="B165" s="15" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2">
+      <c r="B166" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2">
+      <c r="B167" s="15" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2">
+      <c r="B168" s="15" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2">
+      <c r="B169" s="15" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2">
+      <c r="B170" s="15" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2">
+      <c r="B171" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2">
+      <c r="B172" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2" ht="15">
+      <c r="B174" s="67" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2">
+      <c r="B176" s="15" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="15" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179" s="15" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="180" spans="2:2">
+      <c r="B180" s="15" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2">
+      <c r="B181" s="15" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2">
+      <c r="B182" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2">
+      <c r="B183" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="184" spans="2:2">
+      <c r="B184" s="15" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2">
+      <c r="B185" s="15" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2">
+      <c r="B186" s="15" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2">
+      <c r="B187" s="15" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2">
+      <c r="B188" s="15" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2">
+      <c r="B189" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2">
+      <c r="B190" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2">
+      <c r="B191" s="15" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2">
+      <c r="B192" s="15" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2">
+      <c r="B193" s="15" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" ht="15">
+      <c r="B197" s="10" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2" ht="15">
+      <c r="B199" s="67" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="201" spans="2:2">
+      <c r="B201" s="15" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2">
+      <c r="B202" s="15" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2">
+      <c r="B203" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2">
+      <c r="B204" s="15" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2">
+      <c r="B205" s="15" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2">
+      <c r="B206" s="15" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2">
+      <c r="B207" s="15" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2">
+      <c r="B208" s="15" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2">
+      <c r="B209" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2">
+      <c r="B210" s="15" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2">
+      <c r="B211" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2">
+      <c r="B212" s="15" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2">
+      <c r="B213" s="15" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="214" spans="2:2">
+      <c r="B214" s="15" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2">
+      <c r="B215" s="15" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="216" spans="2:2">
+      <c r="B216" s="15" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2">
+      <c r="B217" s="15" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="218" spans="2:2">
+      <c r="B218" s="15" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2">
+      <c r="B219" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="220" spans="2:2">
+      <c r="B220" s="15" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2">
+      <c r="B221" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2" ht="15">
+      <c r="B223" s="67" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="225" spans="2:2">
+      <c r="B225" s="15" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="226" spans="2:2">
+      <c r="B226" s="15" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2">
+      <c r="B227" s="69"/>
+    </row>
+    <row r="228" spans="2:2">
+      <c r="B228" s="15" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="229" spans="2:2">
+      <c r="B229" s="15" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="230" spans="2:2">
+      <c r="B230" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="231" spans="2:2">
+      <c r="B231" s="69"/>
+    </row>
+    <row r="232" spans="2:2">
+      <c r="B232" s="15" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="233" spans="2:2">
+      <c r="B233" s="15" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="234" spans="2:2">
+      <c r="B234" s="15" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="235" spans="2:2">
+      <c r="B235" s="15" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="236" spans="2:2">
+      <c r="B236" s="15" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="237" spans="2:2">
+      <c r="B237" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="238" spans="2:2">
+      <c r="B238" s="15" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="239" spans="2:2">
+      <c r="B239" s="15" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="240" spans="2:2">
+      <c r="B240" s="15" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="241" spans="2:2">
+      <c r="B241" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="243" spans="2:2" ht="15">
+      <c r="B243" s="10" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="245" spans="2:2" ht="15">
+      <c r="B245" s="67" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="247" spans="2:2">
+      <c r="B247" s="15" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="248" spans="2:2">
+      <c r="B248" s="15" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="249" spans="2:2">
+      <c r="B249" s="15" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="250" spans="2:2">
+      <c r="B250" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="251" spans="2:2">
+      <c r="B251" s="15" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="252" spans="2:2">
+      <c r="B252" s="15" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="253" spans="2:2">
+      <c r="B253" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="254" spans="2:2">
+      <c r="B254" s="15" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="255" spans="2:2">
+      <c r="B255" s="15" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="256" spans="2:2">
+      <c r="B256" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="258" spans="2:2" ht="15">
+      <c r="B258" s="67" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="260" spans="2:2">
+      <c r="B260" s="15" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="261" spans="2:2">
+      <c r="B261" s="15" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="262" spans="2:2">
+      <c r="B262" s="15" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="263" spans="2:2">
+      <c r="B263" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="264" spans="2:2">
+      <c r="B264" s="15" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="265" spans="2:2">
+      <c r="B265" s="15" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="266" spans="2:2">
+      <c r="B266" s="15" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="267" spans="2:2">
+      <c r="B267" s="15" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="268" spans="2:2">
+      <c r="B268" s="15" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="269" spans="2:2">
+      <c r="B269" s="15" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="270" spans="2:2">
+      <c r="B270" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="272" spans="2:2" ht="15">
+      <c r="B272" s="67" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="274" spans="2:2">
+      <c r="B274" s="15" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="275" spans="2:2">
+      <c r="B275" s="15" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="276" spans="2:2">
+      <c r="B276" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="277" spans="2:2">
+      <c r="B277" s="15" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="278" spans="2:2">
+      <c r="B278" s="15" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="279" spans="2:2">
+      <c r="B279" s="15" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="280" spans="2:2">
+      <c r="B280" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="281" spans="2:2">
+      <c r="B281" s="15" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="282" spans="2:2">
+      <c r="B282" s="15" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="283" spans="2:2">
+      <c r="B283" s="15" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="284" spans="2:2">
+      <c r="B284" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="285" spans="2:2">
+      <c r="B285" s="15" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="286" spans="2:2">
+      <c r="B286" s="15" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="287" spans="2:2">
+      <c r="B287" s="15" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="288" spans="2:2">
+      <c r="B288" s="15" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="289" spans="2:2">
+      <c r="B289" s="15" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="290" spans="2:2">
+      <c r="B290" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="292" spans="2:2" ht="15">
+      <c r="B292" s="10" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="294" spans="2:2" ht="15">
+      <c r="B294" s="67" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="296" spans="2:2">
+      <c r="B296" s="15" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="297" spans="2:2">
+      <c r="B297" s="15" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="298" spans="2:2">
+      <c r="B298" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="299" spans="2:2">
+      <c r="B299" s="15" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="300" spans="2:2">
+      <c r="B300" s="15" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="301" spans="2:2">
+      <c r="B301" s="15" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="302" spans="2:2">
+      <c r="B302" s="15" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="303" spans="2:2">
+      <c r="B303" s="15" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="304" spans="2:2">
+      <c r="B304" s="15" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="305" spans="2:2">
+      <c r="B305" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="306" spans="2:2">
+      <c r="B306" s="15" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="307" spans="2:2">
+      <c r="B307" s="15" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="308" spans="2:2">
+      <c r="B308" s="15" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="309" spans="2:2">
+      <c r="B309" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="310" spans="2:2">
+      <c r="B310" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="311" spans="2:2">
+      <c r="B311" s="15" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="312" spans="2:2">
+      <c r="B312" s="15" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="313" spans="2:2">
+      <c r="B313" s="15" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="314" spans="2:2">
+      <c r="B314" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="315" spans="2:2">
+      <c r="B315" s="15" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="316" spans="2:2">
+      <c r="B316" s="15" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="317" spans="2:2">
+      <c r="B317" s="15" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="318" spans="2:2">
+      <c r="B318" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="320" spans="2:2" ht="15">
+      <c r="B320" s="67" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="322" spans="2:2">
+      <c r="B322" s="15" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="323" spans="2:2">
+      <c r="B323" s="15" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="324" spans="2:2">
+      <c r="B324" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="325" spans="2:2">
+      <c r="B325" s="15" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="326" spans="2:2">
+      <c r="B326" s="15" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="327" spans="2:2">
+      <c r="B327" s="15" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="328" spans="2:2">
+      <c r="B328" s="15" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="329" spans="2:2">
+      <c r="B329" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="330" spans="2:2">
+      <c r="B330" s="15" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="331" spans="2:2">
+      <c r="B331" s="15" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="332" spans="2:2">
+      <c r="B332" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="333" spans="2:2">
+      <c r="B333" s="15" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="334" spans="2:2">
+      <c r="B334" s="15" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="335" spans="2:2">
+      <c r="B335" s="15" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="336" spans="2:2">
+      <c r="B336" s="15" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="337" spans="2:2">
+      <c r="B337" s="15" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="338" spans="2:2">
+      <c r="B338" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="339" spans="2:2">
+      <c r="B339" s="15" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="340" spans="2:2">
+      <c r="B340" s="15" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="341" spans="2:2">
+      <c r="B341" s="15" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="342" spans="2:2">
+      <c r="B342" s="15" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="343" spans="2:2">
+      <c r="B343" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="344" spans="2:2">
+      <c r="B344" s="15" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="345" spans="2:2">
+      <c r="B345" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="347" spans="2:2" ht="15">
+      <c r="B347" s="10" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="349" spans="2:2" ht="15">
+      <c r="B349" s="10" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="351" spans="2:2">
+      <c r="B351" s="15" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="352" spans="2:2">
+      <c r="B352" s="15" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="353" spans="2:2">
+      <c r="B353" s="15" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="354" spans="2:2">
+      <c r="B354" s="15" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="355" spans="2:2">
+      <c r="B355" s="15" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="356" spans="2:2">
+      <c r="B356" s="15" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="357" spans="2:2">
+      <c r="B357" s="15" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="358" spans="2:2">
+      <c r="B358" s="15" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="359" spans="2:2">
+      <c r="B359" s="15" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="360" spans="2:2">
+      <c r="B360" s="15" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="361" spans="2:2">
+      <c r="B361" s="15" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="362" spans="2:2">
+      <c r="B362" s="15" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="363" spans="2:2">
+      <c r="B363" s="15" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="364" spans="2:2">
+      <c r="B364" s="15" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="365" spans="2:2">
+      <c r="B365" s="15" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="366" spans="2:2">
+      <c r="B366" s="15" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="367" spans="2:2">
+      <c r="B367" s="15" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="368" spans="2:2">
+      <c r="B368" s="15" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="369" spans="2:2">
+      <c r="B369" s="15" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="370" spans="2:2">
+      <c r="B370" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="371" spans="2:2">
+      <c r="B371" s="15" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="372" spans="2:2">
+      <c r="B372" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="373" spans="2:2">
+      <c r="B373" s="15" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="374" spans="2:2">
+      <c r="B374" s="15" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="375" spans="2:2">
+      <c r="B375" s="15" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="376" spans="2:2">
+      <c r="B376" s="15" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="377" spans="2:2">
+      <c r="B377" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="379" spans="2:2" ht="15">
+      <c r="B379" s="10" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="381" spans="2:2" ht="15">
+      <c r="B381" s="67" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="383" spans="2:2">
+      <c r="B383" s="15" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="384" spans="2:2">
+      <c r="B384" s="15" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="385" spans="2:2">
+      <c r="B385" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="386" spans="2:2">
+      <c r="B386" s="15" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="387" spans="2:2">
+      <c r="B387" s="15" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="388" spans="2:2">
+      <c r="B388" s="15" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="389" spans="2:2">
+      <c r="B389" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="390" spans="2:2">
+      <c r="B390" s="15" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="391" spans="2:2">
+      <c r="B391" s="15" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="392" spans="2:2">
+      <c r="B392" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="394" spans="2:2" ht="15">
+      <c r="B394" s="67" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="396" spans="2:2">
+      <c r="B396" s="15" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="397" spans="2:2">
+      <c r="B397" s="15" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="398" spans="2:2">
+      <c r="B398" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="399" spans="2:2">
+      <c r="B399" s="15" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="400" spans="2:2">
+      <c r="B400" s="15" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="401" spans="2:2">
+      <c r="B401" s="15" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="402" spans="2:2">
+      <c r="B402" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="403" spans="2:2">
+      <c r="B403" s="15" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="404" spans="2:2">
+      <c r="B404" s="15" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="405" spans="2:2">
+      <c r="B405" s="15" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="406" spans="2:2">
+      <c r="B406" s="15" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="407" spans="2:2">
+      <c r="B407" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="408" spans="2:2">
+      <c r="B408" s="15" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="409" spans="2:2">
+      <c r="B409" s="15" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="410" spans="2:2">
+      <c r="B410" s="15" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="411" spans="2:2">
+      <c r="B411" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="413" spans="2:2" ht="15">
+      <c r="B413" s="10" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="415" spans="2:2" ht="15">
+      <c r="B415" s="67" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="417" spans="2:2">
+      <c r="B417" s="15" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="418" spans="2:2">
+      <c r="B418" s="15" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="419" spans="2:2">
+      <c r="B419" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="420" spans="2:2">
+      <c r="B420" s="15" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="421" spans="2:2">
+      <c r="B421" s="15" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="422" spans="2:2">
+      <c r="B422" s="15" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="423" spans="2:2">
+      <c r="B423" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="424" spans="2:2">
+      <c r="B424" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="425" spans="2:2">
+      <c r="B425" s="15" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="426" spans="2:2">
+      <c r="B426" s="15" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="427" spans="2:2">
+      <c r="B427" s="15" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="428" spans="2:2">
+      <c r="B428" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="429" spans="2:2">
+      <c r="B429" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="430" spans="2:2">
+      <c r="B430" s="15" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="431" spans="2:2">
+      <c r="B431" s="15" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="432" spans="2:2">
+      <c r="B432" s="15" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="433" spans="2:2">
+      <c r="B433" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="434" spans="2:2">
+      <c r="B434" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="436" spans="2:2" ht="15">
+      <c r="B436" s="67" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="438" spans="2:2">
+      <c r="B438" s="15" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="439" spans="2:2">
+      <c r="B439" s="15" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="440" spans="2:2">
+      <c r="B440" s="15" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="441" spans="2:2">
+      <c r="B441" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="442" spans="2:2">
+      <c r="B442" s="15" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="443" spans="2:2">
+      <c r="B443" s="15" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="444" spans="2:2">
+      <c r="B444" s="15" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="445" spans="2:2">
+      <c r="B445" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="446" spans="2:2">
+      <c r="B446" s="15" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="447" spans="2:2">
+      <c r="B447" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="448" spans="2:2">
+      <c r="B448" s="15" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="449" spans="2:2">
+      <c r="B449" s="15" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="450" spans="2:2">
+      <c r="B450" s="15" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="451" spans="2:2">
+      <c r="B451" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="452" spans="2:2">
+      <c r="B452" s="15" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="453" spans="2:2">
+      <c r="B453" s="15" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="454" spans="2:2">
+      <c r="B454" s="15" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="455" spans="2:2">
+      <c r="B455" s="15" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="456" spans="2:2">
+      <c r="B456" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="458" spans="2:2" ht="15">
+      <c r="B458" s="67" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="460" spans="2:2">
+      <c r="B460" s="15" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="461" spans="2:2">
+      <c r="B461" s="15" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="462" spans="2:2">
+      <c r="B462" s="15" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="463" spans="2:2">
+      <c r="B463" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="464" spans="2:2">
+      <c r="B464" s="15" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="465" spans="2:2">
+      <c r="B465" s="15" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="466" spans="2:2">
+      <c r="B466" s="15" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="467" spans="2:2">
+      <c r="B467" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="468" spans="2:2">
+      <c r="B468" s="15" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="469" spans="2:2">
+      <c r="B469" s="15" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="470" spans="2:2">
+      <c r="B470" s="15" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="471" spans="2:2">
+      <c r="B471" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="473" spans="2:2" ht="15">
+      <c r="B473" s="67" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="475" spans="2:2">
+      <c r="B475" s="15" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="476" spans="2:2">
+      <c r="B476" s="15" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="477" spans="2:2">
+      <c r="B477" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="478" spans="2:2">
+      <c r="B478" s="15" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="479" spans="2:2">
+      <c r="B479" s="15" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="480" spans="2:2">
+      <c r="B480" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="481" spans="2:2">
+      <c r="B481" s="15" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="482" spans="2:2">
+      <c r="B482" s="15" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="483" spans="2:2">
+      <c r="B483" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="484" spans="2:2">
+      <c r="B484" s="15" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="485" spans="2:2">
+      <c r="B485" s="15" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="486" spans="2:2">
+      <c r="B486" s="15" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="487" spans="2:2">
+      <c r="B487" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="489" spans="2:2" ht="15">
+      <c r="B489" s="67" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="491" spans="2:2">
+      <c r="B491" s="15" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="492" spans="2:2">
+      <c r="B492" s="15" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="493" spans="2:2">
+      <c r="B493" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="494" spans="2:2">
+      <c r="B494" s="15" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="495" spans="2:2">
+      <c r="B495" s="15" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="496" spans="2:2">
+      <c r="B496" s="15" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="497" spans="2:2">
+      <c r="B497" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="498" spans="2:2">
+      <c r="B498" s="15" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="499" spans="2:2">
+      <c r="B499" s="15" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="500" spans="2:2">
+      <c r="B500" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="502" spans="2:2" ht="15">
+      <c r="B502" s="10" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="504" spans="2:2" ht="15">
+      <c r="B504" s="67" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="506" spans="2:2">
+      <c r="B506" s="15" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="507" spans="2:2">
+      <c r="B507" s="15" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="508" spans="2:2">
+      <c r="B508" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="509" spans="2:2">
+      <c r="B509" s="15" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="510" spans="2:2">
+      <c r="B510" s="15" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="511" spans="2:2">
+      <c r="B511" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="512" spans="2:2">
+      <c r="B512" s="15" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="513" spans="2:2">
+      <c r="B513" s="15" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="514" spans="2:2">
+      <c r="B514" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="515" spans="2:2">
+      <c r="B515" s="15" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="516" spans="2:2">
+      <c r="B516" s="15" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="517" spans="2:2">
+      <c r="B517" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="518" spans="2:2">
+      <c r="B518" s="15" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="519" spans="2:2">
+      <c r="B519" s="15" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="520" spans="2:2">
+      <c r="B520" s="15" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="521" spans="2:2">
+      <c r="B521" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="522" spans="2:2">
+      <c r="B522" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="523" spans="2:2">
+      <c r="B523" s="15" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="524" spans="2:2">
+      <c r="B524" s="15" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="525" spans="2:2">
+      <c r="B525" s="15" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="526" spans="2:2">
+      <c r="B526" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="527" spans="2:2">
+      <c r="B527" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="529" spans="2:2" ht="15">
+      <c r="B529" s="67" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="531" spans="2:2">
+      <c r="B531" s="15" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="532" spans="2:2">
+      <c r="B532" s="15" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="533" spans="2:2">
+      <c r="B533" s="15" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="534" spans="2:2">
+      <c r="B534" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="535" spans="2:2">
+      <c r="B535" s="15" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="536" spans="2:2">
+      <c r="B536" s="15" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="537" spans="2:2">
+      <c r="B537" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="538" spans="2:2">
+      <c r="B538" s="15" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="539" spans="2:2">
+      <c r="B539" s="15" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="540" spans="2:2">
+      <c r="B540" s="15" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="541" spans="2:2">
+      <c r="B541" s="15" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="542" spans="2:2">
+      <c r="B542" s="15" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="543" spans="2:2">
+      <c r="B543" s="15" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="544" spans="2:2">
+      <c r="B544" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="546" spans="2:2" ht="15">
+      <c r="B546" s="10" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="548" spans="2:2" ht="15">
+      <c r="B548" s="10" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="550" spans="2:2" ht="15">
+      <c r="B550" s="67" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="552" spans="2:2">
+      <c r="B552" s="15" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="553" spans="2:2">
+      <c r="B553" s="15" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="554" spans="2:2">
+      <c r="B554" s="15" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="555" spans="2:2">
+      <c r="B555" s="15" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="556" spans="2:2">
+      <c r="B556" s="15" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="557" spans="2:2">
+      <c r="B557" s="15" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="558" spans="2:2">
+      <c r="B558" s="15" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="559" spans="2:2">
+      <c r="B559" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="560" spans="2:2">
+      <c r="B560" s="15" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="561" spans="2:2">
+      <c r="B561" s="15" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="562" spans="2:2">
+      <c r="B562" s="15" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="563" spans="2:2">
+      <c r="B563" s="15" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="564" spans="2:2">
+      <c r="B564" s="15" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="565" spans="2:2">
+      <c r="B565" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="566" spans="2:2">
+      <c r="B566" s="15" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="567" spans="2:2">
+      <c r="B567" s="15" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="568" spans="2:2">
+      <c r="B568" s="15" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="569" spans="2:2">
+      <c r="B569" s="15" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="570" spans="2:2">
+      <c r="B570" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="572" spans="2:2" ht="15">
+      <c r="B572" s="67" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="574" spans="2:2">
+      <c r="B574" s="15" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="575" spans="2:2">
+      <c r="B575" s="15" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="576" spans="2:2">
+      <c r="B576" s="15" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="577" spans="2:2">
+      <c r="B577" s="15" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="578" spans="2:2">
+      <c r="B578" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="579" spans="2:2">
+      <c r="B579" s="15" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="580" spans="2:2">
+      <c r="B580" s="15" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="581" spans="2:2">
+      <c r="B581" s="15" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="582" spans="2:2">
+      <c r="B582" s="15" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="583" spans="2:2">
+      <c r="B583" s="15" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="584" spans="2:2">
+      <c r="B584" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="585" spans="2:2">
+      <c r="B585" s="15" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="586" spans="2:2">
+      <c r="B586" s="15" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="587" spans="2:2">
+      <c r="B587" s="15" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="588" spans="2:2">
+      <c r="B588" s="15" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="589" spans="2:2">
+      <c r="B589" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="591" spans="2:2" ht="15">
+      <c r="B591" s="10" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="593" spans="2:2" ht="15">
+      <c r="B593" s="67" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="595" spans="2:2">
+      <c r="B595" s="15" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="596" spans="2:2">
+      <c r="B596" s="15" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="597" spans="2:2">
+      <c r="B597" s="15" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="598" spans="2:2">
+      <c r="B598" s="69"/>
+    </row>
+    <row r="599" spans="2:2">
+      <c r="B599" s="15" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="600" spans="2:2">
+      <c r="B600" s="15" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="601" spans="2:2">
+      <c r="B601" s="15" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="602" spans="2:2">
+      <c r="B602" s="15" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="603" spans="2:2">
+      <c r="B603" s="15" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="604" spans="2:2">
+      <c r="B604" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="605" spans="2:2">
+      <c r="B605" s="15" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="606" spans="2:2">
+      <c r="B606" s="15" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="607" spans="2:2">
+      <c r="B607" s="15" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="608" spans="2:2">
+      <c r="B608" s="15" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="609" spans="2:2">
+      <c r="B609" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="611" spans="2:2" ht="15">
+      <c r="B611" s="67" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="613" spans="2:2">
+      <c r="B613" s="15" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="614" spans="2:2">
+      <c r="B614" s="15" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="615" spans="2:2">
+      <c r="B615" s="15" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="616" spans="2:2">
+      <c r="B616" s="15" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="617" spans="2:2">
+      <c r="B617" s="15" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="618" spans="2:2">
+      <c r="B618" s="15" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="619" spans="2:2">
+      <c r="B619" s="15" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="620" spans="2:2">
+      <c r="B620" s="15" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="621" spans="2:2">
+      <c r="B621" s="69"/>
+    </row>
+    <row r="622" spans="2:2">
+      <c r="B622" s="15" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="623" spans="2:2">
+      <c r="B623" s="15" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="624" spans="2:2">
+      <c r="B624" s="15" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="625" spans="2:2">
+      <c r="B625" s="15" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="626" spans="2:2">
+      <c r="B626" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="627" spans="2:2">
+      <c r="B627" s="15" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="628" spans="2:2">
+      <c r="B628" s="15" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="629" spans="2:2">
+      <c r="B629" s="15" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="630" spans="2:2">
+      <c r="B630" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="632" spans="2:2" ht="15">
+      <c r="B632" s="10" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="634" spans="2:2" ht="15">
+      <c r="B634" s="67" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="636" spans="2:2">
+      <c r="B636" s="15" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="637" spans="2:2">
+      <c r="B637" s="15" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="638" spans="2:2">
+      <c r="B638" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="639" spans="2:2">
+      <c r="B639" s="15" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="640" spans="2:2">
+      <c r="B640" s="15" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="641" spans="2:2">
+      <c r="B641" s="15" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="642" spans="2:2">
+      <c r="B642" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="643" spans="2:2">
+      <c r="B643" s="15" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="644" spans="2:2">
+      <c r="B644" s="15" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="645" spans="2:2">
+      <c r="B645" s="15" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="646" spans="2:2">
+      <c r="B646" s="15" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="647" spans="2:2">
+      <c r="B647" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="648" spans="2:2">
+      <c r="B648" s="15" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="649" spans="2:2">
+      <c r="B649" s="15" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="650" spans="2:2">
+      <c r="B650" s="15" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="651" spans="2:2">
+      <c r="B651" s="15" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="652" spans="2:2">
+      <c r="B652" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="653" spans="2:2">
+      <c r="B653" s="15" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="654" spans="2:2">
+      <c r="B654" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="656" spans="2:2" ht="15">
+      <c r="B656" s="67" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="658" spans="2:2">
+      <c r="B658" s="15" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="659" spans="2:2">
+      <c r="B659" s="15" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="660" spans="2:2">
+      <c r="B660" s="15" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="661" spans="2:2">
+      <c r="B661" s="15" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="662" spans="2:2">
+      <c r="B662" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="663" spans="2:2">
+      <c r="B663" s="15" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="664" spans="2:2">
+      <c r="B664" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="665" spans="2:2">
+      <c r="B665" s="69"/>
+    </row>
+    <row r="666" spans="2:2">
+      <c r="B666" s="15" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="667" spans="2:2">
+      <c r="B667" s="15" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="668" spans="2:2">
+      <c r="B668" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="669" spans="2:2">
+      <c r="B669" s="15" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="670" spans="2:2">
+      <c r="B670" s="15" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="671" spans="2:2">
+      <c r="B671" s="15" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="672" spans="2:2">
+      <c r="B672" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="673" spans="2:2">
+      <c r="B673" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="674" spans="2:2">
+      <c r="B674" s="15" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="675" spans="2:2">
+      <c r="B675" s="15" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="676" spans="2:2">
+      <c r="B676" s="15" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="677" spans="2:2">
+      <c r="B677" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="678" spans="2:2">
+      <c r="B678" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="680" spans="2:2" ht="15">
+      <c r="B680" s="10" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="682" spans="2:2" ht="15">
+      <c r="B682" s="67" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="684" spans="2:2">
+      <c r="B684" s="15" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="685" spans="2:2">
+      <c r="B685" s="15" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="686" spans="2:2">
+      <c r="B686" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="687" spans="2:2">
+      <c r="B687" s="15" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="688" spans="2:2">
+      <c r="B688" s="15" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="689" spans="2:2">
+      <c r="B689" s="15" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="690" spans="2:2">
+      <c r="B690" s="15" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="691" spans="2:2">
+      <c r="B691" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="692" spans="2:2">
+      <c r="B692" s="15" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="693" spans="2:2">
+      <c r="B693" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="694" spans="2:2">
+      <c r="B694" s="15" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="695" spans="2:2">
+      <c r="B695" s="15" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="696" spans="2:2">
+      <c r="B696" s="15" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="697" spans="2:2">
+      <c r="B697" s="15" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="698" spans="2:2">
+      <c r="B698" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="699" spans="2:2">
+      <c r="B699" s="15" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="700" spans="2:2">
+      <c r="B700" s="15" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="701" spans="2:2">
+      <c r="B701" s="15" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="702" spans="2:2">
+      <c r="B702" s="15" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="703" spans="2:2">
+      <c r="B703" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="705" spans="2:2" ht="15">
+      <c r="B705" s="10" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="707" spans="2:2" ht="15">
+      <c r="B707" s="10" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="708" spans="2:2">
+      <c r="B708" s="13"/>
+    </row>
+    <row r="709" spans="2:2" ht="15">
+      <c r="B709" s="103" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="710" spans="2:2" ht="15">
+      <c r="B710" s="103" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="711" spans="2:2" ht="15">
+      <c r="B711" s="103" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="712" spans="2:2" ht="15">
+      <c r="B712" s="103" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="713" spans="2:2" ht="15">
+      <c r="B713" s="103" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="714" spans="2:2" ht="15">
+      <c r="B714" s="103" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="715" spans="2:2" ht="15">
+      <c r="B715" s="103" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="716" spans="2:2" ht="15">
+      <c r="B716" s="103" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="718" spans="2:2" ht="15">
+      <c r="B718" s="10" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="719" spans="2:2">
+      <c r="B719" s="13"/>
+    </row>
+    <row r="720" spans="2:2" ht="15">
+      <c r="B720" s="103" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="721" spans="2:2" ht="15">
+      <c r="B721" s="103" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="722" spans="2:2" ht="15">
+      <c r="B722" s="103" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="723" spans="2:2" ht="15">
+      <c r="B723" s="103" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="724" spans="2:2" ht="15">
+      <c r="B724" s="103" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="725" spans="2:2" ht="15">
+      <c r="B725" s="103" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="726" spans="2:2" ht="15">
+      <c r="B726" s="103" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="728" spans="2:2">
+      <c r="B728" s="11" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Kỹ Thuật lập trình/C/C.xlsx
+++ b/Kỹ Thuật lập trình/C/C.xlsx
@@ -1,24 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Linux\Kỹ Thuật lập trình\C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8632AB2B-7969-4080-8484-18EFB498E7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D515FE12-8DDF-4954-9F3B-744B83BED5E7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23160" windowHeight="8610" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="CheckList C" sheetId="2" r:id="rId1"/>
     <sheet name="1. Basic Syntax &amp; Data Types" sheetId="3" r:id="rId2"/>
     <sheet name="2. Variables &amp; Storage Classes_x0009_" sheetId="4" r:id="rId3"/>
     <sheet name="3. Operators &amp; Expressions" sheetId="5" r:id="rId4"/>
+    <sheet name="4. Control Flow" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet3" sheetId="8" r:id="rId7"/>
+    <sheet name="Sheet4" sheetId="9" r:id="rId8"/>
+    <sheet name="Sheet5" sheetId="10" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2448" uniqueCount="2082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2832" uniqueCount="2344">
   <si>
     <t>🔧 TOOLS &amp; ENVIRONMENT</t>
   </si>
@@ -13745,33 +13749,6 @@
     <t xml:space="preserve">           (n &amp;&amp; !(n &amp; (n - 1))) ? "Yes" : "No");</t>
   </si>
   <si>
-    <t xml:space="preserve">    // Count set bits (Brian Kernighan's algorithm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    unsigned int count = 0;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    unsigned int temp = n;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    while (temp) {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        temp &amp;= temp - 1;  // Clear lowest set bit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        count++;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    printf("Number of set bits in %u: %u\n", n, count);</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    // Isolate rightmost set bit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    printf("Rightmost set bit of %u: %u\n", n, n &amp; -n);</t>
-  </si>
-  <si>
     <t>2. Logical &amp; Relational Operators</t>
   </si>
   <si>
@@ -15131,143 +15108,909 @@
     <t xml:space="preserve">    printf("After a += b: a=%d, b=%d\n", a, b);</t>
   </si>
   <si>
-    <t>6. Tóm tắt Best Practices</t>
-  </si>
-  <si>
-    <t>6.1 Operator Usage Guidelines</t>
-  </si>
-  <si>
-    <t>6.2 Common Mistakes to Avoid</t>
-  </si>
-  <si>
-    <t>Hiểu rõ operators và expressions là fundamental để viết C code hiệu quả và bug-free. Những kiến thức này giúp tránh được nhiều pitfalls phổ biến và tối ưu hóa performance.</t>
-  </si>
-  <si>
-    <r>
-      <t>1. Always use parentheses</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> khi không chắc chắn về precedence</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2. Avoid complex expressions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - chia nhỏ thành multiple statements</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3. Be careful with side effects</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - tránh modify variable nhiều lần trong cùng expression</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>4. Use appropriate types</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - tránh unexpected type conversions</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>5. Test edge cases</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - overflow, underflow, division by zero</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>6. Use const</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> cho values không thay đổi</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>7. Initialize variables</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> trước khi sử dụng</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>8. Check return values</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> của functions</t>
+    <t>Control Flow trong C - Tổng hợp Lý thuyết và Thực hành</t>
+  </si>
+  <si>
+    <t>1. Conditional Statements (Câu lệnh điều kiện)</t>
+  </si>
+  <si>
+    <t>1.1 if-else statements</t>
+  </si>
+  <si>
+    <t>Cú pháp cơ bản:</t>
+  </si>
+  <si>
+    <t>if (condition) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // statements</t>
+  </si>
+  <si>
+    <t>} else if (condition2) {</t>
+  </si>
+  <si>
+    <t>} else {</t>
+  </si>
+  <si>
+    <t>Ví dụ và cạm bẫy:</t>
+  </si>
+  <si>
+    <t>// CẠM BẪY 1: Dangling else</t>
+  </si>
+  <si>
+    <t>if (x &gt; 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (y &gt; 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Both positive");</t>
+  </si>
+  <si>
+    <t>else  // else này thuộc về if(y &gt; 0), không phải if(x &gt; 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("x is not positive");</t>
+  </si>
+  <si>
+    <t>// ĐÚNG:</t>
+  </si>
+  <si>
+    <t>if (x &gt; 0) {</t>
+  </si>
+  <si>
+    <t>// CẠM BẪY 2: Assignment thay vì comparison</t>
+  </si>
+  <si>
+    <t>int x = 5;</t>
+  </si>
+  <si>
+    <t>if (x = 0) {  // Gán x = 0, không phải so sánh x == 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Never prints");</t>
+  </si>
+  <si>
+    <t>// x bây giờ = 0</t>
+  </si>
+  <si>
+    <t>// CẠM BẪY 3: Floating-point comparison</t>
+  </si>
+  <si>
+    <t>float f = 0.1f + 0.2f;</t>
+  </si>
+  <si>
+    <t>if (f == 0.3f) {  // Có thể false do lỗi làm tròn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("May not print");</t>
+  </si>
+  <si>
+    <t>if (fabs(f - 0.3f) &lt; 1e-6) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Approximately equal");</t>
+  </si>
+  <si>
+    <t>1.2 switch-case statements</t>
+  </si>
+  <si>
+    <t>Cú pháp và đặc điểm:</t>
+  </si>
+  <si>
+    <t>switch (expression) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case constant1:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        statements;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        break;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case constant2:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    default:</t>
+  </si>
+  <si>
+    <t>Fall-through behavior:</t>
+  </si>
+  <si>
+    <t>// Fall-through có chủ đích</t>
+  </si>
+  <si>
+    <t>switch (day) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case 1: case 2: case 3: case 4: case 5:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Weekday");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case 6: case 7:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Weekend");</t>
+  </si>
+  <si>
+    <t>// CẠM BẪY: Fall-through không chủ đích</t>
+  </si>
+  <si>
+    <t>switch (grade) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case 'A':</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Excellent");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // Thiếu break - sẽ thực hiện tiếp case 'B'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case 'B':</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Good");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case 'C':</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Average");</t>
+  </si>
+  <si>
+    <t>default case placement:</t>
+  </si>
+  <si>
+    <t>// default có thể đặt ở bất kỳ đâu</t>
+  </si>
+  <si>
+    <t>switch (value) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    default:  // Có thể đặt đầu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Default case");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case 1:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("One");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    case 2:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("Two");</t>
+  </si>
+  <si>
+    <t>// Nhưng thông thường đặt cuối để dễ đọc</t>
+  </si>
+  <si>
+    <t>2. Loops (Vòng lặp)</t>
+  </si>
+  <si>
+    <t>2.1 for loops và variations</t>
+  </si>
+  <si>
+    <t>for (initialization; condition; increment) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // body</t>
+  </si>
+  <si>
+    <t>Variations nâng cao:</t>
+  </si>
+  <si>
+    <t>// Multiple variables</t>
+  </si>
+  <si>
+    <t>for (int i = 0, j = 10; i &lt; j; i++, j--) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("%d %d\n", i, j);</t>
+  </si>
+  <si>
+    <t>// Empty sections</t>
+  </si>
+  <si>
+    <t>int i = 0;</t>
+  </si>
+  <si>
+    <t>for (; i &lt; 10; ) {  // Chỉ có condition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("%d\n", i++);</t>
+  </si>
+  <si>
+    <t>// Infinite loop</t>
+  </si>
+  <si>
+    <t>for (;;) {  // Tất cả sections trống</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Infinite loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (condition) break;</t>
+  </si>
+  <si>
+    <t>// Complex increment</t>
+  </si>
+  <si>
+    <t>for (int i = 1; i &lt; 1000; i *= 2) {  // Exponential growth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("%d\n", i);</t>
+  </si>
+  <si>
+    <t>Cạm bẫy với for loops:</t>
+  </si>
+  <si>
+    <t>// CẠM BẪY 1: Variable scope</t>
+  </si>
+  <si>
+    <t>for (int i = 0; i &lt; 10; i++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // i chỉ có scope trong loop</t>
+  </si>
+  <si>
+    <t>// printf("%d", i);  // Error - i không tồn tại</t>
+  </si>
+  <si>
+    <t>// CẠM BẪY 2: Signed/Unsigned comparison</t>
+  </si>
+  <si>
+    <t>for (unsigned int i = 10; i &gt;= 0; i--) {  // Infinite loop!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("%u\n", i);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // i không bao giờ &lt; 0 vì unsigned</t>
+  </si>
+  <si>
+    <t>// CẠM BẪY 3: Modifying loop variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (i == 5) i = 8;  // Có thể gây nhầm lẫn</t>
+  </si>
+  <si>
+    <t>2.2 while và do-while loops</t>
+  </si>
+  <si>
+    <t>while loop:</t>
+  </si>
+  <si>
+    <t>while (condition) {</t>
+  </si>
+  <si>
+    <t>// Ví dụ thực tế</t>
+  </si>
+  <si>
+    <t>char c;</t>
+  </si>
+  <si>
+    <t>while ((c = getchar()) != EOF) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    putchar(c);</t>
+  </si>
+  <si>
+    <t>do-while loop:</t>
+  </si>
+  <si>
+    <t>do {</t>
+  </si>
+  <si>
+    <t>} while (condition);</t>
+  </si>
+  <si>
+    <t>// Ví dụ: Menu loop</t>
+  </si>
+  <si>
+    <t>int choice;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("1. Option A\n2. Option B\n0. Exit\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    scanf("%d", &amp;choice);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Process choice</t>
+  </si>
+  <si>
+    <t>} while (choice != 0);</t>
+  </si>
+  <si>
+    <t>So sánh while vs do-while:</t>
+  </si>
+  <si>
+    <t>// while - có thể không thực hiện lần nào</t>
+  </si>
+  <si>
+    <t>int x = 10;</t>
+  </si>
+  <si>
+    <t>while (x &lt; 5) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Never executes\n");</t>
+  </si>
+  <si>
+    <t>// do-while - luôn thực hiện ít nhất 1 lần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Executes once\n");</t>
+  </si>
+  <si>
+    <t>} while (x &lt; 5);</t>
+  </si>
+  <si>
+    <t>2.3 break và continue statements</t>
+  </si>
+  <si>
+    <t>break statement:</t>
+  </si>
+  <si>
+    <t>// Thoát khỏi loop gần nhất</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (i == 5) break;  // Thoát khi i = 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("%d\n", i);  // In 0,1,2,3,4</t>
+  </si>
+  <si>
+    <t>// Với nested loops</t>
+  </si>
+  <si>
+    <t>for (int i = 0; i &lt; 3; i++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    for (int j = 0; j &lt; 3; j++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (j == 1) break;  // Chỉ thoát inner loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("(%d,%d) ", i, j);</t>
+  </si>
+  <si>
+    <t>// Output: (0,0) (1,0) (2,0)</t>
+  </si>
+  <si>
+    <t>continue statement:</t>
+  </si>
+  <si>
+    <t>// Bỏ qua iteration hiện tại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (i % 2 == 0) continue;  // Bỏ qua số chẵn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("%d ", i);  // In 1 3 5 7 9</t>
+  </si>
+  <si>
+    <t>// Với while loop</t>
+  </si>
+  <si>
+    <t>while (i &lt; 10) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    i++;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (i % 3 == 0) continue;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("%d ", i);</t>
+  </si>
+  <si>
+    <t>2.4 Nested loops và performance</t>
+  </si>
+  <si>
+    <t>Hiệu năng nested loops:</t>
+  </si>
+  <si>
+    <t>// O(n²) complexity</t>
+  </si>
+  <si>
+    <t>for (int i = 0; i &lt; n; i++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    for (int j = 0; j &lt; n; j++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // n² operations</t>
+  </si>
+  <si>
+    <t>// Optimization: Giảm số iterations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    for (int j = i + 1; j &lt; n; j++) {  // j bắt đầu từ i+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // Chỉ n(n-1)/2 operations</t>
+  </si>
+  <si>
+    <t>Loop unrolling:</t>
+  </si>
+  <si>
+    <t>// Thay vì:</t>
+  </si>
+  <si>
+    <t>for (int i = 0; i &lt; 100; i++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    array[i] = 0;</t>
+  </si>
+  <si>
+    <t>// Có thể unroll:</t>
+  </si>
+  <si>
+    <t>for (int i = 0; i &lt; 100; i += 4) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    array[i+1] = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    array[i+2] = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    array[i+3] = 0;</t>
+  </si>
+  <si>
+    <t>3. Unconditional Jumps (Nhảy vô điều kiện)</t>
+  </si>
+  <si>
+    <t>3.1 goto statement - when appropriate</t>
+  </si>
+  <si>
+    <t>Cú pháp:</t>
+  </si>
+  <si>
+    <t>label:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    statements;</t>
+  </si>
+  <si>
+    <t>goto label;</t>
+  </si>
+  <si>
+    <t>Sử dụng hợp lý của goto:</t>
+  </si>
+  <si>
+    <t>// 1. Error handling trong C (trước khi có exceptions)</t>
+  </si>
+  <si>
+    <t>int process_data(void) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    char *buffer = malloc(1024);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    FILE *file = fopen("data.txt", "r");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (!buffer) goto cleanup_none;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (!file) goto cleanup_buffer;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Process data...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (error_occurred) goto cleanup_all;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Success path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    fclose(file);</t>
+  </si>
+  <si>
+    <t>cleanup_all:</t>
+  </si>
+  <si>
+    <t>cleanup_buffer:</t>
+  </si>
+  <si>
+    <t>cleanup_none:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return -1;</t>
+  </si>
+  <si>
+    <t>// 2. Breaking out of deeply nested loops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    for (int j = 0; j &lt; 100; j++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        for (int k = 0; k &lt; 100; k++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            if (found_target) goto found;</t>
+  </si>
+  <si>
+    <t>// Continue normal execution</t>
+  </si>
+  <si>
+    <t>goto not_found;</t>
+  </si>
+  <si>
+    <t>found:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Found at (%d,%d,%d)\n", i, j, k);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return;</t>
+  </si>
+  <si>
+    <t>not_found:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Not found\n");</t>
+  </si>
+  <si>
+    <t>Cạm bẫy với goto:</t>
+  </si>
+  <si>
+    <t>// CẠM BẪY 1: Bỏ qua variable initialization</t>
+  </si>
+  <si>
+    <t>goto skip_init;</t>
+  </si>
+  <si>
+    <t>int x = 10;  // Bị bỏ qua</t>
+  </si>
+  <si>
+    <t>skip_init:</t>
+  </si>
+  <si>
+    <t>printf("%d\n", x);  // Undefined behavior</t>
+  </si>
+  <si>
+    <t>// CẠM BẪY 2: Goto into scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    goto inside_block;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int local_var = 5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    inside_block:  // Error: jumping into scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("%d", local_var);</t>
+  </si>
+  <si>
+    <t>3.2 return statement</t>
+  </si>
+  <si>
+    <t>Multiple return points:</t>
+  </si>
+  <si>
+    <t>// Early return pattern</t>
+  </si>
+  <si>
+    <t>int validate_input(int value) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (value &lt; 0) return -1;        // Early return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (value &gt; 100) return -1;      // Early return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (value % 2 != 0) return -1;   // Early return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return 0;  // Success</t>
+  </si>
+  <si>
+    <t>// vs Single return point</t>
+  </si>
+  <si>
+    <t>int validate_input_single(int value) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int result = -1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (value &gt;= 0 &amp;&amp; value &lt;= 100 &amp;&amp; value % 2 == 0) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        result = 0;</t>
+  </si>
+  <si>
+    <t>return trong main():</t>
+  </si>
+  <si>
+    <t>// return codes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (initialization_failed()) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return EXIT_FAILURE;  // hoặc return 1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Normal execution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return EXIT_SUCCESS;  // hoặc return 0;</t>
+  </si>
+  <si>
+    <t>3.3 Exit functions</t>
+  </si>
+  <si>
+    <t>exit() function:</t>
+  </si>
+  <si>
+    <t>#include &lt;stdlib.h&gt;</t>
+  </si>
+  <si>
+    <t>void cleanup_handler(void) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Cleaning up...\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Cleanup code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Register cleanup function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    atexit(cleanup_handler);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (critical_error()) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        exit(EXIT_FAILURE);  // Calls atexit functions, flushes buffers</t>
+  </si>
+  <si>
+    <t>_Exit() và quick_exit():</t>
+  </si>
+  <si>
+    <t>// _Exit() - immediate termination</t>
+  </si>
+  <si>
+    <t>void emergency_shutdown(void) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    _Exit(2);  // No cleanup, no atexit functions</t>
+  </si>
+  <si>
+    <t>// quick_exit() - limited cleanup</t>
+  </si>
+  <si>
+    <t>void quick_cleanup(void) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Quick cleanup\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    at_quick_exit(quick_cleanup);  // For quick_exit only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    atexit(normal_cleanup);        // For normal exit only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (quick_shutdown_needed) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        quick_exit(1);  // Only calls at_quick_exit functions</t>
+  </si>
+  <si>
+    <t>4. Advanced Topics và Best Practices</t>
+  </si>
+  <si>
+    <t>4.1 Performance Considerations</t>
+  </si>
+  <si>
+    <t>Branch prediction:</t>
+  </si>
+  <si>
+    <t>// Predictable branches are faster</t>
+  </si>
+  <si>
+    <t>if (likely_true_condition) {  // CPU predicts this branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Hot path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Cold path</t>
+  </si>
+  <si>
+    <t>// Random conditions are slower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (random_condition()) {  // Unpredictable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // This hurts performance</t>
+  </si>
+  <si>
+    <t>Loop optimization:</t>
+  </si>
+  <si>
+    <t>// Hoist invariant computations</t>
+  </si>
+  <si>
+    <t>// BAD:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        result[i][j] = sqrt(constant_value) * data[i][j];</t>
+  </si>
+  <si>
+    <t>// GOOD:</t>
+  </si>
+  <si>
+    <t>double sqrt_constant = sqrt(constant_value);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        result[i][j] = sqrt_constant * data[i][j];</t>
+  </si>
+  <si>
+    <t>4.2 Common Pitfalls Summary</t>
+  </si>
+  <si>
+    <t>4.3 Best Practices</t>
+  </si>
+  <si>
+    <t>4.4 Modern C Features (C99+)</t>
+  </si>
+  <si>
+    <t>// C99: Variable length arrays in loops</t>
+  </si>
+  <si>
+    <t>void process_matrix(int n) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int matrix[n][n];  // VLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    for (int i = 0; i &lt; n; i++) {  // i declared in loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        for (int j = 0; j &lt; n; j++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            matrix[i][j] = i + j;</t>
+  </si>
+  <si>
+    <t>// C99: Mixed declarations và statements</t>
+  </si>
+  <si>
+    <t>void mixed_example(void) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    printf("Starting...\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    for (int i = 0; i &lt; 10; i++) {  // Declaration in for loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        int square = i * i;         // Declaration anywhere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("%d^2 = %d\n", i, square);</t>
+  </si>
+  <si>
+    <t>Đây là tổng hợp đầy đủ về Control Flow trong C, từ cơ bản đến nâng cao, bao gồm các cạm bẫy thường gặp và best practices để viết code hiệu quả và an toàn.</t>
+  </si>
+  <si>
+    <r>
+      <t>Short-circuit evaluation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Trong biểu thức logic phức tạp, C sẽ dừng đánh giá khi kết quả đã xác định</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Dangling else problem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: else luôn gắn với if gần nhất</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Zero/Non-zero evaluation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Mọi giá trị khác 0 được coi là true</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Jump table optimization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Compiler có thể tối ưu switch thành bảng nhảy</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Constant expression requirement</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: case labels phải là hằng số tại compile time</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Integer promotion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: expression được promote thành int</t>
     </r>
   </si>
   <si>
@@ -15283,7 +16026,7 @@
         <charset val="163"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> (</t>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
@@ -15291,7 +16034,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>=</t>
+      <t>if (x = 0)</t>
     </r>
     <r>
       <rPr>
@@ -15310,34 +16053,23 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>==</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2. Bitwise vs Logical</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
+      <t>if (x == 0)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Unsigned underflow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
@@ -15345,18 +16077,23 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>&amp;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vs </t>
+      <t>for (unsigned i = 10; i &gt;= 0; i--)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Fall-through in switch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Thiếu </t>
     </r>
     <r>
       <rPr>
@@ -15364,7 +16101,151 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>&amp;&amp;</t>
+      <t>break</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. Dangling else</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Không dùng braces </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>{}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5. Variable scope</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Loop variables không tồn tại ngoài loop</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6. Infinite loops</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Logic điều kiện sai</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>7. goto pitfalls</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Jump qua initialization, vào scope</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. Luôn dùng braces</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cho readability</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. const correctness</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Dùng const cho variables không thay đổi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Avoid deep nesting</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Sử dụng early return</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. Meaningful variable names</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>i</t>
     </r>
     <r>
       <rPr>
@@ -15383,18 +16264,18 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> vs </t>
+      <t>j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -15402,105 +16283,73 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>||</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3. Precedence assumptions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - luôn dùng parentheses</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>4. Integer overflow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - check bounds trước arithmetic</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>5. Floating-point equality</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - sử dụng epsilon comparison</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>6. Undefined behavior</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - tránh modify variables nhiều lần</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>7. Side effects trong macros</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - cẩn thận với arguments được evaluate nhiều lần</t>
+      <t>k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> chỉ cho simple loops</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5. Comment complex logic</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Đặc biệt với goto và complex conditions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6. Use static analysis tools</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Để catch common mistakes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>7. Profile before optimizing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Measure performance impacts</t>
     </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="27">
     <font>
       <sz val="11"/>
@@ -15882,7 +16731,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -16123,6 +16972,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -16132,9 +16984,15 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16610,7 +17468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4948059D-9E31-4AC4-80F2-5CDB6F28266D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:W1239"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <sheetData>
@@ -21597,7 +22455,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B9A591E-590E-4D73-9F12-919C572F7BCA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:CJ195"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <cols>
@@ -22020,29 +22878,29 @@
       <c r="BB13" s="23"/>
       <c r="BC13" s="24"/>
       <c r="BE13" s="21"/>
-      <c r="BF13" s="100" t="s">
+      <c r="BF13" s="101" t="s">
         <v>806</v>
       </c>
-      <c r="BG13" s="100"/>
-      <c r="BH13" s="100"/>
-      <c r="BI13" s="100"/>
-      <c r="BJ13" s="100" t="s">
+      <c r="BG13" s="101"/>
+      <c r="BH13" s="101"/>
+      <c r="BI13" s="101"/>
+      <c r="BJ13" s="101" t="s">
         <v>807</v>
       </c>
-      <c r="BK13" s="100"/>
-      <c r="BL13" s="100"/>
-      <c r="BM13" s="100"/>
-      <c r="BN13" s="100"/>
-      <c r="BO13" s="100"/>
-      <c r="BP13" s="100" t="s">
+      <c r="BK13" s="101"/>
+      <c r="BL13" s="101"/>
+      <c r="BM13" s="101"/>
+      <c r="BN13" s="101"/>
+      <c r="BO13" s="101"/>
+      <c r="BP13" s="101" t="s">
         <v>808</v>
       </c>
-      <c r="BQ13" s="100"/>
-      <c r="BR13" s="100"/>
-      <c r="BS13" s="100"/>
-      <c r="BT13" s="100"/>
-      <c r="BU13" s="100"/>
-      <c r="BV13" s="100"/>
+      <c r="BQ13" s="101"/>
+      <c r="BR13" s="101"/>
+      <c r="BS13" s="101"/>
+      <c r="BT13" s="101"/>
+      <c r="BU13" s="101"/>
+      <c r="BV13" s="101"/>
       <c r="BW13" s="24"/>
     </row>
     <row r="14" spans="2:75" ht="15.75" thickBot="1">
@@ -22067,29 +22925,29 @@
       <c r="BB14" s="30"/>
       <c r="BC14" s="31"/>
       <c r="BE14" s="21"/>
-      <c r="BF14" s="102" t="s">
+      <c r="BF14" s="103" t="s">
         <v>809</v>
       </c>
-      <c r="BG14" s="102"/>
-      <c r="BH14" s="102"/>
-      <c r="BI14" s="102"/>
-      <c r="BJ14" s="101" t="s">
+      <c r="BG14" s="103"/>
+      <c r="BH14" s="103"/>
+      <c r="BI14" s="103"/>
+      <c r="BJ14" s="102" t="s">
         <v>810</v>
       </c>
-      <c r="BK14" s="101"/>
-      <c r="BL14" s="101"/>
-      <c r="BM14" s="101"/>
-      <c r="BN14" s="101"/>
-      <c r="BO14" s="101"/>
-      <c r="BP14" s="101" t="s">
+      <c r="BK14" s="102"/>
+      <c r="BL14" s="102"/>
+      <c r="BM14" s="102"/>
+      <c r="BN14" s="102"/>
+      <c r="BO14" s="102"/>
+      <c r="BP14" s="102" t="s">
         <v>810</v>
       </c>
-      <c r="BQ14" s="101"/>
-      <c r="BR14" s="101"/>
-      <c r="BS14" s="101"/>
-      <c r="BT14" s="101"/>
-      <c r="BU14" s="101"/>
-      <c r="BV14" s="101"/>
+      <c r="BQ14" s="102"/>
+      <c r="BR14" s="102"/>
+      <c r="BS14" s="102"/>
+      <c r="BT14" s="102"/>
+      <c r="BU14" s="102"/>
+      <c r="BV14" s="102"/>
       <c r="BW14" s="24"/>
     </row>
     <row r="15" spans="2:75" ht="15.75" thickBot="1">
@@ -22098,29 +22956,29 @@
       </c>
       <c r="AL15" s="13"/>
       <c r="BE15" s="21"/>
-      <c r="BF15" s="102" t="s">
+      <c r="BF15" s="103" t="s">
         <v>811</v>
       </c>
-      <c r="BG15" s="102"/>
-      <c r="BH15" s="102"/>
-      <c r="BI15" s="102"/>
-      <c r="BJ15" s="101" t="s">
+      <c r="BG15" s="103"/>
+      <c r="BH15" s="103"/>
+      <c r="BI15" s="103"/>
+      <c r="BJ15" s="102" t="s">
         <v>812</v>
       </c>
-      <c r="BK15" s="101"/>
-      <c r="BL15" s="101"/>
-      <c r="BM15" s="101"/>
-      <c r="BN15" s="101"/>
-      <c r="BO15" s="101"/>
-      <c r="BP15" s="101" t="s">
+      <c r="BK15" s="102"/>
+      <c r="BL15" s="102"/>
+      <c r="BM15" s="102"/>
+      <c r="BN15" s="102"/>
+      <c r="BO15" s="102"/>
+      <c r="BP15" s="102" t="s">
         <v>813</v>
       </c>
-      <c r="BQ15" s="101"/>
-      <c r="BR15" s="101"/>
-      <c r="BS15" s="101"/>
-      <c r="BT15" s="101"/>
-      <c r="BU15" s="101"/>
-      <c r="BV15" s="101"/>
+      <c r="BQ15" s="102"/>
+      <c r="BR15" s="102"/>
+      <c r="BS15" s="102"/>
+      <c r="BT15" s="102"/>
+      <c r="BU15" s="102"/>
+      <c r="BV15" s="102"/>
       <c r="BW15" s="24"/>
     </row>
     <row r="16" spans="2:75" ht="15">
@@ -22148,29 +23006,29 @@
       <c r="BB16" s="19"/>
       <c r="BC16" s="20"/>
       <c r="BE16" s="21"/>
-      <c r="BF16" s="102" t="s">
+      <c r="BF16" s="103" t="s">
         <v>814</v>
       </c>
-      <c r="BG16" s="102"/>
-      <c r="BH16" s="102"/>
-      <c r="BI16" s="102"/>
-      <c r="BJ16" s="101" t="s">
+      <c r="BG16" s="103"/>
+      <c r="BH16" s="103"/>
+      <c r="BI16" s="103"/>
+      <c r="BJ16" s="102" t="s">
         <v>815</v>
       </c>
-      <c r="BK16" s="101"/>
-      <c r="BL16" s="101"/>
-      <c r="BM16" s="101"/>
-      <c r="BN16" s="101"/>
-      <c r="BO16" s="101"/>
-      <c r="BP16" s="101" t="s">
+      <c r="BK16" s="102"/>
+      <c r="BL16" s="102"/>
+      <c r="BM16" s="102"/>
+      <c r="BN16" s="102"/>
+      <c r="BO16" s="102"/>
+      <c r="BP16" s="102" t="s">
         <v>815</v>
       </c>
-      <c r="BQ16" s="101"/>
-      <c r="BR16" s="101"/>
-      <c r="BS16" s="101"/>
-      <c r="BT16" s="101"/>
-      <c r="BU16" s="101"/>
-      <c r="BV16" s="101"/>
+      <c r="BQ16" s="102"/>
+      <c r="BR16" s="102"/>
+      <c r="BS16" s="102"/>
+      <c r="BT16" s="102"/>
+      <c r="BU16" s="102"/>
+      <c r="BV16" s="102"/>
       <c r="BW16" s="24"/>
     </row>
     <row r="17" spans="2:88" ht="15">
@@ -22681,33 +23539,33 @@
         <v>962</v>
       </c>
       <c r="AL28" s="21"/>
-      <c r="AM28" s="100" t="s">
+      <c r="AM28" s="101" t="s">
         <v>806</v>
       </c>
-      <c r="AN28" s="100"/>
-      <c r="AO28" s="100"/>
-      <c r="AP28" s="100" t="s">
+      <c r="AN28" s="101"/>
+      <c r="AO28" s="101"/>
+      <c r="AP28" s="101" t="s">
         <v>822</v>
       </c>
-      <c r="AQ28" s="100"/>
-      <c r="AR28" s="100"/>
-      <c r="AS28" s="100"/>
-      <c r="AT28" s="100"/>
-      <c r="AU28" s="100"/>
-      <c r="AV28" s="100"/>
-      <c r="AW28" s="100"/>
-      <c r="AX28" s="100" t="s">
+      <c r="AQ28" s="101"/>
+      <c r="AR28" s="101"/>
+      <c r="AS28" s="101"/>
+      <c r="AT28" s="101"/>
+      <c r="AU28" s="101"/>
+      <c r="AV28" s="101"/>
+      <c r="AW28" s="101"/>
+      <c r="AX28" s="101" t="s">
         <v>823</v>
       </c>
-      <c r="AY28" s="100"/>
-      <c r="AZ28" s="100"/>
-      <c r="BA28" s="100"/>
-      <c r="BB28" s="100" t="s">
+      <c r="AY28" s="101"/>
+      <c r="AZ28" s="101"/>
+      <c r="BA28" s="101"/>
+      <c r="BB28" s="101" t="s">
         <v>824</v>
       </c>
-      <c r="BC28" s="100"/>
-      <c r="BD28" s="100"/>
-      <c r="BE28" s="100"/>
+      <c r="BC28" s="101"/>
+      <c r="BD28" s="101"/>
+      <c r="BE28" s="101"/>
       <c r="BF28" s="24"/>
       <c r="BH28" s="29" t="s">
         <v>841</v>
@@ -22743,33 +23601,33 @@
     </row>
     <row r="29" spans="2:88" ht="15" thickBot="1">
       <c r="AL29" s="21"/>
-      <c r="AM29" s="102" t="s">
+      <c r="AM29" s="103" t="s">
         <v>825</v>
       </c>
-      <c r="AN29" s="102"/>
-      <c r="AO29" s="102"/>
-      <c r="AP29" s="101" t="s">
+      <c r="AN29" s="103"/>
+      <c r="AO29" s="103"/>
+      <c r="AP29" s="102" t="s">
         <v>963</v>
       </c>
-      <c r="AQ29" s="101"/>
-      <c r="AR29" s="101"/>
-      <c r="AS29" s="101"/>
-      <c r="AT29" s="101"/>
-      <c r="AU29" s="101"/>
-      <c r="AV29" s="101"/>
-      <c r="AW29" s="101"/>
-      <c r="AX29" s="101" t="s">
+      <c r="AQ29" s="102"/>
+      <c r="AR29" s="102"/>
+      <c r="AS29" s="102"/>
+      <c r="AT29" s="102"/>
+      <c r="AU29" s="102"/>
+      <c r="AV29" s="102"/>
+      <c r="AW29" s="102"/>
+      <c r="AX29" s="102" t="s">
         <v>826</v>
       </c>
-      <c r="AY29" s="101"/>
-      <c r="AZ29" s="101"/>
-      <c r="BA29" s="101"/>
-      <c r="BB29" s="102" t="s">
+      <c r="AY29" s="102"/>
+      <c r="AZ29" s="102"/>
+      <c r="BA29" s="102"/>
+      <c r="BB29" s="103" t="s">
         <v>827</v>
       </c>
-      <c r="BC29" s="102"/>
-      <c r="BD29" s="102"/>
-      <c r="BE29" s="102"/>
+      <c r="BC29" s="103"/>
+      <c r="BD29" s="103"/>
+      <c r="BE29" s="103"/>
       <c r="BF29" s="24"/>
     </row>
     <row r="30" spans="2:88" ht="15">
@@ -22777,33 +23635,33 @@
         <v>774</v>
       </c>
       <c r="AL30" s="21"/>
-      <c r="AM30" s="102" t="s">
+      <c r="AM30" s="103" t="s">
         <v>828</v>
       </c>
-      <c r="AN30" s="102"/>
-      <c r="AO30" s="102"/>
-      <c r="AP30" s="101" t="s">
+      <c r="AN30" s="103"/>
+      <c r="AO30" s="103"/>
+      <c r="AP30" s="102" t="s">
         <v>829</v>
       </c>
-      <c r="AQ30" s="101"/>
-      <c r="AR30" s="101"/>
-      <c r="AS30" s="101"/>
-      <c r="AT30" s="101"/>
-      <c r="AU30" s="101"/>
-      <c r="AV30" s="101"/>
-      <c r="AW30" s="101"/>
-      <c r="AX30" s="101" t="s">
+      <c r="AQ30" s="102"/>
+      <c r="AR30" s="102"/>
+      <c r="AS30" s="102"/>
+      <c r="AT30" s="102"/>
+      <c r="AU30" s="102"/>
+      <c r="AV30" s="102"/>
+      <c r="AW30" s="102"/>
+      <c r="AX30" s="102" t="s">
         <v>830</v>
       </c>
-      <c r="AY30" s="101"/>
-      <c r="AZ30" s="101"/>
-      <c r="BA30" s="101"/>
-      <c r="BB30" s="102" t="s">
+      <c r="AY30" s="102"/>
+      <c r="AZ30" s="102"/>
+      <c r="BA30" s="102"/>
+      <c r="BB30" s="103" t="s">
         <v>831</v>
       </c>
-      <c r="BC30" s="102"/>
-      <c r="BD30" s="102"/>
-      <c r="BE30" s="102"/>
+      <c r="BC30" s="103"/>
+      <c r="BD30" s="103"/>
+      <c r="BE30" s="103"/>
       <c r="BF30" s="24"/>
       <c r="BH30" s="18" t="s">
         <v>842</v>
@@ -22835,33 +23693,33 @@
         <v>775</v>
       </c>
       <c r="AL31" s="21"/>
-      <c r="AM31" s="102" t="s">
+      <c r="AM31" s="103" t="s">
         <v>831</v>
       </c>
-      <c r="AN31" s="102"/>
-      <c r="AO31" s="102"/>
-      <c r="AP31" s="101" t="s">
+      <c r="AN31" s="103"/>
+      <c r="AO31" s="103"/>
+      <c r="AP31" s="102" t="s">
         <v>832</v>
       </c>
-      <c r="AQ31" s="101"/>
-      <c r="AR31" s="101"/>
-      <c r="AS31" s="101"/>
-      <c r="AT31" s="101"/>
-      <c r="AU31" s="101"/>
-      <c r="AV31" s="101"/>
-      <c r="AW31" s="101"/>
-      <c r="AX31" s="101" t="s">
+      <c r="AQ31" s="102"/>
+      <c r="AR31" s="102"/>
+      <c r="AS31" s="102"/>
+      <c r="AT31" s="102"/>
+      <c r="AU31" s="102"/>
+      <c r="AV31" s="102"/>
+      <c r="AW31" s="102"/>
+      <c r="AX31" s="102" t="s">
         <v>830</v>
       </c>
-      <c r="AY31" s="101"/>
-      <c r="AZ31" s="101"/>
-      <c r="BA31" s="101"/>
-      <c r="BB31" s="102" t="s">
+      <c r="AY31" s="102"/>
+      <c r="AZ31" s="102"/>
+      <c r="BA31" s="102"/>
+      <c r="BB31" s="103" t="s">
         <v>833</v>
       </c>
-      <c r="BC31" s="102"/>
-      <c r="BD31" s="102"/>
-      <c r="BE31" s="102"/>
+      <c r="BC31" s="103"/>
+      <c r="BD31" s="103"/>
+      <c r="BE31" s="103"/>
       <c r="BF31" s="24"/>
       <c r="BH31" s="27" t="s">
         <v>843</v>
@@ -28185,22 +29043,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="AX28:BA28"/>
-    <mergeCell ref="AX29:BA29"/>
-    <mergeCell ref="AX30:BA30"/>
-    <mergeCell ref="AX31:BA31"/>
-    <mergeCell ref="BB28:BE28"/>
-    <mergeCell ref="BB29:BE29"/>
-    <mergeCell ref="BB30:BE30"/>
-    <mergeCell ref="BB31:BE31"/>
-    <mergeCell ref="AM28:AO28"/>
-    <mergeCell ref="AM29:AO29"/>
-    <mergeCell ref="AM30:AO30"/>
-    <mergeCell ref="AM31:AO31"/>
-    <mergeCell ref="AP28:AW28"/>
-    <mergeCell ref="AP29:AW29"/>
-    <mergeCell ref="AP30:AW30"/>
-    <mergeCell ref="AP31:AW31"/>
     <mergeCell ref="BP13:BV13"/>
     <mergeCell ref="BP14:BV14"/>
     <mergeCell ref="BP15:BV15"/>
@@ -28213,6 +29055,22 @@
     <mergeCell ref="BJ14:BO14"/>
     <mergeCell ref="BJ15:BO15"/>
     <mergeCell ref="BJ16:BO16"/>
+    <mergeCell ref="AM28:AO28"/>
+    <mergeCell ref="AM29:AO29"/>
+    <mergeCell ref="AM30:AO30"/>
+    <mergeCell ref="AM31:AO31"/>
+    <mergeCell ref="AP28:AW28"/>
+    <mergeCell ref="AP29:AW29"/>
+    <mergeCell ref="AP30:AW30"/>
+    <mergeCell ref="AP31:AW31"/>
+    <mergeCell ref="AX28:BA28"/>
+    <mergeCell ref="AX29:BA29"/>
+    <mergeCell ref="AX30:BA30"/>
+    <mergeCell ref="AX31:BA31"/>
+    <mergeCell ref="BB28:BE28"/>
+    <mergeCell ref="BB29:BE29"/>
+    <mergeCell ref="BB30:BE30"/>
+    <mergeCell ref="BB31:BE31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -28220,7 +29078,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD678391-01EC-4BBB-A4FC-EBED70F213C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BU211"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <cols>
@@ -30687,8 +31545,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E705242-2605-4ED2-A504-13435F2B53FF}">
-  <dimension ref="A1:CB728"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:CF422"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="16384" width="3" style="11"/>
@@ -31760,130 +32618,205 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="82" spans="1:67">
-      <c r="BO82" s="15" t="s">
+    <row r="82" spans="1:67" ht="15" thickBot="1"/>
+    <row r="83" spans="1:67" s="16" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A83" s="92"/>
+      <c r="B83" s="93" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="84" spans="1:67" ht="15">
+      <c r="B84" s="43" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C84" s="44"/>
+      <c r="D84" s="44"/>
+      <c r="E84" s="44"/>
+      <c r="F84" s="44"/>
+      <c r="G84" s="44"/>
+      <c r="H84" s="44"/>
+      <c r="I84" s="44"/>
+      <c r="AB84" s="43" t="s">
+        <v>1636</v>
+      </c>
+      <c r="AC84" s="44"/>
+      <c r="AD84" s="44"/>
+      <c r="AE84" s="44"/>
+      <c r="AF84" s="44"/>
+      <c r="AG84" s="44"/>
+      <c r="AH84" s="44"/>
+      <c r="AI84" s="44"/>
+      <c r="AY84" s="43" t="s">
+        <v>1664</v>
+      </c>
+      <c r="AZ84" s="44"/>
+      <c r="BA84" s="44"/>
+      <c r="BB84" s="44"/>
+      <c r="BC84" s="44"/>
+      <c r="BD84" s="44"/>
+      <c r="BE84" s="44"/>
+    </row>
+    <row r="85" spans="1:67" ht="15">
+      <c r="B85" s="98" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C85" s="99"/>
+      <c r="D85" s="99"/>
+      <c r="E85" s="99"/>
+      <c r="F85" s="99"/>
+      <c r="G85" s="99"/>
+      <c r="AB85" s="98" t="s">
+        <v>1637</v>
+      </c>
+      <c r="AC85" s="99"/>
+      <c r="AD85" s="99"/>
+      <c r="AE85" s="99"/>
+      <c r="AF85" s="99"/>
+      <c r="AG85" s="99"/>
+      <c r="AH85" s="99"/>
+      <c r="AI85" s="99"/>
+      <c r="AJ85" s="99"/>
+      <c r="AK85" s="99"/>
+      <c r="AY85" s="98" t="s">
+        <v>1665</v>
+      </c>
+      <c r="AZ85" s="99"/>
+      <c r="BA85" s="99"/>
+      <c r="BB85" s="99"/>
+      <c r="BC85" s="99"/>
+      <c r="BD85" s="99"/>
+      <c r="BE85" s="99"/>
+    </row>
+    <row r="86" spans="1:67">
+      <c r="B86" s="15" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="87" spans="1:67">
+      <c r="B87" s="15" t="s">
+        <v>1605</v>
+      </c>
+      <c r="AB87" s="15" t="s">
+        <v>1638</v>
+      </c>
+      <c r="AY87" s="15" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="88" spans="1:67">
+      <c r="B88" s="15" t="s">
+        <v>1606</v>
+      </c>
+      <c r="AB88" s="15" t="s">
+        <v>1639</v>
+      </c>
+      <c r="AY88" s="15" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="89" spans="1:67">
+      <c r="B89" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AB89" s="15" t="s">
+        <v>1640</v>
+      </c>
+      <c r="AY89" s="15" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="90" spans="1:67">
+      <c r="B90" s="69"/>
+      <c r="AB90" s="15" t="s">
         <v>1083</v>
       </c>
-    </row>
-    <row r="83" spans="1:67">
-      <c r="BO83" s="15" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="84" spans="1:67">
-      <c r="BO84" s="15" t="s">
-        <v>1602</v>
-      </c>
-    </row>
-    <row r="85" spans="1:67">
-      <c r="BO85" s="15" t="s">
-        <v>1603</v>
-      </c>
-    </row>
-    <row r="86" spans="1:67">
-      <c r="BO86" s="15" t="s">
-        <v>1604</v>
-      </c>
-    </row>
-    <row r="87" spans="1:67">
-      <c r="BO87" s="15" t="s">
-        <v>1605</v>
-      </c>
-    </row>
-    <row r="88" spans="1:67">
-      <c r="BO88" s="15" t="s">
-        <v>1606</v>
-      </c>
-    </row>
-    <row r="89" spans="1:67">
-      <c r="BO89" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="90" spans="1:67">
-      <c r="BO90" s="15" t="s">
+      <c r="AY90" s="15" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="91" spans="1:67">
+      <c r="B91" s="15" t="s">
         <v>1607</v>
       </c>
-    </row>
-    <row r="91" spans="1:67">
-      <c r="BO91" s="15" t="s">
+      <c r="AB91" s="15" t="s">
+        <v>1641</v>
+      </c>
+      <c r="AY91" s="15" t="s">
         <v>1083</v>
       </c>
     </row>
-    <row r="92" spans="1:67">
-      <c r="BO92" s="15" t="s">
+    <row r="92" spans="1:67" ht="15">
+      <c r="B92" s="15" t="s">
         <v>1608</v>
       </c>
+      <c r="AB92" s="96" t="s">
+        <v>1642</v>
+      </c>
+      <c r="AY92" s="15" t="s">
+        <v>1670</v>
+      </c>
     </row>
     <row r="93" spans="1:67">
-      <c r="BO93" s="15" t="s">
+      <c r="B93" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AB93" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AY93" s="15" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="94" spans="1:67">
+      <c r="B94" s="15" t="s">
         <v>1609</v>
       </c>
-    </row>
-    <row r="94" spans="1:67">
-      <c r="BO94" s="15" t="s">
+      <c r="AB94" s="15" t="s">
+        <v>1643</v>
+      </c>
+      <c r="AY94" s="15" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="95" spans="1:67">
+      <c r="B95" s="88" t="s">
+        <v>1610</v>
+      </c>
+      <c r="AB95" s="15" t="s">
+        <v>1644</v>
+      </c>
+      <c r="AY95" s="15" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="96" spans="1:67">
+      <c r="B96" s="15" t="s">
+        <v>1611</v>
+      </c>
+      <c r="AB96" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AY96" s="15" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="95" spans="1:67" ht="15" thickBot="1"/>
-    <row r="96" spans="1:67" s="16" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A96" s="92"/>
-      <c r="B96" s="93" t="s">
-        <v>1610</v>
-      </c>
-    </row>
-    <row r="97" spans="2:62" ht="15">
-      <c r="B97" s="43" t="s">
-        <v>1611</v>
-      </c>
-      <c r="C97" s="44"/>
-      <c r="D97" s="44"/>
-      <c r="E97" s="44"/>
-      <c r="F97" s="44"/>
-      <c r="G97" s="44"/>
-      <c r="H97" s="44"/>
-      <c r="I97" s="44"/>
-      <c r="AB97" s="43" t="s">
+    <row r="97" spans="2:62">
+      <c r="B97" s="15" t="s">
+        <v>1612</v>
+      </c>
+      <c r="AB97" s="15" t="s">
         <v>1645</v>
       </c>
-      <c r="AC97" s="44"/>
-      <c r="AD97" s="44"/>
-      <c r="AE97" s="44"/>
-      <c r="AF97" s="44"/>
-      <c r="AG97" s="44"/>
-      <c r="AH97" s="44"/>
-      <c r="AI97" s="44"/>
-      <c r="AY97" s="43" t="s">
-        <v>1673</v>
-      </c>
-      <c r="AZ97" s="44"/>
-      <c r="BA97" s="44"/>
-      <c r="BB97" s="44"/>
-      <c r="BC97" s="44"/>
-      <c r="BD97" s="44"/>
-      <c r="BE97" s="44"/>
     </row>
     <row r="98" spans="2:62" ht="15">
-      <c r="B98" s="98" t="s">
-        <v>1612</v>
-      </c>
-      <c r="C98" s="99"/>
-      <c r="D98" s="99"/>
-      <c r="E98" s="99"/>
-      <c r="F98" s="99"/>
-      <c r="G98" s="99"/>
-      <c r="AB98" s="98" t="s">
+      <c r="B98" s="15" t="s">
+        <v>1613</v>
+      </c>
+      <c r="AB98" s="88" t="s">
         <v>1646</v>
       </c>
-      <c r="AC98" s="99"/>
-      <c r="AD98" s="99"/>
-      <c r="AE98" s="99"/>
-      <c r="AF98" s="99"/>
-      <c r="AG98" s="99"/>
-      <c r="AH98" s="99"/>
-      <c r="AI98" s="99"/>
-      <c r="AJ98" s="99"/>
-      <c r="AK98" s="99"/>
+      <c r="AC98" s="62"/>
+      <c r="AD98" s="62"/>
       <c r="AY98" s="98" t="s">
         <v>1674</v>
       </c>
@@ -31893,968 +32826,3559 @@
       <c r="BC98" s="99"/>
       <c r="BD98" s="99"/>
       <c r="BE98" s="99"/>
+      <c r="BF98" s="99"/>
+      <c r="BG98" s="99"/>
+      <c r="BH98" s="99"/>
+      <c r="BI98" s="99"/>
+      <c r="BJ98" s="99"/>
     </row>
     <row r="99" spans="2:62">
       <c r="B99" s="15" t="s">
-        <v>1613</v>
+        <v>1086</v>
+      </c>
+      <c r="AB99" s="88" t="s">
+        <v>1647</v>
+      </c>
+      <c r="AC99" s="62"/>
+      <c r="AD99" s="62"/>
+      <c r="AY99" s="15" t="s">
+        <v>1675</v>
       </c>
     </row>
     <row r="100" spans="2:62">
       <c r="B100" s="15" t="s">
-        <v>1614</v>
+        <v>1083</v>
       </c>
       <c r="AB100" s="15" t="s">
-        <v>1647</v>
+        <v>901</v>
       </c>
       <c r="AY100" s="15" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="101" spans="2:62">
       <c r="B101" s="15" t="s">
+        <v>1614</v>
+      </c>
+      <c r="AY101" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="102" spans="2:62" ht="15">
+      <c r="B102" s="88" t="s">
         <v>1615</v>
       </c>
-      <c r="AB101" s="15" t="s">
+      <c r="AB102" s="98" t="s">
         <v>1648</v>
       </c>
-      <c r="AY101" s="15" t="s">
-        <v>1676</v>
-      </c>
-    </row>
-    <row r="102" spans="2:62">
+      <c r="AC102" s="99"/>
+      <c r="AD102" s="99"/>
+      <c r="AE102" s="99"/>
+      <c r="AF102" s="99"/>
+      <c r="AG102" s="99"/>
+      <c r="AH102" s="99"/>
+      <c r="AI102" s="99"/>
+      <c r="AJ102" s="99"/>
+      <c r="AY102" s="88" t="s">
+        <v>1677</v>
+      </c>
+      <c r="AZ102" s="62"/>
+      <c r="BA102" s="62"/>
+      <c r="BB102" s="62"/>
+      <c r="BC102" s="62"/>
+    </row>
+    <row r="103" spans="2:62">
+      <c r="B103" s="15" t="s">
+        <v>1611</v>
+      </c>
+      <c r="AB103" s="15" t="s">
+        <v>1471</v>
+      </c>
+      <c r="AY103" s="88" t="s">
+        <v>1678</v>
+      </c>
+      <c r="AZ103" s="62"/>
+      <c r="BA103" s="62"/>
+      <c r="BB103" s="62"/>
+      <c r="BC103" s="62"/>
+    </row>
+    <row r="104" spans="2:62">
+      <c r="B104" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AB104" s="15" t="s">
+        <v>1472</v>
+      </c>
+      <c r="AY104" s="88" t="s">
+        <v>1679</v>
+      </c>
+      <c r="AZ104" s="62"/>
+      <c r="BA104" s="62"/>
+      <c r="BB104" s="62"/>
+      <c r="BC104" s="62"/>
+    </row>
+    <row r="105" spans="2:62">
+      <c r="B105" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AB105" s="69"/>
+      <c r="AY105" s="88" t="s">
+        <v>1680</v>
+      </c>
+      <c r="AZ105" s="62"/>
+      <c r="BA105" s="62"/>
+      <c r="BB105" s="62"/>
+      <c r="BC105" s="62"/>
+    </row>
+    <row r="106" spans="2:62">
+      <c r="AB106" s="88" t="s">
+        <v>1649</v>
+      </c>
+      <c r="AY106" s="88" t="s">
+        <v>1681</v>
+      </c>
+      <c r="AZ106" s="62"/>
+      <c r="BA106" s="62"/>
+      <c r="BB106" s="62"/>
+      <c r="BC106" s="62"/>
+    </row>
+    <row r="107" spans="2:62" ht="15">
+      <c r="B107" s="98" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C107" s="99"/>
+      <c r="D107" s="99"/>
+      <c r="E107" s="99"/>
+      <c r="F107" s="99"/>
+      <c r="AB107" s="88" t="s">
+        <v>1650</v>
+      </c>
+      <c r="AY107" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="108" spans="2:62">
+      <c r="B108" s="15" t="s">
+        <v>1617</v>
+      </c>
+      <c r="AB108" s="88" t="s">
+        <v>901</v>
+      </c>
+      <c r="AY108" s="15" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="109" spans="2:62">
+      <c r="B109" s="15" t="s">
+        <v>1618</v>
+      </c>
+      <c r="AB109" s="69"/>
+      <c r="AY109" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="110" spans="2:62">
+      <c r="B110" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AB110" s="15" t="s">
+        <v>1651</v>
+      </c>
+      <c r="AY110" s="15" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="111" spans="2:62">
+      <c r="B111" s="15" t="s">
+        <v>1619</v>
+      </c>
+      <c r="AB111" s="15" t="s">
+        <v>1652</v>
+      </c>
+      <c r="AY111" s="15" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="112" spans="2:62">
+      <c r="B112" s="88" t="s">
+        <v>1620</v>
+      </c>
+      <c r="AB112" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AY112" s="15" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="113" spans="2:58">
+      <c r="B113" s="15" t="s">
+        <v>1621</v>
+      </c>
+      <c r="AB113" s="15" t="s">
+        <v>1653</v>
+      </c>
+      <c r="AY113" s="15" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="114" spans="2:58">
+      <c r="B114" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AB114" s="15" t="s">
+        <v>1654</v>
+      </c>
+      <c r="AY114" s="15" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="115" spans="2:58">
+      <c r="B115" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AB115" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AY115" s="15" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="116" spans="2:58">
+      <c r="B116" s="15" t="s">
+        <v>1622</v>
+      </c>
+      <c r="AB116" s="15" t="s">
+        <v>1655</v>
+      </c>
+      <c r="AY116" s="15" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="117" spans="2:58">
+      <c r="B117" s="15" t="s">
+        <v>1619</v>
+      </c>
+      <c r="AB117" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AY117" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="118" spans="2:58">
+      <c r="B118" s="88" t="s">
+        <v>1623</v>
+      </c>
+      <c r="AB118" s="69"/>
+      <c r="AY118" s="15" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="119" spans="2:58">
+      <c r="B119" s="15" t="s">
+        <v>1621</v>
+      </c>
+      <c r="AB119" s="15" t="s">
+        <v>1656</v>
+      </c>
+      <c r="AY119" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="120" spans="2:58">
+      <c r="B120" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AB120" s="15" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="121" spans="2:58" ht="15">
+      <c r="B121" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AB121" s="15" t="s">
+        <v>1658</v>
+      </c>
+      <c r="AY121" s="98" t="s">
+        <v>1691</v>
+      </c>
+      <c r="AZ121" s="99"/>
+      <c r="BA121" s="99"/>
+      <c r="BB121" s="99"/>
+      <c r="BC121" s="99"/>
+      <c r="BD121" s="99"/>
+      <c r="BE121" s="99"/>
+      <c r="BF121" s="99"/>
+    </row>
+    <row r="122" spans="2:58">
+      <c r="AB122" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AY122" s="15" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="123" spans="2:58" ht="15">
+      <c r="B123" s="98" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C123" s="99"/>
+      <c r="D123" s="99"/>
+      <c r="E123" s="99"/>
+      <c r="F123" s="99"/>
+      <c r="G123" s="99"/>
+      <c r="H123" s="99"/>
+      <c r="I123" s="99"/>
+      <c r="J123" s="99"/>
+      <c r="AB123" s="15" t="s">
+        <v>1659</v>
+      </c>
+      <c r="AY123" s="15" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="124" spans="2:58">
+      <c r="B124" s="15" t="s">
+        <v>1625</v>
+      </c>
+      <c r="AB124" s="15" t="s">
+        <v>1660</v>
+      </c>
+      <c r="AY124" s="15" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="125" spans="2:58">
+      <c r="B125" s="15" t="s">
+        <v>1626</v>
+      </c>
+      <c r="AB125" s="15" t="s">
+        <v>1661</v>
+      </c>
+      <c r="AY125" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="126" spans="2:58">
+      <c r="B126" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AB126" s="15" t="s">
+        <v>1662</v>
+      </c>
+      <c r="AY126" s="15" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="127" spans="2:58">
+      <c r="B127" s="15" t="s">
+        <v>1627</v>
+      </c>
+      <c r="AB127" s="15" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AY127" s="15" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="128" spans="2:58">
+      <c r="B128" s="15" t="s">
+        <v>1628</v>
+      </c>
+      <c r="AB128" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AY128" s="15" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="129" spans="1:51">
+      <c r="B129" s="15" t="s">
+        <v>1629</v>
+      </c>
+      <c r="AY129" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="130" spans="1:51">
+      <c r="B130" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AY130" s="15" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="131" spans="1:51">
+      <c r="B131" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AY131" s="15" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="132" spans="1:51">
+      <c r="B132" s="15" t="s">
+        <v>1630</v>
+      </c>
+      <c r="AY132" s="15" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="133" spans="1:51">
+      <c r="B133" s="15" t="s">
+        <v>1631</v>
+      </c>
+      <c r="AY133" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="134" spans="1:51">
+      <c r="B134" s="15" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="135" spans="1:51">
+      <c r="B135" s="15" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="136" spans="1:51">
+      <c r="B136" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="137" spans="1:51">
+      <c r="B137" s="15" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="138" spans="1:51">
+      <c r="B138" s="15" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="139" spans="1:51">
+      <c r="B139" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="140" spans="1:51" ht="15" thickBot="1">
+      <c r="B140" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="141" spans="1:51" s="16" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A141" s="92"/>
+      <c r="B141" s="93" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="142" spans="1:51" ht="15">
+      <c r="B142" s="43" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C142" s="44"/>
+      <c r="D142" s="44"/>
+      <c r="E142" s="44"/>
+      <c r="F142" s="44"/>
+      <c r="G142" s="44"/>
+      <c r="H142" s="44"/>
+      <c r="I142" s="44"/>
+      <c r="V142" s="43" t="s">
+        <v>1726</v>
+      </c>
+      <c r="W142" s="44"/>
+      <c r="X142" s="44"/>
+      <c r="Y142" s="44"/>
+      <c r="Z142" s="44"/>
+      <c r="AA142" s="44"/>
+      <c r="AB142" s="44"/>
+      <c r="AC142" s="44"/>
+      <c r="AD142" s="44"/>
+      <c r="AE142" s="44"/>
+      <c r="AF142" s="44"/>
+      <c r="AM142" s="43" t="s">
+        <v>1757</v>
+      </c>
+      <c r="AN142" s="44"/>
+      <c r="AO142" s="44"/>
+      <c r="AP142" s="44"/>
+      <c r="AQ142" s="44"/>
+      <c r="AR142" s="44"/>
+      <c r="AS142" s="44"/>
+      <c r="AT142" s="44"/>
+      <c r="AU142" s="44"/>
+      <c r="AV142" s="44"/>
+      <c r="AW142" s="44"/>
+    </row>
+    <row r="143" spans="1:51" ht="15">
+      <c r="B143" s="98" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C143" s="99"/>
+      <c r="D143" s="99"/>
+      <c r="E143" s="99"/>
+      <c r="F143" s="99"/>
+      <c r="G143" s="99"/>
+      <c r="V143" s="98" t="s">
+        <v>1727</v>
+      </c>
+      <c r="W143" s="99"/>
+      <c r="X143" s="99"/>
+      <c r="Y143" s="99"/>
+      <c r="Z143" s="99"/>
+      <c r="AA143" s="99"/>
+      <c r="AB143" s="99"/>
+      <c r="AC143" s="99"/>
+      <c r="AD143" s="99"/>
+      <c r="AE143" s="99"/>
+      <c r="AM143" s="98" t="s">
+        <v>1758</v>
+      </c>
+      <c r="AN143" s="99"/>
+      <c r="AO143" s="99"/>
+      <c r="AP143" s="99"/>
+      <c r="AQ143" s="99"/>
+      <c r="AR143" s="99"/>
+      <c r="AS143" s="99"/>
+    </row>
+    <row r="144" spans="1:51">
+      <c r="B144" s="15" t="s">
+        <v>1704</v>
+      </c>
+      <c r="V144" s="15" t="s">
+        <v>1728</v>
+      </c>
+      <c r="AM144" s="15" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="145" spans="2:49">
+      <c r="B145" s="15" t="s">
+        <v>1705</v>
+      </c>
+      <c r="V145" s="15" t="s">
+        <v>1729</v>
+      </c>
+      <c r="AM145" s="15" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="146" spans="2:49">
+      <c r="B146" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V146" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AM146" s="15" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="147" spans="2:49">
+      <c r="B147" s="15" t="s">
+        <v>1706</v>
+      </c>
+      <c r="V147" s="88" t="s">
+        <v>1730</v>
+      </c>
+      <c r="AM147" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="148" spans="2:49" ht="15">
+      <c r="B148" s="15" t="s">
+        <v>1707</v>
+      </c>
+      <c r="V148" s="88" t="s">
+        <v>1731</v>
+      </c>
+      <c r="AM148" s="96" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="149" spans="2:49" ht="15">
+      <c r="B149" s="15" t="s">
+        <v>1708</v>
+      </c>
+      <c r="V149" s="88" t="s">
+        <v>1732</v>
+      </c>
+      <c r="AM149" s="96" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="150" spans="2:49">
+      <c r="B150" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V150" s="88" t="s">
+        <v>1733</v>
+      </c>
+      <c r="AM150" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="151" spans="2:49">
+      <c r="B151" s="15" t="s">
+        <v>1709</v>
+      </c>
+      <c r="V151" s="88" t="s">
+        <v>1734</v>
+      </c>
+      <c r="AM151" s="15" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="152" spans="2:49">
+      <c r="B152" s="15" t="s">
+        <v>1710</v>
+      </c>
+      <c r="V152" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AM152" s="15" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="153" spans="2:49">
+      <c r="B153" s="88" t="s">
+        <v>1711</v>
+      </c>
+      <c r="V153" s="15" t="s">
+        <v>1735</v>
+      </c>
+      <c r="AM153" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="154" spans="2:49">
+      <c r="B154" s="15" t="s">
+        <v>1712</v>
+      </c>
+      <c r="V154" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="155" spans="2:49" ht="15">
+      <c r="B155" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="V155" s="15" t="s">
+        <v>1736</v>
+      </c>
+      <c r="AM155" s="98" t="s">
+        <v>1766</v>
+      </c>
+      <c r="AN155" s="99"/>
+      <c r="AO155" s="99"/>
+      <c r="AP155" s="99"/>
+      <c r="AQ155" s="99"/>
+      <c r="AR155" s="99"/>
+      <c r="AS155" s="99"/>
+      <c r="AT155" s="99"/>
+      <c r="AU155" s="99"/>
+      <c r="AV155" s="99"/>
+      <c r="AW155" s="99"/>
+    </row>
+    <row r="156" spans="2:49">
+      <c r="B156" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="V156" s="15" t="s">
+        <v>1737</v>
+      </c>
+      <c r="AM156" s="15" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="157" spans="2:49">
+      <c r="V157" s="88" t="s">
+        <v>1738</v>
+      </c>
+      <c r="AM157" s="15" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="158" spans="2:49" ht="15">
+      <c r="B158" s="98" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C158" s="99"/>
+      <c r="D158" s="99"/>
+      <c r="E158" s="99"/>
+      <c r="F158" s="99"/>
+      <c r="G158" s="99"/>
+      <c r="H158" s="99"/>
+      <c r="V158" s="88" t="s">
+        <v>1739</v>
+      </c>
+      <c r="AM158" s="15" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="159" spans="2:49">
+      <c r="B159" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="V159" s="88" t="s">
+        <v>1740</v>
+      </c>
+      <c r="AM159" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="160" spans="2:49">
+      <c r="B160" s="15" t="s">
+        <v>1715</v>
+      </c>
+      <c r="V160" s="88" t="s">
+        <v>1741</v>
+      </c>
+      <c r="AM160" s="88" t="s">
+        <v>1770</v>
+      </c>
+      <c r="AN160" s="62"/>
+    </row>
+    <row r="161" spans="2:48">
+      <c r="B161" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V161" s="88" t="s">
+        <v>1742</v>
+      </c>
+      <c r="AM161" s="88" t="s">
+        <v>1771</v>
+      </c>
+      <c r="AN161" s="62"/>
+    </row>
+    <row r="162" spans="2:48">
+      <c r="B162" s="88" t="s">
+        <v>1716</v>
+      </c>
+      <c r="V162" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AM162" s="88" t="s">
+        <v>1772</v>
+      </c>
+      <c r="AN162" s="62"/>
+    </row>
+    <row r="163" spans="2:48">
+      <c r="B163" s="88" t="s">
+        <v>1717</v>
+      </c>
+      <c r="V163" s="15" t="s">
+        <v>1743</v>
+      </c>
+      <c r="AM163" s="88" t="s">
+        <v>1773</v>
+      </c>
+      <c r="AN163" s="62"/>
+    </row>
+    <row r="164" spans="2:48">
+      <c r="B164" s="15" t="s">
+        <v>1718</v>
+      </c>
+      <c r="V164" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AM164" s="88" t="s">
+        <v>1774</v>
+      </c>
+      <c r="AN164" s="62"/>
+    </row>
+    <row r="165" spans="2:48">
+      <c r="B165" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AM165" s="88" t="s">
+        <v>1775</v>
+      </c>
+      <c r="AN165" s="62"/>
+    </row>
+    <row r="166" spans="2:48" ht="15">
+      <c r="B166" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V166" s="98" t="s">
+        <v>1744</v>
+      </c>
+      <c r="W166" s="99"/>
+      <c r="X166" s="99"/>
+      <c r="Y166" s="99"/>
+      <c r="Z166" s="99"/>
+      <c r="AA166" s="99"/>
+      <c r="AB166" s="99"/>
+      <c r="AC166" s="99"/>
+      <c r="AD166" s="99"/>
+      <c r="AE166" s="99"/>
+      <c r="AF166" s="99"/>
+      <c r="AG166" s="99"/>
+      <c r="AM166" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="167" spans="2:48">
+      <c r="B167" s="88" t="s">
+        <v>1719</v>
+      </c>
+      <c r="V167" s="15" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="168" spans="2:48" ht="15">
+      <c r="B168" s="88" t="s">
+        <v>1720</v>
+      </c>
+      <c r="V168" s="15" t="s">
+        <v>1746</v>
+      </c>
+      <c r="AM168" s="98" t="s">
+        <v>1776</v>
+      </c>
+      <c r="AN168" s="99"/>
+      <c r="AO168" s="99"/>
+      <c r="AP168" s="99"/>
+      <c r="AQ168" s="99"/>
+      <c r="AR168" s="99"/>
+      <c r="AS168" s="99"/>
+      <c r="AT168" s="99"/>
+      <c r="AU168" s="99"/>
+      <c r="AV168" s="99"/>
+    </row>
+    <row r="169" spans="2:48">
+      <c r="B169" s="15" t="s">
+        <v>1721</v>
+      </c>
+      <c r="V169" s="69"/>
+      <c r="AM169" s="15" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="170" spans="2:48">
+      <c r="B170" s="15" t="s">
+        <v>1612</v>
+      </c>
+      <c r="V170" s="15" t="s">
+        <v>1747</v>
+      </c>
+      <c r="AM170" s="15" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="171" spans="2:48">
+      <c r="B171" s="15" t="s">
+        <v>1722</v>
+      </c>
+      <c r="V171" s="15" t="s">
+        <v>1748</v>
+      </c>
+      <c r="AM171" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="172" spans="2:48">
+      <c r="B172" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="V172" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AM172" s="15" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="173" spans="2:48">
+      <c r="B173" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V173" s="69"/>
+      <c r="AM173" s="15" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="174" spans="2:48">
+      <c r="B174" s="15" t="s">
+        <v>1723</v>
+      </c>
+      <c r="V174" s="15" t="s">
+        <v>1749</v>
+      </c>
+      <c r="AM174" s="15" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="175" spans="2:48">
+      <c r="B175" s="15" t="s">
+        <v>1724</v>
+      </c>
+      <c r="V175" s="15" t="s">
+        <v>1750</v>
+      </c>
+      <c r="AM175" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="176" spans="2:48">
+      <c r="B176" s="15" t="s">
+        <v>1725</v>
+      </c>
+      <c r="V176" s="15" t="s">
+        <v>1751</v>
+      </c>
+      <c r="AM176" s="15" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="177" spans="1:39">
+      <c r="B177" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="V177" s="15" t="s">
+        <v>1752</v>
+      </c>
+      <c r="AM177" s="15" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="178" spans="1:39">
+      <c r="B178" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="V178" s="15" t="s">
+        <v>1753</v>
+      </c>
+      <c r="AM178" s="15" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="179" spans="1:39">
+      <c r="V179" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AM179" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="180" spans="1:39">
+      <c r="V180" s="15" t="s">
+        <v>1754</v>
+      </c>
+      <c r="AM180" s="15" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="181" spans="1:39">
+      <c r="V181" s="15" t="s">
+        <v>1755</v>
+      </c>
+      <c r="AM181" s="15" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="182" spans="1:39">
+      <c r="V182" s="15" t="s">
+        <v>1756</v>
+      </c>
+      <c r="AM182" s="15" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="183" spans="1:39">
+      <c r="V183" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AM183" s="15" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="184" spans="1:39">
+      <c r="AM184" s="15" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="185" spans="1:39" ht="15" thickBot="1">
+      <c r="AM185" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="186" spans="1:39" s="16" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A186" s="92"/>
+      <c r="B186" s="93" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="187" spans="1:39" ht="15">
+      <c r="B187" s="104" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C187" s="44"/>
+      <c r="D187" s="44"/>
+      <c r="E187" s="44"/>
+      <c r="F187" s="44"/>
+      <c r="G187" s="44"/>
+      <c r="H187" s="44"/>
+      <c r="I187" s="44"/>
+      <c r="V187" s="104" t="s">
+        <v>1809</v>
+      </c>
+      <c r="W187" s="44"/>
+      <c r="X187" s="44"/>
+      <c r="Y187" s="44"/>
+      <c r="Z187" s="44"/>
+      <c r="AA187" s="44"/>
+      <c r="AB187" s="44"/>
+      <c r="AC187" s="44"/>
+      <c r="AD187" s="44"/>
+    </row>
+    <row r="188" spans="1:39">
+      <c r="B188" s="15" t="s">
+        <v>1792</v>
+      </c>
+      <c r="V188" s="15" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="189" spans="1:39">
+      <c r="B189" s="15" t="s">
+        <v>1793</v>
+      </c>
+      <c r="V189" s="15" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="190" spans="1:39">
+      <c r="B190" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V190" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="191" spans="1:39">
+      <c r="B191" s="15" t="s">
+        <v>1794</v>
+      </c>
+      <c r="V191" s="15" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="192" spans="1:39">
+      <c r="B192" s="15" t="s">
+        <v>1795</v>
+      </c>
+      <c r="V192" s="15" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="193" spans="2:22">
+      <c r="B193" s="15" t="s">
+        <v>1796</v>
+      </c>
+      <c r="V193" s="15" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="194" spans="2:22">
+      <c r="B194" s="15" t="s">
+        <v>1797</v>
+      </c>
+      <c r="V194" s="15" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="195" spans="2:22">
+      <c r="B195" s="15" t="s">
+        <v>1798</v>
+      </c>
+      <c r="V195" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="196" spans="2:22">
+      <c r="B196" s="15" t="s">
+        <v>1799</v>
+      </c>
+      <c r="V196" s="15" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="197" spans="2:22">
+      <c r="B197" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V197" s="15" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="198" spans="2:22">
+      <c r="B198" s="15" t="s">
+        <v>1800</v>
+      </c>
+      <c r="V198" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="199" spans="2:22">
+      <c r="B199" s="15" t="s">
+        <v>1801</v>
+      </c>
+      <c r="V199" s="15" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="200" spans="2:22">
+      <c r="B200" s="15" t="s">
+        <v>1802</v>
+      </c>
+      <c r="V200" s="15" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="201" spans="2:22">
+      <c r="B201" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="V201" s="15" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="202" spans="2:22">
+      <c r="B202" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V202" s="15" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="203" spans="2:22">
+      <c r="B203" s="15" t="s">
+        <v>1803</v>
+      </c>
+      <c r="V203" s="15" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="204" spans="2:22">
+      <c r="B204" s="15" t="s">
+        <v>1804</v>
+      </c>
+      <c r="V204" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="205" spans="2:22">
+      <c r="B205" s="15" t="s">
+        <v>1805</v>
+      </c>
+      <c r="V205" s="15" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="206" spans="2:22">
+      <c r="B206" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V206" s="15" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="207" spans="2:22">
+      <c r="B207" s="15" t="s">
+        <v>1806</v>
+      </c>
+      <c r="V207" s="15" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="208" spans="2:22">
+      <c r="B208" s="15" t="s">
+        <v>1807</v>
+      </c>
+      <c r="V208" s="15" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="209" spans="1:33">
+      <c r="B209" s="15" t="s">
+        <v>1808</v>
+      </c>
+      <c r="V209" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="210" spans="1:33">
+      <c r="B210" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="V210" s="15" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="211" spans="1:33">
+      <c r="V211" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="212" spans="1:33" ht="15" thickBot="1"/>
+    <row r="213" spans="1:33" s="16" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A213" s="92"/>
+      <c r="B213" s="93" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="214" spans="1:33" ht="15">
+      <c r="B214" s="43" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C214" s="44"/>
+      <c r="D214" s="44"/>
+      <c r="E214" s="44"/>
+      <c r="F214" s="44"/>
+      <c r="G214" s="44"/>
+      <c r="H214" s="44"/>
+      <c r="I214" s="44"/>
+      <c r="J214" s="44"/>
+      <c r="K214" s="44"/>
+      <c r="Z214" s="43" t="s">
+        <v>1853</v>
+      </c>
+      <c r="AA214" s="44"/>
+      <c r="AB214" s="44"/>
+      <c r="AC214" s="44"/>
+      <c r="AD214" s="44"/>
+      <c r="AE214" s="44"/>
+      <c r="AF214" s="44"/>
+    </row>
+    <row r="215" spans="1:33" ht="15">
+      <c r="B215" s="15" t="s">
+        <v>1829</v>
+      </c>
+      <c r="Z215" s="98" t="s">
+        <v>1854</v>
+      </c>
+      <c r="AA215" s="99"/>
+      <c r="AB215" s="99"/>
+      <c r="AC215" s="99"/>
+      <c r="AD215" s="99"/>
+      <c r="AE215" s="99"/>
+      <c r="AF215" s="99"/>
+      <c r="AG215" s="99"/>
+    </row>
+    <row r="216" spans="1:33">
+      <c r="B216" s="15" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="217" spans="1:33" ht="15">
+      <c r="B217" s="105" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C217" s="84"/>
+      <c r="Z217" s="15" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="218" spans="1:33" ht="15">
+      <c r="B218" s="105" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C218" s="84"/>
+      <c r="Z218" s="15" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="219" spans="1:33" ht="15">
+      <c r="B219" s="105" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C219" s="84"/>
+      <c r="Z219" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="220" spans="1:33" ht="15">
+      <c r="B220" s="105" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C220" s="84"/>
+      <c r="Z220" s="96" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="221" spans="1:33" ht="15">
+      <c r="B221" s="105" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C221" s="84"/>
+      <c r="Z221" s="96" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="222" spans="1:33" ht="15">
+      <c r="B222" s="105" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C222" s="84"/>
+      <c r="Z222" s="96" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="223" spans="1:33" ht="15">
+      <c r="B223" s="105" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C223" s="84"/>
+      <c r="Z223" s="96" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="224" spans="1:33" ht="15">
+      <c r="B224" s="105" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C224" s="84"/>
+      <c r="Z224" s="96" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="225" spans="2:33" ht="15">
+      <c r="B225" s="105" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C225" s="84"/>
+      <c r="Z225" s="96" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="226" spans="2:33" ht="15">
+      <c r="B226" s="105" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C226" s="84"/>
+      <c r="Z226" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="227" spans="2:33" ht="15">
+      <c r="B227" s="105" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C227" s="84"/>
+    </row>
+    <row r="228" spans="2:33" ht="15">
+      <c r="B228" s="105" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C228" s="84"/>
+      <c r="Z228" s="98" t="s">
+        <v>1862</v>
+      </c>
+      <c r="AA228" s="99"/>
+      <c r="AB228" s="99"/>
+      <c r="AC228" s="99"/>
+      <c r="AD228" s="99"/>
+      <c r="AE228" s="99"/>
+      <c r="AF228" s="99"/>
+      <c r="AG228" s="99"/>
+    </row>
+    <row r="229" spans="2:33" ht="15">
+      <c r="B229" s="105" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C229" s="84"/>
+      <c r="Z229" s="15" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="230" spans="2:33" ht="15">
+      <c r="B230" s="105" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C230" s="84"/>
+      <c r="Z230" s="15" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="231" spans="2:33" ht="15">
+      <c r="B231" s="105" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C231" s="84"/>
+      <c r="Z231" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="232" spans="2:33" ht="15">
+      <c r="B232" s="105" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C232" s="84"/>
+      <c r="Z232" s="15" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="233" spans="2:33" ht="15">
+      <c r="B233" s="105" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C233" s="84"/>
+      <c r="Z233" s="15" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="234" spans="2:33">
+      <c r="B234" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Z234" s="15" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="235" spans="2:33">
+      <c r="B235" s="15" t="s">
+        <v>1848</v>
+      </c>
+      <c r="Z235" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="236" spans="2:33">
+      <c r="B236" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Z236" s="15" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="237" spans="2:33">
+      <c r="B237" s="15" t="s">
+        <v>1849</v>
+      </c>
+      <c r="Z237" s="15" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="238" spans="2:33">
+      <c r="B238" s="15" t="s">
+        <v>1850</v>
+      </c>
+      <c r="Z238" s="15" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="239" spans="2:33">
+      <c r="B239" s="15" t="s">
+        <v>1851</v>
+      </c>
+      <c r="Z239" s="15" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="240" spans="2:33">
+      <c r="B240" s="15" t="s">
+        <v>1852</v>
+      </c>
+      <c r="Z240" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="241" spans="2:84">
+      <c r="B241" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="Z241" s="15" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="242" spans="2:84">
+      <c r="Z242" s="15" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="243" spans="2:84">
+      <c r="Z243" s="15" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="244" spans="2:84">
+      <c r="Z244" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="245" spans="2:84" s="106" customFormat="1" ht="15">
+      <c r="B245" s="107" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C245" s="108"/>
+      <c r="D245" s="108"/>
+      <c r="E245" s="108"/>
+      <c r="F245" s="108"/>
+      <c r="G245" s="108"/>
+      <c r="H245" s="108"/>
+      <c r="I245" s="108"/>
+      <c r="J245" s="108"/>
+      <c r="K245" s="108"/>
+    </row>
+    <row r="246" spans="2:84" ht="15">
+      <c r="B246" s="67" t="s">
+        <v>1874</v>
+      </c>
+      <c r="V246" s="67" t="s">
+        <v>1886</v>
+      </c>
+      <c r="AP246" s="67" t="s">
+        <v>1899</v>
+      </c>
+      <c r="BJ246" s="67" t="s">
+        <v>1907</v>
+      </c>
+      <c r="CF246" s="67" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="247" spans="2:84">
+      <c r="V247" s="15" t="s">
+        <v>1887</v>
+      </c>
+      <c r="AP247" s="15" t="s">
+        <v>1900</v>
+      </c>
+      <c r="BJ247" s="15" t="s">
+        <v>1908</v>
+      </c>
+      <c r="CF247" s="15" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="248" spans="2:84">
+      <c r="B248" s="15" t="s">
+        <v>1875</v>
+      </c>
+      <c r="V248" s="15" t="s">
+        <v>1631</v>
+      </c>
+      <c r="AP248" s="15" t="s">
+        <v>1782</v>
+      </c>
+      <c r="BJ248" s="15" t="s">
+        <v>1592</v>
+      </c>
+      <c r="CF248" s="15" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="249" spans="2:84">
+      <c r="B249" s="15" t="s">
+        <v>1876</v>
+      </c>
+      <c r="V249" s="15" t="s">
+        <v>1769</v>
+      </c>
+      <c r="AP249" s="15" t="s">
+        <v>1769</v>
+      </c>
+      <c r="BJ249" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="CF249" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="250" spans="2:84">
+      <c r="B250" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V250" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AP250" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="BJ250" s="15" t="s">
+        <v>1909</v>
+      </c>
+      <c r="CF250" s="15" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="251" spans="2:84">
+      <c r="B251" s="15" t="s">
+        <v>1877</v>
+      </c>
+      <c r="V251" s="15" t="s">
+        <v>1888</v>
+      </c>
+      <c r="AP251" s="15" t="s">
+        <v>1901</v>
+      </c>
+      <c r="BJ251" s="15" t="s">
+        <v>1910</v>
+      </c>
+      <c r="CF251" s="15" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="252" spans="2:84">
+      <c r="B252" s="15" t="s">
+        <v>1878</v>
+      </c>
+      <c r="V252" s="15" t="s">
+        <v>1889</v>
+      </c>
+      <c r="AP252" s="15" t="s">
+        <v>1902</v>
+      </c>
+      <c r="BJ252" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="CF252" s="15" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="253" spans="2:84">
+      <c r="B253" s="15" t="s">
+        <v>1879</v>
+      </c>
+      <c r="V253" s="15" t="s">
+        <v>1890</v>
+      </c>
+      <c r="AP253" s="15" t="s">
+        <v>1903</v>
+      </c>
+      <c r="BJ253" s="15" t="s">
+        <v>1911</v>
+      </c>
+      <c r="CF253" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="254" spans="2:84">
+      <c r="B254" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="V254" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AP254" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="BJ254" s="15" t="s">
+        <v>1912</v>
+      </c>
+      <c r="CF254" s="15" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="255" spans="2:84">
+      <c r="B255" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V255" s="15" t="s">
+        <v>1891</v>
+      </c>
+      <c r="AP255" s="15" t="s">
+        <v>1904</v>
+      </c>
+      <c r="BJ255" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="CF255" s="15" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="256" spans="2:84">
+      <c r="B256" s="15" t="s">
+        <v>1880</v>
+      </c>
+      <c r="V256" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AP256" s="15" t="s">
+        <v>1905</v>
+      </c>
+      <c r="BJ256" s="15" t="s">
+        <v>1880</v>
+      </c>
+      <c r="CF256" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="257" spans="2:62">
+      <c r="B257" s="15" t="s">
+        <v>1881</v>
+      </c>
+      <c r="V257" s="15" t="s">
+        <v>1892</v>
+      </c>
+      <c r="AP257" s="15" t="s">
+        <v>1906</v>
+      </c>
+      <c r="BJ257" s="15" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="258" spans="2:62">
+      <c r="B258" s="15" t="s">
+        <v>1882</v>
+      </c>
+      <c r="V258" s="15" t="s">
+        <v>1893</v>
+      </c>
+      <c r="AP258" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BJ258" s="15" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="259" spans="2:62">
+      <c r="B259" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="V259" s="15" t="s">
+        <v>1894</v>
+      </c>
+      <c r="BJ259" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="260" spans="2:62">
+      <c r="B260" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V260" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="261" spans="2:62">
+      <c r="B261" s="15" t="s">
+        <v>1883</v>
+      </c>
+      <c r="V261" s="15" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="262" spans="2:62">
+      <c r="B262" s="15" t="s">
+        <v>1884</v>
+      </c>
+      <c r="V262" s="15" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="263" spans="2:62">
+      <c r="B263" s="15" t="s">
+        <v>1885</v>
+      </c>
+      <c r="V263" s="15" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="264" spans="2:62">
+      <c r="B264" s="15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="V264" s="15" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="265" spans="2:62">
+      <c r="B265" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="V265" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="267" spans="2:62" ht="15">
+      <c r="B267" s="43" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C267" s="44"/>
+      <c r="D267" s="44"/>
+      <c r="E267" s="44"/>
+      <c r="F267" s="44"/>
+      <c r="G267" s="44"/>
+      <c r="H267" s="44"/>
+      <c r="I267" s="44"/>
+      <c r="J267" s="44"/>
+      <c r="K267" s="44"/>
+      <c r="L267" s="44"/>
+      <c r="M267" s="44"/>
+    </row>
+    <row r="268" spans="2:62" ht="15">
+      <c r="B268" s="67" t="s">
+        <v>1924</v>
+      </c>
+      <c r="T268" s="67" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="269" spans="2:62">
+      <c r="B269" s="15" t="s">
+        <v>1925</v>
+      </c>
+      <c r="T269" s="15" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="270" spans="2:62">
+      <c r="B270" s="15" t="s">
+        <v>1856</v>
+      </c>
+      <c r="T270" s="15" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="271" spans="2:62">
+      <c r="B271" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="T271" s="15" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="272" spans="2:62">
+      <c r="B272" s="15" t="s">
+        <v>1926</v>
+      </c>
+      <c r="T272" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="273" spans="2:20">
+      <c r="B273" s="15" t="s">
+        <v>1927</v>
+      </c>
+      <c r="T273" s="15" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="274" spans="2:20">
+      <c r="B274" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="T274" s="15" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="275" spans="2:20">
+      <c r="B275" s="15" t="s">
+        <v>1928</v>
+      </c>
+      <c r="T275" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="276" spans="2:20">
+      <c r="B276" s="15" t="s">
+        <v>1929</v>
+      </c>
+      <c r="T276" s="15" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="277" spans="2:20">
+      <c r="B277" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="T277" s="15" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="278" spans="2:20">
+      <c r="B278" s="15" t="s">
+        <v>1930</v>
+      </c>
+      <c r="T278" s="15" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="279" spans="2:20">
+      <c r="B279" s="15" t="s">
+        <v>1931</v>
+      </c>
+      <c r="T279" s="15" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="280" spans="2:20">
+      <c r="B280" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="T280" s="15" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="281" spans="2:20">
+      <c r="B281" s="15" t="s">
+        <v>1932</v>
+      </c>
+      <c r="T281" s="15" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="282" spans="2:20">
+      <c r="B282" s="15" t="s">
+        <v>1933</v>
+      </c>
+      <c r="T282" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="283" spans="2:20">
+      <c r="B283" s="15" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="284" spans="2:20">
+      <c r="B284" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="285" spans="2:20">
+      <c r="B285" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="286" spans="2:20">
+      <c r="B286" s="15" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="287" spans="2:20">
+      <c r="B287" s="15" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="288" spans="2:20">
+      <c r="B288" s="15" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="289" spans="1:72">
+      <c r="B289" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="290" spans="1:72">
+      <c r="B290" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="291" spans="1:72" ht="15" thickBot="1"/>
+    <row r="292" spans="1:72" s="16" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A292" s="92"/>
+      <c r="B292" s="93" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="293" spans="1:72" ht="15">
+      <c r="B293" s="43" t="s">
+        <v>1949</v>
+      </c>
+      <c r="C293" s="44"/>
+      <c r="D293" s="44"/>
+      <c r="E293" s="44"/>
+      <c r="F293" s="44"/>
+      <c r="G293" s="44"/>
+      <c r="H293" s="44"/>
+      <c r="I293" s="44"/>
+      <c r="J293" s="44"/>
+      <c r="K293" s="44"/>
+      <c r="L293" s="44"/>
+      <c r="M293" s="44"/>
+      <c r="V293" s="43" t="s">
+        <v>1980</v>
+      </c>
+      <c r="W293" s="44"/>
+      <c r="X293" s="44"/>
+      <c r="Y293" s="44"/>
+      <c r="Z293" s="44"/>
+      <c r="AA293" s="44"/>
+      <c r="AB293" s="44"/>
+      <c r="AC293" s="44"/>
+      <c r="AD293" s="44"/>
+      <c r="AE293" s="44"/>
+      <c r="AF293" s="44"/>
+      <c r="AR293" s="43" t="s">
+        <v>2008</v>
+      </c>
+      <c r="AS293" s="44"/>
+      <c r="AT293" s="44"/>
+      <c r="AU293" s="44"/>
+      <c r="AV293" s="44"/>
+      <c r="AW293" s="44"/>
+      <c r="AX293" s="44"/>
+      <c r="AY293" s="44"/>
+      <c r="AZ293" s="44"/>
+      <c r="BA293" s="44"/>
+      <c r="BK293" s="43" t="s">
+        <v>2037</v>
+      </c>
+      <c r="BL293" s="44"/>
+      <c r="BM293" s="44"/>
+      <c r="BN293" s="44"/>
+      <c r="BO293" s="44"/>
+      <c r="BP293" s="44"/>
+      <c r="BQ293" s="44"/>
+      <c r="BR293" s="44"/>
+      <c r="BS293" s="44"/>
+      <c r="BT293" s="44"/>
+    </row>
+    <row r="294" spans="1:72" ht="15">
+      <c r="B294" s="67" t="s">
+        <v>1950</v>
+      </c>
+      <c r="V294" s="67" t="s">
+        <v>1981</v>
+      </c>
+      <c r="AR294" s="67" t="s">
+        <v>2009</v>
+      </c>
+      <c r="BK294" s="67" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="295" spans="1:72">
+      <c r="B295" s="15" t="s">
+        <v>1951</v>
+      </c>
+      <c r="V295" s="15" t="s">
+        <v>1982</v>
+      </c>
+      <c r="AR295" s="15" t="s">
+        <v>2010</v>
+      </c>
+      <c r="BK295" s="15" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="296" spans="1:72">
+      <c r="B296" s="15" t="s">
+        <v>1952</v>
+      </c>
+      <c r="V296" s="15" t="s">
+        <v>1983</v>
+      </c>
+      <c r="AR296" s="15" t="s">
+        <v>1426</v>
+      </c>
+      <c r="BK296" s="15" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="297" spans="1:72">
+      <c r="B297" s="15" t="s">
+        <v>1953</v>
+      </c>
+      <c r="V297" s="15" t="s">
+        <v>1984</v>
+      </c>
+      <c r="AR297" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="BK297" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="298" spans="1:72">
+      <c r="B298" s="15" t="s">
+        <v>1954</v>
+      </c>
+      <c r="V298" s="69"/>
+      <c r="AR298" s="15" t="s">
+        <v>2011</v>
+      </c>
+      <c r="BK298" s="15" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="299" spans="1:72">
+      <c r="B299" s="15" t="s">
+        <v>1955</v>
+      </c>
+      <c r="V299" s="15" t="s">
+        <v>1985</v>
+      </c>
+      <c r="AR299" s="15" t="s">
+        <v>2012</v>
+      </c>
+      <c r="BK299" s="15" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="300" spans="1:72">
+      <c r="B300" s="15" t="s">
+        <v>1694</v>
+      </c>
+      <c r="V300" s="15" t="s">
+        <v>1592</v>
+      </c>
+      <c r="AR300" s="15" t="s">
+        <v>2013</v>
+      </c>
+      <c r="BK300" s="15" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="301" spans="1:72">
+      <c r="B301" s="15" t="s">
+        <v>1956</v>
+      </c>
+      <c r="V301" s="15" t="s">
+        <v>1986</v>
+      </c>
+      <c r="AR301" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="BK301" s="15" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="302" spans="1:72">
+      <c r="B302" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V302" s="15" t="s">
+        <v>1987</v>
+      </c>
+      <c r="AR302" s="15" t="s">
+        <v>2014</v>
+      </c>
+      <c r="BK302" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="303" spans="1:72">
+      <c r="B303" s="15" t="s">
+        <v>1957</v>
+      </c>
+      <c r="V303" s="15" t="s">
+        <v>1988</v>
+      </c>
+      <c r="AR303" s="15" t="s">
+        <v>2015</v>
+      </c>
+      <c r="BK303" s="15" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="304" spans="1:72">
+      <c r="B304" s="15" t="s">
+        <v>1958</v>
+      </c>
+      <c r="V304" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AR304" s="15" t="s">
+        <v>2016</v>
+      </c>
+      <c r="BK304" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="305" spans="2:63">
+      <c r="B305" s="15" t="s">
+        <v>1959</v>
+      </c>
+      <c r="V305" s="15" t="s">
+        <v>1989</v>
+      </c>
+      <c r="AR305" s="15" t="s">
+        <v>2017</v>
+      </c>
+      <c r="BK305" s="15" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="306" spans="2:63">
+      <c r="B306" s="15" t="s">
+        <v>1960</v>
+      </c>
+      <c r="V306" s="15" t="s">
+        <v>1671</v>
+      </c>
+      <c r="AR306" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="BK306" s="15" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="307" spans="2:63">
+      <c r="B307" s="15" t="s">
+        <v>1961</v>
+      </c>
+      <c r="V307" s="15" t="s">
+        <v>1990</v>
+      </c>
+      <c r="AR307" s="15" t="s">
+        <v>2018</v>
+      </c>
+      <c r="BK307" s="15" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="308" spans="2:63">
+      <c r="B308" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V308" s="15" t="s">
+        <v>1991</v>
+      </c>
+      <c r="AR308" s="15" t="s">
+        <v>2019</v>
+      </c>
+      <c r="BK308" s="15" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="309" spans="2:63">
+      <c r="B309" s="15" t="s">
+        <v>1962</v>
+      </c>
+      <c r="V309" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AR309" s="15" t="s">
+        <v>2020</v>
+      </c>
+      <c r="BK309" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="310" spans="2:63">
+      <c r="B310" s="15" t="s">
+        <v>1963</v>
+      </c>
+      <c r="AR310" s="15" t="s">
+        <v>2021</v>
+      </c>
+      <c r="BK310" s="15" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="311" spans="2:63" ht="15">
+      <c r="B311" s="15" t="s">
+        <v>1964</v>
+      </c>
+      <c r="V311" s="67" t="s">
+        <v>1992</v>
+      </c>
+      <c r="AR311" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="BK311" s="15" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="312" spans="2:63">
+      <c r="B312" s="15" t="s">
+        <v>1965</v>
+      </c>
+      <c r="V312" s="15" t="s">
+        <v>1993</v>
+      </c>
+      <c r="AR312" s="15" t="s">
+        <v>2022</v>
+      </c>
+      <c r="BK312" s="15" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="313" spans="2:63">
+      <c r="B313" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="V313" s="15" t="s">
+        <v>1994</v>
+      </c>
+      <c r="AR313" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="BK313" s="15" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="314" spans="2:63">
+      <c r="V314" s="15" t="s">
+        <v>1995</v>
+      </c>
+      <c r="BK314" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="315" spans="2:63" ht="15">
+      <c r="B315" s="67" t="s">
+        <v>1966</v>
+      </c>
+      <c r="V315" s="15" t="s">
+        <v>1996</v>
+      </c>
+      <c r="AR315" s="67" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="316" spans="2:63">
+      <c r="B316" s="15" t="s">
+        <v>1967</v>
+      </c>
+      <c r="V316" s="15" t="s">
+        <v>1997</v>
+      </c>
+      <c r="AR316" s="15" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="317" spans="2:63">
+      <c r="B317" s="15" t="s">
+        <v>1968</v>
+      </c>
+      <c r="V317" s="15" t="s">
+        <v>1998</v>
+      </c>
+      <c r="AR317" s="15" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="318" spans="2:63">
+      <c r="B318" s="15" t="s">
+        <v>1969</v>
+      </c>
+      <c r="V318" s="15" t="s">
+        <v>1999</v>
+      </c>
+      <c r="AR318" s="15" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="319" spans="2:63">
+      <c r="B319" s="15" t="s">
+        <v>1970</v>
+      </c>
+      <c r="V319" s="15" t="s">
+        <v>2000</v>
+      </c>
+      <c r="AR319" s="15" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="320" spans="2:63">
+      <c r="B320" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V320" s="69"/>
+      <c r="AR320" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="321" spans="2:44">
+      <c r="B321" s="15" t="s">
+        <v>1971</v>
+      </c>
+      <c r="V321" s="15" t="s">
+        <v>2001</v>
+      </c>
+      <c r="AR321" s="15" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="322" spans="2:44">
+      <c r="B322" s="15" t="s">
+        <v>1972</v>
+      </c>
+      <c r="V322" s="15" t="s">
+        <v>2002</v>
+      </c>
+      <c r="AR322" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="323" spans="2:44">
+      <c r="B323" s="15" t="s">
+        <v>1973</v>
+      </c>
+      <c r="V323" s="15" t="s">
+        <v>2003</v>
+      </c>
+      <c r="AR323" s="69"/>
+    </row>
+    <row r="324" spans="2:44">
+      <c r="B324" s="15" t="s">
+        <v>1974</v>
+      </c>
+      <c r="V324" s="15" t="s">
+        <v>2004</v>
+      </c>
+      <c r="AR324" s="15" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="325" spans="2:44">
+      <c r="B325" s="15" t="s">
+        <v>1975</v>
+      </c>
+      <c r="V325" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AR325" s="15" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="326" spans="2:44">
+      <c r="B326" s="15" t="s">
+        <v>1083</v>
+      </c>
+      <c r="V326" s="15" t="s">
+        <v>2005</v>
+      </c>
+      <c r="AR326" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="327" spans="2:44">
+      <c r="B327" s="15" t="s">
+        <v>1976</v>
+      </c>
+      <c r="V327" s="15" t="s">
+        <v>2006</v>
+      </c>
+      <c r="AR327" s="15" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="328" spans="2:44">
+      <c r="B328" s="15" t="s">
+        <v>1977</v>
+      </c>
+      <c r="V328" s="15" t="s">
+        <v>2007</v>
+      </c>
+      <c r="AR328" s="15" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="329" spans="2:44">
+      <c r="B329" s="15" t="s">
+        <v>1978</v>
+      </c>
+      <c r="V329" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AR329" s="15" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="330" spans="2:44">
+      <c r="B330" s="15" t="s">
+        <v>1979</v>
+      </c>
+      <c r="AR330" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="331" spans="2:44">
+      <c r="B331" s="15" t="s">
+        <v>901</v>
+      </c>
+      <c r="AR331" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="332" spans="2:44">
+      <c r="AR332" s="15" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="333" spans="2:44">
+      <c r="AR333" s="15" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="334" spans="2:44">
+      <c r="AR334" s="15" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="335" spans="2:44">
+      <c r="AR335" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="336" spans="2:44">
+      <c r="AR336" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="401" spans="2:2" ht="15">
+      <c r="B401" s="10"/>
+    </row>
+    <row r="403" spans="2:2" ht="15">
+      <c r="B403" s="10"/>
+    </row>
+    <row r="404" spans="2:2">
+      <c r="B404" s="13"/>
+    </row>
+    <row r="405" spans="2:2" ht="15">
+      <c r="B405" s="100"/>
+    </row>
+    <row r="406" spans="2:2" ht="15">
+      <c r="B406" s="100"/>
+    </row>
+    <row r="407" spans="2:2" ht="15">
+      <c r="B407" s="100"/>
+    </row>
+    <row r="408" spans="2:2" ht="15">
+      <c r="B408" s="100"/>
+    </row>
+    <row r="409" spans="2:2" ht="15">
+      <c r="B409" s="100"/>
+    </row>
+    <row r="410" spans="2:2" ht="15">
+      <c r="B410" s="100"/>
+    </row>
+    <row r="411" spans="2:2" ht="15">
+      <c r="B411" s="100"/>
+    </row>
+    <row r="412" spans="2:2" ht="15">
+      <c r="B412" s="100"/>
+    </row>
+    <row r="414" spans="2:2" ht="15">
+      <c r="B414" s="10"/>
+    </row>
+    <row r="415" spans="2:2">
+      <c r="B415" s="13"/>
+    </row>
+    <row r="416" spans="2:2" ht="15">
+      <c r="B416" s="100"/>
+    </row>
+    <row r="417" spans="2:2" ht="15">
+      <c r="B417" s="100"/>
+    </row>
+    <row r="418" spans="2:2" ht="15">
+      <c r="B418" s="100"/>
+    </row>
+    <row r="419" spans="2:2" ht="15">
+      <c r="B419" s="100"/>
+    </row>
+    <row r="420" spans="2:2" ht="15">
+      <c r="B420" s="100"/>
+    </row>
+    <row r="421" spans="2:2" ht="15">
+      <c r="B421" s="100"/>
+    </row>
+    <row r="422" spans="2:2" ht="15">
+      <c r="B422" s="100"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:B521"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="16384" width="3" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:2" ht="15">
+      <c r="B1" s="10" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" ht="15">
+      <c r="B3" s="10" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" ht="15">
+      <c r="B5" s="10" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" ht="15">
+      <c r="B7" s="10" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="15" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" s="15" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" s="15" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="15" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" s="15" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="15" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" ht="15">
+      <c r="B17" s="10" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="13"/>
+    </row>
+    <row r="19" spans="2:2" ht="15">
+      <c r="B19" s="100" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" ht="15">
+      <c r="B20" s="100" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" ht="15">
+      <c r="B21" s="100" t="s">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" ht="15">
+      <c r="B23" s="10" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="15" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="15" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="15" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="15" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="15" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="15" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="69"/>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="15" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="15" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="15" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="15" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="15" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="15" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="69"/>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="15" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="15" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="15" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="15" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="15" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="69"/>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="15" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="15" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="15" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="15" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="15" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="15" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="15" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" ht="15">
+      <c r="B57" s="10" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" ht="15">
+      <c r="B59" s="10" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="15" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="15" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="15" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="15" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="15" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="15" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="15" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="15" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="15" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="15" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" ht="15">
+      <c r="B73" s="10" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="13"/>
+    </row>
+    <row r="75" spans="2:2" ht="15">
+      <c r="B75" s="100" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" ht="15">
+      <c r="B76" s="100" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" ht="15">
+      <c r="B77" s="100" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" ht="15">
+      <c r="B79" s="10" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="15" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="15" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="15" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="15" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="15" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="15" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="15" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" s="15" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" s="69"/>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91" s="15" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92" s="15" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93" s="15" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" s="15" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" s="15" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="15" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="15" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98" s="15" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" s="15" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" s="15" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" s="15" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2">
       <c r="B102" s="15" t="s">
         <v>901</v>
       </c>
-      <c r="AB102" s="15" t="s">
-        <v>1649</v>
-      </c>
-      <c r="AY102" s="15" t="s">
-        <v>1677</v>
-      </c>
-    </row>
-    <row r="103" spans="2:62">
-      <c r="B103" s="69"/>
-      <c r="AB103" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AY103" s="15" t="s">
-        <v>1678</v>
-      </c>
-    </row>
-    <row r="104" spans="2:62">
-      <c r="B104" s="15" t="s">
-        <v>1616</v>
-      </c>
-      <c r="AB104" s="15" t="s">
-        <v>1650</v>
-      </c>
-      <c r="AY104" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="105" spans="2:62" ht="15">
-      <c r="B105" s="15" t="s">
-        <v>1617</v>
-      </c>
-      <c r="AB105" s="96" t="s">
-        <v>1651</v>
-      </c>
-      <c r="AY105" s="15" t="s">
-        <v>1679</v>
-      </c>
-    </row>
-    <row r="106" spans="2:62">
+    </row>
+    <row r="104" spans="2:2" ht="15">
+      <c r="B104" s="10" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2">
       <c r="B106" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AB106" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AY106" s="15" t="s">
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="107" spans="2:62">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
       <c r="B107" s="15" t="s">
-        <v>1618</v>
-      </c>
-      <c r="AB107" s="15" t="s">
-        <v>1652</v>
-      </c>
-      <c r="AY107" s="15" t="s">
-        <v>1681</v>
-      </c>
-    </row>
-    <row r="108" spans="2:62">
-      <c r="B108" s="88" t="s">
-        <v>1619</v>
-      </c>
-      <c r="AB108" s="15" t="s">
-        <v>1653</v>
-      </c>
-      <c r="AY108" s="15" t="s">
-        <v>1682</v>
-      </c>
-    </row>
-    <row r="109" spans="2:62">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2">
+      <c r="B108" s="15" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2">
       <c r="B109" s="15" t="s">
-        <v>1620</v>
-      </c>
-      <c r="AB109" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AY109" s="15" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110" s="15" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111" s="15" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112" s="15" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113" s="15" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2">
+      <c r="B114" s="15" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115" s="15" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116" s="15" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117" s="15" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="110" spans="2:62">
-      <c r="B110" s="15" t="s">
-        <v>1621</v>
-      </c>
-      <c r="AB110" s="15" t="s">
-        <v>1654</v>
-      </c>
-    </row>
-    <row r="111" spans="2:62" ht="15">
-      <c r="B111" s="15" t="s">
-        <v>1622</v>
-      </c>
-      <c r="AB111" s="88" t="s">
-        <v>1655</v>
-      </c>
-      <c r="AC111" s="62"/>
-      <c r="AD111" s="62"/>
-      <c r="AY111" s="98" t="s">
-        <v>1683</v>
-      </c>
-      <c r="AZ111" s="99"/>
-      <c r="BA111" s="99"/>
-      <c r="BB111" s="99"/>
-      <c r="BC111" s="99"/>
-      <c r="BD111" s="99"/>
-      <c r="BE111" s="99"/>
-      <c r="BF111" s="99"/>
-      <c r="BG111" s="99"/>
-      <c r="BH111" s="99"/>
-      <c r="BI111" s="99"/>
-      <c r="BJ111" s="99"/>
-    </row>
-    <row r="112" spans="2:62">
-      <c r="B112" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="AB112" s="88" t="s">
-        <v>1656</v>
-      </c>
-      <c r="AC112" s="62"/>
-      <c r="AD112" s="62"/>
-      <c r="AY112" s="15" t="s">
-        <v>1684</v>
-      </c>
-    </row>
-    <row r="113" spans="2:55">
-      <c r="B113" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AB113" s="15" t="s">
+    <row r="118" spans="2:2">
+      <c r="B118" s="69"/>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119" s="15" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" ht="15">
+      <c r="B121" s="10" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" ht="15">
+      <c r="B123" s="10" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" ht="15">
+      <c r="B125" s="10" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127" s="15" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2">
+      <c r="B128" s="15" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129" s="15" t="s">
         <v>901</v>
       </c>
-      <c r="AY113" s="15" t="s">
-        <v>1685</v>
-      </c>
-    </row>
-    <row r="114" spans="2:55">
-      <c r="B114" s="15" t="s">
-        <v>1623</v>
-      </c>
-      <c r="AY114" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="115" spans="2:55" ht="15">
-      <c r="B115" s="88" t="s">
-        <v>1624</v>
-      </c>
-      <c r="AB115" s="98" t="s">
-        <v>1657</v>
-      </c>
-      <c r="AC115" s="99"/>
-      <c r="AD115" s="99"/>
-      <c r="AE115" s="99"/>
-      <c r="AF115" s="99"/>
-      <c r="AG115" s="99"/>
-      <c r="AH115" s="99"/>
-      <c r="AI115" s="99"/>
-      <c r="AJ115" s="99"/>
-      <c r="AY115" s="88" t="s">
-        <v>1686</v>
-      </c>
-      <c r="AZ115" s="62"/>
-      <c r="BA115" s="62"/>
-      <c r="BB115" s="62"/>
-      <c r="BC115" s="62"/>
-    </row>
-    <row r="116" spans="2:55">
-      <c r="B116" s="15" t="s">
-        <v>1620</v>
-      </c>
-      <c r="AB116" s="15" t="s">
-        <v>1471</v>
-      </c>
-      <c r="AY116" s="88" t="s">
-        <v>1687</v>
-      </c>
-      <c r="AZ116" s="62"/>
-      <c r="BA116" s="62"/>
-      <c r="BB116" s="62"/>
-      <c r="BC116" s="62"/>
-    </row>
-    <row r="117" spans="2:55">
-      <c r="B117" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="AB117" s="15" t="s">
-        <v>1472</v>
-      </c>
-      <c r="AY117" s="88" t="s">
-        <v>1688</v>
-      </c>
-      <c r="AZ117" s="62"/>
-      <c r="BA117" s="62"/>
-      <c r="BB117" s="62"/>
-      <c r="BC117" s="62"/>
-    </row>
-    <row r="118" spans="2:55">
-      <c r="B118" s="15" t="s">
+    </row>
+    <row r="131" spans="2:2" ht="15">
+      <c r="B131" s="10" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2">
+      <c r="B133" s="15" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2">
+      <c r="B134" s="15" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2">
+      <c r="B135" s="15" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2">
+      <c r="B136" s="15" t="s">
         <v>901</v>
       </c>
-      <c r="AB118" s="69"/>
-      <c r="AY118" s="88" t="s">
-        <v>1689</v>
-      </c>
-      <c r="AZ118" s="62"/>
-      <c r="BA118" s="62"/>
-      <c r="BB118" s="62"/>
-      <c r="BC118" s="62"/>
-    </row>
-    <row r="119" spans="2:55">
-      <c r="AB119" s="88" t="s">
-        <v>1658</v>
-      </c>
-      <c r="AY119" s="88" t="s">
-        <v>1690</v>
-      </c>
-      <c r="AZ119" s="62"/>
-      <c r="BA119" s="62"/>
-      <c r="BB119" s="62"/>
-      <c r="BC119" s="62"/>
-    </row>
-    <row r="120" spans="2:55" ht="15">
-      <c r="B120" s="98" t="s">
-        <v>1625</v>
-      </c>
-      <c r="C120" s="99"/>
-      <c r="D120" s="99"/>
-      <c r="E120" s="99"/>
-      <c r="F120" s="99"/>
-      <c r="AB120" s="88" t="s">
-        <v>1659</v>
-      </c>
-      <c r="AY120" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="121" spans="2:55">
-      <c r="B121" s="15" t="s">
-        <v>1626</v>
-      </c>
-      <c r="AB121" s="88" t="s">
+    </row>
+    <row r="137" spans="2:2">
+      <c r="B137" s="69"/>
+    </row>
+    <row r="138" spans="2:2">
+      <c r="B138" s="15" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2">
+      <c r="B139" s="15" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2">
+      <c r="B140" s="15" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2">
+      <c r="B141" s="15" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2">
+      <c r="B142" s="15" t="s">
         <v>901</v>
       </c>
-      <c r="AY121" s="15" t="s">
-        <v>1691</v>
-      </c>
-    </row>
-    <row r="122" spans="2:55">
-      <c r="B122" s="15" t="s">
-        <v>1627</v>
-      </c>
-      <c r="AB122" s="69"/>
-      <c r="AY122" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="123" spans="2:55">
-      <c r="B123" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AB123" s="15" t="s">
-        <v>1660</v>
-      </c>
-      <c r="AY123" s="15" t="s">
-        <v>1692</v>
-      </c>
-    </row>
-    <row r="124" spans="2:55">
-      <c r="B124" s="15" t="s">
-        <v>1628</v>
-      </c>
-      <c r="AB124" s="15" t="s">
-        <v>1661</v>
-      </c>
-      <c r="AY124" s="15" t="s">
-        <v>1693</v>
-      </c>
-    </row>
-    <row r="125" spans="2:55">
-      <c r="B125" s="88" t="s">
-        <v>1629</v>
-      </c>
-      <c r="AB125" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AY125" s="15" t="s">
-        <v>1694</v>
-      </c>
-    </row>
-    <row r="126" spans="2:55">
-      <c r="B126" s="15" t="s">
-        <v>1630</v>
-      </c>
-      <c r="AB126" s="15" t="s">
-        <v>1662</v>
-      </c>
-      <c r="AY126" s="15" t="s">
-        <v>1695</v>
-      </c>
-    </row>
-    <row r="127" spans="2:55">
-      <c r="B127" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="AB127" s="15" t="s">
-        <v>1663</v>
-      </c>
-      <c r="AY127" s="15" t="s">
-        <v>1696</v>
-      </c>
-    </row>
-    <row r="128" spans="2:55">
-      <c r="B128" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AB128" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AY128" s="15" t="s">
-        <v>1697</v>
-      </c>
-    </row>
-    <row r="129" spans="2:58">
-      <c r="B129" s="15" t="s">
-        <v>1631</v>
-      </c>
-      <c r="AB129" s="15" t="s">
-        <v>1664</v>
-      </c>
-      <c r="AY129" s="15" t="s">
-        <v>1698</v>
-      </c>
-    </row>
-    <row r="130" spans="2:58">
-      <c r="B130" s="15" t="s">
-        <v>1628</v>
-      </c>
-      <c r="AB130" s="15" t="s">
+    </row>
+    <row r="143" spans="2:2">
+      <c r="B143" s="69"/>
+    </row>
+    <row r="144" spans="2:2">
+      <c r="B144" s="15" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2">
+      <c r="B145" s="15" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2">
+      <c r="B146" s="15" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2">
+      <c r="B147" s="15" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="148" spans="2:2">
+      <c r="B148" s="15" t="s">
         <v>901</v>
       </c>
-      <c r="AY130" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="131" spans="2:58">
-      <c r="B131" s="88" t="s">
-        <v>1632</v>
-      </c>
-      <c r="AB131" s="69"/>
-      <c r="AY131" s="15" t="s">
-        <v>1699</v>
-      </c>
-    </row>
-    <row r="132" spans="2:58">
-      <c r="B132" s="15" t="s">
-        <v>1630</v>
-      </c>
-      <c r="AB132" s="15" t="s">
-        <v>1665</v>
-      </c>
-      <c r="AY132" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="133" spans="2:58">
-      <c r="B133" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="AB133" s="15" t="s">
-        <v>1666</v>
-      </c>
-    </row>
-    <row r="134" spans="2:58" ht="15">
-      <c r="B134" s="15" t="s">
-        <v>901</v>
-      </c>
-      <c r="AB134" s="15" t="s">
-        <v>1667</v>
-      </c>
-      <c r="AY134" s="98" t="s">
-        <v>1700</v>
-      </c>
-      <c r="AZ134" s="99"/>
-      <c r="BA134" s="99"/>
-      <c r="BB134" s="99"/>
-      <c r="BC134" s="99"/>
-      <c r="BD134" s="99"/>
-      <c r="BE134" s="99"/>
-      <c r="BF134" s="99"/>
-    </row>
-    <row r="135" spans="2:58">
-      <c r="AB135" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AY135" s="15" t="s">
-        <v>1701</v>
-      </c>
-    </row>
-    <row r="136" spans="2:58" ht="15">
-      <c r="B136" s="98" t="s">
-        <v>1633</v>
-      </c>
-      <c r="C136" s="99"/>
-      <c r="D136" s="99"/>
-      <c r="E136" s="99"/>
-      <c r="F136" s="99"/>
-      <c r="G136" s="99"/>
-      <c r="H136" s="99"/>
-      <c r="I136" s="99"/>
-      <c r="J136" s="99"/>
-      <c r="AB136" s="15" t="s">
-        <v>1668</v>
-      </c>
-      <c r="AY136" s="15" t="s">
-        <v>1702</v>
-      </c>
-    </row>
-    <row r="137" spans="2:58">
-      <c r="B137" s="15" t="s">
-        <v>1634</v>
-      </c>
-      <c r="AB137" s="15" t="s">
-        <v>1669</v>
-      </c>
-      <c r="AY137" s="15" t="s">
-        <v>1703</v>
-      </c>
-    </row>
-    <row r="138" spans="2:58">
-      <c r="B138" s="15" t="s">
-        <v>1635</v>
-      </c>
-      <c r="AB138" s="15" t="s">
-        <v>1670</v>
-      </c>
-      <c r="AY138" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="139" spans="2:58">
-      <c r="B139" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AB139" s="15" t="s">
-        <v>1671</v>
-      </c>
-      <c r="AY139" s="15" t="s">
-        <v>1704</v>
-      </c>
-    </row>
-    <row r="140" spans="2:58">
-      <c r="B140" s="15" t="s">
-        <v>1636</v>
-      </c>
-      <c r="AB140" s="15" t="s">
-        <v>1672</v>
-      </c>
-      <c r="AY140" s="15" t="s">
-        <v>1705</v>
-      </c>
-    </row>
-    <row r="141" spans="2:58">
-      <c r="B141" s="15" t="s">
-        <v>1637</v>
-      </c>
-      <c r="AB141" s="15" t="s">
-        <v>901</v>
-      </c>
-      <c r="AY141" s="15" t="s">
-        <v>1706</v>
-      </c>
-    </row>
-    <row r="142" spans="2:58">
-      <c r="B142" s="15" t="s">
-        <v>1638</v>
-      </c>
-      <c r="AY142" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="143" spans="2:58">
-      <c r="B143" s="15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="AY143" s="15" t="s">
-        <v>1707</v>
-      </c>
-    </row>
-    <row r="144" spans="2:58">
-      <c r="B144" s="15" t="s">
-        <v>1083</v>
-      </c>
-      <c r="AY144" s="15" t="s">
-        <v>1708</v>
-      </c>
-    </row>
-    <row r="145" spans="1:51">
-      <c r="B145" s="15" t="s">
-        <v>1639</v>
-      </c>
-      <c r="AY145" s="15" t="s">
-        <v>1709</v>
-      </c>
-    </row>
-    <row r="146" spans="1:51">
-      <c r="B146" s="15" t="s">
-        <v>1640</v>
-      </c>
-      <c r="AY146" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="147" spans="1:51">
-      <c r="B147" s="15" t="s">
-        <v>1641</v>
-      </c>
-    </row>
-    <row r="148" spans="1:51">
-      <c r="B148" s="15" t="s">
-        <v>1642</v>
-      </c>
-    </row>
-    <row r="149" spans="1:51">
-      <c r="B149" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="150" spans="1:51">
+    </row>
+    <row r="149" spans="2:2">
+      <c r="B149" s="69"/>
+    </row>
+    <row r="150" spans="2:2">
       <c r="B150" s="15" t="s">
-        <v>1643</v>
-      </c>
-    </row>
-    <row r="151" spans="1:51">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2">
       <c r="B151" s="15" t="s">
-        <v>1644</v>
-      </c>
-    </row>
-    <row r="152" spans="1:51">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2">
       <c r="B152" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="153" spans="1:51" ht="15" thickBot="1">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2">
       <c r="B153" s="15" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="154" spans="1:51" s="16" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A154" s="92"/>
-      <c r="B154" s="93" t="s">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="156" spans="1:51" ht="15">
-      <c r="B156" s="10" t="s">
-        <v>1711</v>
-      </c>
-    </row>
-    <row r="158" spans="1:51" ht="15">
-      <c r="B158" s="67" t="s">
-        <v>1712</v>
-      </c>
-    </row>
-    <row r="160" spans="1:51">
+    <row r="155" spans="2:2" ht="15">
+      <c r="B155" s="10" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2">
+      <c r="B157" s="15" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2">
+      <c r="B158" s="15" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2">
+      <c r="B159" s="15" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2">
       <c r="B160" s="15" t="s">
-        <v>1713</v>
+        <v>901</v>
       </c>
     </row>
     <row r="161" spans="2:2">
       <c r="B161" s="15" t="s">
-        <v>1714</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="162" spans="2:2">
-      <c r="B162" s="15" t="s">
-        <v>1083</v>
-      </c>
+      <c r="B162" s="69"/>
     </row>
     <row r="163" spans="2:2">
       <c r="B163" s="15" t="s">
-        <v>1715</v>
+        <v>2140</v>
       </c>
     </row>
     <row r="164" spans="2:2">
       <c r="B164" s="15" t="s">
-        <v>1716</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" s="15" t="s">
-        <v>1717</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="166" spans="2:2">
       <c r="B166" s="15" t="s">
-        <v>1083</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="167" spans="2:2">
       <c r="B167" s="15" t="s">
-        <v>1718</v>
+        <v>901</v>
       </c>
     </row>
     <row r="168" spans="2:2">
-      <c r="B168" s="15" t="s">
-        <v>1719</v>
-      </c>
+      <c r="B168" s="69"/>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" s="15" t="s">
-        <v>1720</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="170" spans="2:2">
       <c r="B170" s="15" t="s">
-        <v>1721</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" s="15" t="s">
-        <v>1086</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="172" spans="2:2">
       <c r="B172" s="15" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2">
+      <c r="B173" s="15" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="174" spans="2:2" ht="15">
-      <c r="B174" s="67" t="s">
-        <v>1722</v>
-      </c>
-    </row>
-    <row r="176" spans="2:2">
-      <c r="B176" s="15" t="s">
-        <v>1723</v>
-      </c>
-    </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="15" t="s">
-        <v>1724</v>
-      </c>
-    </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="15" t="s">
-        <v>1083</v>
+    <row r="175" spans="2:2" ht="15">
+      <c r="B175" s="10" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2" ht="15">
+      <c r="B177" s="10" t="s">
+        <v>2147</v>
       </c>
     </row>
     <row r="179" spans="2:2">
       <c r="B179" s="15" t="s">
-        <v>1725</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="180" spans="2:2">
       <c r="B180" s="15" t="s">
-        <v>1726</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="181" spans="2:2">
       <c r="B181" s="15" t="s">
-        <v>1727</v>
+        <v>901</v>
       </c>
     </row>
     <row r="182" spans="2:2">
-      <c r="B182" s="15" t="s">
-        <v>1086</v>
-      </c>
+      <c r="B182" s="69"/>
     </row>
     <row r="183" spans="2:2">
       <c r="B183" s="15" t="s">
-        <v>1083</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="184" spans="2:2">
       <c r="B184" s="15" t="s">
-        <v>1728</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="185" spans="2:2">
       <c r="B185" s="15" t="s">
-        <v>1729</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="186" spans="2:2">
       <c r="B186" s="15" t="s">
-        <v>1730</v>
+        <v>2152</v>
       </c>
     </row>
     <row r="187" spans="2:2">
       <c r="B187" s="15" t="s">
-        <v>1621</v>
-      </c>
-    </row>
-    <row r="188" spans="2:2">
-      <c r="B188" s="15" t="s">
-        <v>1731</v>
-      </c>
-    </row>
-    <row r="189" spans="2:2">
-      <c r="B189" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="190" spans="2:2">
-      <c r="B190" s="15" t="s">
-        <v>1083</v>
+        <v>901</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2" ht="15">
+      <c r="B189" s="10" t="s">
+        <v>2153</v>
       </c>
     </row>
     <row r="191" spans="2:2">
       <c r="B191" s="15" t="s">
-        <v>1732</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="192" spans="2:2">
       <c r="B192" s="15" t="s">
-        <v>1733</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" s="15" t="s">
-        <v>1734</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="194" spans="2:2">
-      <c r="B194" s="15" t="s">
-        <v>1086</v>
-      </c>
+      <c r="B194" s="69"/>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="197" spans="2:2" ht="15">
-      <c r="B197" s="10" t="s">
-        <v>1735</v>
-      </c>
-    </row>
-    <row r="199" spans="2:2" ht="15">
-      <c r="B199" s="67" t="s">
-        <v>1736</v>
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="15" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="15" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2">
+      <c r="B198" s="15" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2">
+      <c r="B199" s="15" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2">
+      <c r="B200" s="15" t="s">
+        <v>2160</v>
       </c>
     </row>
     <row r="201" spans="2:2">
       <c r="B201" s="15" t="s">
-        <v>1737</v>
-      </c>
-    </row>
-    <row r="202" spans="2:2">
-      <c r="B202" s="15" t="s">
-        <v>1738</v>
-      </c>
-    </row>
-    <row r="203" spans="2:2">
-      <c r="B203" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="204" spans="2:2">
-      <c r="B204" s="15" t="s">
-        <v>1739</v>
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2" ht="15">
+      <c r="B203" s="10" t="s">
+        <v>2162</v>
       </c>
     </row>
     <row r="205" spans="2:2">
       <c r="B205" s="15" t="s">
-        <v>1740</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="206" spans="2:2">
       <c r="B206" s="15" t="s">
-        <v>1741</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="207" spans="2:2">
       <c r="B207" s="15" t="s">
-        <v>1742</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="208" spans="2:2">
       <c r="B208" s="15" t="s">
-        <v>1743</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="209" spans="2:2">
       <c r="B209" s="15" t="s">
-        <v>1083</v>
+        <v>901</v>
       </c>
     </row>
     <row r="210" spans="2:2">
-      <c r="B210" s="15" t="s">
-        <v>1744</v>
-      </c>
+      <c r="B210" s="69"/>
     </row>
     <row r="211" spans="2:2">
       <c r="B211" s="15" t="s">
-        <v>1083</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="212" spans="2:2">
       <c r="B212" s="15" t="s">
-        <v>1745</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="213" spans="2:2">
       <c r="B213" s="15" t="s">
-        <v>1746</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="214" spans="2:2">
       <c r="B214" s="15" t="s">
-        <v>1747</v>
-      </c>
-    </row>
-    <row r="215" spans="2:2">
-      <c r="B215" s="15" t="s">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="216" spans="2:2">
-      <c r="B216" s="15" t="s">
-        <v>1749</v>
-      </c>
-    </row>
-    <row r="217" spans="2:2">
-      <c r="B217" s="15" t="s">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="218" spans="2:2">
-      <c r="B218" s="15" t="s">
-        <v>1751</v>
-      </c>
-    </row>
-    <row r="219" spans="2:2">
-      <c r="B219" s="15" t="s">
-        <v>1083</v>
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="216" spans="2:2" ht="15">
+      <c r="B216" s="10" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="218" spans="2:2" ht="15">
+      <c r="B218" s="10" t="s">
+        <v>2171</v>
       </c>
     </row>
     <row r="220" spans="2:2">
       <c r="B220" s="15" t="s">
-        <v>1752</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="221" spans="2:2">
       <c r="B221" s="15" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="222" spans="2:2">
+      <c r="B222" s="15" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2">
+      <c r="B223" s="15" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2">
+      <c r="B224" s="15" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="223" spans="2:2" ht="15">
-      <c r="B223" s="67" t="s">
-        <v>1753</v>
-      </c>
-    </row>
     <row r="225" spans="2:2">
-      <c r="B225" s="15" t="s">
-        <v>1754</v>
-      </c>
+      <c r="B225" s="69"/>
     </row>
     <row r="226" spans="2:2">
       <c r="B226" s="15" t="s">
-        <v>1755</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="227" spans="2:2">
-      <c r="B227" s="69"/>
+      <c r="B227" s="15" t="s">
+        <v>2176</v>
+      </c>
     </row>
     <row r="228" spans="2:2">
       <c r="B228" s="15" t="s">
-        <v>1756</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="229" spans="2:2">
       <c r="B229" s="15" t="s">
-        <v>1757</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="230" spans="2:2">
       <c r="B230" s="15" t="s">
-        <v>901</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="231" spans="2:2">
-      <c r="B231" s="69"/>
+      <c r="B231" s="15" t="s">
+        <v>1086</v>
+      </c>
     </row>
     <row r="232" spans="2:2">
       <c r="B232" s="15" t="s">
-        <v>1758</v>
+        <v>901</v>
       </c>
     </row>
     <row r="233" spans="2:2">
       <c r="B233" s="15" t="s">
-        <v>1759</v>
-      </c>
-    </row>
-    <row r="234" spans="2:2">
-      <c r="B234" s="15" t="s">
-        <v>1760</v>
-      </c>
-    </row>
-    <row r="235" spans="2:2">
-      <c r="B235" s="15" t="s">
-        <v>1761</v>
-      </c>
-    </row>
-    <row r="236" spans="2:2">
-      <c r="B236" s="15" t="s">
-        <v>1762</v>
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="235" spans="2:2" ht="15">
+      <c r="B235" s="10" t="s">
+        <v>2181</v>
       </c>
     </row>
     <row r="237" spans="2:2">
       <c r="B237" s="15" t="s">
-        <v>1083</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="238" spans="2:2">
       <c r="B238" s="15" t="s">
-        <v>1763</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="239" spans="2:2">
       <c r="B239" s="15" t="s">
-        <v>1764</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="240" spans="2:2">
       <c r="B240" s="15" t="s">
-        <v>1765</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="241" spans="2:2">
@@ -32862,729 +36386,700 @@
         <v>901</v>
       </c>
     </row>
-    <row r="243" spans="2:2" ht="15">
-      <c r="B243" s="10" t="s">
-        <v>1766</v>
-      </c>
-    </row>
-    <row r="245" spans="2:2" ht="15">
-      <c r="B245" s="67" t="s">
-        <v>1767</v>
+    <row r="242" spans="2:2">
+      <c r="B242" s="69"/>
+    </row>
+    <row r="243" spans="2:2">
+      <c r="B243" s="15" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="244" spans="2:2">
+      <c r="B244" s="15" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="245" spans="2:2">
+      <c r="B245" s="15" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="246" spans="2:2">
+      <c r="B246" s="15" t="s">
+        <v>2187</v>
       </c>
     </row>
     <row r="247" spans="2:2">
       <c r="B247" s="15" t="s">
-        <v>1768</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="248" spans="2:2">
       <c r="B248" s="15" t="s">
-        <v>1769</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="249" spans="2:2">
       <c r="B249" s="15" t="s">
-        <v>1770</v>
-      </c>
-    </row>
-    <row r="250" spans="2:2">
-      <c r="B250" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="251" spans="2:2">
-      <c r="B251" s="15" t="s">
-        <v>1771</v>
-      </c>
-    </row>
-    <row r="252" spans="2:2">
-      <c r="B252" s="15" t="s">
-        <v>1772</v>
-      </c>
-    </row>
-    <row r="253" spans="2:2">
-      <c r="B253" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="254" spans="2:2">
-      <c r="B254" s="15" t="s">
-        <v>1773</v>
+        <v>901</v>
+      </c>
+    </row>
+    <row r="251" spans="2:2" ht="15">
+      <c r="B251" s="10" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="253" spans="2:2" ht="15">
+      <c r="B253" s="10" t="s">
+        <v>2191</v>
       </c>
     </row>
     <row r="255" spans="2:2">
       <c r="B255" s="15" t="s">
-        <v>1774</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="256" spans="2:2">
       <c r="B256" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="258" spans="2:2" ht="15">
-      <c r="B258" s="67" t="s">
-        <v>1775</v>
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="257" spans="2:2">
+      <c r="B257" s="15" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="258" spans="2:2">
+      <c r="B258" s="15" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="259" spans="2:2">
+      <c r="B259" s="15" t="s">
+        <v>1086</v>
       </c>
     </row>
     <row r="260" spans="2:2">
       <c r="B260" s="15" t="s">
-        <v>1776</v>
+        <v>901</v>
       </c>
     </row>
     <row r="261" spans="2:2">
-      <c r="B261" s="15" t="s">
-        <v>1777</v>
-      </c>
+      <c r="B261" s="69"/>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" s="15" t="s">
-        <v>1778</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" s="15" t="s">
-        <v>1083</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="264" spans="2:2">
       <c r="B264" s="15" t="s">
-        <v>1779</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="265" spans="2:2">
       <c r="B265" s="15" t="s">
-        <v>1780</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="266" spans="2:2">
       <c r="B266" s="15" t="s">
-        <v>1781</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="267" spans="2:2">
       <c r="B267" s="15" t="s">
-        <v>1782</v>
-      </c>
-    </row>
-    <row r="268" spans="2:2">
-      <c r="B268" s="15" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="269" spans="2:2">
-      <c r="B269" s="15" t="s">
-        <v>1784</v>
-      </c>
-    </row>
-    <row r="270" spans="2:2">
-      <c r="B270" s="15" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="272" spans="2:2" ht="15">
-      <c r="B272" s="67" t="s">
-        <v>1785</v>
+    <row r="269" spans="2:2" ht="15">
+      <c r="B269" s="10" t="s">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="271" spans="2:2">
+      <c r="B271" s="15" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="272" spans="2:2">
+      <c r="B272" s="15" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="273" spans="2:2">
+      <c r="B273" s="15" t="s">
+        <v>2202</v>
       </c>
     </row>
     <row r="274" spans="2:2">
       <c r="B274" s="15" t="s">
-        <v>1786</v>
+        <v>901</v>
       </c>
     </row>
     <row r="275" spans="2:2">
-      <c r="B275" s="15" t="s">
-        <v>1787</v>
-      </c>
+      <c r="B275" s="69"/>
     </row>
     <row r="276" spans="2:2">
       <c r="B276" s="15" t="s">
-        <v>1083</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="277" spans="2:2">
       <c r="B277" s="15" t="s">
-        <v>1788</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="278" spans="2:2">
       <c r="B278" s="15" t="s">
-        <v>1789</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="279" spans="2:2">
       <c r="B279" s="15" t="s">
-        <v>1790</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="280" spans="2:2">
       <c r="B280" s="15" t="s">
-        <v>1083</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="281" spans="2:2">
       <c r="B281" s="15" t="s">
-        <v>1791</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="282" spans="2:2">
       <c r="B282" s="15" t="s">
-        <v>1792</v>
-      </c>
-    </row>
-    <row r="283" spans="2:2">
-      <c r="B283" s="15" t="s">
-        <v>1793</v>
-      </c>
-    </row>
-    <row r="284" spans="2:2">
-      <c r="B284" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="285" spans="2:2">
-      <c r="B285" s="15" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="286" spans="2:2">
-      <c r="B286" s="15" t="s">
-        <v>1795</v>
-      </c>
-    </row>
-    <row r="287" spans="2:2">
-      <c r="B287" s="15" t="s">
-        <v>1796</v>
-      </c>
-    </row>
-    <row r="288" spans="2:2">
-      <c r="B288" s="15" t="s">
-        <v>1797</v>
-      </c>
-    </row>
-    <row r="289" spans="2:2">
-      <c r="B289" s="15" t="s">
-        <v>1798</v>
+        <v>901</v>
+      </c>
+    </row>
+    <row r="284" spans="2:2" ht="15">
+      <c r="B284" s="10" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="286" spans="2:2" ht="15">
+      <c r="B286" s="10" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="288" spans="2:2" ht="15">
+      <c r="B288" s="10" t="s">
+        <v>2210</v>
       </c>
     </row>
     <row r="290" spans="2:2">
       <c r="B290" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="292" spans="2:2" ht="15">
-      <c r="B292" s="10" t="s">
-        <v>1799</v>
-      </c>
-    </row>
-    <row r="294" spans="2:2" ht="15">
-      <c r="B294" s="67" t="s">
-        <v>1800</v>
-      </c>
-    </row>
-    <row r="296" spans="2:2">
-      <c r="B296" s="15" t="s">
-        <v>1801</v>
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="291" spans="2:2">
+      <c r="B291" s="15" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="292" spans="2:2">
+      <c r="B292" s="69"/>
+    </row>
+    <row r="293" spans="2:2">
+      <c r="B293" s="15" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="295" spans="2:2" ht="15">
+      <c r="B295" s="10" t="s">
+        <v>2214</v>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" s="15" t="s">
-        <v>1802</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="298" spans="2:2">
       <c r="B298" s="15" t="s">
-        <v>1083</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" s="15" t="s">
-        <v>1803</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" s="15" t="s">
-        <v>1804</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="301" spans="2:2">
       <c r="B301" s="15" t="s">
-        <v>1805</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="302" spans="2:2">
       <c r="B302" s="15" t="s">
-        <v>1806</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="303" spans="2:2">
       <c r="B303" s="15" t="s">
-        <v>1807</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" s="15" t="s">
-        <v>1808</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" s="15" t="s">
-        <v>1083</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="306" spans="2:2">
       <c r="B306" s="15" t="s">
-        <v>1809</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="307" spans="2:2">
       <c r="B307" s="15" t="s">
-        <v>1810</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="308" spans="2:2">
       <c r="B308" s="15" t="s">
-        <v>1811</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="309" spans="2:2">
       <c r="B309" s="15" t="s">
-        <v>1086</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="310" spans="2:2">
       <c r="B310" s="15" t="s">
-        <v>1083</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="311" spans="2:2">
       <c r="B311" s="15" t="s">
-        <v>1812</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="312" spans="2:2">
-      <c r="B312" s="15" t="s">
-        <v>1813</v>
-      </c>
+      <c r="B312" s="69"/>
     </row>
     <row r="313" spans="2:2">
       <c r="B313" s="15" t="s">
-        <v>1814</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="314" spans="2:2">
       <c r="B314" s="15" t="s">
-        <v>1083</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="315" spans="2:2">
       <c r="B315" s="15" t="s">
-        <v>1815</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="316" spans="2:2">
       <c r="B316" s="15" t="s">
-        <v>1816</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="317" spans="2:2">
       <c r="B317" s="15" t="s">
-        <v>1817</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="318" spans="2:2">
       <c r="B318" s="15" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="319" spans="2:2">
+      <c r="B319" s="15" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="320" spans="2:2" ht="15">
-      <c r="B320" s="67" t="s">
-        <v>1818</v>
+    <row r="320" spans="2:2">
+      <c r="B320" s="69"/>
+    </row>
+    <row r="321" spans="2:2">
+      <c r="B321" s="15" t="s">
+        <v>2229</v>
       </c>
     </row>
     <row r="322" spans="2:2">
       <c r="B322" s="15" t="s">
-        <v>1819</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="323" spans="2:2">
       <c r="B323" s="15" t="s">
-        <v>1820</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="324" spans="2:2">
       <c r="B324" s="15" t="s">
-        <v>1083</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="325" spans="2:2">
       <c r="B325" s="15" t="s">
-        <v>1821</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="326" spans="2:2">
       <c r="B326" s="15" t="s">
-        <v>1822</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="327" spans="2:2">
       <c r="B327" s="15" t="s">
-        <v>1823</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="328" spans="2:2">
       <c r="B328" s="15" t="s">
-        <v>1824</v>
+        <v>901</v>
       </c>
     </row>
     <row r="329" spans="2:2">
       <c r="B329" s="15" t="s">
-        <v>1083</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="330" spans="2:2">
       <c r="B330" s="15" t="s">
-        <v>1825</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="331" spans="2:2">
-      <c r="B331" s="15" t="s">
-        <v>1826</v>
-      </c>
+      <c r="B331" s="69"/>
     </row>
     <row r="332" spans="2:2">
       <c r="B332" s="15" t="s">
-        <v>1083</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="333" spans="2:2">
       <c r="B333" s="15" t="s">
-        <v>1827</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="334" spans="2:2">
       <c r="B334" s="15" t="s">
-        <v>1828</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="335" spans="2:2">
-      <c r="B335" s="15" t="s">
-        <v>1829</v>
-      </c>
+      <c r="B335" s="69"/>
     </row>
     <row r="336" spans="2:2">
       <c r="B336" s="15" t="s">
-        <v>1830</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="337" spans="2:2">
       <c r="B337" s="15" t="s">
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="338" spans="2:2">
-      <c r="B338" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="339" spans="2:2">
-      <c r="B339" s="15" t="s">
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="340" spans="2:2">
-      <c r="B340" s="15" t="s">
-        <v>1832</v>
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="339" spans="2:2" ht="15">
+      <c r="B339" s="10" t="s">
+        <v>2240</v>
       </c>
     </row>
     <row r="341" spans="2:2">
       <c r="B341" s="15" t="s">
-        <v>1833</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="342" spans="2:2">
       <c r="B342" s="15" t="s">
-        <v>1834</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="343" spans="2:2">
       <c r="B343" s="15" t="s">
-        <v>1083</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="344" spans="2:2">
       <c r="B344" s="15" t="s">
-        <v>1835</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="345" spans="2:2">
       <c r="B345" s="15" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="346" spans="2:2">
+      <c r="B346" s="69"/>
+    </row>
+    <row r="347" spans="2:2">
+      <c r="B347" s="15" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="348" spans="2:2">
+      <c r="B348" s="15" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="349" spans="2:2">
+      <c r="B349" s="15" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="350" spans="2:2">
+      <c r="B350" s="15" t="s">
         <v>901</v>
-      </c>
-    </row>
-    <row r="347" spans="2:2" ht="15">
-      <c r="B347" s="10" t="s">
-        <v>1836</v>
-      </c>
-    </row>
-    <row r="349" spans="2:2" ht="15">
-      <c r="B349" s="10" t="s">
-        <v>1837</v>
       </c>
     </row>
     <row r="351" spans="2:2">
       <c r="B351" s="15" t="s">
-        <v>1838</v>
+        <v>936</v>
       </c>
     </row>
     <row r="352" spans="2:2">
       <c r="B352" s="15" t="s">
-        <v>1839</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="353" spans="2:2">
       <c r="B353" s="15" t="s">
-        <v>1840</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="354" spans="2:2">
       <c r="B354" s="15" t="s">
-        <v>1841</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="355" spans="2:2">
       <c r="B355" s="15" t="s">
-        <v>1842</v>
-      </c>
-    </row>
-    <row r="356" spans="2:2">
-      <c r="B356" s="15" t="s">
-        <v>1843</v>
-      </c>
-    </row>
-    <row r="357" spans="2:2">
-      <c r="B357" s="15" t="s">
-        <v>1844</v>
-      </c>
-    </row>
-    <row r="358" spans="2:2">
-      <c r="B358" s="15" t="s">
-        <v>1845</v>
-      </c>
-    </row>
-    <row r="359" spans="2:2">
-      <c r="B359" s="15" t="s">
-        <v>1846</v>
-      </c>
-    </row>
-    <row r="360" spans="2:2">
-      <c r="B360" s="15" t="s">
-        <v>1847</v>
+        <v>901</v>
+      </c>
+    </row>
+    <row r="357" spans="2:2" ht="15">
+      <c r="B357" s="10" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="359" spans="2:2" ht="15">
+      <c r="B359" s="10" t="s">
+        <v>2252</v>
       </c>
     </row>
     <row r="361" spans="2:2">
       <c r="B361" s="15" t="s">
-        <v>1848</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="362" spans="2:2">
       <c r="B362" s="15" t="s">
-        <v>1849</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="363" spans="2:2">
       <c r="B363" s="15" t="s">
-        <v>1850</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="364" spans="2:2">
       <c r="B364" s="15" t="s">
-        <v>1851</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="365" spans="2:2">
       <c r="B365" s="15" t="s">
-        <v>1852</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="366" spans="2:2">
       <c r="B366" s="15" t="s">
-        <v>1853</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="367" spans="2:2">
       <c r="B367" s="15" t="s">
-        <v>1854</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="368" spans="2:2">
       <c r="B368" s="15" t="s">
-        <v>1855</v>
+        <v>901</v>
       </c>
     </row>
     <row r="369" spans="2:2">
-      <c r="B369" s="15" t="s">
-        <v>1856</v>
-      </c>
+      <c r="B369" s="69"/>
     </row>
     <row r="370" spans="2:2">
       <c r="B370" s="15" t="s">
-        <v>1083</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="371" spans="2:2">
       <c r="B371" s="15" t="s">
-        <v>1857</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="372" spans="2:2">
       <c r="B372" s="15" t="s">
-        <v>1083</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="373" spans="2:2">
       <c r="B373" s="15" t="s">
-        <v>1858</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="374" spans="2:2">
       <c r="B374" s="15" t="s">
-        <v>1859</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="375" spans="2:2">
       <c r="B375" s="15" t="s">
-        <v>1860</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="376" spans="2:2">
       <c r="B376" s="15" t="s">
-        <v>1861</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="377" spans="2:2">
       <c r="B377" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="378" spans="2:2">
+      <c r="B378" s="15" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="379" spans="2:2">
+      <c r="B379" s="15" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="379" spans="2:2" ht="15">
-      <c r="B379" s="10" t="s">
-        <v>1862</v>
-      </c>
-    </row>
     <row r="381" spans="2:2" ht="15">
-      <c r="B381" s="67" t="s">
-        <v>1863</v>
+      <c r="B381" s="10" t="s">
+        <v>2264</v>
       </c>
     </row>
     <row r="383" spans="2:2">
       <c r="B383" s="15" t="s">
-        <v>1864</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="384" spans="2:2">
       <c r="B384" s="15" t="s">
-        <v>1865</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="385" spans="2:2">
       <c r="B385" s="15" t="s">
-        <v>1083</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="386" spans="2:2">
       <c r="B386" s="15" t="s">
-        <v>1866</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="387" spans="2:2">
       <c r="B387" s="15" t="s">
-        <v>1867</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="388" spans="2:2">
       <c r="B388" s="15" t="s">
-        <v>1868</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="389" spans="2:2">
       <c r="B389" s="15" t="s">
-        <v>1083</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="390" spans="2:2">
       <c r="B390" s="15" t="s">
-        <v>1869</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="391" spans="2:2">
       <c r="B391" s="15" t="s">
-        <v>1870</v>
-      </c>
-    </row>
-    <row r="392" spans="2:2">
-      <c r="B392" s="15" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="394" spans="2:2" ht="15">
-      <c r="B394" s="67" t="s">
-        <v>1871</v>
-      </c>
-    </row>
-    <row r="396" spans="2:2">
-      <c r="B396" s="15" t="s">
-        <v>1872</v>
+    <row r="393" spans="2:2" ht="15">
+      <c r="B393" s="10" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="395" spans="2:2" ht="15">
+      <c r="B395" s="10" t="s">
+        <v>2271</v>
       </c>
     </row>
     <row r="397" spans="2:2">
       <c r="B397" s="15" t="s">
-        <v>1873</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="398" spans="2:2">
-      <c r="B398" s="15" t="s">
-        <v>1083</v>
-      </c>
+      <c r="B398" s="69"/>
     </row>
     <row r="399" spans="2:2">
       <c r="B399" s="15" t="s">
-        <v>1874</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="400" spans="2:2">
       <c r="B400" s="15" t="s">
-        <v>1875</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="401" spans="2:2">
       <c r="B401" s="15" t="s">
-        <v>1717</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="402" spans="2:2">
       <c r="B402" s="15" t="s">
-        <v>1083</v>
+        <v>901</v>
       </c>
     </row>
     <row r="403" spans="2:2">
-      <c r="B403" s="15" t="s">
-        <v>1876</v>
-      </c>
+      <c r="B403" s="69"/>
     </row>
     <row r="404" spans="2:2">
       <c r="B404" s="15" t="s">
-        <v>1680</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="405" spans="2:2">
       <c r="B405" s="15" t="s">
-        <v>1877</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="406" spans="2:2">
       <c r="B406" s="15" t="s">
-        <v>1878</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="407" spans="2:2">
@@ -33594,462 +37089,456 @@
     </row>
     <row r="408" spans="2:2">
       <c r="B408" s="15" t="s">
-        <v>1879</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="409" spans="2:2">
       <c r="B409" s="15" t="s">
-        <v>1880</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="410" spans="2:2">
       <c r="B410" s="15" t="s">
-        <v>1881</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="411" spans="2:2">
       <c r="B411" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="412" spans="2:2">
+      <c r="B412" s="15" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="413" spans="2:2">
+      <c r="B413" s="15" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="413" spans="2:2" ht="15">
-      <c r="B413" s="10" t="s">
-        <v>1882</v>
-      </c>
-    </row>
     <row r="415" spans="2:2" ht="15">
-      <c r="B415" s="67" t="s">
-        <v>1883</v>
+      <c r="B415" s="10" t="s">
+        <v>2280</v>
       </c>
     </row>
     <row r="417" spans="2:2">
       <c r="B417" s="15" t="s">
-        <v>1884</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="418" spans="2:2">
-      <c r="B418" s="15" t="s">
-        <v>1885</v>
-      </c>
+      <c r="B418" s="69"/>
     </row>
     <row r="419" spans="2:2">
       <c r="B419" s="15" t="s">
-        <v>1083</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="420" spans="2:2">
       <c r="B420" s="15" t="s">
-        <v>1886</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="421" spans="2:2">
       <c r="B421" s="15" t="s">
-        <v>1887</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="422" spans="2:2">
       <c r="B422" s="15" t="s">
-        <v>1888</v>
+        <v>901</v>
       </c>
     </row>
     <row r="423" spans="2:2">
-      <c r="B423" s="15" t="s">
-        <v>1086</v>
-      </c>
+      <c r="B423" s="69"/>
     </row>
     <row r="424" spans="2:2">
       <c r="B424" s="15" t="s">
-        <v>1083</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="425" spans="2:2">
       <c r="B425" s="15" t="s">
-        <v>1889</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="426" spans="2:2">
       <c r="B426" s="15" t="s">
-        <v>1890</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="427" spans="2:2">
       <c r="B427" s="15" t="s">
-        <v>1891</v>
+        <v>901</v>
       </c>
     </row>
     <row r="428" spans="2:2">
-      <c r="B428" s="15" t="s">
-        <v>1086</v>
-      </c>
+      <c r="B428" s="69"/>
     </row>
     <row r="429" spans="2:2">
       <c r="B429" s="15" t="s">
-        <v>1083</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="430" spans="2:2">
       <c r="B430" s="15" t="s">
-        <v>1892</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="431" spans="2:2">
       <c r="B431" s="15" t="s">
-        <v>1893</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="432" spans="2:2">
       <c r="B432" s="15" t="s">
-        <v>1894</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="433" spans="2:2">
       <c r="B433" s="15" t="s">
-        <v>1086</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="434" spans="2:2">
       <c r="B434" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="436" spans="2:2" ht="15">
-      <c r="B436" s="67" t="s">
-        <v>1895</v>
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="435" spans="2:2">
+      <c r="B435" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="436" spans="2:2">
+      <c r="B436" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="437" spans="2:2">
+      <c r="B437" s="15" t="s">
+        <v>1155</v>
       </c>
     </row>
     <row r="438" spans="2:2">
       <c r="B438" s="15" t="s">
-        <v>1896</v>
-      </c>
-    </row>
-    <row r="439" spans="2:2">
-      <c r="B439" s="15" t="s">
-        <v>1640</v>
-      </c>
-    </row>
-    <row r="440" spans="2:2">
-      <c r="B440" s="15" t="s">
-        <v>1778</v>
-      </c>
-    </row>
-    <row r="441" spans="2:2">
-      <c r="B441" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="442" spans="2:2">
-      <c r="B442" s="15" t="s">
-        <v>1897</v>
-      </c>
-    </row>
-    <row r="443" spans="2:2">
-      <c r="B443" s="15" t="s">
-        <v>1898</v>
-      </c>
-    </row>
-    <row r="444" spans="2:2">
-      <c r="B444" s="15" t="s">
-        <v>1899</v>
-      </c>
-    </row>
-    <row r="445" spans="2:2">
-      <c r="B445" s="15" t="s">
-        <v>1083</v>
+        <v>901</v>
+      </c>
+    </row>
+    <row r="440" spans="2:2" ht="15">
+      <c r="B440" s="10" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="442" spans="2:2" ht="15">
+      <c r="B442" s="10" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="444" spans="2:2" ht="15">
+      <c r="B444" s="10" t="s">
+        <v>2293</v>
       </c>
     </row>
     <row r="446" spans="2:2">
       <c r="B446" s="15" t="s">
-        <v>1900</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="447" spans="2:2">
       <c r="B447" s="15" t="s">
-        <v>1083</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="448" spans="2:2">
       <c r="B448" s="15" t="s">
-        <v>1901</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="449" spans="2:2">
       <c r="B449" s="15" t="s">
-        <v>1902</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="450" spans="2:2">
       <c r="B450" s="15" t="s">
-        <v>1903</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="451" spans="2:2">
       <c r="B451" s="15" t="s">
-        <v>1083</v>
+        <v>901</v>
       </c>
     </row>
     <row r="452" spans="2:2">
-      <c r="B452" s="15" t="s">
-        <v>1904</v>
-      </c>
+      <c r="B452" s="69"/>
     </row>
     <row r="453" spans="2:2">
       <c r="B453" s="15" t="s">
-        <v>1905</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="454" spans="2:2">
       <c r="B454" s="15" t="s">
-        <v>1906</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="455" spans="2:2">
       <c r="B455" s="15" t="s">
-        <v>1907</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="456" spans="2:2">
       <c r="B456" s="15" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="457" spans="2:2">
+      <c r="B457" s="15" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="458" spans="2:2">
+      <c r="B458" s="15" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="458" spans="2:2" ht="15">
-      <c r="B458" s="67" t="s">
-        <v>1908</v>
-      </c>
-    </row>
-    <row r="460" spans="2:2">
-      <c r="B460" s="15" t="s">
-        <v>1909</v>
-      </c>
-    </row>
-    <row r="461" spans="2:2">
-      <c r="B461" s="15" t="s">
-        <v>1791</v>
+    <row r="460" spans="2:2" ht="15">
+      <c r="B460" s="10" t="s">
+        <v>2301</v>
       </c>
     </row>
     <row r="462" spans="2:2">
       <c r="B462" s="15" t="s">
-        <v>1778</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="463" spans="2:2">
       <c r="B463" s="15" t="s">
-        <v>1083</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="464" spans="2:2">
       <c r="B464" s="15" t="s">
-        <v>1910</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="465" spans="2:2">
       <c r="B465" s="15" t="s">
-        <v>1911</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="466" spans="2:2">
       <c r="B466" s="15" t="s">
-        <v>1912</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="467" spans="2:2">
       <c r="B467" s="15" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="468" spans="2:2">
       <c r="B468" s="15" t="s">
-        <v>1913</v>
+        <v>901</v>
       </c>
     </row>
     <row r="469" spans="2:2">
-      <c r="B469" s="15" t="s">
-        <v>1914</v>
-      </c>
+      <c r="B469" s="69"/>
     </row>
     <row r="470" spans="2:2">
       <c r="B470" s="15" t="s">
-        <v>1915</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="471" spans="2:2">
       <c r="B471" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="473" spans="2:2" ht="15">
-      <c r="B473" s="67" t="s">
-        <v>1916</v>
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="472" spans="2:2">
+      <c r="B472" s="15" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="473" spans="2:2">
+      <c r="B473" s="15" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="474" spans="2:2">
+      <c r="B474" s="15" t="s">
+        <v>2307</v>
       </c>
     </row>
     <row r="475" spans="2:2">
       <c r="B475" s="15" t="s">
-        <v>1917</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="476" spans="2:2">
       <c r="B476" s="15" t="s">
-        <v>1592</v>
-      </c>
-    </row>
-    <row r="477" spans="2:2">
-      <c r="B477" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="478" spans="2:2">
-      <c r="B478" s="15" t="s">
-        <v>1918</v>
+        <v>901</v>
+      </c>
+    </row>
+    <row r="478" spans="2:2" ht="15">
+      <c r="B478" s="10" t="s">
+        <v>2308</v>
       </c>
     </row>
     <row r="479" spans="2:2">
-      <c r="B479" s="15" t="s">
-        <v>1919</v>
-      </c>
-    </row>
-    <row r="480" spans="2:2">
-      <c r="B480" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="481" spans="2:2">
-      <c r="B481" s="15" t="s">
-        <v>1920</v>
-      </c>
-    </row>
-    <row r="482" spans="2:2">
-      <c r="B482" s="15" t="s">
-        <v>1921</v>
-      </c>
-    </row>
-    <row r="483" spans="2:2">
-      <c r="B483" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="484" spans="2:2">
-      <c r="B484" s="15" t="s">
-        <v>1889</v>
-      </c>
-    </row>
-    <row r="485" spans="2:2">
-      <c r="B485" s="15" t="s">
-        <v>1922</v>
-      </c>
-    </row>
-    <row r="486" spans="2:2">
-      <c r="B486" s="15" t="s">
-        <v>1923</v>
-      </c>
-    </row>
-    <row r="487" spans="2:2">
-      <c r="B487" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="489" spans="2:2" ht="15">
-      <c r="B489" s="67" t="s">
-        <v>1924</v>
-      </c>
-    </row>
-    <row r="491" spans="2:2">
-      <c r="B491" s="15" t="s">
-        <v>1925</v>
-      </c>
-    </row>
-    <row r="492" spans="2:2">
-      <c r="B492" s="15" t="s">
-        <v>1926</v>
-      </c>
-    </row>
-    <row r="493" spans="2:2">
-      <c r="B493" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="494" spans="2:2">
-      <c r="B494" s="15" t="s">
-        <v>1927</v>
-      </c>
-    </row>
-    <row r="495" spans="2:2">
-      <c r="B495" s="15" t="s">
-        <v>1928</v>
-      </c>
-    </row>
-    <row r="496" spans="2:2">
-      <c r="B496" s="15" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="497" spans="2:2">
-      <c r="B497" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="498" spans="2:2">
-      <c r="B498" s="15" t="s">
-        <v>1930</v>
-      </c>
-    </row>
-    <row r="499" spans="2:2">
-      <c r="B499" s="15" t="s">
-        <v>1931</v>
+      <c r="B479" s="13"/>
+    </row>
+    <row r="480" spans="2:2" ht="15">
+      <c r="B480" s="100" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="481" spans="2:2" ht="15">
+      <c r="B481" s="100" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="482" spans="2:2" ht="15">
+      <c r="B482" s="100" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="483" spans="2:2" ht="15">
+      <c r="B483" s="100" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="484" spans="2:2" ht="15">
+      <c r="B484" s="100" t="s">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="485" spans="2:2" ht="15">
+      <c r="B485" s="100" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="486" spans="2:2" ht="15">
+      <c r="B486" s="100" t="s">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="488" spans="2:2" ht="15">
+      <c r="B488" s="10" t="s">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="489" spans="2:2">
+      <c r="B489" s="13"/>
+    </row>
+    <row r="490" spans="2:2" ht="15">
+      <c r="B490" s="100" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="491" spans="2:2" ht="15">
+      <c r="B491" s="100" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="492" spans="2:2" ht="15">
+      <c r="B492" s="100" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="493" spans="2:2" ht="15">
+      <c r="B493" s="100" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="494" spans="2:2" ht="15">
+      <c r="B494" s="100" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="495" spans="2:2" ht="15">
+      <c r="B495" s="100" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="496" spans="2:2" ht="15">
+      <c r="B496" s="100" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="498" spans="2:2" ht="15">
+      <c r="B498" s="10" t="s">
+        <v>2310</v>
       </c>
     </row>
     <row r="500" spans="2:2">
       <c r="B500" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="502" spans="2:2" ht="15">
-      <c r="B502" s="10" t="s">
-        <v>1932</v>
-      </c>
-    </row>
-    <row r="504" spans="2:2" ht="15">
-      <c r="B504" s="67" t="s">
-        <v>1933</v>
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="501" spans="2:2">
+      <c r="B501" s="15" t="s">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="502" spans="2:2">
+      <c r="B502" s="15" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="503" spans="2:2">
+      <c r="B503" s="15" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="504" spans="2:2">
+      <c r="B504" s="15" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="505" spans="2:2">
+      <c r="B505" s="15" t="s">
+        <v>2315</v>
       </c>
     </row>
     <row r="506" spans="2:2">
       <c r="B506" s="15" t="s">
-        <v>1934</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="507" spans="2:2">
       <c r="B507" s="15" t="s">
-        <v>1865</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="508" spans="2:2">
       <c r="B508" s="15" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="509" spans="2:2">
       <c r="B509" s="15" t="s">
-        <v>1935</v>
+        <v>901</v>
       </c>
     </row>
     <row r="510" spans="2:2">
-      <c r="B510" s="15" t="s">
-        <v>1936</v>
-      </c>
+      <c r="B510" s="69"/>
     </row>
     <row r="511" spans="2:2">
       <c r="B511" s="15" t="s">
-        <v>1083</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="512" spans="2:2">
       <c r="B512" s="15" t="s">
-        <v>1937</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="513" spans="2:2">
       <c r="B513" s="15" t="s">
-        <v>1938</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="514" spans="2:2">
@@ -34059,940 +37548,71 @@
     </row>
     <row r="515" spans="2:2">
       <c r="B515" s="15" t="s">
-        <v>1939</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="516" spans="2:2">
       <c r="B516" s="15" t="s">
-        <v>1940</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="517" spans="2:2">
       <c r="B517" s="15" t="s">
-        <v>1083</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="518" spans="2:2">
       <c r="B518" s="15" t="s">
-        <v>1941</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="519" spans="2:2">
       <c r="B519" s="15" t="s">
-        <v>1942</v>
-      </c>
-    </row>
-    <row r="520" spans="2:2">
-      <c r="B520" s="15" t="s">
-        <v>1943</v>
+        <v>901</v>
       </c>
     </row>
     <row r="521" spans="2:2">
-      <c r="B521" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="522" spans="2:2">
-      <c r="B522" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="523" spans="2:2">
-      <c r="B523" s="15" t="s">
-        <v>1904</v>
-      </c>
-    </row>
-    <row r="524" spans="2:2">
-      <c r="B524" s="15" t="s">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="525" spans="2:2">
-      <c r="B525" s="15" t="s">
-        <v>1945</v>
-      </c>
-    </row>
-    <row r="526" spans="2:2">
-      <c r="B526" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="527" spans="2:2">
-      <c r="B527" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="529" spans="2:2" ht="15">
-      <c r="B529" s="67" t="s">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="531" spans="2:2">
-      <c r="B531" s="15" t="s">
-        <v>1947</v>
-      </c>
-    </row>
-    <row r="532" spans="2:2">
-      <c r="B532" s="15" t="s">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="533" spans="2:2">
-      <c r="B533" s="15" t="s">
-        <v>1802</v>
-      </c>
-    </row>
-    <row r="534" spans="2:2">
-      <c r="B534" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="535" spans="2:2">
-      <c r="B535" s="15" t="s">
-        <v>1949</v>
-      </c>
-    </row>
-    <row r="536" spans="2:2">
-      <c r="B536" s="15" t="s">
-        <v>1950</v>
-      </c>
-    </row>
-    <row r="537" spans="2:2">
-      <c r="B537" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="538" spans="2:2">
-      <c r="B538" s="15" t="s">
-        <v>1951</v>
-      </c>
-    </row>
-    <row r="539" spans="2:2">
-      <c r="B539" s="15" t="s">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="540" spans="2:2">
-      <c r="B540" s="15" t="s">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="541" spans="2:2">
-      <c r="B541" s="15" t="s">
-        <v>1954</v>
-      </c>
-    </row>
-    <row r="542" spans="2:2">
-      <c r="B542" s="15" t="s">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="543" spans="2:2">
-      <c r="B543" s="15" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="544" spans="2:2">
-      <c r="B544" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="546" spans="2:2" ht="15">
-      <c r="B546" s="10" t="s">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="548" spans="2:2" ht="15">
-      <c r="B548" s="10" t="s">
-        <v>1958</v>
-      </c>
-    </row>
-    <row r="550" spans="2:2" ht="15">
-      <c r="B550" s="67" t="s">
-        <v>1959</v>
-      </c>
-    </row>
-    <row r="552" spans="2:2">
-      <c r="B552" s="15" t="s">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="553" spans="2:2">
-      <c r="B553" s="15" t="s">
-        <v>1961</v>
-      </c>
-    </row>
-    <row r="554" spans="2:2">
-      <c r="B554" s="15" t="s">
-        <v>1962</v>
-      </c>
-    </row>
-    <row r="555" spans="2:2">
-      <c r="B555" s="15" t="s">
-        <v>1963</v>
-      </c>
-    </row>
-    <row r="556" spans="2:2">
-      <c r="B556" s="15" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="557" spans="2:2">
-      <c r="B557" s="15" t="s">
-        <v>1703</v>
-      </c>
-    </row>
-    <row r="558" spans="2:2">
-      <c r="B558" s="15" t="s">
-        <v>1965</v>
-      </c>
-    </row>
-    <row r="559" spans="2:2">
-      <c r="B559" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="560" spans="2:2">
-      <c r="B560" s="15" t="s">
-        <v>1966</v>
-      </c>
-    </row>
-    <row r="561" spans="2:2">
-      <c r="B561" s="15" t="s">
-        <v>1967</v>
-      </c>
-    </row>
-    <row r="562" spans="2:2">
-      <c r="B562" s="15" t="s">
-        <v>1968</v>
-      </c>
-    </row>
-    <row r="563" spans="2:2">
-      <c r="B563" s="15" t="s">
-        <v>1969</v>
-      </c>
-    </row>
-    <row r="564" spans="2:2">
-      <c r="B564" s="15" t="s">
-        <v>1970</v>
-      </c>
-    </row>
-    <row r="565" spans="2:2">
-      <c r="B565" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="566" spans="2:2">
-      <c r="B566" s="15" t="s">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="567" spans="2:2">
-      <c r="B567" s="15" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="568" spans="2:2">
-      <c r="B568" s="15" t="s">
-        <v>1973</v>
-      </c>
-    </row>
-    <row r="569" spans="2:2">
-      <c r="B569" s="15" t="s">
-        <v>1974</v>
-      </c>
-    </row>
-    <row r="570" spans="2:2">
-      <c r="B570" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="572" spans="2:2" ht="15">
-      <c r="B572" s="67" t="s">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="574" spans="2:2">
-      <c r="B574" s="15" t="s">
-        <v>1976</v>
-      </c>
-    </row>
-    <row r="575" spans="2:2">
-      <c r="B575" s="15" t="s">
-        <v>1977</v>
-      </c>
-    </row>
-    <row r="576" spans="2:2">
-      <c r="B576" s="15" t="s">
-        <v>1978</v>
-      </c>
-    </row>
-    <row r="577" spans="2:2">
-      <c r="B577" s="15" t="s">
-        <v>1979</v>
-      </c>
-    </row>
-    <row r="578" spans="2:2">
-      <c r="B578" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="579" spans="2:2">
-      <c r="B579" s="15" t="s">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="580" spans="2:2">
-      <c r="B580" s="15" t="s">
-        <v>1981</v>
-      </c>
-    </row>
-    <row r="581" spans="2:2">
-      <c r="B581" s="15" t="s">
-        <v>1982</v>
-      </c>
-    </row>
-    <row r="582" spans="2:2">
-      <c r="B582" s="15" t="s">
-        <v>1983</v>
-      </c>
-    </row>
-    <row r="583" spans="2:2">
-      <c r="B583" s="15" t="s">
-        <v>1984</v>
-      </c>
-    </row>
-    <row r="584" spans="2:2">
-      <c r="B584" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="585" spans="2:2">
-      <c r="B585" s="15" t="s">
-        <v>1985</v>
-      </c>
-    </row>
-    <row r="586" spans="2:2">
-      <c r="B586" s="15" t="s">
-        <v>1986</v>
-      </c>
-    </row>
-    <row r="587" spans="2:2">
-      <c r="B587" s="15" t="s">
-        <v>1987</v>
-      </c>
-    </row>
-    <row r="588" spans="2:2">
-      <c r="B588" s="15" t="s">
-        <v>1988</v>
-      </c>
-    </row>
-    <row r="589" spans="2:2">
-      <c r="B589" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="591" spans="2:2" ht="15">
-      <c r="B591" s="10" t="s">
-        <v>1989</v>
-      </c>
-    </row>
-    <row r="593" spans="2:2" ht="15">
-      <c r="B593" s="67" t="s">
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="595" spans="2:2">
-      <c r="B595" s="15" t="s">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="596" spans="2:2">
-      <c r="B596" s="15" t="s">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="597" spans="2:2">
-      <c r="B597" s="15" t="s">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="598" spans="2:2">
-      <c r="B598" s="69"/>
-    </row>
-    <row r="599" spans="2:2">
-      <c r="B599" s="15" t="s">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="600" spans="2:2">
-      <c r="B600" s="15" t="s">
-        <v>1592</v>
-      </c>
-    </row>
-    <row r="601" spans="2:2">
-      <c r="B601" s="15" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="602" spans="2:2">
-      <c r="B602" s="15" t="s">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="603" spans="2:2">
-      <c r="B603" s="15" t="s">
-        <v>1997</v>
-      </c>
-    </row>
-    <row r="604" spans="2:2">
-      <c r="B604" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="605" spans="2:2">
-      <c r="B605" s="15" t="s">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="606" spans="2:2">
-      <c r="B606" s="15" t="s">
-        <v>1680</v>
-      </c>
-    </row>
-    <row r="607" spans="2:2">
-      <c r="B607" s="15" t="s">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="608" spans="2:2">
-      <c r="B608" s="15" t="s">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="609" spans="2:2">
-      <c r="B609" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="611" spans="2:2" ht="15">
-      <c r="B611" s="67" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="613" spans="2:2">
-      <c r="B613" s="15" t="s">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="614" spans="2:2">
-      <c r="B614" s="15" t="s">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="615" spans="2:2">
-      <c r="B615" s="15" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="616" spans="2:2">
-      <c r="B616" s="15" t="s">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="617" spans="2:2">
-      <c r="B617" s="15" t="s">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="618" spans="2:2">
-      <c r="B618" s="15" t="s">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="619" spans="2:2">
-      <c r="B619" s="15" t="s">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="620" spans="2:2">
-      <c r="B620" s="15" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="621" spans="2:2">
-      <c r="B621" s="69"/>
-    </row>
-    <row r="622" spans="2:2">
-      <c r="B622" s="15" t="s">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="623" spans="2:2">
-      <c r="B623" s="15" t="s">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="624" spans="2:2">
-      <c r="B624" s="15" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="625" spans="2:2">
-      <c r="B625" s="15" t="s">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="626" spans="2:2">
-      <c r="B626" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="627" spans="2:2">
-      <c r="B627" s="15" t="s">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="628" spans="2:2">
-      <c r="B628" s="15" t="s">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="629" spans="2:2">
-      <c r="B629" s="15" t="s">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="630" spans="2:2">
-      <c r="B630" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="632" spans="2:2" ht="15">
-      <c r="B632" s="10" t="s">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="634" spans="2:2" ht="15">
-      <c r="B634" s="67" t="s">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="636" spans="2:2">
-      <c r="B636" s="15" t="s">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="637" spans="2:2">
-      <c r="B637" s="15" t="s">
-        <v>1426</v>
-      </c>
-    </row>
-    <row r="638" spans="2:2">
-      <c r="B638" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="639" spans="2:2">
-      <c r="B639" s="15" t="s">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="640" spans="2:2">
-      <c r="B640" s="15" t="s">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="641" spans="2:2">
-      <c r="B641" s="15" t="s">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="642" spans="2:2">
-      <c r="B642" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="643" spans="2:2">
-      <c r="B643" s="15" t="s">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="644" spans="2:2">
-      <c r="B644" s="15" t="s">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="645" spans="2:2">
-      <c r="B645" s="15" t="s">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="646" spans="2:2">
-      <c r="B646" s="15" t="s">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="647" spans="2:2">
-      <c r="B647" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="648" spans="2:2">
-      <c r="B648" s="15" t="s">
-        <v>2027</v>
-      </c>
-    </row>
-    <row r="649" spans="2:2">
-      <c r="B649" s="15" t="s">
-        <v>2028</v>
-      </c>
-    </row>
-    <row r="650" spans="2:2">
-      <c r="B650" s="15" t="s">
-        <v>2029</v>
-      </c>
-    </row>
-    <row r="651" spans="2:2">
-      <c r="B651" s="15" t="s">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="652" spans="2:2">
-      <c r="B652" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="653" spans="2:2">
-      <c r="B653" s="15" t="s">
-        <v>2031</v>
-      </c>
-    </row>
-    <row r="654" spans="2:2">
-      <c r="B654" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="656" spans="2:2" ht="15">
-      <c r="B656" s="67" t="s">
-        <v>2032</v>
-      </c>
-    </row>
-    <row r="658" spans="2:2">
-      <c r="B658" s="15" t="s">
-        <v>2033</v>
-      </c>
-    </row>
-    <row r="659" spans="2:2">
-      <c r="B659" s="15" t="s">
-        <v>2034</v>
-      </c>
-    </row>
-    <row r="660" spans="2:2">
-      <c r="B660" s="15" t="s">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="661" spans="2:2">
-      <c r="B661" s="15" t="s">
-        <v>2036</v>
-      </c>
-    </row>
-    <row r="662" spans="2:2">
-      <c r="B662" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="663" spans="2:2">
-      <c r="B663" s="15" t="s">
-        <v>2037</v>
-      </c>
-    </row>
-    <row r="664" spans="2:2">
-      <c r="B664" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="665" spans="2:2">
-      <c r="B665" s="69"/>
-    </row>
-    <row r="666" spans="2:2">
-      <c r="B666" s="15" t="s">
-        <v>2038</v>
-      </c>
-    </row>
-    <row r="667" spans="2:2">
-      <c r="B667" s="15" t="s">
-        <v>2039</v>
-      </c>
-    </row>
-    <row r="668" spans="2:2">
-      <c r="B668" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="669" spans="2:2">
-      <c r="B669" s="15" t="s">
-        <v>2040</v>
-      </c>
-    </row>
-    <row r="670" spans="2:2">
-      <c r="B670" s="15" t="s">
-        <v>2041</v>
-      </c>
-    </row>
-    <row r="671" spans="2:2">
-      <c r="B671" s="15" t="s">
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="672" spans="2:2">
-      <c r="B672" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="673" spans="2:2">
-      <c r="B673" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="674" spans="2:2">
-      <c r="B674" s="15" t="s">
-        <v>2043</v>
-      </c>
-    </row>
-    <row r="675" spans="2:2">
-      <c r="B675" s="15" t="s">
-        <v>2044</v>
-      </c>
-    </row>
-    <row r="676" spans="2:2">
-      <c r="B676" s="15" t="s">
-        <v>2045</v>
-      </c>
-    </row>
-    <row r="677" spans="2:2">
-      <c r="B677" s="15" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="678" spans="2:2">
-      <c r="B678" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="680" spans="2:2" ht="15">
-      <c r="B680" s="10" t="s">
-        <v>2046</v>
-      </c>
-    </row>
-    <row r="682" spans="2:2" ht="15">
-      <c r="B682" s="67" t="s">
-        <v>2047</v>
-      </c>
-    </row>
-    <row r="684" spans="2:2">
-      <c r="B684" s="15" t="s">
-        <v>2048</v>
-      </c>
-    </row>
-    <row r="685" spans="2:2">
-      <c r="B685" s="15" t="s">
-        <v>2049</v>
-      </c>
-    </row>
-    <row r="686" spans="2:2">
-      <c r="B686" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="687" spans="2:2">
-      <c r="B687" s="15" t="s">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="688" spans="2:2">
-      <c r="B688" s="15" t="s">
-        <v>2051</v>
-      </c>
-    </row>
-    <row r="689" spans="2:2">
-      <c r="B689" s="15" t="s">
-        <v>2052</v>
-      </c>
-    </row>
-    <row r="690" spans="2:2">
-      <c r="B690" s="15" t="s">
-        <v>2053</v>
-      </c>
-    </row>
-    <row r="691" spans="2:2">
-      <c r="B691" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="692" spans="2:2">
-      <c r="B692" s="15" t="s">
-        <v>2054</v>
-      </c>
-    </row>
-    <row r="693" spans="2:2">
-      <c r="B693" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="694" spans="2:2">
-      <c r="B694" s="15" t="s">
-        <v>2055</v>
-      </c>
-    </row>
-    <row r="695" spans="2:2">
-      <c r="B695" s="15" t="s">
-        <v>2056</v>
-      </c>
-    </row>
-    <row r="696" spans="2:2">
-      <c r="B696" s="15" t="s">
-        <v>2057</v>
-      </c>
-    </row>
-    <row r="697" spans="2:2">
-      <c r="B697" s="15" t="s">
-        <v>2058</v>
-      </c>
-    </row>
-    <row r="698" spans="2:2">
-      <c r="B698" s="15" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="699" spans="2:2">
-      <c r="B699" s="15" t="s">
-        <v>2059</v>
-      </c>
-    </row>
-    <row r="700" spans="2:2">
-      <c r="B700" s="15" t="s">
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="701" spans="2:2">
-      <c r="B701" s="15" t="s">
-        <v>2061</v>
-      </c>
-    </row>
-    <row r="702" spans="2:2">
-      <c r="B702" s="15" t="s">
-        <v>2062</v>
-      </c>
-    </row>
-    <row r="703" spans="2:2">
-      <c r="B703" s="15" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="705" spans="2:2" ht="15">
-      <c r="B705" s="10" t="s">
-        <v>2063</v>
-      </c>
-    </row>
-    <row r="707" spans="2:2" ht="15">
-      <c r="B707" s="10" t="s">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="708" spans="2:2">
-      <c r="B708" s="13"/>
-    </row>
-    <row r="709" spans="2:2" ht="15">
-      <c r="B709" s="103" t="s">
-        <v>2067</v>
-      </c>
-    </row>
-    <row r="710" spans="2:2" ht="15">
-      <c r="B710" s="103" t="s">
-        <v>2068</v>
-      </c>
-    </row>
-    <row r="711" spans="2:2" ht="15">
-      <c r="B711" s="103" t="s">
-        <v>2069</v>
-      </c>
-    </row>
-    <row r="712" spans="2:2" ht="15">
-      <c r="B712" s="103" t="s">
-        <v>2070</v>
-      </c>
-    </row>
-    <row r="713" spans="2:2" ht="15">
-      <c r="B713" s="103" t="s">
-        <v>2071</v>
-      </c>
-    </row>
-    <row r="714" spans="2:2" ht="15">
-      <c r="B714" s="103" t="s">
-        <v>2072</v>
-      </c>
-    </row>
-    <row r="715" spans="2:2" ht="15">
-      <c r="B715" s="103" t="s">
-        <v>2073</v>
-      </c>
-    </row>
-    <row r="716" spans="2:2" ht="15">
-      <c r="B716" s="103" t="s">
-        <v>2074</v>
-      </c>
-    </row>
-    <row r="718" spans="2:2" ht="15">
-      <c r="B718" s="10" t="s">
-        <v>2065</v>
-      </c>
-    </row>
-    <row r="719" spans="2:2">
-      <c r="B719" s="13"/>
-    </row>
-    <row r="720" spans="2:2" ht="15">
-      <c r="B720" s="103" t="s">
-        <v>2075</v>
-      </c>
-    </row>
-    <row r="721" spans="2:2" ht="15">
-      <c r="B721" s="103" t="s">
-        <v>2076</v>
-      </c>
-    </row>
-    <row r="722" spans="2:2" ht="15">
-      <c r="B722" s="103" t="s">
-        <v>2077</v>
-      </c>
-    </row>
-    <row r="723" spans="2:2" ht="15">
-      <c r="B723" s="103" t="s">
-        <v>2078</v>
-      </c>
-    </row>
-    <row r="724" spans="2:2" ht="15">
-      <c r="B724" s="103" t="s">
-        <v>2079</v>
-      </c>
-    </row>
-    <row r="725" spans="2:2" ht="15">
-      <c r="B725" s="103" t="s">
-        <v>2080</v>
-      </c>
-    </row>
-    <row r="726" spans="2:2" ht="15">
-      <c r="B726" s="103" t="s">
-        <v>2081</v>
-      </c>
-    </row>
-    <row r="728" spans="2:2">
-      <c r="B728" s="11" t="s">
-        <v>2066</v>
+      <c r="B521" s="11" t="s">
+        <v>2323</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>